--- a/Documentation/Documents/SQL Generator/Data Initial/SysConfig.TblAppObject_MenuGroupMember.xlsx
+++ b/Documentation/Documents/SQL Generator/Data Initial/SysConfig.TblAppObject_MenuGroupMember.xlsx
@@ -14,12 +14,12 @@
     <externalReference r:id="rId3"/>
     <externalReference r:id="rId4"/>
   </externalReferences>
-  <calcPr calcId="152511" iterateDelta="1E-4"/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="9">
   <si>
     <t>Home</t>
   </si>
@@ -45,22 +45,7 @@
     <t>Inventory</t>
   </si>
   <si>
-    <t>Process</t>
-  </si>
-  <si>
-    <t>Country</t>
-  </si>
-  <si>
-    <t>Province / State</t>
-  </si>
-  <si>
-    <t>Municipality / Regency</t>
-  </si>
-  <si>
-    <t>District</t>
-  </si>
-  <si>
-    <t>Urban Village / Village</t>
+    <t>Advance &amp; Trip</t>
   </si>
 </sst>
 </file>
@@ -239,10 +224,10 @@
             <v>97000000000004</v>
           </cell>
           <cell r="F5" t="str">
-            <v>Dashboard.DocumentTracking</v>
+            <v>Dashboard.Home</v>
           </cell>
           <cell r="G5" t="str">
-            <v>Document Tracking</v>
+            <v>Dashboard</v>
           </cell>
         </row>
         <row r="6">
@@ -250,10 +235,10 @@
             <v>97000000000005</v>
           </cell>
           <cell r="F6" t="str">
-            <v>Dashboard.MyDocumentTracking</v>
+            <v>Dashboard.DocumentTracking</v>
           </cell>
           <cell r="G6" t="str">
-            <v>My Document Tracking</v>
+            <v>Document Tracking</v>
           </cell>
         </row>
         <row r="7">
@@ -261,10 +246,10 @@
             <v>97000000000006</v>
           </cell>
           <cell r="F7" t="str">
-            <v>Dashboard.MyDocumentDisposition</v>
+            <v>Dashboard.MyDocumentTracking</v>
           </cell>
           <cell r="G7" t="str">
-            <v>My Document Disposition</v>
+            <v>My Document Tracking</v>
           </cell>
         </row>
         <row r="8">
@@ -272,10 +257,10 @@
             <v>97000000000007</v>
           </cell>
           <cell r="F8" t="str">
-            <v>Module.General.MasterData.Country.Transaction</v>
+            <v>Dashboard.MyDocumentDisposition</v>
           </cell>
           <cell r="G8" t="str">
-            <v>Country</v>
+            <v>My Document Disposition</v>
           </cell>
         </row>
         <row r="9">
@@ -283,10 +268,10 @@
             <v>97000000000008</v>
           </cell>
           <cell r="F9" t="str">
-            <v>Module.General.MasterData.CountryAdministrativeAreaLevel1.Transaction</v>
+            <v>Module.General.MasterData.Country.Transaction</v>
           </cell>
           <cell r="G9" t="str">
-            <v>Province / State</v>
+            <v>Country</v>
           </cell>
         </row>
         <row r="10">
@@ -294,10 +279,10 @@
             <v>97000000000009</v>
           </cell>
           <cell r="F10" t="str">
-            <v>Module.General.MasterData.CountryAdministrativeAreaLevel2.Transaction</v>
+            <v>Module.General.MasterData.CountryAdministrativeAreaLevel1.Transaction</v>
           </cell>
           <cell r="G10" t="str">
-            <v>Municipality / Regency</v>
+            <v>Province / State</v>
           </cell>
         </row>
         <row r="11">
@@ -305,10 +290,10 @@
             <v>97000000000010</v>
           </cell>
           <cell r="F11" t="str">
-            <v>Module.General.MasterData.CountryAdministrativeAreaLevel3.Transaction</v>
+            <v>Module.General.MasterData.CountryAdministrativeAreaLevel2.Transaction</v>
           </cell>
           <cell r="G11" t="str">
-            <v>District</v>
+            <v>Municipality / Regency</v>
           </cell>
         </row>
         <row r="12">
@@ -316,10 +301,10 @@
             <v>97000000000011</v>
           </cell>
           <cell r="F12" t="str">
-            <v>Module.General.MasterData.CountryAdministrativeAreaLevel4.Transaction</v>
+            <v>Module.General.MasterData.CountryAdministrativeAreaLevel3.Transaction</v>
           </cell>
           <cell r="G12" t="str">
-            <v>Urban Village / Village</v>
+            <v>District</v>
           </cell>
         </row>
         <row r="13">
@@ -327,10 +312,10 @@
             <v>97000000000012</v>
           </cell>
           <cell r="F13" t="str">
-            <v>Module.General.MasterData.BusinessDocumentType.Transaction</v>
+            <v>Module.General.MasterData.CountryAdministrativeAreaLevel4.Transaction</v>
           </cell>
           <cell r="G13" t="str">
-            <v>Business Document Type</v>
+            <v>Urban Village / Village</v>
           </cell>
         </row>
         <row r="14">
@@ -338,10 +323,10 @@
             <v>97000000000013</v>
           </cell>
           <cell r="F14" t="str">
-            <v>Module.General.MasterData.BusinessDocument.Transaction</v>
+            <v>Module.General.MasterData.BusinessDocumentType.Transaction</v>
           </cell>
           <cell r="G14" t="str">
-            <v>Business Document</v>
+            <v>Business Document Type</v>
           </cell>
         </row>
         <row r="15">
@@ -349,10 +334,10 @@
             <v>97000000000014</v>
           </cell>
           <cell r="F15" t="str">
-            <v>Module.General.MasterData.BusinessDocumentVersion.Transaction</v>
+            <v>Module.General.MasterData.BusinessDocument.Transaction</v>
           </cell>
           <cell r="G15" t="str">
-            <v>Business Document Version</v>
+            <v>Business Document</v>
           </cell>
         </row>
         <row r="16">
@@ -360,10 +345,10 @@
             <v>97000000000015</v>
           </cell>
           <cell r="F16" t="str">
-            <v>Module.General.MasterData.MenuManagement.Transaction</v>
+            <v>Module.General.MasterData.BusinessDocumentVersion.Transaction</v>
           </cell>
           <cell r="G16" t="str">
-            <v>Menu Management</v>
+            <v>Business Document Version</v>
           </cell>
         </row>
         <row r="17">
@@ -371,10 +356,10 @@
             <v>97000000000016</v>
           </cell>
           <cell r="F17" t="str">
-            <v>Module.General.MasterData.WorkflowRoute.Transaction</v>
+            <v>Module.General.MasterData.MenuManagement.Transaction</v>
           </cell>
           <cell r="G17" t="str">
-            <v>Workflow Route</v>
+            <v>Menu Management</v>
           </cell>
         </row>
         <row r="18">
@@ -382,10 +367,10 @@
             <v>97000000000017</v>
           </cell>
           <cell r="F18" t="str">
-            <v>Module.Budgeting.Data.Budget.Transaction</v>
+            <v>Module.General.MasterData.PrivilegeMenu.Transaction</v>
           </cell>
           <cell r="G18" t="str">
-            <v>Budget</v>
+            <v>Privilege Menu</v>
           </cell>
         </row>
         <row r="19">
@@ -393,10 +378,10 @@
             <v>97000000000018</v>
           </cell>
           <cell r="F19" t="str">
-            <v>Module.Budgeting.Data.ModifyBudget.Report.Resume</v>
+            <v>Module.General.MasterData.Workflow.Transaction</v>
           </cell>
           <cell r="G19" t="str">
-            <v>Report Modify Budget Summary</v>
+            <v>Workflow</v>
           </cell>
         </row>
         <row r="20">
@@ -404,10 +389,10 @@
             <v>97000000000019</v>
           </cell>
           <cell r="F20" t="str">
-            <v>Module.Budgeting.Data.CFS.Report.Resume</v>
+            <v>Module.Budgeting.MasterData.Budget.Transaction</v>
           </cell>
           <cell r="G20" t="str">
-            <v>Report Cost Financial Structure</v>
+            <v>Budget</v>
           </cell>
         </row>
         <row r="21">
@@ -415,10 +400,10 @@
             <v>97000000000020</v>
           </cell>
           <cell r="F21" t="str">
-            <v>Module.General.MasterData.Religion.Transaction</v>
+            <v>Module.Budgeting.MasterData.BudgetSection.Transaction</v>
           </cell>
           <cell r="G21" t="str">
-            <v>Religion</v>
+            <v>Sub Budget</v>
           </cell>
         </row>
         <row r="22">
@@ -426,10 +411,10 @@
             <v>97000000000021</v>
           </cell>
           <cell r="F22" t="str">
-            <v>Module.General.MasterData.BloodAglutinogenType.Transaction</v>
+            <v>Module.Budgeting.Data.ModifyBudget.Transaction</v>
           </cell>
           <cell r="G22" t="str">
-            <v>Blood Aglutinogen Type</v>
+            <v>Modify Budget</v>
           </cell>
         </row>
         <row r="23">
@@ -437,10 +422,10 @@
             <v>97000000000022</v>
           </cell>
           <cell r="F23" t="str">
-            <v>Module.HumanResource.Data.PersonWorkTimeSheet.Transaction</v>
+            <v>Module.Budgeting.Data.ModifyBudget.Report.Resume</v>
           </cell>
           <cell r="G23" t="str">
-            <v>Person Work Time Sheet</v>
+            <v>Report Modify Budget Summary</v>
           </cell>
         </row>
         <row r="24">
@@ -448,10 +433,10 @@
             <v>97000000000023</v>
           </cell>
           <cell r="F24" t="str">
-            <v>Module.General.MasterData.Warehouse.Transaction</v>
+            <v>Module.Budgeting.Data.Work.Transaction</v>
           </cell>
           <cell r="G24" t="str">
-            <v>Warehouse</v>
+            <v>Work</v>
           </cell>
         </row>
         <row r="25">
@@ -459,10 +444,10 @@
             <v>97000000000024</v>
           </cell>
           <cell r="F25" t="str">
-            <v>Module.General.MasterData.ProductType.Transaction</v>
+            <v>Module.Budgeting.Data.CFS.Report.Resume</v>
           </cell>
           <cell r="G25" t="str">
-            <v>Product Type</v>
+            <v>Report Cost Financial Structure</v>
           </cell>
         </row>
         <row r="26">
@@ -470,10 +455,10 @@
             <v>97000000000025</v>
           </cell>
           <cell r="F26" t="str">
-            <v>Module.General.MasterData.Product.Transaction</v>
+            <v>Module.General.MasterData.BloodAglutinogenType.Transaction</v>
           </cell>
           <cell r="G26" t="str">
-            <v>Product</v>
+            <v>Blood Aglutinogen Type</v>
           </cell>
         </row>
         <row r="27">
@@ -481,10 +466,10 @@
             <v>97000000000026</v>
           </cell>
           <cell r="F27" t="str">
-            <v>Module.SupplyChain.Data.DeliveryOrder.Report.DataList</v>
+            <v>Module.General.MasterData.Person.Transaction</v>
           </cell>
           <cell r="G27" t="str">
-            <v>Report DO Summary</v>
+            <v>Person</v>
           </cell>
         </row>
         <row r="28">
@@ -492,10 +477,10 @@
             <v>97000000000027</v>
           </cell>
           <cell r="F28" t="str">
-            <v>Module.SupplyChain.Data.DeliveryOrder.Transaction</v>
+            <v>Module.General.MasterData.Religion.Transaction</v>
           </cell>
           <cell r="G28" t="str">
-            <v>Delivery Order</v>
+            <v>Religion</v>
           </cell>
         </row>
         <row r="29">
@@ -503,10 +488,10 @@
             <v>97000000000028</v>
           </cell>
           <cell r="F29" t="str">
-            <v>Module.SupplyChain.Data.MaterialReceive.Transaction</v>
+            <v>Module.General.MasterData.UserRole.Transaction</v>
           </cell>
           <cell r="G29" t="str">
-            <v>Material Receive</v>
+            <v>Role</v>
           </cell>
         </row>
         <row r="30">
@@ -514,10 +499,10 @@
             <v>97000000000029</v>
           </cell>
           <cell r="F30" t="str">
-            <v>Module.SupplyChain.Data.MaterialReturn.Report.DataList</v>
+            <v>Module.HumanResource.MasterData.OrganizationalDepartment.Transaction</v>
           </cell>
           <cell r="G30" t="str">
-            <v>Report Material Return Summary</v>
+            <v>Department</v>
           </cell>
         </row>
         <row r="31">
@@ -525,10 +510,10 @@
             <v>97000000000030</v>
           </cell>
           <cell r="F31" t="str">
-            <v>Module.SupplyChain.Data.MaterialReturn.Transaction</v>
+            <v>Module.HumanResource.Data.PersonWorkTimeSheet.Transaction</v>
           </cell>
           <cell r="G31" t="str">
-            <v>Material Return</v>
+            <v>Person Work Time Sheet</v>
           </cell>
         </row>
         <row r="32">
@@ -536,10 +521,10 @@
             <v>97000000000031</v>
           </cell>
           <cell r="F32" t="str">
-            <v>Module.Finance.Data.Advance.Report.DataList</v>
+            <v>Module.HumanResource.Data.PersonWorkTimeSheet.Report.DataList</v>
           </cell>
           <cell r="G32" t="str">
-            <v>Report Advance Summary</v>
+            <v>Person Work Time Sheet Summary</v>
           </cell>
         </row>
         <row r="33">
@@ -547,10 +532,10 @@
             <v>97000000000032</v>
           </cell>
           <cell r="F33" t="str">
-            <v>Module.Finance.Data.Advance.Transaction</v>
+            <v>Module.HumanResource.Data.SallaryAllocation.Transaction</v>
           </cell>
           <cell r="G33" t="str">
-            <v>Advance Request</v>
+            <v>Sallary Allocation</v>
           </cell>
         </row>
         <row r="34">
@@ -558,10 +543,10 @@
             <v>97000000000033</v>
           </cell>
           <cell r="F34" t="str">
-            <v>Module.Finance.Data.AdvanceSettlement.Report.DataList</v>
+            <v>Module.HumanResource.Data.SallaryAllocation.Report.DataList</v>
           </cell>
           <cell r="G34" t="str">
-            <v>Report Advance Settlement Summary</v>
+            <v>Sallary Allocation Summary</v>
           </cell>
         </row>
         <row r="35">
@@ -569,10 +554,10 @@
             <v>97000000000034</v>
           </cell>
           <cell r="F35" t="str">
-            <v>Module.Finance.Data.AdvanceSettlement.Transaction</v>
+            <v>Module.General.MasterData.Warehouse.Transaction</v>
           </cell>
           <cell r="G35" t="str">
-            <v>AdvanceSettlement</v>
+            <v>Warehouse</v>
           </cell>
         </row>
         <row r="36">
@@ -580,10 +565,10 @@
             <v>97000000000035</v>
           </cell>
           <cell r="F36" t="str">
-            <v>Module.Finance.Data.PersonBusinessTripSettlement.Report.DataList</v>
+            <v>Module.General.MasterData.ProductType.Transaction</v>
           </cell>
           <cell r="G36" t="str">
-            <v>Report BusinessTrip Settlement Summary</v>
+            <v>Product Type</v>
           </cell>
         </row>
         <row r="37">
@@ -591,10 +576,10 @@
             <v>97000000000036</v>
           </cell>
           <cell r="F37" t="str">
-            <v>Module.Finance.Data.PersonBusinessTripSettlement.Transaction</v>
+            <v>Module.General.MasterData.Product.Transaction</v>
           </cell>
           <cell r="G37" t="str">
-            <v>BusinessTrip Settlement</v>
+            <v>Product</v>
           </cell>
         </row>
         <row r="38">
@@ -602,10 +587,10 @@
             <v>97000000000037</v>
           </cell>
           <cell r="F38" t="str">
-            <v>Module.Finance.Data.PersonBusinessTrip.Report.DataList</v>
+            <v>Module.SupplyChain.Data.DeliveryOrder.Transaction</v>
           </cell>
           <cell r="G38" t="str">
-            <v>Report BusinessTrip Request Summary</v>
+            <v>Delivery Order</v>
           </cell>
         </row>
         <row r="39">
@@ -613,10 +598,10 @@
             <v>97000000000038</v>
           </cell>
           <cell r="F39" t="str">
-            <v>Module.Finance.Data.PersonBusinessTrip.Transaction</v>
+            <v>Module.SupplyChain.Data.DeliveryOrder.Report.DataList</v>
           </cell>
           <cell r="G39" t="str">
-            <v>BusinessTrip Request</v>
+            <v>Report DO Summary</v>
           </cell>
         </row>
         <row r="40">
@@ -624,10 +609,10 @@
             <v>97000000000039</v>
           </cell>
           <cell r="F40" t="str">
-            <v>Module.SupplyChain.MasterData.Supplier.Transaction</v>
+            <v>Module.SupplyChain.Data.DeliveryOrderToMaterialReceive.Report.DataList</v>
           </cell>
           <cell r="G40" t="str">
-            <v>Supplier</v>
+            <v>Report DO to Material Receive</v>
           </cell>
         </row>
         <row r="41">
@@ -635,10 +620,10 @@
             <v>97000000000040</v>
           </cell>
           <cell r="F41" t="str">
-            <v>Module.SupplyChain.Data.PurchaseRequisition.Report.DataList</v>
+            <v>Module.SupplyChain.Data.MaterialReceive.Transaction</v>
           </cell>
           <cell r="G41" t="str">
-            <v>Report Purchase Requisition Summary</v>
+            <v>Material Receive</v>
           </cell>
         </row>
         <row r="42">
@@ -646,10 +631,10 @@
             <v>97000000000041</v>
           </cell>
           <cell r="F42" t="str">
-            <v>Module.SupplyChain.Data.PurchaseRequisitionToPurchaseOrder.Report.DataList</v>
+            <v>Module.SupplyChain.Data.MaterialReceive.Report.DataList</v>
           </cell>
           <cell r="G42" t="str">
-            <v>Report Purchase Requisition To Purchase Order</v>
+            <v>Report Material Receive Summary</v>
           </cell>
         </row>
         <row r="43">
@@ -657,10 +642,10 @@
             <v>97000000000042</v>
           </cell>
           <cell r="F43" t="str">
-            <v>Module.SupplyChain.Data.PurchaseRequisition.Transaction</v>
+            <v>Module.SupplyChain.Data.MaterialReceiveToMaterialReturn.Report.DataList</v>
           </cell>
           <cell r="G43" t="str">
-            <v>Purchase Requisition</v>
+            <v>Report Material Receive to Material Return</v>
           </cell>
         </row>
         <row r="44">
@@ -668,10 +653,10 @@
             <v>97000000000043</v>
           </cell>
           <cell r="F44" t="str">
-            <v>Module.SupplyChain.Data.PurchaseOrder.Report.DataList</v>
+            <v>Module.SupplyChain.Data.MaterialReturn.Transaction</v>
           </cell>
           <cell r="G44" t="str">
-            <v>Report Purchase Order Summary</v>
+            <v>Material Return</v>
           </cell>
         </row>
         <row r="45">
@@ -679,10 +664,10 @@
             <v>97000000000044</v>
           </cell>
           <cell r="F45" t="str">
-            <v>Module.SupplyChain.Data.PurchaseOrder.Transaction</v>
+            <v>Module.SupplyChain.Data.MaterialReturn.Report.DataList</v>
           </cell>
           <cell r="G45" t="str">
-            <v>Purchase Order</v>
+            <v>Report Material Return Summary</v>
           </cell>
         </row>
         <row r="46">
@@ -690,10 +675,10 @@
             <v>97000000000045</v>
           </cell>
           <cell r="F46" t="str">
-            <v>Module.General.MasterData.Period.Transaction</v>
+            <v>Module.Finance.Data.Advance.Transaction</v>
           </cell>
           <cell r="G46" t="str">
-            <v>Period</v>
+            <v>Advance Request</v>
           </cell>
         </row>
         <row r="47">
@@ -701,10 +686,10 @@
             <v>97000000000046</v>
           </cell>
           <cell r="F47" t="str">
-            <v>Module.General.MasterData.Currency.Transaction</v>
+            <v>Module.Finance.Data.Advance.Report.DataList</v>
           </cell>
           <cell r="G47" t="str">
-            <v>Currency</v>
+            <v>Report Advance Summary</v>
           </cell>
         </row>
         <row r="48">
@@ -712,10 +697,10 @@
             <v>97000000000047</v>
           </cell>
           <cell r="F48" t="str">
-            <v>Module.Finance.Data.Reimbursement.Transaction</v>
+            <v>Module.Finance.Data.AdvanceToAdvanceSettlement.Report.DataList</v>
           </cell>
           <cell r="G48" t="str">
-            <v>Reimbursement</v>
+            <v>Report Advance to Advance Settlement</v>
           </cell>
         </row>
         <row r="49">
@@ -723,10 +708,10 @@
             <v>97000000000048</v>
           </cell>
           <cell r="F49" t="str">
-            <v>Module.Finance.Data.Reimbursement.Report.DataList</v>
+            <v>Module.Finance.Data.AdvanceSettlement.Transaction</v>
           </cell>
           <cell r="G49" t="str">
-            <v>Reimbursement Summary</v>
+            <v>AdvanceSettlement</v>
           </cell>
         </row>
         <row r="50">
@@ -734,10 +719,10 @@
             <v>97000000000049</v>
           </cell>
           <cell r="F50" t="str">
-            <v>Module.Finance.Data.DebitNote.Transaction</v>
+            <v>Module.Finance.Data.AdvanceSettlement.Report.DataList</v>
           </cell>
           <cell r="G50" t="str">
-            <v>Debit Note</v>
+            <v>Report Advance Settlement Summary</v>
           </cell>
         </row>
         <row r="51">
@@ -745,10 +730,10 @@
             <v>97000000000050</v>
           </cell>
           <cell r="F51" t="str">
-            <v>Module.Finance.Data.DebitNote.Report.DataList</v>
+            <v>Module.Finance.Data.PersonBusinessTrip.Transaction</v>
           </cell>
           <cell r="G51" t="str">
-            <v>Debit Note Summary</v>
+            <v>BusinessTrip Request</v>
           </cell>
         </row>
         <row r="52">
@@ -756,10 +741,10 @@
             <v>97000000000051</v>
           </cell>
           <cell r="F52" t="str">
-            <v>Module.Finance.Data.ReimbursementToDebitNote.Report.DataList</v>
+            <v>Module.Finance.Data.PersonBusinessTrip.Report.DataList</v>
           </cell>
           <cell r="G52" t="str">
-            <v>Reimbursement to Debit Note</v>
+            <v>Report BusinessTrip Request Summary</v>
           </cell>
         </row>
         <row r="53">
@@ -767,10 +752,10 @@
             <v>97000000000052</v>
           </cell>
           <cell r="F53" t="str">
-            <v>Module.Finance.Data.CreditNote.Transaction</v>
+            <v>Module.Finance.Data.PersonBusinessTripToPersonBusinessTripSettlement.Report.DataList</v>
           </cell>
           <cell r="G53" t="str">
-            <v>Credit Note</v>
+            <v>Report BusinessTrip to BusinessTrip Settlement</v>
           </cell>
         </row>
         <row r="54">
@@ -778,10 +763,10 @@
             <v>97000000000053</v>
           </cell>
           <cell r="F54" t="str">
-            <v>Module.Finance.Data.CreditNote.Report.DataList</v>
+            <v>Module.Finance.Data.PersonBusinessTripSettlement.Transaction</v>
           </cell>
           <cell r="G54" t="str">
-            <v>Credit Note Summary</v>
+            <v>BusinessTrip Settlement</v>
           </cell>
         </row>
         <row r="55">
@@ -789,10 +774,10 @@
             <v>97000000000054</v>
           </cell>
           <cell r="F55" t="str">
-            <v>Module.Finance.Data.Loan.Transaction</v>
+            <v>Module.Finance.Data.PersonBusinessTripSettlement.Report.DataList</v>
           </cell>
           <cell r="G55" t="str">
-            <v>Loan</v>
+            <v>Report BusinessTrip Settlement Summary</v>
           </cell>
         </row>
         <row r="56">
@@ -800,10 +785,10 @@
             <v>97000000000055</v>
           </cell>
           <cell r="F56" t="str">
-            <v>Module.Finance.Data.Loan.Report.DataList</v>
+            <v>Module.SupplyChain.MasterData.Supplier.Transaction</v>
           </cell>
           <cell r="G56" t="str">
-            <v>Loan Summary</v>
+            <v>Supplier</v>
           </cell>
         </row>
         <row r="57">
@@ -811,10 +796,10 @@
             <v>97000000000056</v>
           </cell>
           <cell r="F57" t="str">
-            <v>Module.Finance.Data.LoanSettlement.Transaction</v>
+            <v>Module.SupplyChain.Data.PurchaseRequisition.Transaction</v>
           </cell>
           <cell r="G57" t="str">
-            <v>Loan Settlement</v>
+            <v>Purchase Requisition</v>
           </cell>
         </row>
         <row r="58">
@@ -822,10 +807,10 @@
             <v>97000000000057</v>
           </cell>
           <cell r="F58" t="str">
-            <v>Module.Finance.Data.LoanSettlement.Report.DataList</v>
+            <v>Module.SupplyChain.Data.PurchaseRequisition.Report.DataList</v>
           </cell>
           <cell r="G58" t="str">
-            <v>Loan Settlement Summary</v>
+            <v>Report Purchase Requisition Summary</v>
           </cell>
         </row>
         <row r="59">
@@ -833,10 +818,10 @@
             <v>97000000000058</v>
           </cell>
           <cell r="F59" t="str">
-            <v>Module.Finance.Data.LoanToLoanSettlement.Report.DataList</v>
+            <v>Module.SupplyChain.Data.PurchaseRequisitionToPurchaseOrder.Report.DataList</v>
           </cell>
           <cell r="G59" t="str">
-            <v>Loan to Loan Settlement</v>
+            <v>Report Purchase Requisition To Purchase Order</v>
           </cell>
         </row>
         <row r="60">
@@ -844,10 +829,10 @@
             <v>97000000000059</v>
           </cell>
           <cell r="F60" t="str">
-            <v>Module.Finance.Data.CashBank.Transaction</v>
+            <v>Module.SupplyChain.Data.PurchaseOrder.Transaction</v>
           </cell>
           <cell r="G60" t="str">
-            <v>Cash &amp; Bank</v>
+            <v>Purchase Order</v>
           </cell>
         </row>
         <row r="61">
@@ -855,10 +840,10 @@
             <v>97000000000060</v>
           </cell>
           <cell r="F61" t="str">
-            <v>Module.Finance.Data.CashBank.Report.DataList</v>
+            <v>Module.SupplyChain.Data.PurchaseOrder.Report.DataList</v>
           </cell>
           <cell r="G61" t="str">
-            <v>Cash &amp; Bank Report</v>
+            <v>Report Purchase Order Summary</v>
           </cell>
         </row>
         <row r="62">
@@ -866,10 +851,10 @@
             <v>97000000000061</v>
           </cell>
           <cell r="F62" t="str">
-            <v>Module.Finance.Data.PaymentInstruction.Transaction</v>
+            <v>Module.SupplyChain.Data.PurchaseOrderToPaymentInstruction.Report.DataList</v>
           </cell>
           <cell r="G62" t="str">
-            <v>Account Payable</v>
+            <v>Purchase Order to Account Payable</v>
           </cell>
         </row>
         <row r="63">
@@ -877,10 +862,10 @@
             <v>97000000000062</v>
           </cell>
           <cell r="F63" t="str">
-            <v>Module.Finance.Data.PaymentInstruction.Report.DataList</v>
+            <v>Module.General.MasterData.Bank.Transaction</v>
           </cell>
           <cell r="G63" t="str">
-            <v>Account Payable Summary</v>
+            <v>Bank</v>
           </cell>
         </row>
         <row r="64">
@@ -888,10 +873,384 @@
             <v>97000000000063</v>
           </cell>
           <cell r="F64" t="str">
-            <v>Module.SupplyChain.Data.PurchaseOrderToPaymentInstruction.Report.DataList</v>
+            <v>Module.General.MasterData.BankAccount.Transaction</v>
           </cell>
           <cell r="G64" t="str">
-            <v>Purchase Order to Account Payable</v>
+            <v>Bank Account</v>
+          </cell>
+        </row>
+        <row r="65">
+          <cell r="E65">
+            <v>97000000000064</v>
+          </cell>
+          <cell r="F65" t="str">
+            <v>Module.General.MasterData.Currency.Transaction</v>
+          </cell>
+          <cell r="G65" t="str">
+            <v>Currency</v>
+          </cell>
+        </row>
+        <row r="66">
+          <cell r="E66">
+            <v>97000000000065</v>
+          </cell>
+          <cell r="F66" t="str">
+            <v>Module.General.MasterData.CurrencyExchangeRate.Transaction</v>
+          </cell>
+          <cell r="G66" t="str">
+            <v>Exchange Rate</v>
+          </cell>
+        </row>
+        <row r="67">
+          <cell r="E67">
+            <v>97000000000066</v>
+          </cell>
+          <cell r="F67" t="str">
+            <v>Module.General.MasterData.CurrencyExchangeRate.Report.DataList</v>
+          </cell>
+          <cell r="G67" t="str">
+            <v>Exchange Rate Summary</v>
+          </cell>
+        </row>
+        <row r="68">
+          <cell r="E68">
+            <v>97000000000067</v>
+          </cell>
+          <cell r="F68" t="str">
+            <v>Module.General.MasterData.PaymentTerm.Transaction</v>
+          </cell>
+          <cell r="G68" t="str">
+            <v>Payment Term</v>
+          </cell>
+        </row>
+        <row r="69">
+          <cell r="E69">
+            <v>97000000000068</v>
+          </cell>
+          <cell r="F69" t="str">
+            <v>Module.General.MasterData.Period.Transaction</v>
+          </cell>
+          <cell r="G69" t="str">
+            <v>Period</v>
+          </cell>
+        </row>
+        <row r="70">
+          <cell r="E70">
+            <v>97000000000069</v>
+          </cell>
+          <cell r="F70" t="str">
+            <v>Module.Accounting.MasterData.AssetCategory.Transaction</v>
+          </cell>
+          <cell r="G70" t="str">
+            <v>Asset Category</v>
+          </cell>
+        </row>
+        <row r="71">
+          <cell r="E71">
+            <v>97000000000070</v>
+          </cell>
+          <cell r="F71" t="str">
+            <v>Module.Accounting.MasterData.ChartOfAccount.Transaction</v>
+          </cell>
+          <cell r="G71" t="str">
+            <v>Chart of Account</v>
+          </cell>
+        </row>
+        <row r="72">
+          <cell r="E72">
+            <v>97000000000071</v>
+          </cell>
+          <cell r="F72" t="str">
+            <v>Module.Accounting.MasterData.DepreciationMethod.Transaction</v>
+          </cell>
+          <cell r="G72" t="str">
+            <v>Depreciation Method</v>
+          </cell>
+        </row>
+        <row r="73">
+          <cell r="E73">
+            <v>97000000000072</v>
+          </cell>
+          <cell r="F73" t="str">
+            <v>Module.Accounting.MasterData.DepreciationRateYears.Transaction</v>
+          </cell>
+          <cell r="G73" t="str">
+            <v>Depreciation Rate Years</v>
+          </cell>
+        </row>
+        <row r="74">
+          <cell r="E74">
+            <v>97000000000073</v>
+          </cell>
+          <cell r="F74" t="str">
+            <v>Module.Taxation.MasterData.ValueAddedTax.Transaction</v>
+          </cell>
+          <cell r="G74" t="str">
+            <v>Value Added Tax</v>
+          </cell>
+        </row>
+        <row r="75">
+          <cell r="E75">
+            <v>97000000000074</v>
+          </cell>
+          <cell r="F75" t="str">
+            <v>Module.Accounting.Data.GeneralJournal.Transaction</v>
+          </cell>
+          <cell r="G75" t="str">
+            <v>General Journal</v>
+          </cell>
+        </row>
+        <row r="76">
+          <cell r="E76">
+            <v>97000000000075</v>
+          </cell>
+          <cell r="F76" t="str">
+            <v>Module.Accounting.Data.GeneralJournal.Report.DataList</v>
+          </cell>
+          <cell r="G76" t="str">
+            <v>General Journal Summary</v>
+          </cell>
+        </row>
+        <row r="77">
+          <cell r="E77">
+            <v>97000000000076</v>
+          </cell>
+          <cell r="F77" t="str">
+            <v>Module.Finance.Data.Reimbursement.Transaction</v>
+          </cell>
+          <cell r="G77" t="str">
+            <v>Reimbursement</v>
+          </cell>
+        </row>
+        <row r="78">
+          <cell r="E78">
+            <v>97000000000077</v>
+          </cell>
+          <cell r="F78" t="str">
+            <v>Module.Finance.Data.Reimbursement.Report.DataList</v>
+          </cell>
+          <cell r="G78" t="str">
+            <v>Reimbursement Summary</v>
+          </cell>
+        </row>
+        <row r="79">
+          <cell r="E79">
+            <v>97000000000078</v>
+          </cell>
+          <cell r="F79" t="str">
+            <v>Module.Finance.Data.ReimbursementToDebitNote.Report.DataList</v>
+          </cell>
+          <cell r="G79" t="str">
+            <v>Reimbursement to Debit Note</v>
+          </cell>
+        </row>
+        <row r="80">
+          <cell r="E80">
+            <v>97000000000079</v>
+          </cell>
+          <cell r="F80" t="str">
+            <v>Module.Finance.Data.DebitNote.Transaction</v>
+          </cell>
+          <cell r="G80" t="str">
+            <v>Debit Note</v>
+          </cell>
+        </row>
+        <row r="81">
+          <cell r="E81">
+            <v>97000000000080</v>
+          </cell>
+          <cell r="F81" t="str">
+            <v>Module.Finance.Data.DebitNote.Report.DataList</v>
+          </cell>
+          <cell r="G81" t="str">
+            <v>Debit Note Summary</v>
+          </cell>
+        </row>
+        <row r="82">
+          <cell r="E82">
+            <v>97000000000081</v>
+          </cell>
+          <cell r="F82" t="str">
+            <v>Module.Finance.Data.CreditNote.Transaction</v>
+          </cell>
+          <cell r="G82" t="str">
+            <v>Credit Note</v>
+          </cell>
+        </row>
+        <row r="83">
+          <cell r="E83">
+            <v>97000000000082</v>
+          </cell>
+          <cell r="F83" t="str">
+            <v>Module.Finance.Data.CreditNote.Report.DataList</v>
+          </cell>
+          <cell r="G83" t="str">
+            <v>Credit Note Summary</v>
+          </cell>
+        </row>
+        <row r="84">
+          <cell r="E84">
+            <v>97000000000083</v>
+          </cell>
+          <cell r="F84" t="str">
+            <v>Module.Finance.Data.Loan.Transaction</v>
+          </cell>
+          <cell r="G84" t="str">
+            <v>Loan</v>
+          </cell>
+        </row>
+        <row r="85">
+          <cell r="E85">
+            <v>97000000000084</v>
+          </cell>
+          <cell r="F85" t="str">
+            <v>Module.Finance.Data.Loan.Report.DataList</v>
+          </cell>
+          <cell r="G85" t="str">
+            <v>Loan Summary</v>
+          </cell>
+        </row>
+        <row r="86">
+          <cell r="E86">
+            <v>97000000000085</v>
+          </cell>
+          <cell r="F86" t="str">
+            <v>Module.Finance.Data.LoanToLoanSettlement.Report.DataList</v>
+          </cell>
+          <cell r="G86" t="str">
+            <v>Loan to Loan Settlement</v>
+          </cell>
+        </row>
+        <row r="87">
+          <cell r="E87">
+            <v>97000000000086</v>
+          </cell>
+          <cell r="F87" t="str">
+            <v>Module.Finance.Data.LoanSettlement.Transaction</v>
+          </cell>
+          <cell r="G87" t="str">
+            <v>Loan Settlement</v>
+          </cell>
+        </row>
+        <row r="88">
+          <cell r="E88">
+            <v>97000000000087</v>
+          </cell>
+          <cell r="F88" t="str">
+            <v>Module.Finance.Data.LoanSettlement.Report.DataList</v>
+          </cell>
+          <cell r="G88" t="str">
+            <v>Loan Settlement Summary</v>
+          </cell>
+        </row>
+        <row r="89">
+          <cell r="E89">
+            <v>97000000000088</v>
+          </cell>
+          <cell r="F89" t="str">
+            <v>Module.Finance.Data.CashBank.Transaction</v>
+          </cell>
+          <cell r="G89" t="str">
+            <v>Cash &amp; Bank</v>
+          </cell>
+        </row>
+        <row r="90">
+          <cell r="E90">
+            <v>97000000000089</v>
+          </cell>
+          <cell r="F90" t="str">
+            <v>Module.Finance.Data.CashBank.Report.DataList</v>
+          </cell>
+          <cell r="G90" t="str">
+            <v>Cash &amp; Bank Summary</v>
+          </cell>
+        </row>
+        <row r="91">
+          <cell r="E91">
+            <v>97000000000090</v>
+          </cell>
+          <cell r="F91" t="str">
+            <v>Module.Finance.Data.PaymentInstruction.Transaction</v>
+          </cell>
+          <cell r="G91" t="str">
+            <v>Account Payable</v>
+          </cell>
+        </row>
+        <row r="92">
+          <cell r="E92">
+            <v>97000000000091</v>
+          </cell>
+          <cell r="F92" t="str">
+            <v>Module.Finance.Data.PaymentInstruction.Report.DataList</v>
+          </cell>
+          <cell r="G92" t="str">
+            <v>Account Payable Summary</v>
+          </cell>
+        </row>
+        <row r="93">
+          <cell r="E93">
+            <v>97000000000092</v>
+          </cell>
+          <cell r="F93" t="str">
+            <v>Module.Finance.Data.SalesInvoice.Transaction</v>
+          </cell>
+          <cell r="G93" t="str">
+            <v>Sales Invoice</v>
+          </cell>
+        </row>
+        <row r="94">
+          <cell r="E94">
+            <v>97000000000093</v>
+          </cell>
+          <cell r="F94" t="str">
+            <v>Module.Finance.Data.SalesInvoice.Report.DataList</v>
+          </cell>
+          <cell r="G94" t="str">
+            <v>Sales Invoice Summary</v>
+          </cell>
+        </row>
+        <row r="95">
+          <cell r="E95">
+            <v>97000000000094</v>
+          </cell>
+          <cell r="F95" t="str">
+            <v>Module.Finance.Data.SalesInvoiceToCreditNote.Report.DataList</v>
+          </cell>
+          <cell r="G95" t="str">
+            <v>Sales Invoice to Credit Note</v>
+          </cell>
+        </row>
+        <row r="96">
+          <cell r="E96">
+            <v>97000000000095</v>
+          </cell>
+          <cell r="F96" t="str">
+            <v>Module.Finance.Data.TaxReconciliation.Transaction</v>
+          </cell>
+          <cell r="G96" t="str">
+            <v>Tax Reconciliation</v>
+          </cell>
+        </row>
+        <row r="97">
+          <cell r="E97">
+            <v>97000000000096</v>
+          </cell>
+          <cell r="F97" t="str">
+            <v>Module.Finance.Data.TaxReconciliation.Report.DataList</v>
+          </cell>
+          <cell r="G97" t="str">
+            <v>Tax Reconciliation Summary</v>
+          </cell>
+        </row>
+        <row r="98">
+          <cell r="E98">
+            <v>97000000000097</v>
+          </cell>
+          <cell r="F98" t="str">
+            <v>Module.CustomerRelation.MasterData.Customer.Transaction</v>
+          </cell>
+          <cell r="G98" t="str">
+            <v>Customer</v>
           </cell>
         </row>
       </sheetData>
@@ -987,7 +1346,7 @@
         </row>
         <row r="9">
           <cell r="B9" t="str">
-            <v>Process</v>
+            <v>Advance &amp; Trip</v>
           </cell>
           <cell r="C9" t="str">
             <v>fas fa-hourglass-start</v>
@@ -1311,7 +1670,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:I64"/>
+  <dimension ref="B1:I98"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.140625" style="2" customWidth="1"/>
@@ -1336,11 +1695,11 @@
         <v>97000000000001</v>
       </c>
       <c r="C2" s="7" t="str">
-        <f>VLOOKUP($B2, [1]Main!$E$2:$G$324, 2, FALSE)</f>
+        <f>VLOOKUP($B2, [1]Main!$E$2:$G$358, 2, FALSE)</f>
         <v>System.Login</v>
       </c>
       <c r="D2" s="8" t="str">
-        <f>VLOOKUP($B2, [1]Main!$E$2:$G$324, 3, FALSE)</f>
+        <f>VLOOKUP($B2, [1]Main!$E$2:$G$358, 3, FALSE)</f>
         <v>Login</v>
       </c>
       <c r="F2" s="10" t="s">
@@ -1364,11 +1723,11 @@
         <v>97000000000002</v>
       </c>
       <c r="C3" s="7" t="str">
-        <f>VLOOKUP($B3, [1]Main!$E$2:$G$324, 2, FALSE)</f>
+        <f>VLOOKUP($B3, [1]Main!$E$2:$G$358, 2, FALSE)</f>
         <v>System.Logout</v>
       </c>
       <c r="D3" s="8" t="str">
-        <f>VLOOKUP($B3, [1]Main!$E$2:$G$324, 3, FALSE)</f>
+        <f>VLOOKUP($B3, [1]Main!$E$2:$G$358, 3, FALSE)</f>
         <v>Logout</v>
       </c>
       <c r="F3" s="10" t="s">
@@ -1382,7 +1741,7 @@
         <v>2</v>
       </c>
       <c r="I3" s="9" t="str">
-        <f t="shared" ref="I3:I62" si="0">IF(EXACT(G3, ""), "", CONCATENATE("PERFORM ""SchSysConfig"".""Func_TblAppObject_MenuGroupMember_SET""(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, ", G3, "::bigint, ", B3, "::bigint);"))</f>
+        <f t="shared" ref="I3:I66" si="0">IF(EXACT(G3, ""), "", CONCATENATE("PERFORM ""SchSysConfig"".""Func_TblAppObject_MenuGroupMember_SET""(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, ", G3, "::bigint, ", B3, "::bigint);"))</f>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000001::bigint, 97000000000002::bigint);</v>
       </c>
     </row>
@@ -1392,11 +1751,11 @@
         <v>97000000000003</v>
       </c>
       <c r="C4" s="7" t="str">
-        <f>VLOOKUP($B4, [1]Main!$E$2:$G$324, 2, FALSE)</f>
+        <f>VLOOKUP($B4, [1]Main!$E$2:$G$358, 2, FALSE)</f>
         <v>System.Lock</v>
       </c>
       <c r="D4" s="8" t="str">
-        <f>VLOOKUP($B4, [1]Main!$E$2:$G$324, 3, FALSE)</f>
+        <f>VLOOKUP($B4, [1]Main!$E$2:$G$358, 3, FALSE)</f>
         <v>Lock</v>
       </c>
       <c r="F4" s="10" t="s">
@@ -1420,12 +1779,12 @@
         <v>97000000000004</v>
       </c>
       <c r="C5" s="7" t="str">
-        <f>VLOOKUP($B5, [1]Main!$E$2:$G$324, 2, FALSE)</f>
-        <v>Dashboard.DocumentTracking</v>
+        <f>VLOOKUP($B5, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <v>Dashboard.Home</v>
       </c>
       <c r="D5" s="8" t="str">
-        <f>VLOOKUP($B5, [1]Main!$E$2:$G$324, 3, FALSE)</f>
-        <v>Document Tracking</v>
+        <f>VLOOKUP($B5, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <v>Dashboard</v>
       </c>
       <c r="F5" s="10" t="s">
         <v>0</v>
@@ -1448,12 +1807,12 @@
         <v>97000000000005</v>
       </c>
       <c r="C6" s="7" t="str">
-        <f>VLOOKUP($B6, [1]Main!$E$2:$G$324, 2, FALSE)</f>
-        <v>Dashboard.MyDocumentTracking</v>
+        <f>VLOOKUP($B6, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <v>Dashboard.DocumentTracking</v>
       </c>
       <c r="D6" s="8" t="str">
-        <f>VLOOKUP($B6, [1]Main!$E$2:$G$324, 3, FALSE)</f>
-        <v>My Document Tracking</v>
+        <f>VLOOKUP($B6, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <v>Document Tracking</v>
       </c>
       <c r="F6" s="10" t="s">
         <v>0</v>
@@ -1476,12 +1835,12 @@
         <v>97000000000006</v>
       </c>
       <c r="C7" s="7" t="str">
-        <f>VLOOKUP($B7, [1]Main!$E$2:$G$324, 2, FALSE)</f>
-        <v>Dashboard.MyDocumentDisposition</v>
+        <f>VLOOKUP($B7, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <v>Dashboard.MyDocumentTracking</v>
       </c>
       <c r="D7" s="8" t="str">
-        <f>VLOOKUP($B7, [1]Main!$E$2:$G$324, 3, FALSE)</f>
-        <v>My Document Disposition</v>
+        <f>VLOOKUP($B7, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <v>My Document Tracking</v>
       </c>
       <c r="F7" s="10" t="s">
         <v>0</v>
@@ -1504,25 +1863,26 @@
         <v>97000000000007</v>
       </c>
       <c r="C8" s="7" t="str">
-        <f>VLOOKUP($B8, [1]Main!$E$2:$G$324, 2, FALSE)</f>
-        <v>Module.General.MasterData.Country.Transaction</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>9</v>
+        <f>VLOOKUP($B8, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <v>Dashboard.MyDocumentDisposition</v>
+      </c>
+      <c r="D8" s="8" t="str">
+        <f>VLOOKUP($B8, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <v>My Document Disposition</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" s="6">
         <f>IF(EXACT($F8, ""), "", VLOOKUP($F8, [2]Main!$B$2:$E$30, 4, FALSE))</f>
-        <v>254000000000002</v>
+        <v>254000000000001</v>
       </c>
       <c r="H8" s="2">
         <v>7</v>
       </c>
       <c r="I8" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000002::bigint, 97000000000007::bigint);</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000001::bigint, 97000000000007::bigint);</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -1531,11 +1891,12 @@
         <v>97000000000008</v>
       </c>
       <c r="C9" s="7" t="str">
-        <f>VLOOKUP($B9, [1]Main!$E$2:$G$324, 2, FALSE)</f>
-        <v>Module.General.MasterData.CountryAdministrativeAreaLevel1.Transaction</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>10</v>
+        <f>VLOOKUP($B9, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <v>Module.General.MasterData.Country.Transaction</v>
+      </c>
+      <c r="D9" s="8" t="str">
+        <f>VLOOKUP($B9, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <v>Country</v>
       </c>
       <c r="F9" s="10" t="s">
         <v>1</v>
@@ -1558,11 +1919,12 @@
         <v>97000000000009</v>
       </c>
       <c r="C10" s="7" t="str">
-        <f>VLOOKUP($B10, [1]Main!$E$2:$G$324, 2, FALSE)</f>
-        <v>Module.General.MasterData.CountryAdministrativeAreaLevel2.Transaction</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>11</v>
+        <f>VLOOKUP($B10, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <v>Module.General.MasterData.CountryAdministrativeAreaLevel1.Transaction</v>
+      </c>
+      <c r="D10" s="8" t="str">
+        <f>VLOOKUP($B10, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <v>Province / State</v>
       </c>
       <c r="F10" s="10" t="s">
         <v>1</v>
@@ -1585,11 +1947,12 @@
         <v>97000000000010</v>
       </c>
       <c r="C11" s="7" t="str">
-        <f>VLOOKUP($B11, [1]Main!$E$2:$G$324, 2, FALSE)</f>
-        <v>Module.General.MasterData.CountryAdministrativeAreaLevel3.Transaction</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>12</v>
+        <f>VLOOKUP($B11, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <v>Module.General.MasterData.CountryAdministrativeAreaLevel2.Transaction</v>
+      </c>
+      <c r="D11" s="8" t="str">
+        <f>VLOOKUP($B11, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <v>Municipality / Regency</v>
       </c>
       <c r="F11" s="10" t="s">
         <v>1</v>
@@ -1612,11 +1975,12 @@
         <v>97000000000011</v>
       </c>
       <c r="C12" s="7" t="str">
-        <f>VLOOKUP($B12, [1]Main!$E$2:$G$324, 2, FALSE)</f>
-        <v>Module.General.MasterData.CountryAdministrativeAreaLevel4.Transaction</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>13</v>
+        <f>VLOOKUP($B12, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <v>Module.General.MasterData.CountryAdministrativeAreaLevel3.Transaction</v>
+      </c>
+      <c r="D12" s="8" t="str">
+        <f>VLOOKUP($B12, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <v>District</v>
       </c>
       <c r="F12" s="10" t="s">
         <v>1</v>
@@ -1639,10 +2003,13 @@
         <v>97000000000012</v>
       </c>
       <c r="C13" s="7" t="str">
-        <f>VLOOKUP($B13, [1]Main!$E$2:$G$324, 2, FALSE)</f>
-        <v>Module.General.MasterData.BusinessDocumentType.Transaction</v>
-      </c>
-      <c r="D13" s="8"/>
+        <f>VLOOKUP($B13, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <v>Module.General.MasterData.CountryAdministrativeAreaLevel4.Transaction</v>
+      </c>
+      <c r="D13" s="8" t="str">
+        <f>VLOOKUP($B13, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <v>Urban Village / Village</v>
+      </c>
       <c r="F13" s="10" t="s">
         <v>1</v>
       </c>
@@ -1664,12 +2031,12 @@
         <v>97000000000013</v>
       </c>
       <c r="C14" s="7" t="str">
-        <f>VLOOKUP($B14, [1]Main!$E$2:$G$324, 2, FALSE)</f>
-        <v>Module.General.MasterData.BusinessDocument.Transaction</v>
+        <f>VLOOKUP($B14, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <v>Module.General.MasterData.BusinessDocumentType.Transaction</v>
       </c>
       <c r="D14" s="8" t="str">
-        <f>VLOOKUP($B14, [1]Main!$E$2:$G$324, 3, FALSE)</f>
-        <v>Business Document</v>
+        <f>VLOOKUP($B14, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <v>Business Document Type</v>
       </c>
       <c r="F14" s="10" t="s">
         <v>1</v>
@@ -1692,12 +2059,12 @@
         <v>97000000000014</v>
       </c>
       <c r="C15" s="7" t="str">
-        <f>VLOOKUP($B15, [1]Main!$E$2:$G$324, 2, FALSE)</f>
-        <v>Module.General.MasterData.BusinessDocumentVersion.Transaction</v>
+        <f>VLOOKUP($B15, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <v>Module.General.MasterData.BusinessDocument.Transaction</v>
       </c>
       <c r="D15" s="8" t="str">
-        <f>VLOOKUP($B15, [1]Main!$E$2:$G$324, 3, FALSE)</f>
-        <v>Business Document Version</v>
+        <f>VLOOKUP($B15, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <v>Business Document</v>
       </c>
       <c r="F15" s="10" t="s">
         <v>1</v>
@@ -1720,12 +2087,12 @@
         <v>97000000000015</v>
       </c>
       <c r="C16" s="7" t="str">
-        <f>VLOOKUP($B16, [1]Main!$E$2:$G$324, 2, FALSE)</f>
-        <v>Module.General.MasterData.MenuManagement.Transaction</v>
+        <f>VLOOKUP($B16, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <v>Module.General.MasterData.BusinessDocumentVersion.Transaction</v>
       </c>
       <c r="D16" s="8" t="str">
-        <f>VLOOKUP($B16, [1]Main!$E$2:$G$324, 3, FALSE)</f>
-        <v>Menu Management</v>
+        <f>VLOOKUP($B16, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <v>Business Document Version</v>
       </c>
       <c r="F16" s="10" t="s">
         <v>1</v>
@@ -1748,12 +2115,12 @@
         <v>97000000000016</v>
       </c>
       <c r="C17" s="7" t="str">
-        <f>VLOOKUP($B17, [1]Main!$E$2:$G$324, 2, FALSE)</f>
-        <v>Module.General.MasterData.WorkflowRoute.Transaction</v>
+        <f>VLOOKUP($B17, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <v>Module.General.MasterData.MenuManagement.Transaction</v>
       </c>
       <c r="D17" s="8" t="str">
-        <f>VLOOKUP($B17, [1]Main!$E$2:$G$324, 3, FALSE)</f>
-        <v>Workflow Route</v>
+        <f>VLOOKUP($B17, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <v>Menu Management</v>
       </c>
       <c r="F17" s="10" t="s">
         <v>1</v>
@@ -1776,26 +2143,26 @@
         <v>97000000000017</v>
       </c>
       <c r="C18" s="7" t="str">
-        <f>VLOOKUP($B18, [1]Main!$E$2:$G$324, 2, FALSE)</f>
-        <v>Module.Budgeting.Data.Budget.Transaction</v>
+        <f>VLOOKUP($B18, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <v>Module.General.MasterData.PrivilegeMenu.Transaction</v>
       </c>
       <c r="D18" s="8" t="str">
-        <f>VLOOKUP($B18, [1]Main!$E$2:$G$324, 3, FALSE)</f>
-        <v>Budget</v>
+        <f>VLOOKUP($B18, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <v>Privilege Menu</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G18" s="6">
         <f>IF(EXACT($F18, ""), "", VLOOKUP($F18, [2]Main!$B$2:$E$30, 4, FALSE))</f>
-        <v>254000000000004</v>
+        <v>254000000000002</v>
       </c>
       <c r="H18" s="2">
         <v>17</v>
       </c>
       <c r="I18" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000004::bigint, 97000000000017::bigint);</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000002::bigint, 97000000000017::bigint);</v>
       </c>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
@@ -1804,26 +2171,26 @@
         <v>97000000000018</v>
       </c>
       <c r="C19" s="7" t="str">
-        <f>VLOOKUP($B19, [1]Main!$E$2:$G$324, 2, FALSE)</f>
-        <v>Module.Budgeting.Data.ModifyBudget.Report.Resume</v>
+        <f>VLOOKUP($B19, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <v>Module.General.MasterData.Workflow.Transaction</v>
       </c>
       <c r="D19" s="8" t="str">
-        <f>VLOOKUP($B19, [1]Main!$E$2:$G$324, 3, FALSE)</f>
-        <v>Report Modify Budget Summary</v>
+        <f>VLOOKUP($B19, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <v>Workflow</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G19" s="6">
         <f>IF(EXACT($F19, ""), "", VLOOKUP($F19, [2]Main!$B$2:$E$30, 4, FALSE))</f>
-        <v>254000000000004</v>
+        <v>254000000000002</v>
       </c>
       <c r="H19" s="2">
         <v>18</v>
       </c>
       <c r="I19" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000004::bigint, 97000000000018::bigint);</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000002::bigint, 97000000000018::bigint);</v>
       </c>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
@@ -1832,12 +2199,12 @@
         <v>97000000000019</v>
       </c>
       <c r="C20" s="7" t="str">
-        <f>VLOOKUP($B20, [1]Main!$E$2:$G$324, 2, FALSE)</f>
-        <v>Module.Budgeting.Data.CFS.Report.Resume</v>
+        <f>VLOOKUP($B20, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <v>Module.Budgeting.MasterData.Budget.Transaction</v>
       </c>
       <c r="D20" s="8" t="str">
-        <f>VLOOKUP($B20, [1]Main!$E$2:$G$324, 3, FALSE)</f>
-        <v>Report Cost Financial Structure</v>
+        <f>VLOOKUP($B20, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <v>Budget</v>
       </c>
       <c r="F20" s="10" t="s">
         <v>6</v>
@@ -1860,26 +2227,26 @@
         <v>97000000000020</v>
       </c>
       <c r="C21" s="7" t="str">
-        <f>VLOOKUP($B21, [1]Main!$E$2:$G$324, 2, FALSE)</f>
-        <v>Module.General.MasterData.Religion.Transaction</v>
+        <f>VLOOKUP($B21, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <v>Module.Budgeting.MasterData.BudgetSection.Transaction</v>
       </c>
       <c r="D21" s="8" t="str">
-        <f>VLOOKUP($B21, [1]Main!$E$2:$G$324, 3, FALSE)</f>
-        <v>Religion</v>
+        <f>VLOOKUP($B21, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <v>Sub Budget</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G21" s="6">
         <f>IF(EXACT($F21, ""), "", VLOOKUP($F21, [2]Main!$B$2:$E$30, 4, FALSE))</f>
-        <v>254000000000007</v>
+        <v>254000000000004</v>
       </c>
       <c r="H21" s="2">
         <v>20</v>
       </c>
       <c r="I21" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000007::bigint, 97000000000020::bigint);</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000004::bigint, 97000000000020::bigint);</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -1888,26 +2255,26 @@
         <v>97000000000021</v>
       </c>
       <c r="C22" s="7" t="str">
-        <f>VLOOKUP($B22, [1]Main!$E$2:$G$324, 2, FALSE)</f>
-        <v>Module.General.MasterData.BloodAglutinogenType.Transaction</v>
+        <f>VLOOKUP($B22, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <v>Module.Budgeting.Data.ModifyBudget.Transaction</v>
       </c>
       <c r="D22" s="8" t="str">
-        <f>VLOOKUP($B22, [1]Main!$E$2:$G$324, 3, FALSE)</f>
-        <v>Blood Aglutinogen Type</v>
+        <f>VLOOKUP($B22, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <v>Modify Budget</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G22" s="6">
         <f>IF(EXACT($F22, ""), "", VLOOKUP($F22, [2]Main!$B$2:$E$30, 4, FALSE))</f>
-        <v>254000000000007</v>
+        <v>254000000000004</v>
       </c>
       <c r="H22" s="2">
         <v>21</v>
       </c>
       <c r="I22" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000007::bigint, 97000000000021::bigint);</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000004::bigint, 97000000000021::bigint);</v>
       </c>
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.2">
@@ -1916,26 +2283,26 @@
         <v>97000000000022</v>
       </c>
       <c r="C23" s="7" t="str">
-        <f>VLOOKUP($B23, [1]Main!$E$2:$G$324, 2, FALSE)</f>
-        <v>Module.HumanResource.Data.PersonWorkTimeSheet.Transaction</v>
+        <f>VLOOKUP($B23, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <v>Module.Budgeting.Data.ModifyBudget.Report.Resume</v>
       </c>
       <c r="D23" s="8" t="str">
-        <f>VLOOKUP($B23, [1]Main!$E$2:$G$324, 3, FALSE)</f>
-        <v>Person Work Time Sheet</v>
+        <f>VLOOKUP($B23, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <v>Report Modify Budget Summary</v>
       </c>
       <c r="F23" s="10" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G23" s="6">
         <f>IF(EXACT($F23, ""), "", VLOOKUP($F23, [2]Main!$B$2:$E$30, 4, FALSE))</f>
-        <v>254000000000007</v>
+        <v>254000000000004</v>
       </c>
       <c r="H23" s="2">
         <v>22</v>
       </c>
       <c r="I23" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000007::bigint, 97000000000022::bigint);</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000004::bigint, 97000000000022::bigint);</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -1944,26 +2311,26 @@
         <v>97000000000023</v>
       </c>
       <c r="C24" s="7" t="str">
-        <f>VLOOKUP($B24, [1]Main!$E$2:$G$324, 2, FALSE)</f>
-        <v>Module.General.MasterData.Warehouse.Transaction</v>
+        <f>VLOOKUP($B24, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <v>Module.Budgeting.Data.Work.Transaction</v>
       </c>
       <c r="D24" s="8" t="str">
-        <f>VLOOKUP($B24, [1]Main!$E$2:$G$324, 3, FALSE)</f>
-        <v>Warehouse</v>
+        <f>VLOOKUP($B24, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <v>Work</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G24" s="6">
         <f>IF(EXACT($F24, ""), "", VLOOKUP($F24, [2]Main!$B$2:$E$30, 4, FALSE))</f>
-        <v>254000000000009</v>
+        <v>254000000000004</v>
       </c>
       <c r="H24" s="2">
         <v>23</v>
       </c>
       <c r="I24" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000009::bigint, 97000000000023::bigint);</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000004::bigint, 97000000000023::bigint);</v>
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
@@ -1972,26 +2339,26 @@
         <v>97000000000024</v>
       </c>
       <c r="C25" s="7" t="str">
-        <f>VLOOKUP($B25, [1]Main!$E$2:$G$324, 2, FALSE)</f>
-        <v>Module.General.MasterData.ProductType.Transaction</v>
+        <f>VLOOKUP($B25, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <v>Module.Budgeting.Data.CFS.Report.Resume</v>
       </c>
       <c r="D25" s="8" t="str">
-        <f>VLOOKUP($B25, [1]Main!$E$2:$G$324, 3, FALSE)</f>
-        <v>Product Type</v>
+        <f>VLOOKUP($B25, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <v>Report Cost Financial Structure</v>
       </c>
       <c r="F25" s="10" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G25" s="6">
         <f>IF(EXACT($F25, ""), "", VLOOKUP($F25, [2]Main!$B$2:$E$30, 4, FALSE))</f>
-        <v>254000000000009</v>
+        <v>254000000000004</v>
       </c>
       <c r="H25" s="2">
         <v>24</v>
       </c>
       <c r="I25" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000009::bigint, 97000000000024::bigint);</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000004::bigint, 97000000000024::bigint);</v>
       </c>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
@@ -2000,26 +2367,26 @@
         <v>97000000000025</v>
       </c>
       <c r="C26" s="7" t="str">
-        <f>VLOOKUP($B26, [1]Main!$E$2:$G$324, 2, FALSE)</f>
-        <v>Module.General.MasterData.Product.Transaction</v>
+        <f>VLOOKUP($B26, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <v>Module.General.MasterData.BloodAglutinogenType.Transaction</v>
       </c>
       <c r="D26" s="8" t="str">
-        <f>VLOOKUP($B26, [1]Main!$E$2:$G$324, 3, FALSE)</f>
-        <v>Product</v>
+        <f>VLOOKUP($B26, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <v>Blood Aglutinogen Type</v>
       </c>
       <c r="F26" s="10" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G26" s="6">
         <f>IF(EXACT($F26, ""), "", VLOOKUP($F26, [2]Main!$B$2:$E$30, 4, FALSE))</f>
-        <v>254000000000009</v>
+        <v>254000000000007</v>
       </c>
       <c r="H26" s="2">
         <v>25</v>
       </c>
       <c r="I26" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000009::bigint, 97000000000025::bigint);</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000007::bigint, 97000000000025::bigint);</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -2028,26 +2395,26 @@
         <v>97000000000026</v>
       </c>
       <c r="C27" s="7" t="str">
-        <f>VLOOKUP($B27, [1]Main!$E$2:$G$324, 2, FALSE)</f>
-        <v>Module.SupplyChain.Data.DeliveryOrder.Report.DataList</v>
+        <f>VLOOKUP($B27, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <v>Module.General.MasterData.Person.Transaction</v>
       </c>
       <c r="D27" s="8" t="str">
-        <f>VLOOKUP($B27, [1]Main!$E$2:$G$324, 3, FALSE)</f>
-        <v>Report DO Summary</v>
+        <f>VLOOKUP($B27, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <v>Person</v>
       </c>
       <c r="F27" s="10" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G27" s="6">
         <f>IF(EXACT($F27, ""), "", VLOOKUP($F27, [2]Main!$B$2:$E$30, 4, FALSE))</f>
-        <v>254000000000009</v>
+        <v>254000000000007</v>
       </c>
       <c r="H27" s="2">
         <v>26</v>
       </c>
       <c r="I27" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000009::bigint, 97000000000026::bigint);</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000007::bigint, 97000000000026::bigint);</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -2056,26 +2423,26 @@
         <v>97000000000027</v>
       </c>
       <c r="C28" s="7" t="str">
-        <f>VLOOKUP($B28, [1]Main!$E$2:$G$324, 2, FALSE)</f>
-        <v>Module.SupplyChain.Data.DeliveryOrder.Transaction</v>
+        <f>VLOOKUP($B28, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <v>Module.General.MasterData.Religion.Transaction</v>
       </c>
       <c r="D28" s="8" t="str">
-        <f>VLOOKUP($B28, [1]Main!$E$2:$G$324, 3, FALSE)</f>
-        <v>Delivery Order</v>
+        <f>VLOOKUP($B28, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <v>Religion</v>
       </c>
       <c r="F28" s="10" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G28" s="6">
         <f>IF(EXACT($F28, ""), "", VLOOKUP($F28, [2]Main!$B$2:$E$30, 4, FALSE))</f>
-        <v>254000000000009</v>
+        <v>254000000000007</v>
       </c>
       <c r="H28" s="2">
         <v>27</v>
       </c>
       <c r="I28" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000009::bigint, 97000000000027::bigint);</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000007::bigint, 97000000000027::bigint);</v>
       </c>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
@@ -2084,26 +2451,26 @@
         <v>97000000000028</v>
       </c>
       <c r="C29" s="7" t="str">
-        <f>VLOOKUP($B29, [1]Main!$E$2:$G$324, 2, FALSE)</f>
-        <v>Module.SupplyChain.Data.MaterialReceive.Transaction</v>
+        <f>VLOOKUP($B29, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <v>Module.General.MasterData.UserRole.Transaction</v>
       </c>
       <c r="D29" s="8" t="str">
-        <f>VLOOKUP($B29, [1]Main!$E$2:$G$324, 3, FALSE)</f>
-        <v>Material Receive</v>
+        <f>VLOOKUP($B29, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <v>Role</v>
       </c>
       <c r="F29" s="10" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G29" s="6">
         <f>IF(EXACT($F29, ""), "", VLOOKUP($F29, [2]Main!$B$2:$E$30, 4, FALSE))</f>
-        <v>254000000000009</v>
+        <v>254000000000007</v>
       </c>
       <c r="H29" s="2">
         <v>28</v>
       </c>
       <c r="I29" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000009::bigint, 97000000000028::bigint);</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000007::bigint, 97000000000028::bigint);</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -2112,26 +2479,26 @@
         <v>97000000000029</v>
       </c>
       <c r="C30" s="7" t="str">
-        <f>VLOOKUP($B30, [1]Main!$E$2:$G$324, 2, FALSE)</f>
-        <v>Module.SupplyChain.Data.MaterialReturn.Report.DataList</v>
+        <f>VLOOKUP($B30, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <v>Module.HumanResource.MasterData.OrganizationalDepartment.Transaction</v>
       </c>
       <c r="D30" s="8" t="str">
-        <f>VLOOKUP($B30, [1]Main!$E$2:$G$324, 3, FALSE)</f>
-        <v>Report Material Return Summary</v>
+        <f>VLOOKUP($B30, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <v>Department</v>
       </c>
       <c r="F30" s="10" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G30" s="6">
         <f>IF(EXACT($F30, ""), "", VLOOKUP($F30, [2]Main!$B$2:$E$30, 4, FALSE))</f>
-        <v>254000000000009</v>
+        <v>254000000000007</v>
       </c>
       <c r="H30" s="2">
         <v>29</v>
       </c>
       <c r="I30" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000009::bigint, 97000000000029::bigint);</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000007::bigint, 97000000000029::bigint);</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -2140,26 +2507,26 @@
         <v>97000000000030</v>
       </c>
       <c r="C31" s="7" t="str">
-        <f>VLOOKUP($B31, [1]Main!$E$2:$G$324, 2, FALSE)</f>
-        <v>Module.SupplyChain.Data.MaterialReturn.Transaction</v>
+        <f>VLOOKUP($B31, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <v>Module.HumanResource.Data.PersonWorkTimeSheet.Transaction</v>
       </c>
       <c r="D31" s="8" t="str">
-        <f>VLOOKUP($B31, [1]Main!$E$2:$G$324, 3, FALSE)</f>
-        <v>Material Return</v>
+        <f>VLOOKUP($B31, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <v>Person Work Time Sheet</v>
       </c>
       <c r="F31" s="10" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G31" s="6">
         <f>IF(EXACT($F31, ""), "", VLOOKUP($F31, [2]Main!$B$2:$E$30, 4, FALSE))</f>
-        <v>254000000000009</v>
+        <v>254000000000007</v>
       </c>
       <c r="H31" s="2">
         <v>30</v>
       </c>
       <c r="I31" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000009::bigint, 97000000000030::bigint);</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000007::bigint, 97000000000030::bigint);</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -2168,26 +2535,26 @@
         <v>97000000000031</v>
       </c>
       <c r="C32" s="7" t="str">
-        <f>VLOOKUP($B32, [1]Main!$E$2:$G$324, 2, FALSE)</f>
-        <v>Module.Finance.Data.Advance.Report.DataList</v>
+        <f>VLOOKUP($B32, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <v>Module.HumanResource.Data.PersonWorkTimeSheet.Report.DataList</v>
       </c>
       <c r="D32" s="8" t="str">
-        <f>VLOOKUP($B32, [1]Main!$E$2:$G$324, 3, FALSE)</f>
-        <v>Report Advance Summary</v>
+        <f>VLOOKUP($B32, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <v>Person Work Time Sheet Summary</v>
       </c>
       <c r="F32" s="10" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G32" s="6">
         <f>IF(EXACT($F32, ""), "", VLOOKUP($F32, [2]Main!$B$2:$E$30, 4, FALSE))</f>
-        <v>254000000000008</v>
+        <v>254000000000007</v>
       </c>
       <c r="H32" s="2">
         <v>31</v>
       </c>
       <c r="I32" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000008::bigint, 97000000000031::bigint);</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000007::bigint, 97000000000031::bigint);</v>
       </c>
     </row>
     <row r="33" spans="2:9" x14ac:dyDescent="0.2">
@@ -2196,26 +2563,26 @@
         <v>97000000000032</v>
       </c>
       <c r="C33" s="7" t="str">
-        <f>VLOOKUP($B33, [1]Main!$E$2:$G$324, 2, FALSE)</f>
-        <v>Module.Finance.Data.Advance.Transaction</v>
+        <f>VLOOKUP($B33, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <v>Module.HumanResource.Data.SallaryAllocation.Transaction</v>
       </c>
       <c r="D33" s="8" t="str">
-        <f>VLOOKUP($B33, [1]Main!$E$2:$G$324, 3, FALSE)</f>
-        <v>Advance Request</v>
+        <f>VLOOKUP($B33, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <v>Sallary Allocation</v>
       </c>
       <c r="F33" s="10" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G33" s="6">
         <f>IF(EXACT($F33, ""), "", VLOOKUP($F33, [2]Main!$B$2:$E$30, 4, FALSE))</f>
-        <v>254000000000008</v>
+        <v>254000000000007</v>
       </c>
       <c r="H33" s="2">
         <v>32</v>
       </c>
       <c r="I33" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000008::bigint, 97000000000032::bigint);</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000007::bigint, 97000000000032::bigint);</v>
       </c>
     </row>
     <row r="34" spans="2:9" x14ac:dyDescent="0.2">
@@ -2224,26 +2591,26 @@
         <v>97000000000033</v>
       </c>
       <c r="C34" s="7" t="str">
-        <f>VLOOKUP($B34, [1]Main!$E$2:$G$324, 2, FALSE)</f>
-        <v>Module.Finance.Data.AdvanceSettlement.Report.DataList</v>
+        <f>VLOOKUP($B34, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <v>Module.HumanResource.Data.SallaryAllocation.Report.DataList</v>
       </c>
       <c r="D34" s="8" t="str">
-        <f>VLOOKUP($B34, [1]Main!$E$2:$G$324, 3, FALSE)</f>
-        <v>Report Advance Settlement Summary</v>
+        <f>VLOOKUP($B34, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <v>Sallary Allocation Summary</v>
       </c>
       <c r="F34" s="10" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G34" s="6">
         <f>IF(EXACT($F34, ""), "", VLOOKUP($F34, [2]Main!$B$2:$E$30, 4, FALSE))</f>
-        <v>254000000000008</v>
+        <v>254000000000007</v>
       </c>
       <c r="H34" s="2">
         <v>33</v>
       </c>
       <c r="I34" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000008::bigint, 97000000000033::bigint);</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000007::bigint, 97000000000033::bigint);</v>
       </c>
     </row>
     <row r="35" spans="2:9" x14ac:dyDescent="0.2">
@@ -2252,26 +2619,26 @@
         <v>97000000000034</v>
       </c>
       <c r="C35" s="7" t="str">
-        <f>VLOOKUP($B35, [1]Main!$E$2:$G$324, 2, FALSE)</f>
-        <v>Module.Finance.Data.AdvanceSettlement.Transaction</v>
+        <f>VLOOKUP($B35, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <v>Module.General.MasterData.Warehouse.Transaction</v>
       </c>
       <c r="D35" s="8" t="str">
-        <f>VLOOKUP($B35, [1]Main!$E$2:$G$324, 3, FALSE)</f>
-        <v>AdvanceSettlement</v>
+        <f>VLOOKUP($B35, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <v>Warehouse</v>
       </c>
       <c r="F35" s="10" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G35" s="6">
         <f>IF(EXACT($F35, ""), "", VLOOKUP($F35, [2]Main!$B$2:$E$30, 4, FALSE))</f>
-        <v>254000000000008</v>
+        <v>254000000000009</v>
       </c>
       <c r="H35" s="2">
         <v>34</v>
       </c>
       <c r="I35" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000008::bigint, 97000000000034::bigint);</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000009::bigint, 97000000000034::bigint);</v>
       </c>
     </row>
     <row r="36" spans="2:9" x14ac:dyDescent="0.2">
@@ -2280,26 +2647,26 @@
         <v>97000000000035</v>
       </c>
       <c r="C36" s="7" t="str">
-        <f>VLOOKUP($B36, [1]Main!$E$2:$G$324, 2, FALSE)</f>
-        <v>Module.Finance.Data.PersonBusinessTripSettlement.Report.DataList</v>
+        <f>VLOOKUP($B36, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <v>Module.General.MasterData.ProductType.Transaction</v>
       </c>
       <c r="D36" s="8" t="str">
-        <f>VLOOKUP($B36, [1]Main!$E$2:$G$324, 3, FALSE)</f>
-        <v>Report BusinessTrip Settlement Summary</v>
+        <f>VLOOKUP($B36, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <v>Product Type</v>
       </c>
       <c r="F36" s="10" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G36" s="6">
         <f>IF(EXACT($F36, ""), "", VLOOKUP($F36, [2]Main!$B$2:$E$30, 4, FALSE))</f>
-        <v>254000000000008</v>
+        <v>254000000000009</v>
       </c>
       <c r="H36" s="2">
         <v>35</v>
       </c>
       <c r="I36" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000008::bigint, 97000000000035::bigint);</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000009::bigint, 97000000000035::bigint);</v>
       </c>
     </row>
     <row r="37" spans="2:9" x14ac:dyDescent="0.2">
@@ -2308,26 +2675,26 @@
         <v>97000000000036</v>
       </c>
       <c r="C37" s="7" t="str">
-        <f>VLOOKUP($B37, [1]Main!$E$2:$G$324, 2, FALSE)</f>
-        <v>Module.Finance.Data.PersonBusinessTripSettlement.Transaction</v>
+        <f>VLOOKUP($B37, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <v>Module.General.MasterData.Product.Transaction</v>
       </c>
       <c r="D37" s="8" t="str">
-        <f>VLOOKUP($B37, [1]Main!$E$2:$G$324, 3, FALSE)</f>
-        <v>BusinessTrip Settlement</v>
+        <f>VLOOKUP($B37, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <v>Product</v>
       </c>
       <c r="F37" s="10" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G37" s="6">
         <f>IF(EXACT($F37, ""), "", VLOOKUP($F37, [2]Main!$B$2:$E$30, 4, FALSE))</f>
-        <v>254000000000008</v>
+        <v>254000000000009</v>
       </c>
       <c r="H37" s="2">
         <v>36</v>
       </c>
       <c r="I37" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000008::bigint, 97000000000036::bigint);</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000009::bigint, 97000000000036::bigint);</v>
       </c>
     </row>
     <row r="38" spans="2:9" x14ac:dyDescent="0.2">
@@ -2336,26 +2703,26 @@
         <v>97000000000037</v>
       </c>
       <c r="C38" s="7" t="str">
-        <f>VLOOKUP($B38, [1]Main!$E$2:$G$324, 2, FALSE)</f>
-        <v>Module.Finance.Data.PersonBusinessTrip.Report.DataList</v>
+        <f>VLOOKUP($B38, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <v>Module.SupplyChain.Data.DeliveryOrder.Transaction</v>
       </c>
       <c r="D38" s="8" t="str">
-        <f>VLOOKUP($B38, [1]Main!$E$2:$G$324, 3, FALSE)</f>
-        <v>Report BusinessTrip Request Summary</v>
+        <f>VLOOKUP($B38, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <v>Delivery Order</v>
       </c>
       <c r="F38" s="10" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G38" s="6">
         <f>IF(EXACT($F38, ""), "", VLOOKUP($F38, [2]Main!$B$2:$E$30, 4, FALSE))</f>
-        <v>254000000000008</v>
+        <v>254000000000009</v>
       </c>
       <c r="H38" s="2">
         <v>37</v>
       </c>
       <c r="I38" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000008::bigint, 97000000000037::bigint);</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000009::bigint, 97000000000037::bigint);</v>
       </c>
     </row>
     <row r="39" spans="2:9" x14ac:dyDescent="0.2">
@@ -2364,26 +2731,26 @@
         <v>97000000000038</v>
       </c>
       <c r="C39" s="7" t="str">
-        <f>VLOOKUP($B39, [1]Main!$E$2:$G$324, 2, FALSE)</f>
-        <v>Module.Finance.Data.PersonBusinessTrip.Transaction</v>
+        <f>VLOOKUP($B39, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <v>Module.SupplyChain.Data.DeliveryOrder.Report.DataList</v>
       </c>
       <c r="D39" s="8" t="str">
-        <f>VLOOKUP($B39, [1]Main!$E$2:$G$324, 3, FALSE)</f>
-        <v>BusinessTrip Request</v>
+        <f>VLOOKUP($B39, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <v>Report DO Summary</v>
       </c>
       <c r="F39" s="10" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G39" s="6">
         <f>IF(EXACT($F39, ""), "", VLOOKUP($F39, [2]Main!$B$2:$E$30, 4, FALSE))</f>
-        <v>254000000000008</v>
+        <v>254000000000009</v>
       </c>
       <c r="H39" s="2">
         <v>38</v>
       </c>
       <c r="I39" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000008::bigint, 97000000000038::bigint);</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000009::bigint, 97000000000038::bigint);</v>
       </c>
     </row>
     <row r="40" spans="2:9" x14ac:dyDescent="0.2">
@@ -2392,26 +2759,26 @@
         <v>97000000000039</v>
       </c>
       <c r="C40" s="7" t="str">
-        <f>VLOOKUP($B40, [1]Main!$E$2:$G$324, 2, FALSE)</f>
-        <v>Module.SupplyChain.MasterData.Supplier.Transaction</v>
+        <f>VLOOKUP($B40, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <v>Module.SupplyChain.Data.DeliveryOrderToMaterialReceive.Report.DataList</v>
       </c>
       <c r="D40" s="8" t="str">
-        <f>VLOOKUP($B40, [1]Main!$E$2:$G$324, 3, FALSE)</f>
-        <v>Supplier</v>
+        <f>VLOOKUP($B40, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <v>Report DO to Material Receive</v>
       </c>
       <c r="F40" s="10" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G40" s="6">
         <f>IF(EXACT($F40, ""), "", VLOOKUP($F40, [2]Main!$B$2:$E$30, 4, FALSE))</f>
-        <v>254000000000010</v>
+        <v>254000000000009</v>
       </c>
       <c r="H40" s="2">
         <v>39</v>
       </c>
       <c r="I40" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000010::bigint, 97000000000039::bigint);</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000009::bigint, 97000000000039::bigint);</v>
       </c>
     </row>
     <row r="41" spans="2:9" x14ac:dyDescent="0.2">
@@ -2420,26 +2787,26 @@
         <v>97000000000040</v>
       </c>
       <c r="C41" s="7" t="str">
-        <f>VLOOKUP($B41, [1]Main!$E$2:$G$324, 2, FALSE)</f>
-        <v>Module.SupplyChain.Data.PurchaseRequisition.Report.DataList</v>
+        <f>VLOOKUP($B41, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <v>Module.SupplyChain.Data.MaterialReceive.Transaction</v>
       </c>
       <c r="D41" s="8" t="str">
-        <f>VLOOKUP($B41, [1]Main!$E$2:$G$324, 3, FALSE)</f>
-        <v>Report Purchase Requisition Summary</v>
+        <f>VLOOKUP($B41, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <v>Material Receive</v>
       </c>
       <c r="F41" s="10" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G41" s="6">
         <f>IF(EXACT($F41, ""), "", VLOOKUP($F41, [2]Main!$B$2:$E$30, 4, FALSE))</f>
-        <v>254000000000010</v>
+        <v>254000000000009</v>
       </c>
       <c r="H41" s="2">
         <v>40</v>
       </c>
       <c r="I41" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000010::bigint, 97000000000040::bigint);</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000009::bigint, 97000000000040::bigint);</v>
       </c>
     </row>
     <row r="42" spans="2:9" x14ac:dyDescent="0.2">
@@ -2448,26 +2815,26 @@
         <v>97000000000041</v>
       </c>
       <c r="C42" s="7" t="str">
-        <f>VLOOKUP($B42, [1]Main!$E$2:$G$324, 2, FALSE)</f>
-        <v>Module.SupplyChain.Data.PurchaseRequisitionToPurchaseOrder.Report.DataList</v>
+        <f>VLOOKUP($B42, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <v>Module.SupplyChain.Data.MaterialReceive.Report.DataList</v>
       </c>
       <c r="D42" s="8" t="str">
-        <f>VLOOKUP($B42, [1]Main!$E$2:$G$324, 3, FALSE)</f>
-        <v>Report Purchase Requisition To Purchase Order</v>
+        <f>VLOOKUP($B42, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <v>Report Material Receive Summary</v>
       </c>
       <c r="F42" s="10" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G42" s="6">
         <f>IF(EXACT($F42, ""), "", VLOOKUP($F42, [2]Main!$B$2:$E$30, 4, FALSE))</f>
-        <v>254000000000010</v>
+        <v>254000000000009</v>
       </c>
       <c r="H42" s="2">
         <v>41</v>
       </c>
       <c r="I42" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000010::bigint, 97000000000041::bigint);</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000009::bigint, 97000000000041::bigint);</v>
       </c>
     </row>
     <row r="43" spans="2:9" x14ac:dyDescent="0.2">
@@ -2476,26 +2843,26 @@
         <v>97000000000042</v>
       </c>
       <c r="C43" s="7" t="str">
-        <f>VLOOKUP($B43, [1]Main!$E$2:$G$324, 2, FALSE)</f>
-        <v>Module.SupplyChain.Data.PurchaseRequisition.Transaction</v>
+        <f>VLOOKUP($B43, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <v>Module.SupplyChain.Data.MaterialReceiveToMaterialReturn.Report.DataList</v>
       </c>
       <c r="D43" s="8" t="str">
-        <f>VLOOKUP($B43, [1]Main!$E$2:$G$324, 3, FALSE)</f>
-        <v>Purchase Requisition</v>
+        <f>VLOOKUP($B43, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <v>Report Material Receive to Material Return</v>
       </c>
       <c r="F43" s="10" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G43" s="6">
         <f>IF(EXACT($F43, ""), "", VLOOKUP($F43, [2]Main!$B$2:$E$30, 4, FALSE))</f>
-        <v>254000000000010</v>
+        <v>254000000000009</v>
       </c>
       <c r="H43" s="2">
         <v>42</v>
       </c>
       <c r="I43" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000010::bigint, 97000000000042::bigint);</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000009::bigint, 97000000000042::bigint);</v>
       </c>
     </row>
     <row r="44" spans="2:9" x14ac:dyDescent="0.2">
@@ -2504,26 +2871,26 @@
         <v>97000000000043</v>
       </c>
       <c r="C44" s="7" t="str">
-        <f>VLOOKUP($B44, [1]Main!$E$2:$G$324, 2, FALSE)</f>
-        <v>Module.SupplyChain.Data.PurchaseOrder.Report.DataList</v>
+        <f>VLOOKUP($B44, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <v>Module.SupplyChain.Data.MaterialReturn.Transaction</v>
       </c>
       <c r="D44" s="8" t="str">
-        <f>VLOOKUP($B44, [1]Main!$E$2:$G$324, 3, FALSE)</f>
-        <v>Report Purchase Order Summary</v>
+        <f>VLOOKUP($B44, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <v>Material Return</v>
       </c>
       <c r="F44" s="10" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G44" s="6">
         <f>IF(EXACT($F44, ""), "", VLOOKUP($F44, [2]Main!$B$2:$E$30, 4, FALSE))</f>
-        <v>254000000000010</v>
+        <v>254000000000009</v>
       </c>
       <c r="H44" s="2">
         <v>43</v>
       </c>
       <c r="I44" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000010::bigint, 97000000000043::bigint);</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000009::bigint, 97000000000043::bigint);</v>
       </c>
     </row>
     <row r="45" spans="2:9" x14ac:dyDescent="0.2">
@@ -2532,26 +2899,26 @@
         <v>97000000000044</v>
       </c>
       <c r="C45" s="7" t="str">
-        <f>VLOOKUP($B45, [1]Main!$E$2:$G$324, 2, FALSE)</f>
-        <v>Module.SupplyChain.Data.PurchaseOrder.Transaction</v>
+        <f>VLOOKUP($B45, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <v>Module.SupplyChain.Data.MaterialReturn.Report.DataList</v>
       </c>
       <c r="D45" s="8" t="str">
-        <f>VLOOKUP($B45, [1]Main!$E$2:$G$324, 3, FALSE)</f>
-        <v>Purchase Order</v>
+        <f>VLOOKUP($B45, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <v>Report Material Return Summary</v>
       </c>
       <c r="F45" s="10" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G45" s="6">
         <f>IF(EXACT($F45, ""), "", VLOOKUP($F45, [2]Main!$B$2:$E$30, 4, FALSE))</f>
-        <v>254000000000010</v>
+        <v>254000000000009</v>
       </c>
       <c r="H45" s="2">
         <v>44</v>
       </c>
       <c r="I45" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000010::bigint, 97000000000044::bigint);</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000009::bigint, 97000000000044::bigint);</v>
       </c>
     </row>
     <row r="46" spans="2:9" x14ac:dyDescent="0.2">
@@ -2560,26 +2927,26 @@
         <v>97000000000045</v>
       </c>
       <c r="C46" s="7" t="str">
-        <f>VLOOKUP($B46, [1]Main!$E$2:$G$324, 2, FALSE)</f>
-        <v>Module.General.MasterData.Period.Transaction</v>
+        <f>VLOOKUP($B46, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <v>Module.Finance.Data.Advance.Transaction</v>
       </c>
       <c r="D46" s="8" t="str">
-        <f>VLOOKUP($B46, [1]Main!$E$2:$G$324, 3, FALSE)</f>
-        <v>Period</v>
+        <f>VLOOKUP($B46, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <v>Advance Request</v>
       </c>
       <c r="F46" s="10" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G46" s="6">
         <f>IF(EXACT($F46, ""), "", VLOOKUP($F46, [2]Main!$B$2:$E$30, 4, FALSE))</f>
-        <v>254000000000006</v>
+        <v>254000000000008</v>
       </c>
       <c r="H46" s="2">
         <v>45</v>
       </c>
       <c r="I46" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000045::bigint);</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000008::bigint, 97000000000045::bigint);</v>
       </c>
     </row>
     <row r="47" spans="2:9" x14ac:dyDescent="0.2">
@@ -2588,26 +2955,26 @@
         <v>97000000000046</v>
       </c>
       <c r="C47" s="7" t="str">
-        <f>VLOOKUP($B47, [1]Main!$E$2:$G$324, 2, FALSE)</f>
-        <v>Module.General.MasterData.Currency.Transaction</v>
+        <f>VLOOKUP($B47, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <v>Module.Finance.Data.Advance.Report.DataList</v>
       </c>
       <c r="D47" s="8" t="str">
-        <f>VLOOKUP($B47, [1]Main!$E$2:$G$324, 3, FALSE)</f>
-        <v>Currency</v>
+        <f>VLOOKUP($B47, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <v>Report Advance Summary</v>
       </c>
       <c r="F47" s="10" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G47" s="6">
         <f>IF(EXACT($F47, ""), "", VLOOKUP($F47, [2]Main!$B$2:$E$30, 4, FALSE))</f>
-        <v>254000000000006</v>
+        <v>254000000000008</v>
       </c>
       <c r="H47" s="2">
         <v>46</v>
       </c>
       <c r="I47" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000046::bigint);</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000008::bigint, 97000000000046::bigint);</v>
       </c>
     </row>
     <row r="48" spans="2:9" x14ac:dyDescent="0.2">
@@ -2616,26 +2983,26 @@
         <v>97000000000047</v>
       </c>
       <c r="C48" s="7" t="str">
-        <f>VLOOKUP($B48, [1]Main!$E$2:$G$324, 2, FALSE)</f>
-        <v>Module.Finance.Data.Reimbursement.Transaction</v>
+        <f>VLOOKUP($B48, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <v>Module.Finance.Data.AdvanceToAdvanceSettlement.Report.DataList</v>
       </c>
       <c r="D48" s="8" t="str">
-        <f>VLOOKUP($B48, [1]Main!$E$2:$G$324, 3, FALSE)</f>
-        <v>Reimbursement</v>
+        <f>VLOOKUP($B48, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <v>Report Advance to Advance Settlement</v>
       </c>
       <c r="F48" s="10" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G48" s="6">
         <f>IF(EXACT($F48, ""), "", VLOOKUP($F48, [2]Main!$B$2:$E$30, 4, FALSE))</f>
-        <v>254000000000006</v>
+        <v>254000000000008</v>
       </c>
       <c r="H48" s="2">
         <v>47</v>
       </c>
       <c r="I48" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000047::bigint);</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000008::bigint, 97000000000047::bigint);</v>
       </c>
     </row>
     <row r="49" spans="2:9" x14ac:dyDescent="0.2">
@@ -2644,26 +3011,26 @@
         <v>97000000000048</v>
       </c>
       <c r="C49" s="7" t="str">
-        <f>VLOOKUP($B49, [1]Main!$E$2:$G$324, 2, FALSE)</f>
-        <v>Module.Finance.Data.Reimbursement.Report.DataList</v>
+        <f>VLOOKUP($B49, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <v>Module.Finance.Data.AdvanceSettlement.Transaction</v>
       </c>
       <c r="D49" s="8" t="str">
-        <f>VLOOKUP($B49, [1]Main!$E$2:$G$324, 3, FALSE)</f>
-        <v>Reimbursement Summary</v>
+        <f>VLOOKUP($B49, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <v>AdvanceSettlement</v>
       </c>
       <c r="F49" s="10" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G49" s="6">
         <f>IF(EXACT($F49, ""), "", VLOOKUP($F49, [2]Main!$B$2:$E$30, 4, FALSE))</f>
-        <v>254000000000006</v>
+        <v>254000000000008</v>
       </c>
       <c r="H49" s="2">
         <v>48</v>
       </c>
       <c r="I49" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000048::bigint);</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000008::bigint, 97000000000048::bigint);</v>
       </c>
     </row>
     <row r="50" spans="2:9" x14ac:dyDescent="0.2">
@@ -2672,26 +3039,26 @@
         <v>97000000000049</v>
       </c>
       <c r="C50" s="7" t="str">
-        <f>VLOOKUP($B50, [1]Main!$E$2:$G$324, 2, FALSE)</f>
-        <v>Module.Finance.Data.DebitNote.Transaction</v>
+        <f>VLOOKUP($B50, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <v>Module.Finance.Data.AdvanceSettlement.Report.DataList</v>
       </c>
       <c r="D50" s="8" t="str">
-        <f>VLOOKUP($B50, [1]Main!$E$2:$G$324, 3, FALSE)</f>
-        <v>Debit Note</v>
+        <f>VLOOKUP($B50, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <v>Report Advance Settlement Summary</v>
       </c>
       <c r="F50" s="10" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G50" s="6">
         <f>IF(EXACT($F50, ""), "", VLOOKUP($F50, [2]Main!$B$2:$E$30, 4, FALSE))</f>
-        <v>254000000000006</v>
+        <v>254000000000008</v>
       </c>
       <c r="H50" s="2">
         <v>49</v>
       </c>
       <c r="I50" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000049::bigint);</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000008::bigint, 97000000000049::bigint);</v>
       </c>
     </row>
     <row r="51" spans="2:9" x14ac:dyDescent="0.2">
@@ -2700,26 +3067,26 @@
         <v>97000000000050</v>
       </c>
       <c r="C51" s="7" t="str">
-        <f>VLOOKUP($B51, [1]Main!$E$2:$G$324, 2, FALSE)</f>
-        <v>Module.Finance.Data.DebitNote.Report.DataList</v>
+        <f>VLOOKUP($B51, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <v>Module.Finance.Data.PersonBusinessTrip.Transaction</v>
       </c>
       <c r="D51" s="8" t="str">
-        <f>VLOOKUP($B51, [1]Main!$E$2:$G$324, 3, FALSE)</f>
-        <v>Debit Note Summary</v>
+        <f>VLOOKUP($B51, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <v>BusinessTrip Request</v>
       </c>
       <c r="F51" s="10" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G51" s="6">
         <f>IF(EXACT($F51, ""), "", VLOOKUP($F51, [2]Main!$B$2:$E$30, 4, FALSE))</f>
-        <v>254000000000006</v>
+        <v>254000000000008</v>
       </c>
       <c r="H51" s="2">
         <v>50</v>
       </c>
       <c r="I51" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000050::bigint);</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000008::bigint, 97000000000050::bigint);</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -2728,26 +3095,26 @@
         <v>97000000000051</v>
       </c>
       <c r="C52" s="7" t="str">
-        <f>VLOOKUP($B52, [1]Main!$E$2:$G$324, 2, FALSE)</f>
-        <v>Module.Finance.Data.ReimbursementToDebitNote.Report.DataList</v>
+        <f>VLOOKUP($B52, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <v>Module.Finance.Data.PersonBusinessTrip.Report.DataList</v>
       </c>
       <c r="D52" s="8" t="str">
-        <f>VLOOKUP($B52, [1]Main!$E$2:$G$324, 3, FALSE)</f>
-        <v>Reimbursement to Debit Note</v>
+        <f>VLOOKUP($B52, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <v>Report BusinessTrip Request Summary</v>
       </c>
       <c r="F52" s="10" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G52" s="6">
         <f>IF(EXACT($F52, ""), "", VLOOKUP($F52, [2]Main!$B$2:$E$30, 4, FALSE))</f>
-        <v>254000000000006</v>
+        <v>254000000000008</v>
       </c>
       <c r="H52" s="2">
         <v>51</v>
       </c>
       <c r="I52" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000051::bigint);</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000008::bigint, 97000000000051::bigint);</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -2756,26 +3123,26 @@
         <v>97000000000052</v>
       </c>
       <c r="C53" s="7" t="str">
-        <f>VLOOKUP($B53, [1]Main!$E$2:$G$324, 2, FALSE)</f>
-        <v>Module.Finance.Data.CreditNote.Transaction</v>
+        <f>VLOOKUP($B53, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <v>Module.Finance.Data.PersonBusinessTripToPersonBusinessTripSettlement.Report.DataList</v>
       </c>
       <c r="D53" s="8" t="str">
-        <f>VLOOKUP($B53, [1]Main!$E$2:$G$324, 3, FALSE)</f>
-        <v>Credit Note</v>
+        <f>VLOOKUP($B53, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <v>Report BusinessTrip to BusinessTrip Settlement</v>
       </c>
       <c r="F53" s="10" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G53" s="6">
         <f>IF(EXACT($F53, ""), "", VLOOKUP($F53, [2]Main!$B$2:$E$30, 4, FALSE))</f>
-        <v>254000000000006</v>
+        <v>254000000000008</v>
       </c>
       <c r="H53" s="2">
         <v>52</v>
       </c>
       <c r="I53" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000052::bigint);</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000008::bigint, 97000000000052::bigint);</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -2784,26 +3151,26 @@
         <v>97000000000053</v>
       </c>
       <c r="C54" s="7" t="str">
-        <f>VLOOKUP($B54, [1]Main!$E$2:$G$324, 2, FALSE)</f>
-        <v>Module.Finance.Data.CreditNote.Report.DataList</v>
+        <f>VLOOKUP($B54, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <v>Module.Finance.Data.PersonBusinessTripSettlement.Transaction</v>
       </c>
       <c r="D54" s="8" t="str">
-        <f>VLOOKUP($B54, [1]Main!$E$2:$G$324, 3, FALSE)</f>
-        <v>Credit Note Summary</v>
+        <f>VLOOKUP($B54, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <v>BusinessTrip Settlement</v>
       </c>
       <c r="F54" s="10" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G54" s="6">
         <f>IF(EXACT($F54, ""), "", VLOOKUP($F54, [2]Main!$B$2:$E$30, 4, FALSE))</f>
-        <v>254000000000006</v>
+        <v>254000000000008</v>
       </c>
       <c r="H54" s="2">
         <v>53</v>
       </c>
       <c r="I54" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000053::bigint);</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000008::bigint, 97000000000053::bigint);</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -2812,26 +3179,26 @@
         <v>97000000000054</v>
       </c>
       <c r="C55" s="7" t="str">
-        <f>VLOOKUP($B55, [1]Main!$E$2:$G$324, 2, FALSE)</f>
-        <v>Module.Finance.Data.Loan.Transaction</v>
+        <f>VLOOKUP($B55, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <v>Module.Finance.Data.PersonBusinessTripSettlement.Report.DataList</v>
       </c>
       <c r="D55" s="8" t="str">
-        <f>VLOOKUP($B55, [1]Main!$E$2:$G$324, 3, FALSE)</f>
-        <v>Loan</v>
+        <f>VLOOKUP($B55, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <v>Report BusinessTrip Settlement Summary</v>
       </c>
       <c r="F55" s="10" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G55" s="6">
         <f>IF(EXACT($F55, ""), "", VLOOKUP($F55, [2]Main!$B$2:$E$30, 4, FALSE))</f>
-        <v>254000000000006</v>
+        <v>254000000000008</v>
       </c>
       <c r="H55" s="2">
         <v>54</v>
       </c>
       <c r="I55" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000054::bigint);</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000008::bigint, 97000000000054::bigint);</v>
       </c>
     </row>
     <row r="56" spans="2:9" x14ac:dyDescent="0.2">
@@ -2840,26 +3207,26 @@
         <v>97000000000055</v>
       </c>
       <c r="C56" s="7" t="str">
-        <f>VLOOKUP($B56, [1]Main!$E$2:$G$324, 2, FALSE)</f>
-        <v>Module.Finance.Data.Loan.Report.DataList</v>
+        <f>VLOOKUP($B56, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <v>Module.SupplyChain.MasterData.Supplier.Transaction</v>
       </c>
       <c r="D56" s="8" t="str">
-        <f>VLOOKUP($B56, [1]Main!$E$2:$G$324, 3, FALSE)</f>
-        <v>Loan Summary</v>
+        <f>VLOOKUP($B56, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <v>Supplier</v>
       </c>
       <c r="F56" s="10" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G56" s="6">
         <f>IF(EXACT($F56, ""), "", VLOOKUP($F56, [2]Main!$B$2:$E$30, 4, FALSE))</f>
-        <v>254000000000006</v>
+        <v>254000000000010</v>
       </c>
       <c r="H56" s="2">
         <v>55</v>
       </c>
       <c r="I56" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000055::bigint);</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000010::bigint, 97000000000055::bigint);</v>
       </c>
     </row>
     <row r="57" spans="2:9" x14ac:dyDescent="0.2">
@@ -2868,26 +3235,26 @@
         <v>97000000000056</v>
       </c>
       <c r="C57" s="7" t="str">
-        <f>VLOOKUP($B57, [1]Main!$E$2:$G$324, 2, FALSE)</f>
-        <v>Module.Finance.Data.LoanSettlement.Transaction</v>
+        <f>VLOOKUP($B57, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <v>Module.SupplyChain.Data.PurchaseRequisition.Transaction</v>
       </c>
       <c r="D57" s="8" t="str">
-        <f>VLOOKUP($B57, [1]Main!$E$2:$G$324, 3, FALSE)</f>
-        <v>Loan Settlement</v>
+        <f>VLOOKUP($B57, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <v>Purchase Requisition</v>
       </c>
       <c r="F57" s="10" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G57" s="6">
         <f>IF(EXACT($F57, ""), "", VLOOKUP($F57, [2]Main!$B$2:$E$30, 4, FALSE))</f>
-        <v>254000000000006</v>
+        <v>254000000000010</v>
       </c>
       <c r="H57" s="2">
         <v>56</v>
       </c>
       <c r="I57" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000056::bigint);</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000010::bigint, 97000000000056::bigint);</v>
       </c>
     </row>
     <row r="58" spans="2:9" x14ac:dyDescent="0.2">
@@ -2896,26 +3263,26 @@
         <v>97000000000057</v>
       </c>
       <c r="C58" s="7" t="str">
-        <f>VLOOKUP($B58, [1]Main!$E$2:$G$324, 2, FALSE)</f>
-        <v>Module.Finance.Data.LoanSettlement.Report.DataList</v>
+        <f>VLOOKUP($B58, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <v>Module.SupplyChain.Data.PurchaseRequisition.Report.DataList</v>
       </c>
       <c r="D58" s="8" t="str">
-        <f>VLOOKUP($B58, [1]Main!$E$2:$G$324, 3, FALSE)</f>
-        <v>Loan Settlement Summary</v>
+        <f>VLOOKUP($B58, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <v>Report Purchase Requisition Summary</v>
       </c>
       <c r="F58" s="10" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G58" s="6">
         <f>IF(EXACT($F58, ""), "", VLOOKUP($F58, [2]Main!$B$2:$E$30, 4, FALSE))</f>
-        <v>254000000000006</v>
+        <v>254000000000010</v>
       </c>
       <c r="H58" s="2">
         <v>57</v>
       </c>
       <c r="I58" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000057::bigint);</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000010::bigint, 97000000000057::bigint);</v>
       </c>
     </row>
     <row r="59" spans="2:9" x14ac:dyDescent="0.2">
@@ -2924,26 +3291,26 @@
         <v>97000000000058</v>
       </c>
       <c r="C59" s="7" t="str">
-        <f>VLOOKUP($B59, [1]Main!$E$2:$G$324, 2, FALSE)</f>
-        <v>Module.Finance.Data.LoanToLoanSettlement.Report.DataList</v>
+        <f>VLOOKUP($B59, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <v>Module.SupplyChain.Data.PurchaseRequisitionToPurchaseOrder.Report.DataList</v>
       </c>
       <c r="D59" s="8" t="str">
-        <f>VLOOKUP($B59, [1]Main!$E$2:$G$324, 3, FALSE)</f>
-        <v>Loan to Loan Settlement</v>
+        <f>VLOOKUP($B59, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <v>Report Purchase Requisition To Purchase Order</v>
       </c>
       <c r="F59" s="10" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G59" s="6">
         <f>IF(EXACT($F59, ""), "", VLOOKUP($F59, [2]Main!$B$2:$E$30, 4, FALSE))</f>
-        <v>254000000000006</v>
+        <v>254000000000010</v>
       </c>
       <c r="H59" s="2">
         <v>58</v>
       </c>
       <c r="I59" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000058::bigint);</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000010::bigint, 97000000000058::bigint);</v>
       </c>
     </row>
     <row r="60" spans="2:9" x14ac:dyDescent="0.2">
@@ -2952,26 +3319,26 @@
         <v>97000000000059</v>
       </c>
       <c r="C60" s="7" t="str">
-        <f>VLOOKUP($B60, [1]Main!$E$2:$G$324, 2, FALSE)</f>
-        <v>Module.Finance.Data.CashBank.Transaction</v>
+        <f>VLOOKUP($B60, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <v>Module.SupplyChain.Data.PurchaseOrder.Transaction</v>
       </c>
       <c r="D60" s="8" t="str">
-        <f>VLOOKUP($B60, [1]Main!$E$2:$G$324, 3, FALSE)</f>
-        <v>Cash &amp; Bank</v>
+        <f>VLOOKUP($B60, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <v>Purchase Order</v>
       </c>
       <c r="F60" s="10" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G60" s="6">
         <f>IF(EXACT($F60, ""), "", VLOOKUP($F60, [2]Main!$B$2:$E$30, 4, FALSE))</f>
-        <v>254000000000006</v>
+        <v>254000000000010</v>
       </c>
       <c r="H60" s="2">
         <v>59</v>
       </c>
       <c r="I60" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000059::bigint);</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000010::bigint, 97000000000059::bigint);</v>
       </c>
     </row>
     <row r="61" spans="2:9" x14ac:dyDescent="0.2">
@@ -2980,26 +3347,26 @@
         <v>97000000000060</v>
       </c>
       <c r="C61" s="7" t="str">
-        <f>VLOOKUP($B61, [1]Main!$E$2:$G$324, 2, FALSE)</f>
-        <v>Module.Finance.Data.CashBank.Report.DataList</v>
+        <f>VLOOKUP($B61, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <v>Module.SupplyChain.Data.PurchaseOrder.Report.DataList</v>
       </c>
       <c r="D61" s="8" t="str">
-        <f>VLOOKUP($B61, [1]Main!$E$2:$G$324, 3, FALSE)</f>
-        <v>Cash &amp; Bank Report</v>
+        <f>VLOOKUP($B61, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <v>Report Purchase Order Summary</v>
       </c>
       <c r="F61" s="10" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G61" s="6">
         <f>IF(EXACT($F61, ""), "", VLOOKUP($F61, [2]Main!$B$2:$E$30, 4, FALSE))</f>
-        <v>254000000000006</v>
+        <v>254000000000010</v>
       </c>
       <c r="H61" s="2">
         <v>60</v>
       </c>
       <c r="I61" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000060::bigint);</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000010::bigint, 97000000000060::bigint);</v>
       </c>
     </row>
     <row r="62" spans="2:9" x14ac:dyDescent="0.2">
@@ -3008,26 +3375,26 @@
         <v>97000000000061</v>
       </c>
       <c r="C62" s="7" t="str">
-        <f>VLOOKUP($B62, [1]Main!$E$2:$G$324, 2, FALSE)</f>
-        <v>Module.Finance.Data.PaymentInstruction.Transaction</v>
+        <f>VLOOKUP($B62, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <v>Module.SupplyChain.Data.PurchaseOrderToPaymentInstruction.Report.DataList</v>
       </c>
       <c r="D62" s="8" t="str">
-        <f>VLOOKUP($B62, [1]Main!$E$2:$G$324, 3, FALSE)</f>
-        <v>Account Payable</v>
+        <f>VLOOKUP($B62, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <v>Purchase Order to Account Payable</v>
       </c>
       <c r="F62" s="10" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G62" s="6">
         <f>IF(EXACT($F62, ""), "", VLOOKUP($F62, [2]Main!$B$2:$E$30, 4, FALSE))</f>
-        <v>254000000000006</v>
+        <v>254000000000010</v>
       </c>
       <c r="H62" s="2">
         <v>61</v>
       </c>
       <c r="I62" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000061::bigint);</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000010::bigint, 97000000000061::bigint);</v>
       </c>
     </row>
     <row r="63" spans="2:9" x14ac:dyDescent="0.2">
@@ -3036,12 +3403,12 @@
         <v>97000000000062</v>
       </c>
       <c r="C63" s="7" t="str">
-        <f>VLOOKUP($B63, [1]Main!$E$2:$G$324, 2, FALSE)</f>
-        <v>Module.Finance.Data.PaymentInstruction.Report.DataList</v>
+        <f>VLOOKUP($B63, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <v>Module.General.MasterData.Bank.Transaction</v>
       </c>
       <c r="D63" s="8" t="str">
-        <f>VLOOKUP($B63, [1]Main!$E$2:$G$324, 3, FALSE)</f>
-        <v>Account Payable Summary</v>
+        <f>VLOOKUP($B63, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <v>Bank</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>2</v>
@@ -3054,7 +3421,7 @@
         <v>62</v>
       </c>
       <c r="I63" s="9" t="str">
-        <f t="shared" ref="I63:I64" si="1">IF(EXACT(G63, ""), "", CONCATENATE("PERFORM ""SchSysConfig"".""Func_TblAppObject_MenuGroupMember_SET""(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, ", G63, "::bigint, ", B63, "::bigint);"))</f>
+        <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000062::bigint);</v>
       </c>
     </row>
@@ -3064,26 +3431,978 @@
         <v>97000000000063</v>
       </c>
       <c r="C64" s="7" t="str">
-        <f>VLOOKUP($B64, [1]Main!$E$2:$G$324, 2, FALSE)</f>
-        <v>Module.SupplyChain.Data.PurchaseOrderToPaymentInstruction.Report.DataList</v>
+        <f>VLOOKUP($B64, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <v>Module.General.MasterData.BankAccount.Transaction</v>
       </c>
       <c r="D64" s="8" t="str">
-        <f>VLOOKUP($B64, [1]Main!$E$2:$G$324, 3, FALSE)</f>
-        <v>Purchase Order to Account Payable</v>
+        <f>VLOOKUP($B64, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <v>Bank Account</v>
       </c>
       <c r="F64" s="10" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G64" s="6">
         <f>IF(EXACT($F64, ""), "", VLOOKUP($F64, [2]Main!$B$2:$E$30, 4, FALSE))</f>
-        <v>254000000000010</v>
+        <v>254000000000006</v>
       </c>
       <c r="H64" s="2">
         <v>63</v>
       </c>
       <c r="I64" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000063::bigint);</v>
+      </c>
+    </row>
+    <row r="65" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B65" s="6">
+        <f>[1]Main!$E65</f>
+        <v>97000000000064</v>
+      </c>
+      <c r="C65" s="7" t="str">
+        <f>VLOOKUP($B65, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <v>Module.General.MasterData.Currency.Transaction</v>
+      </c>
+      <c r="D65" s="8" t="str">
+        <f>VLOOKUP($B65, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <v>Currency</v>
+      </c>
+      <c r="F65" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="G65" s="6">
+        <f>IF(EXACT($F65, ""), "", VLOOKUP($F65, [2]Main!$B$2:$E$30, 4, FALSE))</f>
+        <v>254000000000006</v>
+      </c>
+      <c r="H65" s="2">
+        <v>64</v>
+      </c>
+      <c r="I65" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000064::bigint);</v>
+      </c>
+    </row>
+    <row r="66" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B66" s="6">
+        <f>[1]Main!$E66</f>
+        <v>97000000000065</v>
+      </c>
+      <c r="C66" s="7" t="str">
+        <f>VLOOKUP($B66, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <v>Module.General.MasterData.CurrencyExchangeRate.Transaction</v>
+      </c>
+      <c r="D66" s="8" t="str">
+        <f>VLOOKUP($B66, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <v>Exchange Rate</v>
+      </c>
+      <c r="F66" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="G66" s="6">
+        <f>IF(EXACT($F66, ""), "", VLOOKUP($F66, [2]Main!$B$2:$E$30, 4, FALSE))</f>
+        <v>254000000000006</v>
+      </c>
+      <c r="H66" s="2">
+        <v>65</v>
+      </c>
+      <c r="I66" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000065::bigint);</v>
+      </c>
+    </row>
+    <row r="67" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B67" s="6">
+        <f>[1]Main!$E67</f>
+        <v>97000000000066</v>
+      </c>
+      <c r="C67" s="7" t="str">
+        <f>VLOOKUP($B67, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <v>Module.General.MasterData.CurrencyExchangeRate.Report.DataList</v>
+      </c>
+      <c r="D67" s="8" t="str">
+        <f>VLOOKUP($B67, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <v>Exchange Rate Summary</v>
+      </c>
+      <c r="F67" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="G67" s="6">
+        <f>IF(EXACT($F67, ""), "", VLOOKUP($F67, [2]Main!$B$2:$E$30, 4, FALSE))</f>
+        <v>254000000000006</v>
+      </c>
+      <c r="H67" s="2">
+        <v>66</v>
+      </c>
+      <c r="I67" s="9" t="str">
+        <f t="shared" ref="I67:I98" si="1">IF(EXACT(G67, ""), "", CONCATENATE("PERFORM ""SchSysConfig"".""Func_TblAppObject_MenuGroupMember_SET""(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, ", G67, "::bigint, ", B67, "::bigint);"))</f>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000066::bigint);</v>
+      </c>
+    </row>
+    <row r="68" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B68" s="6">
+        <f>[1]Main!$E68</f>
+        <v>97000000000067</v>
+      </c>
+      <c r="C68" s="7" t="str">
+        <f>VLOOKUP($B68, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <v>Module.General.MasterData.PaymentTerm.Transaction</v>
+      </c>
+      <c r="D68" s="8" t="str">
+        <f>VLOOKUP($B68, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <v>Payment Term</v>
+      </c>
+      <c r="F68" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="G68" s="6">
+        <f>IF(EXACT($F68, ""), "", VLOOKUP($F68, [2]Main!$B$2:$E$30, 4, FALSE))</f>
+        <v>254000000000006</v>
+      </c>
+      <c r="H68" s="2">
+        <v>67</v>
+      </c>
+      <c r="I68" s="9" t="str">
         <f t="shared" si="1"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000010::bigint, 97000000000063::bigint);</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000067::bigint);</v>
+      </c>
+    </row>
+    <row r="69" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B69" s="6">
+        <f>[1]Main!$E69</f>
+        <v>97000000000068</v>
+      </c>
+      <c r="C69" s="7" t="str">
+        <f>VLOOKUP($B69, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <v>Module.General.MasterData.Period.Transaction</v>
+      </c>
+      <c r="D69" s="8" t="str">
+        <f>VLOOKUP($B69, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <v>Period</v>
+      </c>
+      <c r="F69" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="G69" s="6">
+        <f>IF(EXACT($F69, ""), "", VLOOKUP($F69, [2]Main!$B$2:$E$30, 4, FALSE))</f>
+        <v>254000000000006</v>
+      </c>
+      <c r="H69" s="2">
+        <v>68</v>
+      </c>
+      <c r="I69" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000068::bigint);</v>
+      </c>
+    </row>
+    <row r="70" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B70" s="6">
+        <f>[1]Main!$E70</f>
+        <v>97000000000069</v>
+      </c>
+      <c r="C70" s="7" t="str">
+        <f>VLOOKUP($B70, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <v>Module.Accounting.MasterData.AssetCategory.Transaction</v>
+      </c>
+      <c r="D70" s="8" t="str">
+        <f>VLOOKUP($B70, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <v>Asset Category</v>
+      </c>
+      <c r="F70" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="G70" s="6">
+        <f>IF(EXACT($F70, ""), "", VLOOKUP($F70, [2]Main!$B$2:$E$30, 4, FALSE))</f>
+        <v>254000000000006</v>
+      </c>
+      <c r="H70" s="2">
+        <v>69</v>
+      </c>
+      <c r="I70" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000069::bigint);</v>
+      </c>
+    </row>
+    <row r="71" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B71" s="6">
+        <f>[1]Main!$E71</f>
+        <v>97000000000070</v>
+      </c>
+      <c r="C71" s="7" t="str">
+        <f>VLOOKUP($B71, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <v>Module.Accounting.MasterData.ChartOfAccount.Transaction</v>
+      </c>
+      <c r="D71" s="8" t="str">
+        <f>VLOOKUP($B71, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <v>Chart of Account</v>
+      </c>
+      <c r="F71" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="G71" s="6">
+        <f>IF(EXACT($F71, ""), "", VLOOKUP($F71, [2]Main!$B$2:$E$30, 4, FALSE))</f>
+        <v>254000000000006</v>
+      </c>
+      <c r="H71" s="2">
+        <v>70</v>
+      </c>
+      <c r="I71" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000070::bigint);</v>
+      </c>
+    </row>
+    <row r="72" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B72" s="6">
+        <f>[1]Main!$E72</f>
+        <v>97000000000071</v>
+      </c>
+      <c r="C72" s="7" t="str">
+        <f>VLOOKUP($B72, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <v>Module.Accounting.MasterData.DepreciationMethod.Transaction</v>
+      </c>
+      <c r="D72" s="8" t="str">
+        <f>VLOOKUP($B72, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <v>Depreciation Method</v>
+      </c>
+      <c r="F72" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="G72" s="6">
+        <f>IF(EXACT($F72, ""), "", VLOOKUP($F72, [2]Main!$B$2:$E$30, 4, FALSE))</f>
+        <v>254000000000006</v>
+      </c>
+      <c r="H72" s="2">
+        <v>71</v>
+      </c>
+      <c r="I72" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000071::bigint);</v>
+      </c>
+    </row>
+    <row r="73" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B73" s="6">
+        <f>[1]Main!$E73</f>
+        <v>97000000000072</v>
+      </c>
+      <c r="C73" s="7" t="str">
+        <f>VLOOKUP($B73, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <v>Module.Accounting.MasterData.DepreciationRateYears.Transaction</v>
+      </c>
+      <c r="D73" s="8" t="str">
+        <f>VLOOKUP($B73, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <v>Depreciation Rate Years</v>
+      </c>
+      <c r="F73" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="G73" s="6">
+        <f>IF(EXACT($F73, ""), "", VLOOKUP($F73, [2]Main!$B$2:$E$30, 4, FALSE))</f>
+        <v>254000000000006</v>
+      </c>
+      <c r="H73" s="2">
+        <v>72</v>
+      </c>
+      <c r="I73" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000072::bigint);</v>
+      </c>
+    </row>
+    <row r="74" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B74" s="6">
+        <f>[1]Main!$E74</f>
+        <v>97000000000073</v>
+      </c>
+      <c r="C74" s="7" t="str">
+        <f>VLOOKUP($B74, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <v>Module.Taxation.MasterData.ValueAddedTax.Transaction</v>
+      </c>
+      <c r="D74" s="8" t="str">
+        <f>VLOOKUP($B74, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <v>Value Added Tax</v>
+      </c>
+      <c r="F74" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="G74" s="6">
+        <f>IF(EXACT($F74, ""), "", VLOOKUP($F74, [2]Main!$B$2:$E$30, 4, FALSE))</f>
+        <v>254000000000006</v>
+      </c>
+      <c r="H74" s="2">
+        <v>73</v>
+      </c>
+      <c r="I74" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000073::bigint);</v>
+      </c>
+    </row>
+    <row r="75" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B75" s="6">
+        <f>[1]Main!$E75</f>
+        <v>97000000000074</v>
+      </c>
+      <c r="C75" s="7" t="str">
+        <f>VLOOKUP($B75, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <v>Module.Accounting.Data.GeneralJournal.Transaction</v>
+      </c>
+      <c r="D75" s="8" t="str">
+        <f>VLOOKUP($B75, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <v>General Journal</v>
+      </c>
+      <c r="F75" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="G75" s="6">
+        <f>IF(EXACT($F75, ""), "", VLOOKUP($F75, [2]Main!$B$2:$E$30, 4, FALSE))</f>
+        <v>254000000000006</v>
+      </c>
+      <c r="H75" s="2">
+        <v>74</v>
+      </c>
+      <c r="I75" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000074::bigint);</v>
+      </c>
+    </row>
+    <row r="76" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B76" s="6">
+        <f>[1]Main!$E76</f>
+        <v>97000000000075</v>
+      </c>
+      <c r="C76" s="7" t="str">
+        <f>VLOOKUP($B76, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <v>Module.Accounting.Data.GeneralJournal.Report.DataList</v>
+      </c>
+      <c r="D76" s="8" t="str">
+        <f>VLOOKUP($B76, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <v>General Journal Summary</v>
+      </c>
+      <c r="F76" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="G76" s="6">
+        <f>IF(EXACT($F76, ""), "", VLOOKUP($F76, [2]Main!$B$2:$E$30, 4, FALSE))</f>
+        <v>254000000000006</v>
+      </c>
+      <c r="H76" s="2">
+        <v>75</v>
+      </c>
+      <c r="I76" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000075::bigint);</v>
+      </c>
+    </row>
+    <row r="77" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B77" s="6">
+        <f>[1]Main!$E77</f>
+        <v>97000000000076</v>
+      </c>
+      <c r="C77" s="7" t="str">
+        <f>VLOOKUP($B77, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <v>Module.Finance.Data.Reimbursement.Transaction</v>
+      </c>
+      <c r="D77" s="8" t="str">
+        <f>VLOOKUP($B77, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <v>Reimbursement</v>
+      </c>
+      <c r="F77" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="G77" s="6">
+        <f>IF(EXACT($F77, ""), "", VLOOKUP($F77, [2]Main!$B$2:$E$30, 4, FALSE))</f>
+        <v>254000000000006</v>
+      </c>
+      <c r="H77" s="2">
+        <v>76</v>
+      </c>
+      <c r="I77" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000076::bigint);</v>
+      </c>
+    </row>
+    <row r="78" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B78" s="6">
+        <f>[1]Main!$E78</f>
+        <v>97000000000077</v>
+      </c>
+      <c r="C78" s="7" t="str">
+        <f>VLOOKUP($B78, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <v>Module.Finance.Data.Reimbursement.Report.DataList</v>
+      </c>
+      <c r="D78" s="8" t="str">
+        <f>VLOOKUP($B78, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <v>Reimbursement Summary</v>
+      </c>
+      <c r="F78" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="G78" s="6">
+        <f>IF(EXACT($F78, ""), "", VLOOKUP($F78, [2]Main!$B$2:$E$30, 4, FALSE))</f>
+        <v>254000000000006</v>
+      </c>
+      <c r="H78" s="2">
+        <v>77</v>
+      </c>
+      <c r="I78" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000077::bigint);</v>
+      </c>
+    </row>
+    <row r="79" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B79" s="6">
+        <f>[1]Main!$E79</f>
+        <v>97000000000078</v>
+      </c>
+      <c r="C79" s="7" t="str">
+        <f>VLOOKUP($B79, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <v>Module.Finance.Data.ReimbursementToDebitNote.Report.DataList</v>
+      </c>
+      <c r="D79" s="8" t="str">
+        <f>VLOOKUP($B79, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <v>Reimbursement to Debit Note</v>
+      </c>
+      <c r="F79" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="G79" s="6">
+        <f>IF(EXACT($F79, ""), "", VLOOKUP($F79, [2]Main!$B$2:$E$30, 4, FALSE))</f>
+        <v>254000000000006</v>
+      </c>
+      <c r="H79" s="2">
+        <v>78</v>
+      </c>
+      <c r="I79" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000078::bigint);</v>
+      </c>
+    </row>
+    <row r="80" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B80" s="6">
+        <f>[1]Main!$E80</f>
+        <v>97000000000079</v>
+      </c>
+      <c r="C80" s="7" t="str">
+        <f>VLOOKUP($B80, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <v>Module.Finance.Data.DebitNote.Transaction</v>
+      </c>
+      <c r="D80" s="8" t="str">
+        <f>VLOOKUP($B80, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <v>Debit Note</v>
+      </c>
+      <c r="F80" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="G80" s="6">
+        <f>IF(EXACT($F80, ""), "", VLOOKUP($F80, [2]Main!$B$2:$E$30, 4, FALSE))</f>
+        <v>254000000000006</v>
+      </c>
+      <c r="H80" s="2">
+        <v>79</v>
+      </c>
+      <c r="I80" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000079::bigint);</v>
+      </c>
+    </row>
+    <row r="81" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B81" s="6">
+        <f>[1]Main!$E81</f>
+        <v>97000000000080</v>
+      </c>
+      <c r="C81" s="7" t="str">
+        <f>VLOOKUP($B81, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <v>Module.Finance.Data.DebitNote.Report.DataList</v>
+      </c>
+      <c r="D81" s="8" t="str">
+        <f>VLOOKUP($B81, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <v>Debit Note Summary</v>
+      </c>
+      <c r="F81" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="G81" s="6">
+        <f>IF(EXACT($F81, ""), "", VLOOKUP($F81, [2]Main!$B$2:$E$30, 4, FALSE))</f>
+        <v>254000000000006</v>
+      </c>
+      <c r="H81" s="2">
+        <v>80</v>
+      </c>
+      <c r="I81" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000080::bigint);</v>
+      </c>
+    </row>
+    <row r="82" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B82" s="6">
+        <f>[1]Main!$E82</f>
+        <v>97000000000081</v>
+      </c>
+      <c r="C82" s="7" t="str">
+        <f>VLOOKUP($B82, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <v>Module.Finance.Data.CreditNote.Transaction</v>
+      </c>
+      <c r="D82" s="8" t="str">
+        <f>VLOOKUP($B82, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <v>Credit Note</v>
+      </c>
+      <c r="F82" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="G82" s="6">
+        <f>IF(EXACT($F82, ""), "", VLOOKUP($F82, [2]Main!$B$2:$E$30, 4, FALSE))</f>
+        <v>254000000000006</v>
+      </c>
+      <c r="H82" s="2">
+        <v>81</v>
+      </c>
+      <c r="I82" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000081::bigint);</v>
+      </c>
+    </row>
+    <row r="83" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B83" s="6">
+        <f>[1]Main!$E83</f>
+        <v>97000000000082</v>
+      </c>
+      <c r="C83" s="7" t="str">
+        <f>VLOOKUP($B83, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <v>Module.Finance.Data.CreditNote.Report.DataList</v>
+      </c>
+      <c r="D83" s="8" t="str">
+        <f>VLOOKUP($B83, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <v>Credit Note Summary</v>
+      </c>
+      <c r="F83" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="G83" s="6">
+        <f>IF(EXACT($F83, ""), "", VLOOKUP($F83, [2]Main!$B$2:$E$30, 4, FALSE))</f>
+        <v>254000000000006</v>
+      </c>
+      <c r="H83" s="2">
+        <v>82</v>
+      </c>
+      <c r="I83" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000082::bigint);</v>
+      </c>
+    </row>
+    <row r="84" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B84" s="6">
+        <f>[1]Main!$E84</f>
+        <v>97000000000083</v>
+      </c>
+      <c r="C84" s="7" t="str">
+        <f>VLOOKUP($B84, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <v>Module.Finance.Data.Loan.Transaction</v>
+      </c>
+      <c r="D84" s="8" t="str">
+        <f>VLOOKUP($B84, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <v>Loan</v>
+      </c>
+      <c r="F84" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="G84" s="6">
+        <f>IF(EXACT($F84, ""), "", VLOOKUP($F84, [2]Main!$B$2:$E$30, 4, FALSE))</f>
+        <v>254000000000006</v>
+      </c>
+      <c r="H84" s="2">
+        <v>83</v>
+      </c>
+      <c r="I84" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000083::bigint);</v>
+      </c>
+    </row>
+    <row r="85" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B85" s="6">
+        <f>[1]Main!$E85</f>
+        <v>97000000000084</v>
+      </c>
+      <c r="C85" s="7" t="str">
+        <f>VLOOKUP($B85, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <v>Module.Finance.Data.Loan.Report.DataList</v>
+      </c>
+      <c r="D85" s="8" t="str">
+        <f>VLOOKUP($B85, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <v>Loan Summary</v>
+      </c>
+      <c r="F85" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="G85" s="6">
+        <f>IF(EXACT($F85, ""), "", VLOOKUP($F85, [2]Main!$B$2:$E$30, 4, FALSE))</f>
+        <v>254000000000006</v>
+      </c>
+      <c r="H85" s="2">
+        <v>84</v>
+      </c>
+      <c r="I85" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000084::bigint);</v>
+      </c>
+    </row>
+    <row r="86" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B86" s="6">
+        <f>[1]Main!$E86</f>
+        <v>97000000000085</v>
+      </c>
+      <c r="C86" s="7" t="str">
+        <f>VLOOKUP($B86, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <v>Module.Finance.Data.LoanToLoanSettlement.Report.DataList</v>
+      </c>
+      <c r="D86" s="8" t="str">
+        <f>VLOOKUP($B86, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <v>Loan to Loan Settlement</v>
+      </c>
+      <c r="F86" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="G86" s="6">
+        <f>IF(EXACT($F86, ""), "", VLOOKUP($F86, [2]Main!$B$2:$E$30, 4, FALSE))</f>
+        <v>254000000000006</v>
+      </c>
+      <c r="H86" s="2">
+        <v>85</v>
+      </c>
+      <c r="I86" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000085::bigint);</v>
+      </c>
+    </row>
+    <row r="87" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B87" s="6">
+        <f>[1]Main!$E87</f>
+        <v>97000000000086</v>
+      </c>
+      <c r="C87" s="7" t="str">
+        <f>VLOOKUP($B87, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <v>Module.Finance.Data.LoanSettlement.Transaction</v>
+      </c>
+      <c r="D87" s="8" t="str">
+        <f>VLOOKUP($B87, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <v>Loan Settlement</v>
+      </c>
+      <c r="F87" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="G87" s="6">
+        <f>IF(EXACT($F87, ""), "", VLOOKUP($F87, [2]Main!$B$2:$E$30, 4, FALSE))</f>
+        <v>254000000000006</v>
+      </c>
+      <c r="H87" s="2">
+        <v>86</v>
+      </c>
+      <c r="I87" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000086::bigint);</v>
+      </c>
+    </row>
+    <row r="88" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B88" s="6">
+        <f>[1]Main!$E88</f>
+        <v>97000000000087</v>
+      </c>
+      <c r="C88" s="7" t="str">
+        <f>VLOOKUP($B88, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <v>Module.Finance.Data.LoanSettlement.Report.DataList</v>
+      </c>
+      <c r="D88" s="8" t="str">
+        <f>VLOOKUP($B88, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <v>Loan Settlement Summary</v>
+      </c>
+      <c r="F88" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="G88" s="6">
+        <f>IF(EXACT($F88, ""), "", VLOOKUP($F88, [2]Main!$B$2:$E$30, 4, FALSE))</f>
+        <v>254000000000006</v>
+      </c>
+      <c r="H88" s="2">
+        <v>87</v>
+      </c>
+      <c r="I88" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000087::bigint);</v>
+      </c>
+    </row>
+    <row r="89" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B89" s="6">
+        <f>[1]Main!$E89</f>
+        <v>97000000000088</v>
+      </c>
+      <c r="C89" s="7" t="str">
+        <f>VLOOKUP($B89, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <v>Module.Finance.Data.CashBank.Transaction</v>
+      </c>
+      <c r="D89" s="8" t="str">
+        <f>VLOOKUP($B89, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <v>Cash &amp; Bank</v>
+      </c>
+      <c r="F89" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="G89" s="6">
+        <f>IF(EXACT($F89, ""), "", VLOOKUP($F89, [2]Main!$B$2:$E$30, 4, FALSE))</f>
+        <v>254000000000006</v>
+      </c>
+      <c r="H89" s="2">
+        <v>88</v>
+      </c>
+      <c r="I89" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000088::bigint);</v>
+      </c>
+    </row>
+    <row r="90" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B90" s="6">
+        <f>[1]Main!$E90</f>
+        <v>97000000000089</v>
+      </c>
+      <c r="C90" s="7" t="str">
+        <f>VLOOKUP($B90, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <v>Module.Finance.Data.CashBank.Report.DataList</v>
+      </c>
+      <c r="D90" s="8" t="str">
+        <f>VLOOKUP($B90, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <v>Cash &amp; Bank Summary</v>
+      </c>
+      <c r="F90" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="G90" s="6">
+        <f>IF(EXACT($F90, ""), "", VLOOKUP($F90, [2]Main!$B$2:$E$30, 4, FALSE))</f>
+        <v>254000000000006</v>
+      </c>
+      <c r="H90" s="2">
+        <v>89</v>
+      </c>
+      <c r="I90" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000089::bigint);</v>
+      </c>
+    </row>
+    <row r="91" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B91" s="6">
+        <f>[1]Main!$E91</f>
+        <v>97000000000090</v>
+      </c>
+      <c r="C91" s="7" t="str">
+        <f>VLOOKUP($B91, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <v>Module.Finance.Data.PaymentInstruction.Transaction</v>
+      </c>
+      <c r="D91" s="8" t="str">
+        <f>VLOOKUP($B91, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <v>Account Payable</v>
+      </c>
+      <c r="F91" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="G91" s="6">
+        <f>IF(EXACT($F91, ""), "", VLOOKUP($F91, [2]Main!$B$2:$E$30, 4, FALSE))</f>
+        <v>254000000000006</v>
+      </c>
+      <c r="H91" s="2">
+        <v>90</v>
+      </c>
+      <c r="I91" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000090::bigint);</v>
+      </c>
+    </row>
+    <row r="92" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B92" s="6">
+        <f>[1]Main!$E92</f>
+        <v>97000000000091</v>
+      </c>
+      <c r="C92" s="7" t="str">
+        <f>VLOOKUP($B92, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <v>Module.Finance.Data.PaymentInstruction.Report.DataList</v>
+      </c>
+      <c r="D92" s="8" t="str">
+        <f>VLOOKUP($B92, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <v>Account Payable Summary</v>
+      </c>
+      <c r="F92" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="G92" s="6">
+        <f>IF(EXACT($F92, ""), "", VLOOKUP($F92, [2]Main!$B$2:$E$30, 4, FALSE))</f>
+        <v>254000000000006</v>
+      </c>
+      <c r="H92" s="2">
+        <v>91</v>
+      </c>
+      <c r="I92" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000091::bigint);</v>
+      </c>
+    </row>
+    <row r="93" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B93" s="6">
+        <f>[1]Main!$E93</f>
+        <v>97000000000092</v>
+      </c>
+      <c r="C93" s="7" t="str">
+        <f>VLOOKUP($B93, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <v>Module.Finance.Data.SalesInvoice.Transaction</v>
+      </c>
+      <c r="D93" s="8" t="str">
+        <f>VLOOKUP($B93, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <v>Sales Invoice</v>
+      </c>
+      <c r="F93" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="G93" s="6">
+        <f>IF(EXACT($F93, ""), "", VLOOKUP($F93, [2]Main!$B$2:$E$30, 4, FALSE))</f>
+        <v>254000000000006</v>
+      </c>
+      <c r="H93" s="2">
+        <v>92</v>
+      </c>
+      <c r="I93" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000092::bigint);</v>
+      </c>
+    </row>
+    <row r="94" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B94" s="6">
+        <f>[1]Main!$E94</f>
+        <v>97000000000093</v>
+      </c>
+      <c r="C94" s="7" t="str">
+        <f>VLOOKUP($B94, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <v>Module.Finance.Data.SalesInvoice.Report.DataList</v>
+      </c>
+      <c r="D94" s="8" t="str">
+        <f>VLOOKUP($B94, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <v>Sales Invoice Summary</v>
+      </c>
+      <c r="F94" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="G94" s="6">
+        <f>IF(EXACT($F94, ""), "", VLOOKUP($F94, [2]Main!$B$2:$E$30, 4, FALSE))</f>
+        <v>254000000000006</v>
+      </c>
+      <c r="H94" s="2">
+        <v>93</v>
+      </c>
+      <c r="I94" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000093::bigint);</v>
+      </c>
+    </row>
+    <row r="95" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B95" s="6">
+        <f>[1]Main!$E95</f>
+        <v>97000000000094</v>
+      </c>
+      <c r="C95" s="7" t="str">
+        <f>VLOOKUP($B95, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <v>Module.Finance.Data.SalesInvoiceToCreditNote.Report.DataList</v>
+      </c>
+      <c r="D95" s="8" t="str">
+        <f>VLOOKUP($B95, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <v>Sales Invoice to Credit Note</v>
+      </c>
+      <c r="F95" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="G95" s="6">
+        <f>IF(EXACT($F95, ""), "", VLOOKUP($F95, [2]Main!$B$2:$E$30, 4, FALSE))</f>
+        <v>254000000000006</v>
+      </c>
+      <c r="H95" s="2">
+        <v>94</v>
+      </c>
+      <c r="I95" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000094::bigint);</v>
+      </c>
+    </row>
+    <row r="96" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B96" s="6">
+        <f>[1]Main!$E96</f>
+        <v>97000000000095</v>
+      </c>
+      <c r="C96" s="7" t="str">
+        <f>VLOOKUP($B96, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <v>Module.Finance.Data.TaxReconciliation.Transaction</v>
+      </c>
+      <c r="D96" s="8" t="str">
+        <f>VLOOKUP($B96, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <v>Tax Reconciliation</v>
+      </c>
+      <c r="F96" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="G96" s="6">
+        <f>IF(EXACT($F96, ""), "", VLOOKUP($F96, [2]Main!$B$2:$E$30, 4, FALSE))</f>
+        <v>254000000000006</v>
+      </c>
+      <c r="H96" s="2">
+        <v>95</v>
+      </c>
+      <c r="I96" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000095::bigint);</v>
+      </c>
+    </row>
+    <row r="97" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B97" s="6">
+        <f>[1]Main!$E97</f>
+        <v>97000000000096</v>
+      </c>
+      <c r="C97" s="7" t="str">
+        <f>VLOOKUP($B97, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <v>Module.Finance.Data.TaxReconciliation.Report.DataList</v>
+      </c>
+      <c r="D97" s="8" t="str">
+        <f>VLOOKUP($B97, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <v>Tax Reconciliation Summary</v>
+      </c>
+      <c r="F97" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="G97" s="6">
+        <f>IF(EXACT($F97, ""), "", VLOOKUP($F97, [2]Main!$B$2:$E$30, 4, FALSE))</f>
+        <v>254000000000006</v>
+      </c>
+      <c r="H97" s="2">
+        <v>96</v>
+      </c>
+      <c r="I97" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000096::bigint);</v>
+      </c>
+    </row>
+    <row r="98" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B98" s="6">
+        <f>[1]Main!$E98</f>
+        <v>97000000000097</v>
+      </c>
+      <c r="C98" s="7" t="str">
+        <f>VLOOKUP($B98, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <v>Module.CustomerRelation.MasterData.Customer.Transaction</v>
+      </c>
+      <c r="D98" s="8" t="str">
+        <f>VLOOKUP($B98, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <v>Customer</v>
+      </c>
+      <c r="F98" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="G98" s="6">
+        <f>IF(EXACT($F98, ""), "", VLOOKUP($F98, [2]Main!$B$2:$E$30, 4, FALSE))</f>
+        <v>254000000000010</v>
+      </c>
+      <c r="H98" s="2">
+        <v>97</v>
+      </c>
+      <c r="I98" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000010::bigint, 97000000000097::bigint);</v>
       </c>
     </row>
   </sheetData>
@@ -3208,15 +4527,15 @@
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B5" s="1">
-        <f>[1]Main!L5</f>
+        <f>[1]Main!L6</f>
         <v>0</v>
       </c>
       <c r="C5" s="1" t="str">
-        <f>IF(EXACT([1]Main!D5, ""), "", [1]Main!D5)</f>
+        <f>IF(EXACT([1]Main!D6, ""), "", [1]Main!D6)</f>
         <v/>
       </c>
       <c r="D5" s="1">
-        <f>[1]Main!M5</f>
+        <f>[1]Main!M6</f>
         <v>0</v>
       </c>
       <c r="E5" s="1" t="str">
@@ -3239,15 +4558,15 @@
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B6" s="1">
-        <f>[1]Main!L6</f>
+        <f>[1]Main!L7</f>
         <v>0</v>
       </c>
       <c r="C6" s="1" t="str">
-        <f>IF(EXACT([1]Main!D6, ""), "", [1]Main!D6)</f>
+        <f>IF(EXACT([1]Main!D7, ""), "", [1]Main!D7)</f>
         <v/>
       </c>
       <c r="D6" s="1">
-        <f>[1]Main!M6</f>
+        <f>[1]Main!M7</f>
         <v>0</v>
       </c>
       <c r="E6" s="1" t="str">
@@ -3270,15 +4589,15 @@
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B7" s="1">
-        <f>[1]Main!L7</f>
+        <f>[1]Main!L8</f>
         <v>0</v>
       </c>
       <c r="C7" s="1" t="str">
-        <f>IF(EXACT([1]Main!D7, ""), "", [1]Main!D7)</f>
+        <f>IF(EXACT([1]Main!D8, ""), "", [1]Main!D8)</f>
         <v/>
       </c>
       <c r="D7" s="1">
-        <f>[1]Main!M7</f>
+        <f>[1]Main!M8</f>
         <v>0</v>
       </c>
       <c r="E7" s="1" t="str">
@@ -3301,15 +4620,15 @@
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B8" s="1">
-        <f>[1]Main!L8</f>
+        <f>[1]Main!L9</f>
         <v>0</v>
       </c>
       <c r="C8" s="1" t="str">
-        <f>IF(EXACT([1]Main!D8, ""), "", [1]Main!D8)</f>
+        <f>IF(EXACT([1]Main!D9, ""), "", [1]Main!D9)</f>
         <v/>
       </c>
       <c r="D8" s="1">
-        <f>[1]Main!M8</f>
+        <f>[1]Main!M9</f>
         <v>0</v>
       </c>
       <c r="E8" s="1" t="str">
@@ -3332,15 +4651,15 @@
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B9" s="1">
-        <f>[1]Main!L9</f>
+        <f>[1]Main!L10</f>
         <v>0</v>
       </c>
       <c r="C9" s="1" t="str">
-        <f>IF(EXACT([1]Main!D9, ""), "", [1]Main!D9)</f>
+        <f>IF(EXACT([1]Main!D10, ""), "", [1]Main!D10)</f>
         <v/>
       </c>
       <c r="D9" s="1">
-        <f>[1]Main!M9</f>
+        <f>[1]Main!M10</f>
         <v>0</v>
       </c>
       <c r="E9" s="1" t="str">
@@ -3363,15 +4682,15 @@
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B10" s="1">
-        <f>[1]Main!L10</f>
+        <f>[1]Main!L11</f>
         <v>0</v>
       </c>
       <c r="C10" s="1" t="str">
-        <f>IF(EXACT([1]Main!D10, ""), "", [1]Main!D10)</f>
+        <f>IF(EXACT([1]Main!D11, ""), "", [1]Main!D11)</f>
         <v/>
       </c>
       <c r="D10" s="1">
-        <f>[1]Main!M10</f>
+        <f>[1]Main!M11</f>
         <v>0</v>
       </c>
       <c r="E10" s="1" t="str">
@@ -3394,15 +4713,15 @@
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B11" s="1">
-        <f>[1]Main!L11</f>
+        <f>[1]Main!L12</f>
         <v>0</v>
       </c>
       <c r="C11" s="1" t="str">
-        <f>IF(EXACT([1]Main!D11, ""), "", [1]Main!D11)</f>
+        <f>IF(EXACT([1]Main!D12, ""), "", [1]Main!D12)</f>
         <v/>
       </c>
       <c r="D11" s="1">
-        <f>[1]Main!M11</f>
+        <f>[1]Main!M12</f>
         <v>0</v>
       </c>
       <c r="E11" s="1" t="str">
@@ -3425,15 +4744,15 @@
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B12" s="1">
-        <f>[1]Main!L12</f>
+        <f>[1]Main!L13</f>
         <v>0</v>
       </c>
       <c r="C12" s="1" t="str">
-        <f>IF(EXACT([1]Main!D12, ""), "", [1]Main!D12)</f>
+        <f>IF(EXACT([1]Main!D13, ""), "", [1]Main!D13)</f>
         <v/>
       </c>
       <c r="D12" s="1">
-        <f>[1]Main!M12</f>
+        <f>[1]Main!M13</f>
         <v>0</v>
       </c>
       <c r="E12" s="1" t="str">
@@ -3456,15 +4775,15 @@
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B13" s="1">
-        <f>[1]Main!L13</f>
+        <f>[1]Main!L14</f>
         <v>0</v>
       </c>
       <c r="C13" s="1" t="str">
-        <f>IF(EXACT([1]Main!D13, ""), "", [1]Main!D13)</f>
+        <f>IF(EXACT([1]Main!D14, ""), "", [1]Main!D14)</f>
         <v/>
       </c>
       <c r="D13" s="1">
-        <f>[1]Main!M13</f>
+        <f>[1]Main!M14</f>
         <v>0</v>
       </c>
       <c r="E13" s="1" t="str">
@@ -3487,15 +4806,15 @@
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B14" s="1">
-        <f>[1]Main!L14</f>
+        <f>[1]Main!L15</f>
         <v>0</v>
       </c>
       <c r="C14" s="1" t="str">
-        <f>IF(EXACT([1]Main!D14, ""), "", [1]Main!D14)</f>
+        <f>IF(EXACT([1]Main!D15, ""), "", [1]Main!D15)</f>
         <v/>
       </c>
       <c r="D14" s="1">
-        <f>[1]Main!M14</f>
+        <f>[1]Main!M15</f>
         <v>0</v>
       </c>
       <c r="E14" s="1" t="str">
@@ -3518,15 +4837,15 @@
     </row>
     <row r="15" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B15" s="1">
-        <f>[1]Main!L15</f>
+        <f>[1]Main!L16</f>
         <v>0</v>
       </c>
       <c r="C15" s="1" t="str">
-        <f>IF(EXACT([1]Main!D15, ""), "", [1]Main!D15)</f>
+        <f>IF(EXACT([1]Main!D16, ""), "", [1]Main!D16)</f>
         <v/>
       </c>
       <c r="D15" s="1">
-        <f>[1]Main!M15</f>
+        <f>[1]Main!M16</f>
         <v>0</v>
       </c>
       <c r="E15" s="1" t="str">
@@ -3549,15 +4868,15 @@
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B16" s="1">
-        <f>[1]Main!L16</f>
+        <f>[1]Main!L17</f>
         <v>0</v>
       </c>
       <c r="C16" s="1" t="str">
-        <f>IF(EXACT([1]Main!D16, ""), "", [1]Main!D16)</f>
+        <f>IF(EXACT([1]Main!D17, ""), "", [1]Main!D17)</f>
         <v/>
       </c>
       <c r="D16" s="1">
-        <f>[1]Main!M16</f>
+        <f>[1]Main!M17</f>
         <v>0</v>
       </c>
       <c r="E16" s="1" t="str">
@@ -3580,15 +4899,15 @@
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B17" s="1">
-        <f>[1]Main!L17</f>
+        <f>[1]Main!L19</f>
         <v>0</v>
       </c>
       <c r="C17" s="1" t="str">
-        <f>IF(EXACT([1]Main!D17, ""), "", [1]Main!D17)</f>
+        <f>IF(EXACT([1]Main!D19, ""), "", [1]Main!D19)</f>
         <v/>
       </c>
       <c r="D17" s="1">
-        <f>[1]Main!M17</f>
+        <f>[1]Main!M19</f>
         <v>0</v>
       </c>
       <c r="E17" s="1" t="str">
@@ -3611,15 +4930,15 @@
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B18" s="1">
-        <f>[1]Main!L18</f>
+        <f>[1]Main!L22</f>
         <v>0</v>
       </c>
       <c r="C18" s="1" t="str">
-        <f>IF(EXACT([1]Main!D18, ""), "", [1]Main!D18)</f>
+        <f>IF(EXACT([1]Main!D22, ""), "", [1]Main!D22)</f>
         <v/>
       </c>
       <c r="D18" s="1">
-        <f>[1]Main!M18</f>
+        <f>[1]Main!M22</f>
         <v>0</v>
       </c>
       <c r="E18" s="1" t="str">
@@ -3642,15 +4961,15 @@
     </row>
     <row r="19" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B19" s="1">
-        <f>[1]Main!L19</f>
+        <f>[1]Main!L23</f>
         <v>0</v>
       </c>
       <c r="C19" s="1" t="str">
-        <f>IF(EXACT([1]Main!D19, ""), "", [1]Main!D19)</f>
+        <f>IF(EXACT([1]Main!D23, ""), "", [1]Main!D23)</f>
         <v/>
       </c>
       <c r="D19" s="1">
-        <f>[1]Main!M19</f>
+        <f>[1]Main!M23</f>
         <v>0</v>
       </c>
       <c r="E19" s="1" t="str">
@@ -3673,15 +4992,15 @@
     </row>
     <row r="20" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B20" s="1">
-        <f>[1]Main!L20</f>
+        <f>[1]Main!L25</f>
         <v>0</v>
       </c>
       <c r="C20" s="1" t="str">
-        <f>IF(EXACT([1]Main!D20, ""), "", [1]Main!D20)</f>
+        <f>IF(EXACT([1]Main!D25, ""), "", [1]Main!D25)</f>
         <v/>
       </c>
       <c r="D20" s="1">
-        <f>[1]Main!M20</f>
+        <f>[1]Main!M25</f>
         <v>0</v>
       </c>
       <c r="E20" s="1" t="str">
@@ -3704,15 +5023,15 @@
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B21" s="1">
-        <f>[1]Main!L46</f>
+        <f>[1]Main!L69</f>
         <v>0</v>
       </c>
       <c r="C21" s="1" t="str">
-        <f>IF(EXACT([1]Main!D46, ""), "", [1]Main!D46)</f>
+        <f>IF(EXACT([1]Main!D69, ""), "", [1]Main!D69)</f>
         <v/>
       </c>
       <c r="D21" s="1">
-        <f>[1]Main!M46</f>
+        <f>[1]Main!M69</f>
         <v>0</v>
       </c>
       <c r="E21" s="1" t="str">
@@ -3735,15 +5054,15 @@
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B22" s="1">
-        <f>[1]Main!L47</f>
+        <f>[1]Main!L65</f>
         <v>0</v>
       </c>
       <c r="C22" s="1" t="str">
-        <f>IF(EXACT([1]Main!D47, ""), "", [1]Main!D47)</f>
+        <f>IF(EXACT([1]Main!D65, ""), "", [1]Main!D65)</f>
         <v/>
       </c>
       <c r="D22" s="1">
-        <f>[1]Main!M47</f>
+        <f>[1]Main!M65</f>
         <v>0</v>
       </c>
       <c r="E22" s="1" t="str">
@@ -3766,15 +5085,15 @@
     </row>
     <row r="23" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B23" s="1">
-        <f>[1]Main!L21</f>
+        <f>[1]Main!L27</f>
         <v>0</v>
       </c>
       <c r="C23" s="1" t="str">
-        <f>IF(EXACT([1]Main!D21, ""), "", [1]Main!D21)</f>
+        <f>IF(EXACT([1]Main!D27, ""), "", [1]Main!D27)</f>
         <v/>
       </c>
       <c r="D23" s="1">
-        <f>[1]Main!M21</f>
+        <f>[1]Main!M27</f>
         <v>0</v>
       </c>
       <c r="E23" s="1" t="str">
@@ -3797,15 +5116,15 @@
     </row>
     <row r="24" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B24" s="1">
-        <f>[1]Main!L22</f>
+        <f>[1]Main!L26</f>
         <v>0</v>
       </c>
       <c r="C24" s="1" t="str">
-        <f>IF(EXACT([1]Main!D22, ""), "", [1]Main!D22)</f>
+        <f>IF(EXACT([1]Main!D26, ""), "", [1]Main!D26)</f>
         <v/>
       </c>
       <c r="D24" s="1">
-        <f>[1]Main!M22</f>
+        <f>[1]Main!M26</f>
         <v>0</v>
       </c>
       <c r="E24" s="1" t="str">
@@ -3828,15 +5147,15 @@
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B25" s="1">
-        <f>[1]Main!L23</f>
+        <f>[1]Main!L33</f>
         <v>0</v>
       </c>
       <c r="C25" s="1" t="str">
-        <f>IF(EXACT([1]Main!D23, ""), "", [1]Main!D23)</f>
+        <f>IF(EXACT([1]Main!D33, ""), "", [1]Main!D33)</f>
         <v/>
       </c>
       <c r="D25" s="1">
-        <f>[1]Main!M23</f>
+        <f>[1]Main!M33</f>
         <v>0</v>
       </c>
       <c r="E25" s="1" t="str">
@@ -3859,15 +5178,15 @@
     </row>
     <row r="26" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B26" s="1">
-        <f>[1]Main!L24</f>
+        <f>[1]Main!L35</f>
         <v>0</v>
       </c>
       <c r="C26" s="1" t="str">
-        <f>IF(EXACT([1]Main!D24, ""), "", [1]Main!D24)</f>
+        <f>IF(EXACT([1]Main!D35, ""), "", [1]Main!D35)</f>
         <v/>
       </c>
       <c r="D26" s="1">
-        <f>[1]Main!M24</f>
+        <f>[1]Main!M35</f>
         <v>0</v>
       </c>
       <c r="E26" s="1" t="str">
@@ -3890,15 +5209,15 @@
     </row>
     <row r="27" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B27" s="1">
-        <f>[1]Main!L25</f>
+        <f>[1]Main!L36</f>
         <v>0</v>
       </c>
       <c r="C27" s="1" t="str">
-        <f>IF(EXACT([1]Main!D25, ""), "", [1]Main!D25)</f>
+        <f>IF(EXACT([1]Main!D36, ""), "", [1]Main!D36)</f>
         <v/>
       </c>
       <c r="D27" s="1">
-        <f>[1]Main!M25</f>
+        <f>[1]Main!M36</f>
         <v>0</v>
       </c>
       <c r="E27" s="1" t="str">
@@ -3921,15 +5240,15 @@
     </row>
     <row r="28" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B28" s="1">
-        <f>[1]Main!L26</f>
+        <f>[1]Main!L37</f>
         <v>0</v>
       </c>
       <c r="C28" s="1" t="str">
-        <f>IF(EXACT([1]Main!D26, ""), "", [1]Main!D26)</f>
+        <f>IF(EXACT([1]Main!D37, ""), "", [1]Main!D37)</f>
         <v/>
       </c>
       <c r="D28" s="1">
-        <f>[1]Main!M26</f>
+        <f>[1]Main!M37</f>
         <v>0</v>
       </c>
       <c r="E28" s="1" t="str">
@@ -3952,15 +5271,15 @@
     </row>
     <row r="29" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B29" s="1">
-        <f>[1]Main!L27</f>
+        <f>[1]Main!L39</f>
         <v>0</v>
       </c>
       <c r="C29" s="1" t="str">
-        <f>IF(EXACT([1]Main!D27, ""), "", [1]Main!D27)</f>
+        <f>IF(EXACT([1]Main!D39, ""), "", [1]Main!D39)</f>
         <v/>
       </c>
       <c r="D29" s="1">
-        <f>[1]Main!M27</f>
+        <f>[1]Main!M39</f>
         <v>0</v>
       </c>
       <c r="E29" s="1" t="str">
@@ -3983,15 +5302,15 @@
     </row>
     <row r="30" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B30" s="1">
-        <f>[1]Main!L28</f>
+        <f>[1]Main!L38</f>
         <v>0</v>
       </c>
       <c r="C30" s="1" t="str">
-        <f>IF(EXACT([1]Main!D28, ""), "", [1]Main!D28)</f>
+        <f>IF(EXACT([1]Main!D38, ""), "", [1]Main!D38)</f>
         <v/>
       </c>
       <c r="D30" s="1">
-        <f>[1]Main!M28</f>
+        <f>[1]Main!M38</f>
         <v>0</v>
       </c>
       <c r="E30" s="1" t="str">
@@ -4014,15 +5333,15 @@
     </row>
     <row r="31" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B31" s="1">
-        <f>[1]Main!L29</f>
+        <f>[1]Main!L41</f>
         <v>0</v>
       </c>
       <c r="C31" s="1" t="str">
-        <f>IF(EXACT([1]Main!D29, ""), "", [1]Main!D29)</f>
+        <f>IF(EXACT([1]Main!D41, ""), "", [1]Main!D41)</f>
         <v/>
       </c>
       <c r="D31" s="1">
-        <f>[1]Main!M29</f>
+        <f>[1]Main!M41</f>
         <v>0</v>
       </c>
       <c r="E31" s="1" t="str">
@@ -4045,15 +5364,15 @@
     </row>
     <row r="32" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B32" s="1">
-        <f>[1]Main!L30</f>
+        <f>[1]Main!L42</f>
         <v>0</v>
       </c>
       <c r="C32" s="1" t="str">
-        <f>IF(EXACT([1]Main!D30, ""), "", [1]Main!D30)</f>
+        <f>IF(EXACT([1]Main!D42, ""), "", [1]Main!D42)</f>
         <v/>
       </c>
       <c r="D32" s="1">
-        <f>[1]Main!M30</f>
+        <f>[1]Main!M42</f>
         <v>0</v>
       </c>
       <c r="E32" s="1" t="str">
@@ -4065,7 +5384,7 @@
         <v/>
       </c>
       <c r="H32" s="4">
-        <f>IF(EXACT(Main!F7, ""), "", VLOOKUP(Main!F7, [2]Main!$B$2:$D$30, 3, FALSE))</f>
+        <f>IF(EXACT(Main!F8, ""), "", VLOOKUP(Main!F8, [2]Main!$B$2:$D$30, 3, FALSE))</f>
         <v>0</v>
       </c>
       <c r="J32" s="2" t="str">
@@ -4075,15 +5394,15 @@
     </row>
     <row r="33" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B33" s="1">
-        <f>[1]Main!L31</f>
+        <f>[1]Main!L45</f>
         <v>0</v>
       </c>
       <c r="C33" s="1" t="str">
-        <f>IF(EXACT([1]Main!D31, ""), "", [1]Main!D31)</f>
+        <f>IF(EXACT([1]Main!D45, ""), "", [1]Main!D45)</f>
         <v/>
       </c>
       <c r="D33" s="1">
-        <f>[1]Main!M31</f>
+        <f>[1]Main!M45</f>
         <v>0</v>
       </c>
       <c r="E33" s="1" t="str">
@@ -4095,7 +5414,7 @@
         <v/>
       </c>
       <c r="H33" s="4">
-        <f>IF(EXACT(Main!F8, ""), "", VLOOKUP(Main!F8, [2]Main!$B$2:$D$30, 3, FALSE))</f>
+        <f>IF(EXACT(Main!F9, ""), "", VLOOKUP(Main!F9, [2]Main!$B$2:$D$30, 3, FALSE))</f>
         <v>0</v>
       </c>
       <c r="J33" s="2" t="str">
@@ -4105,15 +5424,15 @@
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B34" s="1">
-        <f>[1]Main!L32</f>
+        <f>[1]Main!L47</f>
         <v>0</v>
       </c>
       <c r="C34" s="1" t="str">
-        <f>IF(EXACT([1]Main!D32, ""), "", [1]Main!D32)</f>
+        <f>IF(EXACT([1]Main!D47, ""), "", [1]Main!D47)</f>
         <v/>
       </c>
       <c r="D34" s="1">
-        <f>[1]Main!M32</f>
+        <f>[1]Main!M47</f>
         <v>0</v>
       </c>
       <c r="E34" s="1" t="str">
@@ -4138,15 +5457,15 @@
     </row>
     <row r="35" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B35" s="1">
-        <f>[1]Main!L33</f>
+        <f>[1]Main!L46</f>
         <v>0</v>
       </c>
       <c r="C35" s="1" t="str">
-        <f>IF(EXACT([1]Main!D33, ""), "", [1]Main!D33)</f>
+        <f>IF(EXACT([1]Main!D46, ""), "", [1]Main!D46)</f>
         <v/>
       </c>
       <c r="D35" s="1">
-        <f>[1]Main!M33</f>
+        <f>[1]Main!M46</f>
         <v>0</v>
       </c>
       <c r="E35" s="1" t="str">
@@ -4171,15 +5490,15 @@
     </row>
     <row r="36" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B36" s="1">
-        <f>[1]Main!L34</f>
+        <f>[1]Main!L50</f>
         <v>0</v>
       </c>
       <c r="C36" s="1" t="str">
-        <f>IF(EXACT([1]Main!D34, ""), "", [1]Main!D34)</f>
+        <f>IF(EXACT([1]Main!D50, ""), "", [1]Main!D50)</f>
         <v/>
       </c>
       <c r="D36" s="1">
-        <f>[1]Main!M34</f>
+        <f>[1]Main!M50</f>
         <v>0</v>
       </c>
       <c r="E36" s="1" t="str">
@@ -4204,15 +5523,15 @@
     </row>
     <row r="37" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B37" s="1">
-        <f>[1]Main!L35</f>
+        <f>[1]Main!L49</f>
         <v>0</v>
       </c>
       <c r="C37" s="1" t="str">
-        <f>IF(EXACT([1]Main!D35, ""), "", [1]Main!D35)</f>
+        <f>IF(EXACT([1]Main!D49, ""), "", [1]Main!D49)</f>
         <v/>
       </c>
       <c r="D37" s="1">
-        <f>[1]Main!M35</f>
+        <f>[1]Main!M49</f>
         <v>0</v>
       </c>
       <c r="E37" s="1" t="str">
@@ -4237,15 +5556,15 @@
     </row>
     <row r="38" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B38" s="1">
-        <f>[1]Main!L36</f>
+        <f>[1]Main!L55</f>
         <v>0</v>
       </c>
       <c r="C38" s="1" t="str">
-        <f>IF(EXACT([1]Main!D36, ""), "", [1]Main!D36)</f>
+        <f>IF(EXACT([1]Main!D55, ""), "", [1]Main!D55)</f>
         <v/>
       </c>
       <c r="D38" s="1">
-        <f>[1]Main!M36</f>
+        <f>[1]Main!M55</f>
         <v>0</v>
       </c>
       <c r="E38" s="1" t="str">
@@ -4270,15 +5589,15 @@
     </row>
     <row r="39" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B39" s="1">
-        <f>[1]Main!L37</f>
+        <f>[1]Main!L54</f>
         <v>0</v>
       </c>
       <c r="C39" s="1" t="str">
-        <f>IF(EXACT([1]Main!D37, ""), "", [1]Main!D37)</f>
+        <f>IF(EXACT([1]Main!D54, ""), "", [1]Main!D54)</f>
         <v/>
       </c>
       <c r="D39" s="1">
-        <f>[1]Main!M37</f>
+        <f>[1]Main!M54</f>
         <v>0</v>
       </c>
       <c r="E39" s="1" t="str">
@@ -4303,15 +5622,15 @@
     </row>
     <row r="40" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B40" s="1">
-        <f>[1]Main!L38</f>
+        <f>[1]Main!L52</f>
         <v>0</v>
       </c>
       <c r="C40" s="1" t="str">
-        <f>IF(EXACT([1]Main!D38, ""), "", [1]Main!D38)</f>
+        <f>IF(EXACT([1]Main!D52, ""), "", [1]Main!D52)</f>
         <v/>
       </c>
       <c r="D40" s="1">
-        <f>[1]Main!M38</f>
+        <f>[1]Main!M52</f>
         <v>0</v>
       </c>
       <c r="E40" s="1" t="str">
@@ -4336,15 +5655,15 @@
     </row>
     <row r="41" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B41" s="1">
-        <f>[1]Main!L39</f>
+        <f>[1]Main!L51</f>
         <v>0</v>
       </c>
       <c r="C41" s="1" t="str">
-        <f>IF(EXACT([1]Main!D39, ""), "", [1]Main!D39)</f>
+        <f>IF(EXACT([1]Main!D51, ""), "", [1]Main!D51)</f>
         <v/>
       </c>
       <c r="D41" s="1">
-        <f>[1]Main!M39</f>
+        <f>[1]Main!M51</f>
         <v>0</v>
       </c>
       <c r="E41" s="1" t="str">
@@ -4369,15 +5688,15 @@
     </row>
     <row r="42" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B42" s="1">
-        <f>[1]Main!L40</f>
+        <f>[1]Main!L56</f>
         <v>0</v>
       </c>
       <c r="C42" s="1" t="str">
-        <f>IF(EXACT([1]Main!D40, ""), "", [1]Main!D40)</f>
+        <f>IF(EXACT([1]Main!D56, ""), "", [1]Main!D56)</f>
         <v/>
       </c>
       <c r="D42" s="1">
-        <f>[1]Main!M40</f>
+        <f>[1]Main!M56</f>
         <v>0</v>
       </c>
       <c r="E42" s="1" t="str">
@@ -4402,15 +5721,15 @@
     </row>
     <row r="43" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B43" s="1">
-        <f>[1]Main!L41</f>
+        <f>[1]Main!L58</f>
         <v>0</v>
       </c>
       <c r="C43" s="1" t="str">
-        <f>IF(EXACT([1]Main!D41, ""), "", [1]Main!D41)</f>
+        <f>IF(EXACT([1]Main!D58, ""), "", [1]Main!D58)</f>
         <v/>
       </c>
       <c r="D43" s="1">
-        <f>[1]Main!M41</f>
+        <f>[1]Main!M58</f>
         <v>0</v>
       </c>
       <c r="E43" s="1" t="str">
@@ -4435,15 +5754,15 @@
     </row>
     <row r="44" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B44" s="1">
-        <f>[1]Main!L42</f>
+        <f>[1]Main!L59</f>
         <v>0</v>
       </c>
       <c r="C44" s="1" t="str">
-        <f>IF(EXACT([1]Main!D42, ""), "", [1]Main!D42)</f>
+        <f>IF(EXACT([1]Main!D59, ""), "", [1]Main!D59)</f>
         <v/>
       </c>
       <c r="D44" s="1">
-        <f>[1]Main!M42</f>
+        <f>[1]Main!M59</f>
         <v>0</v>
       </c>
       <c r="E44" s="1" t="str">
@@ -4468,15 +5787,15 @@
     </row>
     <row r="45" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B45" s="1">
-        <f>[1]Main!L43</f>
+        <f>[1]Main!L57</f>
         <v>0</v>
       </c>
       <c r="C45" s="1" t="str">
-        <f>IF(EXACT([1]Main!D43, ""), "", [1]Main!D43)</f>
+        <f>IF(EXACT([1]Main!D57, ""), "", [1]Main!D57)</f>
         <v/>
       </c>
       <c r="D45" s="1">
-        <f>[1]Main!M43</f>
+        <f>[1]Main!M57</f>
         <v>0</v>
       </c>
       <c r="E45" s="1" t="str">
@@ -4501,15 +5820,15 @@
     </row>
     <row r="46" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B46" s="1">
-        <f>[1]Main!L44</f>
+        <f>[1]Main!L61</f>
         <v>0</v>
       </c>
       <c r="C46" s="1" t="str">
-        <f>IF(EXACT([1]Main!D44, ""), "", [1]Main!D44)</f>
+        <f>IF(EXACT([1]Main!D61, ""), "", [1]Main!D61)</f>
         <v/>
       </c>
       <c r="D46" s="1">
-        <f>[1]Main!M44</f>
+        <f>[1]Main!M61</f>
         <v>0</v>
       </c>
       <c r="E46" s="1" t="str">
@@ -4534,15 +5853,15 @@
     </row>
     <row r="47" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B47" s="1">
-        <f>[1]Main!L45</f>
+        <f>[1]Main!L60</f>
         <v>0</v>
       </c>
       <c r="C47" s="1" t="str">
-        <f>IF(EXACT([1]Main!D45, ""), "", [1]Main!D45)</f>
+        <f>IF(EXACT([1]Main!D60, ""), "", [1]Main!D60)</f>
         <v/>
       </c>
       <c r="D47" s="1">
-        <f>[1]Main!M45</f>
+        <f>[1]Main!M60</f>
         <v>0</v>
       </c>
       <c r="E47" s="1" t="str">
@@ -4567,15 +5886,15 @@
     </row>
     <row r="48" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B48" s="1">
-        <f>[1]Main!L48</f>
+        <f>[1]Main!L77</f>
         <v>0</v>
       </c>
       <c r="C48" s="1" t="str">
-        <f>IF(EXACT([1]Main!D48, ""), "", [1]Main!D48)</f>
+        <f>IF(EXACT([1]Main!D77, ""), "", [1]Main!D77)</f>
         <v/>
       </c>
       <c r="D48" s="1">
-        <f>[1]Main!M48</f>
+        <f>[1]Main!M77</f>
         <v>0</v>
       </c>
       <c r="E48" s="1" t="str">
@@ -4600,15 +5919,15 @@
     </row>
     <row r="49" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B49" s="1">
-        <f>[1]Main!L49</f>
+        <f>[1]Main!L78</f>
         <v>0</v>
       </c>
       <c r="C49" s="1" t="str">
-        <f>IF(EXACT([1]Main!D49, ""), "", [1]Main!D49)</f>
+        <f>IF(EXACT([1]Main!D78, ""), "", [1]Main!D78)</f>
         <v/>
       </c>
       <c r="D49" s="1">
-        <f>[1]Main!M49</f>
+        <f>[1]Main!M78</f>
         <v>0</v>
       </c>
       <c r="E49" s="1" t="str">
@@ -4633,15 +5952,15 @@
     </row>
     <row r="50" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B50" s="1">
-        <f>[1]Main!L50</f>
+        <f>[1]Main!L80</f>
         <v>0</v>
       </c>
       <c r="C50" s="1" t="str">
-        <f>IF(EXACT([1]Main!D50, ""), "", [1]Main!D50)</f>
+        <f>IF(EXACT([1]Main!D80, ""), "", [1]Main!D80)</f>
         <v/>
       </c>
       <c r="D50" s="1">
-        <f>[1]Main!M50</f>
+        <f>[1]Main!M80</f>
         <v>0</v>
       </c>
       <c r="E50" s="1" t="str">
@@ -4666,15 +5985,15 @@
     </row>
     <row r="51" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B51" s="1">
-        <f>[1]Main!L51</f>
+        <f>[1]Main!L81</f>
         <v>0</v>
       </c>
       <c r="C51" s="1" t="str">
-        <f>IF(EXACT([1]Main!D51, ""), "", [1]Main!D51)</f>
+        <f>IF(EXACT([1]Main!D81, ""), "", [1]Main!D81)</f>
         <v/>
       </c>
       <c r="D51" s="1">
-        <f>[1]Main!M51</f>
+        <f>[1]Main!M81</f>
         <v>0</v>
       </c>
       <c r="E51" s="1" t="str">
@@ -4699,15 +6018,15 @@
     </row>
     <row r="52" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B52" s="1">
-        <f>[1]Main!L52</f>
+        <f>[1]Main!L79</f>
         <v>0</v>
       </c>
       <c r="C52" s="1" t="str">
-        <f>IF(EXACT([1]Main!D52, ""), "", [1]Main!D52)</f>
+        <f>IF(EXACT([1]Main!D79, ""), "", [1]Main!D79)</f>
         <v/>
       </c>
       <c r="D52" s="1">
-        <f>[1]Main!M52</f>
+        <f>[1]Main!M79</f>
         <v>0</v>
       </c>
       <c r="E52" s="1" t="str">
@@ -4732,15 +6051,15 @@
     </row>
     <row r="53" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B53" s="1">
-        <f>[1]Main!L53</f>
+        <f>[1]Main!L82</f>
         <v>0</v>
       </c>
       <c r="C53" s="1" t="str">
-        <f>IF(EXACT([1]Main!D53, ""), "", [1]Main!D53)</f>
+        <f>IF(EXACT([1]Main!D82, ""), "", [1]Main!D82)</f>
         <v/>
       </c>
       <c r="D53" s="1">
-        <f>[1]Main!M53</f>
+        <f>[1]Main!M82</f>
         <v>0</v>
       </c>
       <c r="E53" s="1" t="str">
@@ -4765,15 +6084,15 @@
     </row>
     <row r="54" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B54" s="1">
-        <f>[1]Main!L54</f>
+        <f>[1]Main!L83</f>
         <v>0</v>
       </c>
       <c r="C54" s="1" t="str">
-        <f>IF(EXACT([1]Main!D54, ""), "", [1]Main!D54)</f>
+        <f>IF(EXACT([1]Main!D83, ""), "", [1]Main!D83)</f>
         <v/>
       </c>
       <c r="D54" s="1">
-        <f>[1]Main!M54</f>
+        <f>[1]Main!M83</f>
         <v>0</v>
       </c>
       <c r="E54" s="1" t="str">
@@ -4798,15 +6117,15 @@
     </row>
     <row r="55" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B55" s="1">
-        <f>[1]Main!L55</f>
+        <f>[1]Main!L84</f>
         <v>0</v>
       </c>
       <c r="C55" s="1" t="str">
-        <f>IF(EXACT([1]Main!D55, ""), "", [1]Main!D55)</f>
+        <f>IF(EXACT([1]Main!D84, ""), "", [1]Main!D84)</f>
         <v/>
       </c>
       <c r="D55" s="1">
-        <f>[1]Main!M55</f>
+        <f>[1]Main!M84</f>
         <v>0</v>
       </c>
       <c r="E55" s="1" t="str">
@@ -4831,15 +6150,15 @@
     </row>
     <row r="56" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B56" s="1">
-        <f>[1]Main!L56</f>
+        <f>[1]Main!L85</f>
         <v>0</v>
       </c>
       <c r="C56" s="1" t="str">
-        <f>IF(EXACT([1]Main!D56, ""), "", [1]Main!D56)</f>
+        <f>IF(EXACT([1]Main!D85, ""), "", [1]Main!D85)</f>
         <v/>
       </c>
       <c r="D56" s="1">
-        <f>[1]Main!M56</f>
+        <f>[1]Main!M85</f>
         <v>0</v>
       </c>
       <c r="E56" s="1" t="str">
@@ -4864,15 +6183,15 @@
     </row>
     <row r="57" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B57" s="1">
-        <f>[1]Main!L57</f>
+        <f>[1]Main!L87</f>
         <v>0</v>
       </c>
       <c r="C57" s="1" t="str">
-        <f>IF(EXACT([1]Main!D57, ""), "", [1]Main!D57)</f>
+        <f>IF(EXACT([1]Main!D87, ""), "", [1]Main!D87)</f>
         <v/>
       </c>
       <c r="D57" s="1">
-        <f>[1]Main!M57</f>
+        <f>[1]Main!M87</f>
         <v>0</v>
       </c>
       <c r="E57" s="1" t="str">
@@ -4897,15 +6216,15 @@
     </row>
     <row r="58" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B58" s="1">
-        <f>[1]Main!L58</f>
+        <f>[1]Main!L88</f>
         <v>0</v>
       </c>
       <c r="C58" s="1" t="str">
-        <f>IF(EXACT([1]Main!D58, ""), "", [1]Main!D58)</f>
+        <f>IF(EXACT([1]Main!D88, ""), "", [1]Main!D88)</f>
         <v/>
       </c>
       <c r="D58" s="1">
-        <f>[1]Main!M58</f>
+        <f>[1]Main!M88</f>
         <v>0</v>
       </c>
       <c r="E58" s="1" t="str">
@@ -4930,15 +6249,15 @@
     </row>
     <row r="59" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B59" s="1">
-        <f>[1]Main!L59</f>
+        <f>[1]Main!L86</f>
         <v>0</v>
       </c>
       <c r="C59" s="1" t="str">
-        <f>IF(EXACT([1]Main!D59, ""), "", [1]Main!D59)</f>
+        <f>IF(EXACT([1]Main!D86, ""), "", [1]Main!D86)</f>
         <v/>
       </c>
       <c r="D59" s="1">
-        <f>[1]Main!M59</f>
+        <f>[1]Main!M86</f>
         <v>0</v>
       </c>
       <c r="E59" s="1" t="str">
@@ -4963,15 +6282,15 @@
     </row>
     <row r="60" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B60" s="1">
-        <f>[1]Main!L60</f>
+        <f>[1]Main!L89</f>
         <v>0</v>
       </c>
       <c r="C60" s="1" t="str">
-        <f>IF(EXACT([1]Main!D60, ""), "", [1]Main!D60)</f>
+        <f>IF(EXACT([1]Main!D89, ""), "", [1]Main!D89)</f>
         <v/>
       </c>
       <c r="D60" s="1">
-        <f>[1]Main!M60</f>
+        <f>[1]Main!M89</f>
         <v>0</v>
       </c>
       <c r="E60" s="1" t="str">
@@ -4996,15 +6315,15 @@
     </row>
     <row r="61" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B61" s="1">
-        <f>[1]Main!L61</f>
+        <f>[1]Main!L90</f>
         <v>0</v>
       </c>
       <c r="C61" s="1" t="str">
-        <f>IF(EXACT([1]Main!D61, ""), "", [1]Main!D61)</f>
+        <f>IF(EXACT([1]Main!D90, ""), "", [1]Main!D90)</f>
         <v/>
       </c>
       <c r="D61" s="1">
-        <f>[1]Main!M61</f>
+        <f>[1]Main!M90</f>
         <v>0</v>
       </c>
       <c r="E61" s="1" t="str">
@@ -5029,15 +6348,15 @@
     </row>
     <row r="62" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B62" s="1">
-        <f>[1]Main!L62</f>
+        <f>[1]Main!L91</f>
         <v>0</v>
       </c>
       <c r="C62" s="1" t="str">
-        <f>IF(EXACT([1]Main!D62, ""), "", [1]Main!D62)</f>
+        <f>IF(EXACT([1]Main!D91, ""), "", [1]Main!D91)</f>
         <v/>
       </c>
       <c r="D62" s="1">
-        <f>[1]Main!M62</f>
+        <f>[1]Main!M91</f>
         <v>0</v>
       </c>
       <c r="E62" s="1" t="str">

--- a/Documentation/Documents/SQL Generator/Data Initial/SysConfig.TblAppObject_MenuGroupMember.xlsx
+++ b/Documentation/Documents/SQL Generator/Data Initial/SysConfig.TblAppObject_MenuGroupMember.xlsx
@@ -1670,7 +1670,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:I98"/>
+  <dimension ref="B1:K98"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.140625" style="2" customWidth="1"/>
@@ -1683,13 +1683,13 @@
     <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B1" s="5" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="5"/>
     </row>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B2" s="6">
         <f>[1]Main!$E2</f>
         <v>97000000000001</v>
@@ -1716,8 +1716,25 @@
         <f>IF(EXACT(G2, ""), "", CONCATENATE("PERFORM ""SchSysConfig"".""Func_TblAppObject_MenuGroupMember_SET""(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, ", G2, "::bigint, ", B2, "::bigint);"))</f>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000001::bigint, 97000000000001::bigint);</v>
       </c>
-    </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K2" s="2" t="str">
+        <f>CONCATENATE(
+"varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT (",
+"'recordID', NULL::bigint,", "'entities', ", "JSON_BUILD_OBJECT (",
+"'sysLoginSession_RefID', varSystemLoginSession::bigint,",
+"'sysDataAnnotation', NULL::varchar,",
+"'sysDataSetDateTimeTZ', NULL::timestamptz,",
+"'sysDataValidityStartDateTimeTZ', NULL::timestamptz,",
+"'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,",
+"'sysPartitionRemovableRecordKey_RefID', NULL::bigint,",
+"'sysBranch_RefID', varInstitutionBranchID::bigint,",
+"'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,",
+"'name', ", IF(EXACT($G2, ""), "null", CONCATENATE("'", SUBSTITUTE($G2, "'", "\'"), "'")), "::varchar,",
+"'iconSource', ", IF(EXACT($B2, ""), "null", CONCATENATE("'", SUBSTITUTE($B2, "'", "\'"), "'")), "::varchar",
+")))::varchar;")</f>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000001'::varchar,'iconSource', '97000000000001'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="3" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B3" s="6">
         <f>[1]Main!$E3</f>
         <v>97000000000002</v>
@@ -1744,8 +1761,25 @@
         <f t="shared" ref="I3:I66" si="0">IF(EXACT(G3, ""), "", CONCATENATE("PERFORM ""SchSysConfig"".""Func_TblAppObject_MenuGroupMember_SET""(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, ", G3, "::bigint, ", B3, "::bigint);"))</f>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000001::bigint, 97000000000002::bigint);</v>
       </c>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K3" s="2" t="str">
+        <f t="shared" ref="K3:K66" si="1">CONCATENATE(
+"varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT (",
+"'recordID', NULL::bigint,", "'entities', ", "JSON_BUILD_OBJECT (",
+"'sysLoginSession_RefID', varSystemLoginSession::bigint,",
+"'sysDataAnnotation', NULL::varchar,",
+"'sysDataSetDateTimeTZ', NULL::timestamptz,",
+"'sysDataValidityStartDateTimeTZ', NULL::timestamptz,",
+"'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,",
+"'sysPartitionRemovableRecordKey_RefID', NULL::bigint,",
+"'sysBranch_RefID', varInstitutionBranchID::bigint,",
+"'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,",
+"'name', ", IF(EXACT($G3, ""), "null", CONCATENATE("'", SUBSTITUTE($G3, "'", "\'"), "'")), "::varchar,",
+"'iconSource', ", IF(EXACT($B3, ""), "null", CONCATENATE("'", SUBSTITUTE($B3, "'", "\'"), "'")), "::varchar",
+")))::varchar;")</f>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000001'::varchar,'iconSource', '97000000000002'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="4" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B4" s="6">
         <f>[1]Main!$E4</f>
         <v>97000000000003</v>
@@ -1772,8 +1806,12 @@
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000001::bigint, 97000000000003::bigint);</v>
       </c>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K4" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000001'::varchar,'iconSource', '97000000000003'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="5" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B5" s="6">
         <f>[1]Main!$E5</f>
         <v>97000000000004</v>
@@ -1800,8 +1838,12 @@
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000001::bigint, 97000000000004::bigint);</v>
       </c>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K5" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000001'::varchar,'iconSource', '97000000000004'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B6" s="6">
         <f>[1]Main!$E6</f>
         <v>97000000000005</v>
@@ -1828,8 +1870,12 @@
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000001::bigint, 97000000000005::bigint);</v>
       </c>
-    </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K6" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000001'::varchar,'iconSource', '97000000000005'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="7" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B7" s="6">
         <f>[1]Main!$E7</f>
         <v>97000000000006</v>
@@ -1856,8 +1902,12 @@
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000001::bigint, 97000000000006::bigint);</v>
       </c>
-    </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K7" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000001'::varchar,'iconSource', '97000000000006'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="8" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B8" s="6">
         <f>[1]Main!$E8</f>
         <v>97000000000007</v>
@@ -1884,8 +1934,12 @@
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000001::bigint, 97000000000007::bigint);</v>
       </c>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K8" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000001'::varchar,'iconSource', '97000000000007'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="9" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B9" s="6">
         <f>[1]Main!$E9</f>
         <v>97000000000008</v>
@@ -1912,8 +1966,12 @@
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000002::bigint, 97000000000008::bigint);</v>
       </c>
-    </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K9" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000002'::varchar,'iconSource', '97000000000008'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="10" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B10" s="6">
         <f>[1]Main!$E10</f>
         <v>97000000000009</v>
@@ -1940,8 +1998,12 @@
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000002::bigint, 97000000000009::bigint);</v>
       </c>
-    </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K10" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000002'::varchar,'iconSource', '97000000000009'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="11" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B11" s="6">
         <f>[1]Main!$E11</f>
         <v>97000000000010</v>
@@ -1968,8 +2030,12 @@
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000002::bigint, 97000000000010::bigint);</v>
       </c>
-    </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K11" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000002'::varchar,'iconSource', '97000000000010'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="12" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B12" s="6">
         <f>[1]Main!$E12</f>
         <v>97000000000011</v>
@@ -1996,8 +2062,12 @@
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000002::bigint, 97000000000011::bigint);</v>
       </c>
-    </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K12" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000002'::varchar,'iconSource', '97000000000011'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="13" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B13" s="6">
         <f>[1]Main!$E13</f>
         <v>97000000000012</v>
@@ -2024,8 +2094,12 @@
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000002::bigint, 97000000000012::bigint);</v>
       </c>
-    </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K13" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000002'::varchar,'iconSource', '97000000000012'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="14" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B14" s="6">
         <f>[1]Main!$E14</f>
         <v>97000000000013</v>
@@ -2052,8 +2126,12 @@
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000002::bigint, 97000000000013::bigint);</v>
       </c>
-    </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K14" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000002'::varchar,'iconSource', '97000000000013'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="15" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B15" s="6">
         <f>[1]Main!$E15</f>
         <v>97000000000014</v>
@@ -2080,8 +2158,12 @@
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000002::bigint, 97000000000014::bigint);</v>
       </c>
-    </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K15" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000002'::varchar,'iconSource', '97000000000014'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="16" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B16" s="6">
         <f>[1]Main!$E16</f>
         <v>97000000000015</v>
@@ -2108,8 +2190,12 @@
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000002::bigint, 97000000000015::bigint);</v>
       </c>
-    </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K16" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000002'::varchar,'iconSource', '97000000000015'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="17" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B17" s="6">
         <f>[1]Main!$E17</f>
         <v>97000000000016</v>
@@ -2136,8 +2222,12 @@
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000002::bigint, 97000000000016::bigint);</v>
       </c>
-    </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K17" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000002'::varchar,'iconSource', '97000000000016'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="18" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B18" s="6">
         <f>[1]Main!$E18</f>
         <v>97000000000017</v>
@@ -2164,8 +2254,12 @@
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000002::bigint, 97000000000017::bigint);</v>
       </c>
-    </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K18" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000002'::varchar,'iconSource', '97000000000017'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="19" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B19" s="6">
         <f>[1]Main!$E19</f>
         <v>97000000000018</v>
@@ -2192,8 +2286,12 @@
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000002::bigint, 97000000000018::bigint);</v>
       </c>
-    </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K19" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000002'::varchar,'iconSource', '97000000000018'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="20" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B20" s="6">
         <f>[1]Main!$E20</f>
         <v>97000000000019</v>
@@ -2220,8 +2318,12 @@
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000004::bigint, 97000000000019::bigint);</v>
       </c>
-    </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K20" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000004'::varchar,'iconSource', '97000000000019'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="21" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B21" s="6">
         <f>[1]Main!$E21</f>
         <v>97000000000020</v>
@@ -2248,8 +2350,12 @@
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000004::bigint, 97000000000020::bigint);</v>
       </c>
-    </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K21" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000004'::varchar,'iconSource', '97000000000020'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="22" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B22" s="6">
         <f>[1]Main!$E22</f>
         <v>97000000000021</v>
@@ -2276,8 +2382,12 @@
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000004::bigint, 97000000000021::bigint);</v>
       </c>
-    </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K22" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000004'::varchar,'iconSource', '97000000000021'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="23" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B23" s="6">
         <f>[1]Main!$E23</f>
         <v>97000000000022</v>
@@ -2304,8 +2414,12 @@
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000004::bigint, 97000000000022::bigint);</v>
       </c>
-    </row>
-    <row r="24" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K23" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000004'::varchar,'iconSource', '97000000000022'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="24" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B24" s="6">
         <f>[1]Main!$E24</f>
         <v>97000000000023</v>
@@ -2332,8 +2446,12 @@
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000004::bigint, 97000000000023::bigint);</v>
       </c>
-    </row>
-    <row r="25" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K24" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000004'::varchar,'iconSource', '97000000000023'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="25" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B25" s="6">
         <f>[1]Main!$E25</f>
         <v>97000000000024</v>
@@ -2360,8 +2478,12 @@
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000004::bigint, 97000000000024::bigint);</v>
       </c>
-    </row>
-    <row r="26" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K25" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000004'::varchar,'iconSource', '97000000000024'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="26" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B26" s="6">
         <f>[1]Main!$E26</f>
         <v>97000000000025</v>
@@ -2388,8 +2510,12 @@
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000007::bigint, 97000000000025::bigint);</v>
       </c>
-    </row>
-    <row r="27" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K26" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000007'::varchar,'iconSource', '97000000000025'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="27" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B27" s="6">
         <f>[1]Main!$E27</f>
         <v>97000000000026</v>
@@ -2416,8 +2542,12 @@
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000007::bigint, 97000000000026::bigint);</v>
       </c>
-    </row>
-    <row r="28" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K27" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000007'::varchar,'iconSource', '97000000000026'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="28" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B28" s="6">
         <f>[1]Main!$E28</f>
         <v>97000000000027</v>
@@ -2444,8 +2574,12 @@
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000007::bigint, 97000000000027::bigint);</v>
       </c>
-    </row>
-    <row r="29" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K28" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000007'::varchar,'iconSource', '97000000000027'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="29" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B29" s="6">
         <f>[1]Main!$E29</f>
         <v>97000000000028</v>
@@ -2472,8 +2606,12 @@
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000007::bigint, 97000000000028::bigint);</v>
       </c>
-    </row>
-    <row r="30" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K29" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000007'::varchar,'iconSource', '97000000000028'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="30" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B30" s="6">
         <f>[1]Main!$E30</f>
         <v>97000000000029</v>
@@ -2500,8 +2638,12 @@
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000007::bigint, 97000000000029::bigint);</v>
       </c>
-    </row>
-    <row r="31" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K30" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000007'::varchar,'iconSource', '97000000000029'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="31" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B31" s="6">
         <f>[1]Main!$E31</f>
         <v>97000000000030</v>
@@ -2528,8 +2670,12 @@
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000007::bigint, 97000000000030::bigint);</v>
       </c>
-    </row>
-    <row r="32" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K31" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000007'::varchar,'iconSource', '97000000000030'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="32" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B32" s="6">
         <f>[1]Main!$E32</f>
         <v>97000000000031</v>
@@ -2556,8 +2702,12 @@
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000007::bigint, 97000000000031::bigint);</v>
       </c>
-    </row>
-    <row r="33" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K32" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000007'::varchar,'iconSource', '97000000000031'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B33" s="6">
         <f>[1]Main!$E33</f>
         <v>97000000000032</v>
@@ -2584,8 +2734,12 @@
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000007::bigint, 97000000000032::bigint);</v>
       </c>
-    </row>
-    <row r="34" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K33" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000007'::varchar,'iconSource', '97000000000032'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B34" s="6">
         <f>[1]Main!$E34</f>
         <v>97000000000033</v>
@@ -2612,8 +2766,12 @@
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000007::bigint, 97000000000033::bigint);</v>
       </c>
-    </row>
-    <row r="35" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K34" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000007'::varchar,'iconSource', '97000000000033'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B35" s="6">
         <f>[1]Main!$E35</f>
         <v>97000000000034</v>
@@ -2640,8 +2798,12 @@
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000009::bigint, 97000000000034::bigint);</v>
       </c>
-    </row>
-    <row r="36" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K35" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000009'::varchar,'iconSource', '97000000000034'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="36" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B36" s="6">
         <f>[1]Main!$E36</f>
         <v>97000000000035</v>
@@ -2668,8 +2830,12 @@
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000009::bigint, 97000000000035::bigint);</v>
       </c>
-    </row>
-    <row r="37" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K36" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000009'::varchar,'iconSource', '97000000000035'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B37" s="6">
         <f>[1]Main!$E37</f>
         <v>97000000000036</v>
@@ -2696,8 +2862,12 @@
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000009::bigint, 97000000000036::bigint);</v>
       </c>
-    </row>
-    <row r="38" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K37" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000009'::varchar,'iconSource', '97000000000036'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B38" s="6">
         <f>[1]Main!$E38</f>
         <v>97000000000037</v>
@@ -2724,8 +2894,12 @@
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000009::bigint, 97000000000037::bigint);</v>
       </c>
-    </row>
-    <row r="39" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K38" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000009'::varchar,'iconSource', '97000000000037'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B39" s="6">
         <f>[1]Main!$E39</f>
         <v>97000000000038</v>
@@ -2752,8 +2926,12 @@
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000009::bigint, 97000000000038::bigint);</v>
       </c>
-    </row>
-    <row r="40" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K39" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000009'::varchar,'iconSource', '97000000000038'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B40" s="6">
         <f>[1]Main!$E40</f>
         <v>97000000000039</v>
@@ -2780,8 +2958,12 @@
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000009::bigint, 97000000000039::bigint);</v>
       </c>
-    </row>
-    <row r="41" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K40" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000009'::varchar,'iconSource', '97000000000039'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B41" s="6">
         <f>[1]Main!$E41</f>
         <v>97000000000040</v>
@@ -2808,8 +2990,12 @@
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000009::bigint, 97000000000040::bigint);</v>
       </c>
-    </row>
-    <row r="42" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K41" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000009'::varchar,'iconSource', '97000000000040'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B42" s="6">
         <f>[1]Main!$E42</f>
         <v>97000000000041</v>
@@ -2836,8 +3022,12 @@
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000009::bigint, 97000000000041::bigint);</v>
       </c>
-    </row>
-    <row r="43" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K42" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000009'::varchar,'iconSource', '97000000000041'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B43" s="6">
         <f>[1]Main!$E43</f>
         <v>97000000000042</v>
@@ -2864,8 +3054,12 @@
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000009::bigint, 97000000000042::bigint);</v>
       </c>
-    </row>
-    <row r="44" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K43" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000009'::varchar,'iconSource', '97000000000042'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B44" s="6">
         <f>[1]Main!$E44</f>
         <v>97000000000043</v>
@@ -2892,8 +3086,12 @@
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000009::bigint, 97000000000043::bigint);</v>
       </c>
-    </row>
-    <row r="45" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K44" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000009'::varchar,'iconSource', '97000000000043'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B45" s="6">
         <f>[1]Main!$E45</f>
         <v>97000000000044</v>
@@ -2920,8 +3118,12 @@
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000009::bigint, 97000000000044::bigint);</v>
       </c>
-    </row>
-    <row r="46" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K45" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000009'::varchar,'iconSource', '97000000000044'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B46" s="6">
         <f>[1]Main!$E46</f>
         <v>97000000000045</v>
@@ -2948,8 +3150,12 @@
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000008::bigint, 97000000000045::bigint);</v>
       </c>
-    </row>
-    <row r="47" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K46" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000008'::varchar,'iconSource', '97000000000045'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B47" s="6">
         <f>[1]Main!$E47</f>
         <v>97000000000046</v>
@@ -2976,8 +3182,12 @@
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000008::bigint, 97000000000046::bigint);</v>
       </c>
-    </row>
-    <row r="48" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K47" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000008'::varchar,'iconSource', '97000000000046'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B48" s="6">
         <f>[1]Main!$E48</f>
         <v>97000000000047</v>
@@ -3004,8 +3214,12 @@
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000008::bigint, 97000000000047::bigint);</v>
       </c>
-    </row>
-    <row r="49" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K48" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000008'::varchar,'iconSource', '97000000000047'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="49" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B49" s="6">
         <f>[1]Main!$E49</f>
         <v>97000000000048</v>
@@ -3032,8 +3246,12 @@
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000008::bigint, 97000000000048::bigint);</v>
       </c>
-    </row>
-    <row r="50" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K49" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000008'::varchar,'iconSource', '97000000000048'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="50" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B50" s="6">
         <f>[1]Main!$E50</f>
         <v>97000000000049</v>
@@ -3060,8 +3278,12 @@
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000008::bigint, 97000000000049::bigint);</v>
       </c>
-    </row>
-    <row r="51" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K50" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000008'::varchar,'iconSource', '97000000000049'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="51" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B51" s="6">
         <f>[1]Main!$E51</f>
         <v>97000000000050</v>
@@ -3088,8 +3310,12 @@
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000008::bigint, 97000000000050::bigint);</v>
       </c>
-    </row>
-    <row r="52" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K51" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000008'::varchar,'iconSource', '97000000000050'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="52" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B52" s="6">
         <f>[1]Main!$E52</f>
         <v>97000000000051</v>
@@ -3116,8 +3342,12 @@
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000008::bigint, 97000000000051::bigint);</v>
       </c>
-    </row>
-    <row r="53" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K52" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000008'::varchar,'iconSource', '97000000000051'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="53" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B53" s="6">
         <f>[1]Main!$E53</f>
         <v>97000000000052</v>
@@ -3144,8 +3374,12 @@
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000008::bigint, 97000000000052::bigint);</v>
       </c>
-    </row>
-    <row r="54" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K53" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000008'::varchar,'iconSource', '97000000000052'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="54" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B54" s="6">
         <f>[1]Main!$E54</f>
         <v>97000000000053</v>
@@ -3172,8 +3406,12 @@
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000008::bigint, 97000000000053::bigint);</v>
       </c>
-    </row>
-    <row r="55" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K54" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000008'::varchar,'iconSource', '97000000000053'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="55" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B55" s="6">
         <f>[1]Main!$E55</f>
         <v>97000000000054</v>
@@ -3200,8 +3438,12 @@
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000008::bigint, 97000000000054::bigint);</v>
       </c>
-    </row>
-    <row r="56" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K55" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000008'::varchar,'iconSource', '97000000000054'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="56" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B56" s="6">
         <f>[1]Main!$E56</f>
         <v>97000000000055</v>
@@ -3228,8 +3470,12 @@
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000010::bigint, 97000000000055::bigint);</v>
       </c>
-    </row>
-    <row r="57" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K56" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000010'::varchar,'iconSource', '97000000000055'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="57" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B57" s="6">
         <f>[1]Main!$E57</f>
         <v>97000000000056</v>
@@ -3256,8 +3502,12 @@
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000010::bigint, 97000000000056::bigint);</v>
       </c>
-    </row>
-    <row r="58" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K57" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000010'::varchar,'iconSource', '97000000000056'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="58" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B58" s="6">
         <f>[1]Main!$E58</f>
         <v>97000000000057</v>
@@ -3284,8 +3534,12 @@
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000010::bigint, 97000000000057::bigint);</v>
       </c>
-    </row>
-    <row r="59" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K58" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000010'::varchar,'iconSource', '97000000000057'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="59" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B59" s="6">
         <f>[1]Main!$E59</f>
         <v>97000000000058</v>
@@ -3312,8 +3566,12 @@
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000010::bigint, 97000000000058::bigint);</v>
       </c>
-    </row>
-    <row r="60" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K59" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000010'::varchar,'iconSource', '97000000000058'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="60" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B60" s="6">
         <f>[1]Main!$E60</f>
         <v>97000000000059</v>
@@ -3340,8 +3598,12 @@
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000010::bigint, 97000000000059::bigint);</v>
       </c>
-    </row>
-    <row r="61" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K60" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000010'::varchar,'iconSource', '97000000000059'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="61" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B61" s="6">
         <f>[1]Main!$E61</f>
         <v>97000000000060</v>
@@ -3368,8 +3630,12 @@
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000010::bigint, 97000000000060::bigint);</v>
       </c>
-    </row>
-    <row r="62" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K61" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000010'::varchar,'iconSource', '97000000000060'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="62" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B62" s="6">
         <f>[1]Main!$E62</f>
         <v>97000000000061</v>
@@ -3396,8 +3662,12 @@
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000010::bigint, 97000000000061::bigint);</v>
       </c>
-    </row>
-    <row r="63" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K62" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000010'::varchar,'iconSource', '97000000000061'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="63" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B63" s="6">
         <f>[1]Main!$E63</f>
         <v>97000000000062</v>
@@ -3424,8 +3694,12 @@
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000062::bigint);</v>
       </c>
-    </row>
-    <row r="64" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K63" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000006'::varchar,'iconSource', '97000000000062'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="64" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B64" s="6">
         <f>[1]Main!$E64</f>
         <v>97000000000063</v>
@@ -3452,8 +3726,12 @@
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000063::bigint);</v>
       </c>
-    </row>
-    <row r="65" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K64" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000006'::varchar,'iconSource', '97000000000063'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B65" s="6">
         <f>[1]Main!$E65</f>
         <v>97000000000064</v>
@@ -3480,8 +3758,12 @@
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000064::bigint);</v>
       </c>
-    </row>
-    <row r="66" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K65" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000006'::varchar,'iconSource', '97000000000064'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B66" s="6">
         <f>[1]Main!$E66</f>
         <v>97000000000065</v>
@@ -3508,8 +3790,12 @@
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000065::bigint);</v>
       </c>
-    </row>
-    <row r="67" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K66" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000006'::varchar,'iconSource', '97000000000065'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B67" s="6">
         <f>[1]Main!$E67</f>
         <v>97000000000066</v>
@@ -3533,11 +3819,28 @@
         <v>66</v>
       </c>
       <c r="I67" s="9" t="str">
-        <f t="shared" ref="I67:I98" si="1">IF(EXACT(G67, ""), "", CONCATENATE("PERFORM ""SchSysConfig"".""Func_TblAppObject_MenuGroupMember_SET""(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, ", G67, "::bigint, ", B67, "::bigint);"))</f>
+        <f t="shared" ref="I67:I98" si="2">IF(EXACT(G67, ""), "", CONCATENATE("PERFORM ""SchSysConfig"".""Func_TblAppObject_MenuGroupMember_SET""(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, ", G67, "::bigint, ", B67, "::bigint);"))</f>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000066::bigint);</v>
       </c>
-    </row>
-    <row r="68" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K67" s="2" t="str">
+        <f t="shared" ref="K67:K98" si="3">CONCATENATE(
+"varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT (",
+"'recordID', NULL::bigint,", "'entities', ", "JSON_BUILD_OBJECT (",
+"'sysLoginSession_RefID', varSystemLoginSession::bigint,",
+"'sysDataAnnotation', NULL::varchar,",
+"'sysDataSetDateTimeTZ', NULL::timestamptz,",
+"'sysDataValidityStartDateTimeTZ', NULL::timestamptz,",
+"'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,",
+"'sysPartitionRemovableRecordKey_RefID', NULL::bigint,",
+"'sysBranch_RefID', varInstitutionBranchID::bigint,",
+"'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,",
+"'name', ", IF(EXACT($G67, ""), "null", CONCATENATE("'", SUBSTITUTE($G67, "'", "\'"), "'")), "::varchar,",
+"'iconSource', ", IF(EXACT($B67, ""), "null", CONCATENATE("'", SUBSTITUTE($B67, "'", "\'"), "'")), "::varchar",
+")))::varchar;")</f>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000006'::varchar,'iconSource', '97000000000066'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B68" s="6">
         <f>[1]Main!$E68</f>
         <v>97000000000067</v>
@@ -3561,11 +3864,15 @@
         <v>67</v>
       </c>
       <c r="I68" s="9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000067::bigint);</v>
       </c>
-    </row>
-    <row r="69" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K68" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000006'::varchar,'iconSource', '97000000000067'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B69" s="6">
         <f>[1]Main!$E69</f>
         <v>97000000000068</v>
@@ -3589,11 +3896,15 @@
         <v>68</v>
       </c>
       <c r="I69" s="9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000068::bigint);</v>
       </c>
-    </row>
-    <row r="70" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K69" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000006'::varchar,'iconSource', '97000000000068'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B70" s="6">
         <f>[1]Main!$E70</f>
         <v>97000000000069</v>
@@ -3617,11 +3928,15 @@
         <v>69</v>
       </c>
       <c r="I70" s="9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000069::bigint);</v>
       </c>
-    </row>
-    <row r="71" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K70" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000006'::varchar,'iconSource', '97000000000069'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B71" s="6">
         <f>[1]Main!$E71</f>
         <v>97000000000070</v>
@@ -3645,11 +3960,15 @@
         <v>70</v>
       </c>
       <c r="I71" s="9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000070::bigint);</v>
       </c>
-    </row>
-    <row r="72" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K71" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000006'::varchar,'iconSource', '97000000000070'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B72" s="6">
         <f>[1]Main!$E72</f>
         <v>97000000000071</v>
@@ -3673,11 +3992,15 @@
         <v>71</v>
       </c>
       <c r="I72" s="9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000071::bigint);</v>
       </c>
-    </row>
-    <row r="73" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K72" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000006'::varchar,'iconSource', '97000000000071'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B73" s="6">
         <f>[1]Main!$E73</f>
         <v>97000000000072</v>
@@ -3701,11 +4024,15 @@
         <v>72</v>
       </c>
       <c r="I73" s="9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000072::bigint);</v>
       </c>
-    </row>
-    <row r="74" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K73" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000006'::varchar,'iconSource', '97000000000072'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B74" s="6">
         <f>[1]Main!$E74</f>
         <v>97000000000073</v>
@@ -3729,11 +4056,15 @@
         <v>73</v>
       </c>
       <c r="I74" s="9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000073::bigint);</v>
       </c>
-    </row>
-    <row r="75" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K74" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000006'::varchar,'iconSource', '97000000000073'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B75" s="6">
         <f>[1]Main!$E75</f>
         <v>97000000000074</v>
@@ -3757,11 +4088,15 @@
         <v>74</v>
       </c>
       <c r="I75" s="9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000074::bigint);</v>
       </c>
-    </row>
-    <row r="76" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K75" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000006'::varchar,'iconSource', '97000000000074'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B76" s="6">
         <f>[1]Main!$E76</f>
         <v>97000000000075</v>
@@ -3785,11 +4120,15 @@
         <v>75</v>
       </c>
       <c r="I76" s="9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000075::bigint);</v>
       </c>
-    </row>
-    <row r="77" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K76" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000006'::varchar,'iconSource', '97000000000075'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B77" s="6">
         <f>[1]Main!$E77</f>
         <v>97000000000076</v>
@@ -3813,11 +4152,15 @@
         <v>76</v>
       </c>
       <c r="I77" s="9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000076::bigint);</v>
       </c>
-    </row>
-    <row r="78" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K77" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000006'::varchar,'iconSource', '97000000000076'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="78" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B78" s="6">
         <f>[1]Main!$E78</f>
         <v>97000000000077</v>
@@ -3841,11 +4184,15 @@
         <v>77</v>
       </c>
       <c r="I78" s="9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000077::bigint);</v>
       </c>
-    </row>
-    <row r="79" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K78" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000006'::varchar,'iconSource', '97000000000077'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B79" s="6">
         <f>[1]Main!$E79</f>
         <v>97000000000078</v>
@@ -3869,11 +4216,15 @@
         <v>78</v>
       </c>
       <c r="I79" s="9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000078::bigint);</v>
       </c>
-    </row>
-    <row r="80" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K79" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000006'::varchar,'iconSource', '97000000000078'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B80" s="6">
         <f>[1]Main!$E80</f>
         <v>97000000000079</v>
@@ -3897,11 +4248,15 @@
         <v>79</v>
       </c>
       <c r="I80" s="9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000079::bigint);</v>
       </c>
-    </row>
-    <row r="81" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K80" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000006'::varchar,'iconSource', '97000000000079'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="81" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B81" s="6">
         <f>[1]Main!$E81</f>
         <v>97000000000080</v>
@@ -3925,11 +4280,15 @@
         <v>80</v>
       </c>
       <c r="I81" s="9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000080::bigint);</v>
       </c>
-    </row>
-    <row r="82" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K81" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000006'::varchar,'iconSource', '97000000000080'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="82" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B82" s="6">
         <f>[1]Main!$E82</f>
         <v>97000000000081</v>
@@ -3953,11 +4312,15 @@
         <v>81</v>
       </c>
       <c r="I82" s="9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000081::bigint);</v>
       </c>
-    </row>
-    <row r="83" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K82" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000006'::varchar,'iconSource', '97000000000081'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="83" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B83" s="6">
         <f>[1]Main!$E83</f>
         <v>97000000000082</v>
@@ -3981,11 +4344,15 @@
         <v>82</v>
       </c>
       <c r="I83" s="9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000082::bigint);</v>
       </c>
-    </row>
-    <row r="84" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K83" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000006'::varchar,'iconSource', '97000000000082'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="84" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B84" s="6">
         <f>[1]Main!$E84</f>
         <v>97000000000083</v>
@@ -4009,11 +4376,15 @@
         <v>83</v>
       </c>
       <c r="I84" s="9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000083::bigint);</v>
       </c>
-    </row>
-    <row r="85" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K84" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000006'::varchar,'iconSource', '97000000000083'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="85" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B85" s="6">
         <f>[1]Main!$E85</f>
         <v>97000000000084</v>
@@ -4037,11 +4408,15 @@
         <v>84</v>
       </c>
       <c r="I85" s="9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000084::bigint);</v>
       </c>
-    </row>
-    <row r="86" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K85" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000006'::varchar,'iconSource', '97000000000084'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="86" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B86" s="6">
         <f>[1]Main!$E86</f>
         <v>97000000000085</v>
@@ -4065,11 +4440,15 @@
         <v>85</v>
       </c>
       <c r="I86" s="9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000085::bigint);</v>
       </c>
-    </row>
-    <row r="87" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K86" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000006'::varchar,'iconSource', '97000000000085'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="87" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B87" s="6">
         <f>[1]Main!$E87</f>
         <v>97000000000086</v>
@@ -4093,11 +4472,15 @@
         <v>86</v>
       </c>
       <c r="I87" s="9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000086::bigint);</v>
       </c>
-    </row>
-    <row r="88" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K87" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000006'::varchar,'iconSource', '97000000000086'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="88" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B88" s="6">
         <f>[1]Main!$E88</f>
         <v>97000000000087</v>
@@ -4121,11 +4504,15 @@
         <v>87</v>
       </c>
       <c r="I88" s="9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000087::bigint);</v>
       </c>
-    </row>
-    <row r="89" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K88" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000006'::varchar,'iconSource', '97000000000087'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="89" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B89" s="6">
         <f>[1]Main!$E89</f>
         <v>97000000000088</v>
@@ -4149,11 +4536,15 @@
         <v>88</v>
       </c>
       <c r="I89" s="9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000088::bigint);</v>
       </c>
-    </row>
-    <row r="90" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K89" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000006'::varchar,'iconSource', '97000000000088'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="90" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B90" s="6">
         <f>[1]Main!$E90</f>
         <v>97000000000089</v>
@@ -4177,11 +4568,15 @@
         <v>89</v>
       </c>
       <c r="I90" s="9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000089::bigint);</v>
       </c>
-    </row>
-    <row r="91" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K90" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000006'::varchar,'iconSource', '97000000000089'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="91" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B91" s="6">
         <f>[1]Main!$E91</f>
         <v>97000000000090</v>
@@ -4205,11 +4600,15 @@
         <v>90</v>
       </c>
       <c r="I91" s="9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000090::bigint);</v>
       </c>
-    </row>
-    <row r="92" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K91" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000006'::varchar,'iconSource', '97000000000090'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="92" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B92" s="6">
         <f>[1]Main!$E92</f>
         <v>97000000000091</v>
@@ -4233,11 +4632,15 @@
         <v>91</v>
       </c>
       <c r="I92" s="9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000091::bigint);</v>
       </c>
-    </row>
-    <row r="93" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K92" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000006'::varchar,'iconSource', '97000000000091'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="93" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B93" s="6">
         <f>[1]Main!$E93</f>
         <v>97000000000092</v>
@@ -4261,11 +4664,15 @@
         <v>92</v>
       </c>
       <c r="I93" s="9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000092::bigint);</v>
       </c>
-    </row>
-    <row r="94" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K93" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000006'::varchar,'iconSource', '97000000000092'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="94" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B94" s="6">
         <f>[1]Main!$E94</f>
         <v>97000000000093</v>
@@ -4289,11 +4696,15 @@
         <v>93</v>
       </c>
       <c r="I94" s="9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000093::bigint);</v>
       </c>
-    </row>
-    <row r="95" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K94" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000006'::varchar,'iconSource', '97000000000093'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="95" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B95" s="6">
         <f>[1]Main!$E95</f>
         <v>97000000000094</v>
@@ -4317,11 +4728,15 @@
         <v>94</v>
       </c>
       <c r="I95" s="9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000094::bigint);</v>
       </c>
-    </row>
-    <row r="96" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K95" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000006'::varchar,'iconSource', '97000000000094'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="96" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B96" s="6">
         <f>[1]Main!$E96</f>
         <v>97000000000095</v>
@@ -4345,11 +4760,15 @@
         <v>95</v>
       </c>
       <c r="I96" s="9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000095::bigint);</v>
       </c>
-    </row>
-    <row r="97" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K96" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000006'::varchar,'iconSource', '97000000000095'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="97" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B97" s="6">
         <f>[1]Main!$E97</f>
         <v>97000000000096</v>
@@ -4373,11 +4792,15 @@
         <v>96</v>
       </c>
       <c r="I97" s="9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000096::bigint);</v>
       </c>
-    </row>
-    <row r="98" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K97" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000006'::varchar,'iconSource', '97000000000096'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="98" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B98" s="6">
         <f>[1]Main!$E98</f>
         <v>97000000000097</v>
@@ -4401,8 +4824,12 @@
         <v>97</v>
       </c>
       <c r="I98" s="9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000010::bigint, 97000000000097::bigint);</v>
+      </c>
+      <c r="K98" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000010'::varchar,'iconSource', '97000000000097'::varchar)))::varchar;</v>
       </c>
     </row>
   </sheetData>

--- a/Documentation/Documents/SQL Generator/Data Initial/SysConfig.TblAppObject_MenuGroupMember.xlsx
+++ b/Documentation/Documents/SQL Generator/Data Initial/SysConfig.TblAppObject_MenuGroupMember.xlsx
@@ -1728,10 +1728,10 @@
 "'sysPartitionRemovableRecordKey_RefID', NULL::bigint,",
 "'sysBranch_RefID', varInstitutionBranchID::bigint,",
 "'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,",
-"'name', ", IF(EXACT($G2, ""), "null", CONCATENATE("'", SUBSTITUTE($G2, "'", "\'"), "'")), "::varchar,",
-"'iconSource', ", IF(EXACT($B2, ""), "null", CONCATENATE("'", SUBSTITUTE($B2, "'", "\'"), "'")), "::varchar",
+"'menuGroup_RefID', ", IF(EXACT($G2, ""), "null", CONCATENATE("'", SUBSTITUTE($G2, "'", "\'"), "'")), "::bigint,",
+"'menu_RefID', ", IF(EXACT($B2, ""), "null", CONCATENATE("'", SUBSTITUTE($B2, "'", "\'"), "'")), "::bigint",
 ")))::varchar;")</f>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000001'::varchar,'iconSource', '97000000000001'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000001'::bigint,'menu_RefID', '97000000000001'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="3" spans="2:11" x14ac:dyDescent="0.2">
@@ -1773,10 +1773,10 @@
 "'sysPartitionRemovableRecordKey_RefID', NULL::bigint,",
 "'sysBranch_RefID', varInstitutionBranchID::bigint,",
 "'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,",
-"'name', ", IF(EXACT($G3, ""), "null", CONCATENATE("'", SUBSTITUTE($G3, "'", "\'"), "'")), "::varchar,",
-"'iconSource', ", IF(EXACT($B3, ""), "null", CONCATENATE("'", SUBSTITUTE($B3, "'", "\'"), "'")), "::varchar",
+"'menuGroup_RefID', ", IF(EXACT($G3, ""), "null", CONCATENATE("'", SUBSTITUTE($G3, "'", "\'"), "'")), "::bigint,",
+"'menu_RefID', ", IF(EXACT($B3, ""), "null", CONCATENATE("'", SUBSTITUTE($B3, "'", "\'"), "'")), "::bigint",
 ")))::varchar;")</f>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000001'::varchar,'iconSource', '97000000000002'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000001'::bigint,'menu_RefID', '97000000000002'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="4" spans="2:11" x14ac:dyDescent="0.2">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="K4" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000001'::varchar,'iconSource', '97000000000003'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000001'::bigint,'menu_RefID', '97000000000003'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.2">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="K5" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000001'::varchar,'iconSource', '97000000000004'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000001'::bigint,'menu_RefID', '97000000000004'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.2">
@@ -1872,7 +1872,7 @@
       </c>
       <c r="K6" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000001'::varchar,'iconSource', '97000000000005'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000001'::bigint,'menu_RefID', '97000000000005'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="7" spans="2:11" x14ac:dyDescent="0.2">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="K7" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000001'::varchar,'iconSource', '97000000000006'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000001'::bigint,'menu_RefID', '97000000000006'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.2">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="K8" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000001'::varchar,'iconSource', '97000000000007'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000001'::bigint,'menu_RefID', '97000000000007'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.2">
@@ -1968,7 +1968,7 @@
       </c>
       <c r="K9" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000002'::varchar,'iconSource', '97000000000008'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000002'::bigint,'menu_RefID', '97000000000008'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.2">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="K10" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000002'::varchar,'iconSource', '97000000000009'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000002'::bigint,'menu_RefID', '97000000000009'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.2">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="K11" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000002'::varchar,'iconSource', '97000000000010'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000002'::bigint,'menu_RefID', '97000000000010'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.2">
@@ -2064,7 +2064,7 @@
       </c>
       <c r="K12" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000002'::varchar,'iconSource', '97000000000011'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000002'::bigint,'menu_RefID', '97000000000011'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.2">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="K13" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000002'::varchar,'iconSource', '97000000000012'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000002'::bigint,'menu_RefID', '97000000000012'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="14" spans="2:11" x14ac:dyDescent="0.2">
@@ -2128,7 +2128,7 @@
       </c>
       <c r="K14" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000002'::varchar,'iconSource', '97000000000013'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000002'::bigint,'menu_RefID', '97000000000013'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.2">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="K15" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000002'::varchar,'iconSource', '97000000000014'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000002'::bigint,'menu_RefID', '97000000000014'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.2">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="K16" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000002'::varchar,'iconSource', '97000000000015'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000002'::bigint,'menu_RefID', '97000000000015'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.2">
@@ -2224,7 +2224,7 @@
       </c>
       <c r="K17" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000002'::varchar,'iconSource', '97000000000016'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000002'::bigint,'menu_RefID', '97000000000016'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.2">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="K18" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000002'::varchar,'iconSource', '97000000000017'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000002'::bigint,'menu_RefID', '97000000000017'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.2">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="K19" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000002'::varchar,'iconSource', '97000000000018'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000002'::bigint,'menu_RefID', '97000000000018'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="20" spans="2:11" x14ac:dyDescent="0.2">
@@ -2320,7 +2320,7 @@
       </c>
       <c r="K20" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000004'::varchar,'iconSource', '97000000000019'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000004'::bigint,'menu_RefID', '97000000000019'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="21" spans="2:11" x14ac:dyDescent="0.2">
@@ -2352,7 +2352,7 @@
       </c>
       <c r="K21" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000004'::varchar,'iconSource', '97000000000020'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000004'::bigint,'menu_RefID', '97000000000020'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="22" spans="2:11" x14ac:dyDescent="0.2">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="K22" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000004'::varchar,'iconSource', '97000000000021'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000004'::bigint,'menu_RefID', '97000000000021'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="23" spans="2:11" x14ac:dyDescent="0.2">
@@ -2416,7 +2416,7 @@
       </c>
       <c r="K23" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000004'::varchar,'iconSource', '97000000000022'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000004'::bigint,'menu_RefID', '97000000000022'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="24" spans="2:11" x14ac:dyDescent="0.2">
@@ -2448,7 +2448,7 @@
       </c>
       <c r="K24" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000004'::varchar,'iconSource', '97000000000023'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000004'::bigint,'menu_RefID', '97000000000023'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="25" spans="2:11" x14ac:dyDescent="0.2">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="K25" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000004'::varchar,'iconSource', '97000000000024'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000004'::bigint,'menu_RefID', '97000000000024'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="26" spans="2:11" x14ac:dyDescent="0.2">
@@ -2512,7 +2512,7 @@
       </c>
       <c r="K26" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000007'::varchar,'iconSource', '97000000000025'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000007'::bigint,'menu_RefID', '97000000000025'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="27" spans="2:11" x14ac:dyDescent="0.2">
@@ -2544,7 +2544,7 @@
       </c>
       <c r="K27" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000007'::varchar,'iconSource', '97000000000026'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000007'::bigint,'menu_RefID', '97000000000026'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="28" spans="2:11" x14ac:dyDescent="0.2">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="K28" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000007'::varchar,'iconSource', '97000000000027'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000007'::bigint,'menu_RefID', '97000000000027'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="29" spans="2:11" x14ac:dyDescent="0.2">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="K29" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000007'::varchar,'iconSource', '97000000000028'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000007'::bigint,'menu_RefID', '97000000000028'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="30" spans="2:11" x14ac:dyDescent="0.2">
@@ -2640,7 +2640,7 @@
       </c>
       <c r="K30" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000007'::varchar,'iconSource', '97000000000029'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000007'::bigint,'menu_RefID', '97000000000029'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="31" spans="2:11" x14ac:dyDescent="0.2">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="K31" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000007'::varchar,'iconSource', '97000000000030'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000007'::bigint,'menu_RefID', '97000000000030'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="32" spans="2:11" x14ac:dyDescent="0.2">
@@ -2704,7 +2704,7 @@
       </c>
       <c r="K32" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000007'::varchar,'iconSource', '97000000000031'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000007'::bigint,'menu_RefID', '97000000000031'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="33" spans="2:11" x14ac:dyDescent="0.2">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="K33" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000007'::varchar,'iconSource', '97000000000032'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000007'::bigint,'menu_RefID', '97000000000032'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="34" spans="2:11" x14ac:dyDescent="0.2">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="K34" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000007'::varchar,'iconSource', '97000000000033'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000007'::bigint,'menu_RefID', '97000000000033'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="35" spans="2:11" x14ac:dyDescent="0.2">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="K35" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000009'::varchar,'iconSource', '97000000000034'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000009'::bigint,'menu_RefID', '97000000000034'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="36" spans="2:11" x14ac:dyDescent="0.2">
@@ -2832,7 +2832,7 @@
       </c>
       <c r="K36" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000009'::varchar,'iconSource', '97000000000035'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000009'::bigint,'menu_RefID', '97000000000035'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="37" spans="2:11" x14ac:dyDescent="0.2">
@@ -2864,7 +2864,7 @@
       </c>
       <c r="K37" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000009'::varchar,'iconSource', '97000000000036'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000009'::bigint,'menu_RefID', '97000000000036'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="38" spans="2:11" x14ac:dyDescent="0.2">
@@ -2896,7 +2896,7 @@
       </c>
       <c r="K38" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000009'::varchar,'iconSource', '97000000000037'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000009'::bigint,'menu_RefID', '97000000000037'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="39" spans="2:11" x14ac:dyDescent="0.2">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="K39" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000009'::varchar,'iconSource', '97000000000038'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000009'::bigint,'menu_RefID', '97000000000038'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="40" spans="2:11" x14ac:dyDescent="0.2">
@@ -2960,7 +2960,7 @@
       </c>
       <c r="K40" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000009'::varchar,'iconSource', '97000000000039'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000009'::bigint,'menu_RefID', '97000000000039'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="41" spans="2:11" x14ac:dyDescent="0.2">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="K41" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000009'::varchar,'iconSource', '97000000000040'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000009'::bigint,'menu_RefID', '97000000000040'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="42" spans="2:11" x14ac:dyDescent="0.2">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="K42" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000009'::varchar,'iconSource', '97000000000041'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000009'::bigint,'menu_RefID', '97000000000041'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="43" spans="2:11" x14ac:dyDescent="0.2">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="K43" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000009'::varchar,'iconSource', '97000000000042'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000009'::bigint,'menu_RefID', '97000000000042'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="44" spans="2:11" x14ac:dyDescent="0.2">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="K44" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000009'::varchar,'iconSource', '97000000000043'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000009'::bigint,'menu_RefID', '97000000000043'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="45" spans="2:11" x14ac:dyDescent="0.2">
@@ -3120,7 +3120,7 @@
       </c>
       <c r="K45" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000009'::varchar,'iconSource', '97000000000044'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000009'::bigint,'menu_RefID', '97000000000044'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="46" spans="2:11" x14ac:dyDescent="0.2">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="K46" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000008'::varchar,'iconSource', '97000000000045'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000008'::bigint,'menu_RefID', '97000000000045'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="47" spans="2:11" x14ac:dyDescent="0.2">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="K47" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000008'::varchar,'iconSource', '97000000000046'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000008'::bigint,'menu_RefID', '97000000000046'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="48" spans="2:11" x14ac:dyDescent="0.2">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="K48" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000008'::varchar,'iconSource', '97000000000047'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000008'::bigint,'menu_RefID', '97000000000047'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="49" spans="2:11" x14ac:dyDescent="0.2">
@@ -3248,7 +3248,7 @@
       </c>
       <c r="K49" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000008'::varchar,'iconSource', '97000000000048'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000008'::bigint,'menu_RefID', '97000000000048'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="50" spans="2:11" x14ac:dyDescent="0.2">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="K50" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000008'::varchar,'iconSource', '97000000000049'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000008'::bigint,'menu_RefID', '97000000000049'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="51" spans="2:11" x14ac:dyDescent="0.2">
@@ -3312,7 +3312,7 @@
       </c>
       <c r="K51" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000008'::varchar,'iconSource', '97000000000050'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000008'::bigint,'menu_RefID', '97000000000050'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="52" spans="2:11" x14ac:dyDescent="0.2">
@@ -3344,7 +3344,7 @@
       </c>
       <c r="K52" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000008'::varchar,'iconSource', '97000000000051'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000008'::bigint,'menu_RefID', '97000000000051'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="53" spans="2:11" x14ac:dyDescent="0.2">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="K53" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000008'::varchar,'iconSource', '97000000000052'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000008'::bigint,'menu_RefID', '97000000000052'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="54" spans="2:11" x14ac:dyDescent="0.2">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="K54" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000008'::varchar,'iconSource', '97000000000053'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000008'::bigint,'menu_RefID', '97000000000053'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="55" spans="2:11" x14ac:dyDescent="0.2">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="K55" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000008'::varchar,'iconSource', '97000000000054'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000008'::bigint,'menu_RefID', '97000000000054'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="56" spans="2:11" x14ac:dyDescent="0.2">
@@ -3472,7 +3472,7 @@
       </c>
       <c r="K56" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000010'::varchar,'iconSource', '97000000000055'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000010'::bigint,'menu_RefID', '97000000000055'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="57" spans="2:11" x14ac:dyDescent="0.2">
@@ -3504,7 +3504,7 @@
       </c>
       <c r="K57" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000010'::varchar,'iconSource', '97000000000056'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000010'::bigint,'menu_RefID', '97000000000056'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="58" spans="2:11" x14ac:dyDescent="0.2">
@@ -3536,7 +3536,7 @@
       </c>
       <c r="K58" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000010'::varchar,'iconSource', '97000000000057'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000010'::bigint,'menu_RefID', '97000000000057'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="59" spans="2:11" x14ac:dyDescent="0.2">
@@ -3568,7 +3568,7 @@
       </c>
       <c r="K59" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000010'::varchar,'iconSource', '97000000000058'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000010'::bigint,'menu_RefID', '97000000000058'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="60" spans="2:11" x14ac:dyDescent="0.2">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="K60" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000010'::varchar,'iconSource', '97000000000059'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000010'::bigint,'menu_RefID', '97000000000059'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="61" spans="2:11" x14ac:dyDescent="0.2">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="K61" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000010'::varchar,'iconSource', '97000000000060'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000010'::bigint,'menu_RefID', '97000000000060'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="62" spans="2:11" x14ac:dyDescent="0.2">
@@ -3664,7 +3664,7 @@
       </c>
       <c r="K62" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000010'::varchar,'iconSource', '97000000000061'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000010'::bigint,'menu_RefID', '97000000000061'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="63" spans="2:11" x14ac:dyDescent="0.2">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="K63" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000006'::varchar,'iconSource', '97000000000062'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000006'::bigint,'menu_RefID', '97000000000062'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="64" spans="2:11" x14ac:dyDescent="0.2">
@@ -3728,7 +3728,7 @@
       </c>
       <c r="K64" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000006'::varchar,'iconSource', '97000000000063'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000006'::bigint,'menu_RefID', '97000000000063'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="65" spans="2:11" x14ac:dyDescent="0.2">
@@ -3760,7 +3760,7 @@
       </c>
       <c r="K65" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000006'::varchar,'iconSource', '97000000000064'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000006'::bigint,'menu_RefID', '97000000000064'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="66" spans="2:11" x14ac:dyDescent="0.2">
@@ -3792,7 +3792,7 @@
       </c>
       <c r="K66" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000006'::varchar,'iconSource', '97000000000065'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000006'::bigint,'menu_RefID', '97000000000065'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="67" spans="2:11" x14ac:dyDescent="0.2">
@@ -3834,10 +3834,10 @@
 "'sysPartitionRemovableRecordKey_RefID', NULL::bigint,",
 "'sysBranch_RefID', varInstitutionBranchID::bigint,",
 "'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,",
-"'name', ", IF(EXACT($G67, ""), "null", CONCATENATE("'", SUBSTITUTE($G67, "'", "\'"), "'")), "::varchar,",
-"'iconSource', ", IF(EXACT($B67, ""), "null", CONCATENATE("'", SUBSTITUTE($B67, "'", "\'"), "'")), "::varchar",
+"'menuGroup_RefID', ", IF(EXACT($G67, ""), "null", CONCATENATE("'", SUBSTITUTE($G67, "'", "\'"), "'")), "::bigint,",
+"'menu_RefID', ", IF(EXACT($B67, ""), "null", CONCATENATE("'", SUBSTITUTE($B67, "'", "\'"), "'")), "::bigint",
 ")))::varchar;")</f>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000006'::varchar,'iconSource', '97000000000066'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000006'::bigint,'menu_RefID', '97000000000066'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="68" spans="2:11" x14ac:dyDescent="0.2">
@@ -3869,7 +3869,7 @@
       </c>
       <c r="K68" s="2" t="str">
         <f t="shared" si="3"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000006'::varchar,'iconSource', '97000000000067'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000006'::bigint,'menu_RefID', '97000000000067'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="69" spans="2:11" x14ac:dyDescent="0.2">
@@ -3901,7 +3901,7 @@
       </c>
       <c r="K69" s="2" t="str">
         <f t="shared" si="3"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000006'::varchar,'iconSource', '97000000000068'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000006'::bigint,'menu_RefID', '97000000000068'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="70" spans="2:11" x14ac:dyDescent="0.2">
@@ -3933,7 +3933,7 @@
       </c>
       <c r="K70" s="2" t="str">
         <f t="shared" si="3"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000006'::varchar,'iconSource', '97000000000069'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000006'::bigint,'menu_RefID', '97000000000069'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="71" spans="2:11" x14ac:dyDescent="0.2">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="K71" s="2" t="str">
         <f t="shared" si="3"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000006'::varchar,'iconSource', '97000000000070'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000006'::bigint,'menu_RefID', '97000000000070'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="72" spans="2:11" x14ac:dyDescent="0.2">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="K72" s="2" t="str">
         <f t="shared" si="3"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000006'::varchar,'iconSource', '97000000000071'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000006'::bigint,'menu_RefID', '97000000000071'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="73" spans="2:11" x14ac:dyDescent="0.2">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="K73" s="2" t="str">
         <f t="shared" si="3"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000006'::varchar,'iconSource', '97000000000072'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000006'::bigint,'menu_RefID', '97000000000072'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="74" spans="2:11" x14ac:dyDescent="0.2">
@@ -4061,7 +4061,7 @@
       </c>
       <c r="K74" s="2" t="str">
         <f t="shared" si="3"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000006'::varchar,'iconSource', '97000000000073'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000006'::bigint,'menu_RefID', '97000000000073'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="75" spans="2:11" x14ac:dyDescent="0.2">
@@ -4093,7 +4093,7 @@
       </c>
       <c r="K75" s="2" t="str">
         <f t="shared" si="3"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000006'::varchar,'iconSource', '97000000000074'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000006'::bigint,'menu_RefID', '97000000000074'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="76" spans="2:11" x14ac:dyDescent="0.2">
@@ -4125,7 +4125,7 @@
       </c>
       <c r="K76" s="2" t="str">
         <f t="shared" si="3"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000006'::varchar,'iconSource', '97000000000075'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000006'::bigint,'menu_RefID', '97000000000075'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="77" spans="2:11" x14ac:dyDescent="0.2">
@@ -4157,7 +4157,7 @@
       </c>
       <c r="K77" s="2" t="str">
         <f t="shared" si="3"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000006'::varchar,'iconSource', '97000000000076'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000006'::bigint,'menu_RefID', '97000000000076'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="78" spans="2:11" x14ac:dyDescent="0.2">
@@ -4189,7 +4189,7 @@
       </c>
       <c r="K78" s="2" t="str">
         <f t="shared" si="3"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000006'::varchar,'iconSource', '97000000000077'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000006'::bigint,'menu_RefID', '97000000000077'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="79" spans="2:11" x14ac:dyDescent="0.2">
@@ -4221,7 +4221,7 @@
       </c>
       <c r="K79" s="2" t="str">
         <f t="shared" si="3"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000006'::varchar,'iconSource', '97000000000078'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000006'::bigint,'menu_RefID', '97000000000078'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="80" spans="2:11" x14ac:dyDescent="0.2">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="K80" s="2" t="str">
         <f t="shared" si="3"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000006'::varchar,'iconSource', '97000000000079'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000006'::bigint,'menu_RefID', '97000000000079'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="81" spans="2:11" x14ac:dyDescent="0.2">
@@ -4285,7 +4285,7 @@
       </c>
       <c r="K81" s="2" t="str">
         <f t="shared" si="3"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000006'::varchar,'iconSource', '97000000000080'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000006'::bigint,'menu_RefID', '97000000000080'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="82" spans="2:11" x14ac:dyDescent="0.2">
@@ -4317,7 +4317,7 @@
       </c>
       <c r="K82" s="2" t="str">
         <f t="shared" si="3"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000006'::varchar,'iconSource', '97000000000081'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000006'::bigint,'menu_RefID', '97000000000081'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="83" spans="2:11" x14ac:dyDescent="0.2">
@@ -4349,7 +4349,7 @@
       </c>
       <c r="K83" s="2" t="str">
         <f t="shared" si="3"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000006'::varchar,'iconSource', '97000000000082'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000006'::bigint,'menu_RefID', '97000000000082'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="84" spans="2:11" x14ac:dyDescent="0.2">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="K84" s="2" t="str">
         <f t="shared" si="3"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000006'::varchar,'iconSource', '97000000000083'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000006'::bigint,'menu_RefID', '97000000000083'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="85" spans="2:11" x14ac:dyDescent="0.2">
@@ -4413,7 +4413,7 @@
       </c>
       <c r="K85" s="2" t="str">
         <f t="shared" si="3"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000006'::varchar,'iconSource', '97000000000084'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000006'::bigint,'menu_RefID', '97000000000084'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="86" spans="2:11" x14ac:dyDescent="0.2">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="K86" s="2" t="str">
         <f t="shared" si="3"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000006'::varchar,'iconSource', '97000000000085'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000006'::bigint,'menu_RefID', '97000000000085'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="87" spans="2:11" x14ac:dyDescent="0.2">
@@ -4477,7 +4477,7 @@
       </c>
       <c r="K87" s="2" t="str">
         <f t="shared" si="3"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000006'::varchar,'iconSource', '97000000000086'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000006'::bigint,'menu_RefID', '97000000000086'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="88" spans="2:11" x14ac:dyDescent="0.2">
@@ -4509,7 +4509,7 @@
       </c>
       <c r="K88" s="2" t="str">
         <f t="shared" si="3"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000006'::varchar,'iconSource', '97000000000087'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000006'::bigint,'menu_RefID', '97000000000087'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="89" spans="2:11" x14ac:dyDescent="0.2">
@@ -4541,7 +4541,7 @@
       </c>
       <c r="K89" s="2" t="str">
         <f t="shared" si="3"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000006'::varchar,'iconSource', '97000000000088'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000006'::bigint,'menu_RefID', '97000000000088'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="90" spans="2:11" x14ac:dyDescent="0.2">
@@ -4573,7 +4573,7 @@
       </c>
       <c r="K90" s="2" t="str">
         <f t="shared" si="3"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000006'::varchar,'iconSource', '97000000000089'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000006'::bigint,'menu_RefID', '97000000000089'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="91" spans="2:11" x14ac:dyDescent="0.2">
@@ -4605,7 +4605,7 @@
       </c>
       <c r="K91" s="2" t="str">
         <f t="shared" si="3"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000006'::varchar,'iconSource', '97000000000090'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000006'::bigint,'menu_RefID', '97000000000090'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="92" spans="2:11" x14ac:dyDescent="0.2">
@@ -4637,7 +4637,7 @@
       </c>
       <c r="K92" s="2" t="str">
         <f t="shared" si="3"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000006'::varchar,'iconSource', '97000000000091'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000006'::bigint,'menu_RefID', '97000000000091'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="93" spans="2:11" x14ac:dyDescent="0.2">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="K93" s="2" t="str">
         <f t="shared" si="3"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000006'::varchar,'iconSource', '97000000000092'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000006'::bigint,'menu_RefID', '97000000000092'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="94" spans="2:11" x14ac:dyDescent="0.2">
@@ -4701,7 +4701,7 @@
       </c>
       <c r="K94" s="2" t="str">
         <f t="shared" si="3"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000006'::varchar,'iconSource', '97000000000093'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000006'::bigint,'menu_RefID', '97000000000093'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="95" spans="2:11" x14ac:dyDescent="0.2">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="K95" s="2" t="str">
         <f t="shared" si="3"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000006'::varchar,'iconSource', '97000000000094'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000006'::bigint,'menu_RefID', '97000000000094'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="96" spans="2:11" x14ac:dyDescent="0.2">
@@ -4765,7 +4765,7 @@
       </c>
       <c r="K96" s="2" t="str">
         <f t="shared" si="3"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000006'::varchar,'iconSource', '97000000000095'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000006'::bigint,'menu_RefID', '97000000000095'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="97" spans="2:11" x14ac:dyDescent="0.2">
@@ -4797,7 +4797,7 @@
       </c>
       <c r="K97" s="2" t="str">
         <f t="shared" si="3"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000006'::varchar,'iconSource', '97000000000096'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000006'::bigint,'menu_RefID', '97000000000096'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="98" spans="2:11" x14ac:dyDescent="0.2">
@@ -4829,7 +4829,7 @@
       </c>
       <c r="K98" s="2" t="str">
         <f t="shared" si="3"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', '254000000000010'::varchar,'iconSource', '97000000000097'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000010'::bigint,'menu_RefID', '97000000000097'::bigint)))::varchar;</v>
       </c>
     </row>
   </sheetData>

--- a/Documentation/Documents/SQL Generator/Data Initial/SysConfig.TblAppObject_MenuGroupMember.xlsx
+++ b/Documentation/Documents/SQL Generator/Data Initial/SysConfig.TblAppObject_MenuGroupMember.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="12">
   <si>
     <t>Home</t>
   </si>
@@ -47,12 +47,21 @@
   <si>
     <t>Advance &amp; Trip</t>
   </si>
+  <si>
+    <t>SHOW SIGN</t>
+  </si>
+  <si>
+    <t>√</t>
+  </si>
+  <si>
+    <t>Sales</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -78,6 +87,12 @@
       <sz val="10"/>
       <color theme="9" tint="-0.499984740745262"/>
       <name val="Arial Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -145,7 +160,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -159,6 +174,12 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -182,6 +203,7 @@
     <sheetNames>
       <sheetName val="MainOLD"/>
       <sheetName val="Main"/>
+      <sheetName val="Sheet1"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
@@ -367,10 +389,10 @@
             <v>97000000000017</v>
           </cell>
           <cell r="F18" t="str">
-            <v>Module.General.MasterData.PrivilegeMenu.Transaction</v>
+            <v>Module.Budgeting.MasterData.Budget.Transaction</v>
           </cell>
           <cell r="G18" t="str">
-            <v>Privilege Menu</v>
+            <v>Budget</v>
           </cell>
         </row>
         <row r="19">
@@ -378,10 +400,10 @@
             <v>97000000000018</v>
           </cell>
           <cell r="F19" t="str">
-            <v>Module.General.MasterData.Workflow.Transaction</v>
+            <v>Module.Budgeting.MasterData.BudgetSection.Transaction</v>
           </cell>
           <cell r="G19" t="str">
-            <v>Workflow</v>
+            <v>Sub Budget</v>
           </cell>
         </row>
         <row r="20">
@@ -389,7 +411,7 @@
             <v>97000000000019</v>
           </cell>
           <cell r="F20" t="str">
-            <v>Module.Budgeting.MasterData.Budget.Transaction</v>
+            <v>Module.Budgeting.Data.Budget.Report.Transaction</v>
           </cell>
           <cell r="G20" t="str">
             <v>Budget</v>
@@ -400,10 +422,10 @@
             <v>97000000000020</v>
           </cell>
           <cell r="F21" t="str">
-            <v>Module.Budgeting.MasterData.BudgetSection.Transaction</v>
+            <v>Module.Budgeting.Data.Budget.Report.Resume</v>
           </cell>
           <cell r="G21" t="str">
-            <v>Sub Budget</v>
+            <v>Report Budget Summary</v>
           </cell>
         </row>
         <row r="22">
@@ -433,10 +455,10 @@
             <v>97000000000023</v>
           </cell>
           <cell r="F24" t="str">
-            <v>Module.Budgeting.Data.Work.Transaction</v>
+            <v>Module.Budgeting.Data.ProgressBudget.Transaction</v>
           </cell>
           <cell r="G24" t="str">
-            <v>Work</v>
+            <v>Progress Budget</v>
           </cell>
         </row>
         <row r="25">
@@ -444,10 +466,10 @@
             <v>97000000000024</v>
           </cell>
           <cell r="F25" t="str">
-            <v>Module.Budgeting.Data.CFS.Report.Resume</v>
+            <v>Module.Budgeting.Data.ProgressBudget.Report.Resume</v>
           </cell>
           <cell r="G25" t="str">
-            <v>Report Cost Financial Structure</v>
+            <v>Report Progress Budget Summary</v>
           </cell>
         </row>
         <row r="26">
@@ -455,10 +477,10 @@
             <v>97000000000025</v>
           </cell>
           <cell r="F26" t="str">
-            <v>Module.General.MasterData.BloodAglutinogenType.Transaction</v>
+            <v>Module.Budgeting.Data.SCurve.Report.Resume</v>
           </cell>
           <cell r="G26" t="str">
-            <v>Blood Aglutinogen Type</v>
+            <v>S-Curve Summary</v>
           </cell>
         </row>
         <row r="27">
@@ -466,10 +488,10 @@
             <v>97000000000026</v>
           </cell>
           <cell r="F27" t="str">
-            <v>Module.General.MasterData.Person.Transaction</v>
+            <v>Module.Budgeting.Data.Work.Transaction</v>
           </cell>
           <cell r="G27" t="str">
-            <v>Person</v>
+            <v>Work</v>
           </cell>
         </row>
         <row r="28">
@@ -477,10 +499,10 @@
             <v>97000000000027</v>
           </cell>
           <cell r="F28" t="str">
-            <v>Module.General.MasterData.Religion.Transaction</v>
+            <v>Module.Budgeting.Data.CFS.Report.Resume</v>
           </cell>
           <cell r="G28" t="str">
-            <v>Religion</v>
+            <v>Report Cost Financial Structure</v>
           </cell>
         </row>
         <row r="29">
@@ -488,10 +510,10 @@
             <v>97000000000028</v>
           </cell>
           <cell r="F29" t="str">
-            <v>Module.General.MasterData.UserRole.Transaction</v>
+            <v>Module.General.MasterData.BloodAglutinogenType.Transaction</v>
           </cell>
           <cell r="G29" t="str">
-            <v>Role</v>
+            <v>Blood Aglutinogen Type</v>
           </cell>
         </row>
         <row r="30">
@@ -499,10 +521,10 @@
             <v>97000000000029</v>
           </cell>
           <cell r="F30" t="str">
-            <v>Module.HumanResource.MasterData.OrganizationalDepartment.Transaction</v>
+            <v>Module.General.MasterData.Person.Transaction</v>
           </cell>
           <cell r="G30" t="str">
-            <v>Department</v>
+            <v>Person</v>
           </cell>
         </row>
         <row r="31">
@@ -510,10 +532,10 @@
             <v>97000000000030</v>
           </cell>
           <cell r="F31" t="str">
-            <v>Module.HumanResource.Data.PersonWorkTimeSheet.Transaction</v>
+            <v>Module.General.MasterData.PrivilegeMenu.Transaction</v>
           </cell>
           <cell r="G31" t="str">
-            <v>Person Work Time Sheet</v>
+            <v>Privilege Menu</v>
           </cell>
         </row>
         <row r="32">
@@ -521,10 +543,10 @@
             <v>97000000000031</v>
           </cell>
           <cell r="F32" t="str">
-            <v>Module.HumanResource.Data.PersonWorkTimeSheet.Report.DataList</v>
+            <v>Module.General.MasterData.Religion.Transaction</v>
           </cell>
           <cell r="G32" t="str">
-            <v>Person Work Time Sheet Summary</v>
+            <v>Religion</v>
           </cell>
         </row>
         <row r="33">
@@ -532,10 +554,10 @@
             <v>97000000000032</v>
           </cell>
           <cell r="F33" t="str">
-            <v>Module.HumanResource.Data.SallaryAllocation.Transaction</v>
+            <v>Module.General.MasterData.User.Transaction</v>
           </cell>
           <cell r="G33" t="str">
-            <v>Sallary Allocation</v>
+            <v>User</v>
           </cell>
         </row>
         <row r="34">
@@ -543,10 +565,10 @@
             <v>97000000000033</v>
           </cell>
           <cell r="F34" t="str">
-            <v>Module.HumanResource.Data.SallaryAllocation.Report.DataList</v>
+            <v>Module.General.MasterData.UserRole.Transaction</v>
           </cell>
           <cell r="G34" t="str">
-            <v>Sallary Allocation Summary</v>
+            <v>Role</v>
           </cell>
         </row>
         <row r="35">
@@ -554,10 +576,10 @@
             <v>97000000000034</v>
           </cell>
           <cell r="F35" t="str">
-            <v>Module.General.MasterData.Warehouse.Transaction</v>
+            <v>Module.General.MasterData.Workflow.Transaction</v>
           </cell>
           <cell r="G35" t="str">
-            <v>Warehouse</v>
+            <v>Workflow</v>
           </cell>
         </row>
         <row r="36">
@@ -565,10 +587,10 @@
             <v>97000000000035</v>
           </cell>
           <cell r="F36" t="str">
-            <v>Module.General.MasterData.ProductType.Transaction</v>
+            <v>Module.HumanResource.MasterData.OrganizationalDepartment.Transaction</v>
           </cell>
           <cell r="G36" t="str">
-            <v>Product Type</v>
+            <v>Department</v>
           </cell>
         </row>
         <row r="37">
@@ -576,10 +598,10 @@
             <v>97000000000036</v>
           </cell>
           <cell r="F37" t="str">
-            <v>Module.General.MasterData.Product.Transaction</v>
+            <v>Module.HumanResource.Data.PersonWorkTimeSheet.Transaction</v>
           </cell>
           <cell r="G37" t="str">
-            <v>Product</v>
+            <v>Person Work Time Sheet</v>
           </cell>
         </row>
         <row r="38">
@@ -587,10 +609,10 @@
             <v>97000000000037</v>
           </cell>
           <cell r="F38" t="str">
-            <v>Module.SupplyChain.Data.DeliveryOrder.Transaction</v>
+            <v>Module.HumanResource.Data.PersonWorkTimeSheet.Report.DataList</v>
           </cell>
           <cell r="G38" t="str">
-            <v>Delivery Order</v>
+            <v>Person Work Time Sheet Summary</v>
           </cell>
         </row>
         <row r="39">
@@ -598,10 +620,10 @@
             <v>97000000000038</v>
           </cell>
           <cell r="F39" t="str">
-            <v>Module.SupplyChain.Data.DeliveryOrder.Report.DataList</v>
+            <v>Module.HumanResource.Data.SallaryAllocation.Transaction</v>
           </cell>
           <cell r="G39" t="str">
-            <v>Report DO Summary</v>
+            <v>Sallary Allocation</v>
           </cell>
         </row>
         <row r="40">
@@ -609,10 +631,10 @@
             <v>97000000000039</v>
           </cell>
           <cell r="F40" t="str">
-            <v>Module.SupplyChain.Data.DeliveryOrderToMaterialReceive.Report.DataList</v>
+            <v>Module.HumanResource.Data.SallaryAllocation.Report.DataList</v>
           </cell>
           <cell r="G40" t="str">
-            <v>Report DO to Material Receive</v>
+            <v>Sallary Allocation Summary</v>
           </cell>
         </row>
         <row r="41">
@@ -620,10 +642,10 @@
             <v>97000000000040</v>
           </cell>
           <cell r="F41" t="str">
-            <v>Module.SupplyChain.Data.MaterialReceive.Transaction</v>
+            <v>Module.General.MasterData.Product.Transaction</v>
           </cell>
           <cell r="G41" t="str">
-            <v>Material Receive</v>
+            <v>Product</v>
           </cell>
         </row>
         <row r="42">
@@ -631,10 +653,10 @@
             <v>97000000000041</v>
           </cell>
           <cell r="F42" t="str">
-            <v>Module.SupplyChain.Data.MaterialReceive.Report.DataList</v>
+            <v>Module.General.MasterData.ProductType.Transaction</v>
           </cell>
           <cell r="G42" t="str">
-            <v>Report Material Receive Summary</v>
+            <v>Product Type</v>
           </cell>
         </row>
         <row r="43">
@@ -642,10 +664,10 @@
             <v>97000000000042</v>
           </cell>
           <cell r="F43" t="str">
-            <v>Module.SupplyChain.Data.MaterialReceiveToMaterialReturn.Report.DataList</v>
+            <v>Module.General.MasterData.Warehouse.Transaction</v>
           </cell>
           <cell r="G43" t="str">
-            <v>Report Material Receive to Material Return</v>
+            <v>Warehouse</v>
           </cell>
         </row>
         <row r="44">
@@ -653,10 +675,10 @@
             <v>97000000000043</v>
           </cell>
           <cell r="F44" t="str">
-            <v>Module.SupplyChain.Data.MaterialReturn.Transaction</v>
+            <v>Module.General.MasterData.Work.Transaction</v>
           </cell>
           <cell r="G44" t="str">
-            <v>Material Return</v>
+            <v>Work</v>
           </cell>
         </row>
         <row r="45">
@@ -664,10 +686,10 @@
             <v>97000000000044</v>
           </cell>
           <cell r="F45" t="str">
-            <v>Module.SupplyChain.Data.MaterialReturn.Report.DataList</v>
+            <v>Module.SupplyChain.Data.DeliveryOrder.Transaction</v>
           </cell>
           <cell r="G45" t="str">
-            <v>Report Material Return Summary</v>
+            <v>Delivery Order</v>
           </cell>
         </row>
         <row r="46">
@@ -675,10 +697,10 @@
             <v>97000000000045</v>
           </cell>
           <cell r="F46" t="str">
-            <v>Module.Finance.Data.Advance.Transaction</v>
+            <v>Module.SupplyChain.Data.DeliveryOrder.Report.DataList</v>
           </cell>
           <cell r="G46" t="str">
-            <v>Advance Request</v>
+            <v>Report DO Summary</v>
           </cell>
         </row>
         <row r="47">
@@ -686,10 +708,10 @@
             <v>97000000000046</v>
           </cell>
           <cell r="F47" t="str">
-            <v>Module.Finance.Data.Advance.Report.DataList</v>
+            <v>Module.SupplyChain.Data.DeliveryOrderToMaterialReceive.Report.DataList</v>
           </cell>
           <cell r="G47" t="str">
-            <v>Report Advance Summary</v>
+            <v>Report DO to Material Receive</v>
           </cell>
         </row>
         <row r="48">
@@ -697,10 +719,10 @@
             <v>97000000000047</v>
           </cell>
           <cell r="F48" t="str">
-            <v>Module.Finance.Data.AdvanceToAdvanceSettlement.Report.DataList</v>
+            <v>Module.SupplyChain.Data.MaterialReceive.Transaction</v>
           </cell>
           <cell r="G48" t="str">
-            <v>Report Advance to Advance Settlement</v>
+            <v>Material Receive</v>
           </cell>
         </row>
         <row r="49">
@@ -708,10 +730,10 @@
             <v>97000000000048</v>
           </cell>
           <cell r="F49" t="str">
-            <v>Module.Finance.Data.AdvanceSettlement.Transaction</v>
+            <v>Module.SupplyChain.Data.MaterialReceive.Report.DataList</v>
           </cell>
           <cell r="G49" t="str">
-            <v>AdvanceSettlement</v>
+            <v>Report Material Receive Summary</v>
           </cell>
         </row>
         <row r="50">
@@ -719,10 +741,10 @@
             <v>97000000000049</v>
           </cell>
           <cell r="F50" t="str">
-            <v>Module.Finance.Data.AdvanceSettlement.Report.DataList</v>
+            <v>Module.SupplyChain.Data.MaterialReceiveToMaterialReturn.Report.DataList</v>
           </cell>
           <cell r="G50" t="str">
-            <v>Report Advance Settlement Summary</v>
+            <v>Report Material Receive to Material Return</v>
           </cell>
         </row>
         <row r="51">
@@ -730,10 +752,10 @@
             <v>97000000000050</v>
           </cell>
           <cell r="F51" t="str">
-            <v>Module.Finance.Data.PersonBusinessTrip.Transaction</v>
+            <v>Module.SupplyChain.Data.MaterialReturn.Transaction</v>
           </cell>
           <cell r="G51" t="str">
-            <v>BusinessTrip Request</v>
+            <v>Material Return</v>
           </cell>
         </row>
         <row r="52">
@@ -741,10 +763,10 @@
             <v>97000000000051</v>
           </cell>
           <cell r="F52" t="str">
-            <v>Module.Finance.Data.PersonBusinessTrip.Report.DataList</v>
+            <v>Module.SupplyChain.Data.MaterialReturn.Report.DataList</v>
           </cell>
           <cell r="G52" t="str">
-            <v>Report BusinessTrip Request Summary</v>
+            <v>Report Material Return Summary</v>
           </cell>
         </row>
         <row r="53">
@@ -752,10 +774,10 @@
             <v>97000000000052</v>
           </cell>
           <cell r="F53" t="str">
-            <v>Module.Finance.Data.PersonBusinessTripToPersonBusinessTripSettlement.Report.DataList</v>
+            <v>Module.SupplyChain.Data.PhysicalInventoryCount.Transaction</v>
           </cell>
           <cell r="G53" t="str">
-            <v>Report BusinessTrip to BusinessTrip Settlement</v>
+            <v>Stock Opname</v>
           </cell>
         </row>
         <row r="54">
@@ -763,10 +785,10 @@
             <v>97000000000053</v>
           </cell>
           <cell r="F54" t="str">
-            <v>Module.Finance.Data.PersonBusinessTripSettlement.Transaction</v>
+            <v>Module.SupplyChain.Data.PhysicalInventoryCount.Report.DataList</v>
           </cell>
           <cell r="G54" t="str">
-            <v>BusinessTrip Settlement</v>
+            <v>Report Stock Opname Summary</v>
           </cell>
         </row>
         <row r="55">
@@ -774,10 +796,10 @@
             <v>97000000000054</v>
           </cell>
           <cell r="F55" t="str">
-            <v>Module.Finance.Data.PersonBusinessTripSettlement.Report.DataList</v>
+            <v>Module.Finance.Data.Advance.Transaction</v>
           </cell>
           <cell r="G55" t="str">
-            <v>Report BusinessTrip Settlement Summary</v>
+            <v>Advance Request</v>
           </cell>
         </row>
         <row r="56">
@@ -785,10 +807,10 @@
             <v>97000000000055</v>
           </cell>
           <cell r="F56" t="str">
-            <v>Module.SupplyChain.MasterData.Supplier.Transaction</v>
+            <v>Module.Finance.Data.Advance.Report.DataList</v>
           </cell>
           <cell r="G56" t="str">
-            <v>Supplier</v>
+            <v>Report Advance Summary</v>
           </cell>
         </row>
         <row r="57">
@@ -796,10 +818,10 @@
             <v>97000000000056</v>
           </cell>
           <cell r="F57" t="str">
-            <v>Module.SupplyChain.Data.PurchaseRequisition.Transaction</v>
+            <v>Module.Finance.Data.AdvanceToAdvanceSettlement.Report.DataList</v>
           </cell>
           <cell r="G57" t="str">
-            <v>Purchase Requisition</v>
+            <v>Report Advance to Advance Settlement</v>
           </cell>
         </row>
         <row r="58">
@@ -807,10 +829,10 @@
             <v>97000000000057</v>
           </cell>
           <cell r="F58" t="str">
-            <v>Module.SupplyChain.Data.PurchaseRequisition.Report.DataList</v>
+            <v>Module.Finance.Data.AdvanceSettlement.Transaction</v>
           </cell>
           <cell r="G58" t="str">
-            <v>Report Purchase Requisition Summary</v>
+            <v>AdvanceSettlement</v>
           </cell>
         </row>
         <row r="59">
@@ -818,10 +840,10 @@
             <v>97000000000058</v>
           </cell>
           <cell r="F59" t="str">
-            <v>Module.SupplyChain.Data.PurchaseRequisitionToPurchaseOrder.Report.DataList</v>
+            <v>Module.Finance.Data.AdvanceSettlement.Report.DataList</v>
           </cell>
           <cell r="G59" t="str">
-            <v>Report Purchase Requisition To Purchase Order</v>
+            <v>Report Advance Settlement Summary</v>
           </cell>
         </row>
         <row r="60">
@@ -829,10 +851,10 @@
             <v>97000000000059</v>
           </cell>
           <cell r="F60" t="str">
-            <v>Module.SupplyChain.Data.PurchaseOrder.Transaction</v>
+            <v>Module.Finance.Data.PersonBusinessTrip.Transaction</v>
           </cell>
           <cell r="G60" t="str">
-            <v>Purchase Order</v>
+            <v>BusinessTrip Request</v>
           </cell>
         </row>
         <row r="61">
@@ -840,10 +862,10 @@
             <v>97000000000060</v>
           </cell>
           <cell r="F61" t="str">
-            <v>Module.SupplyChain.Data.PurchaseOrder.Report.DataList</v>
+            <v>Module.Finance.Data.PersonBusinessTrip.Report.DataList</v>
           </cell>
           <cell r="G61" t="str">
-            <v>Report Purchase Order Summary</v>
+            <v>Report BusinessTrip Request Summary</v>
           </cell>
         </row>
         <row r="62">
@@ -851,10 +873,10 @@
             <v>97000000000061</v>
           </cell>
           <cell r="F62" t="str">
-            <v>Module.SupplyChain.Data.PurchaseOrderToPaymentInstruction.Report.DataList</v>
+            <v>Module.Finance.Data.PersonBusinessTripToPersonBusinessTripSettlement.Report.DataList</v>
           </cell>
           <cell r="G62" t="str">
-            <v>Purchase Order to Account Payable</v>
+            <v>Report BusinessTrip to BusinessTrip Settlement</v>
           </cell>
         </row>
         <row r="63">
@@ -862,10 +884,10 @@
             <v>97000000000062</v>
           </cell>
           <cell r="F63" t="str">
-            <v>Module.General.MasterData.Bank.Transaction</v>
+            <v>Module.Finance.Data.PersonBusinessTripSettlement.Transaction</v>
           </cell>
           <cell r="G63" t="str">
-            <v>Bank</v>
+            <v>BusinessTrip Settlement</v>
           </cell>
         </row>
         <row r="64">
@@ -873,10 +895,10 @@
             <v>97000000000063</v>
           </cell>
           <cell r="F64" t="str">
-            <v>Module.General.MasterData.BankAccount.Transaction</v>
+            <v>Module.Finance.Data.PersonBusinessTripSettlement.Report.DataList</v>
           </cell>
           <cell r="G64" t="str">
-            <v>Bank Account</v>
+            <v>Report BusinessTrip Settlement Summary</v>
           </cell>
         </row>
         <row r="65">
@@ -884,10 +906,10 @@
             <v>97000000000064</v>
           </cell>
           <cell r="F65" t="str">
-            <v>Module.General.MasterData.Currency.Transaction</v>
+            <v>Module.SupplyChain.MasterData.Supplier.Transaction</v>
           </cell>
           <cell r="G65" t="str">
-            <v>Currency</v>
+            <v>Supplier</v>
           </cell>
         </row>
         <row r="66">
@@ -895,10 +917,10 @@
             <v>97000000000065</v>
           </cell>
           <cell r="F66" t="str">
-            <v>Module.General.MasterData.CurrencyExchangeRate.Transaction</v>
+            <v>Module.SupplyChain.MasterData.SupplierCategory.Transaction</v>
           </cell>
           <cell r="G66" t="str">
-            <v>Exchange Rate</v>
+            <v>Supplier Category</v>
           </cell>
         </row>
         <row r="67">
@@ -906,10 +928,10 @@
             <v>97000000000066</v>
           </cell>
           <cell r="F67" t="str">
-            <v>Module.General.MasterData.CurrencyExchangeRate.Report.DataList</v>
+            <v>Module.SupplyChain.MasterData.SupplierSubCategory.Transaction</v>
           </cell>
           <cell r="G67" t="str">
-            <v>Exchange Rate Summary</v>
+            <v>Supplier Sub Category</v>
           </cell>
         </row>
         <row r="68">
@@ -917,10 +939,10 @@
             <v>97000000000067</v>
           </cell>
           <cell r="F68" t="str">
-            <v>Module.General.MasterData.PaymentTerm.Transaction</v>
+            <v>Module.SupplyChain.Data.PurchaseRequisition.Transaction</v>
           </cell>
           <cell r="G68" t="str">
-            <v>Payment Term</v>
+            <v>Purchase Requisition</v>
           </cell>
         </row>
         <row r="69">
@@ -928,10 +950,10 @@
             <v>97000000000068</v>
           </cell>
           <cell r="F69" t="str">
-            <v>Module.General.MasterData.Period.Transaction</v>
+            <v>Module.SupplyChain.Data.PurchaseRequisition.Report.DataList</v>
           </cell>
           <cell r="G69" t="str">
-            <v>Period</v>
+            <v>Report Purchase Requisition Summary</v>
           </cell>
         </row>
         <row r="70">
@@ -939,10 +961,10 @@
             <v>97000000000069</v>
           </cell>
           <cell r="F70" t="str">
-            <v>Module.Accounting.MasterData.AssetCategory.Transaction</v>
+            <v>Module.SupplyChain.Data.PurchaseRequisitionToPurchaseOrder.Report.DataList</v>
           </cell>
           <cell r="G70" t="str">
-            <v>Asset Category</v>
+            <v>Report Purchase Requisition To Purchase Order</v>
           </cell>
         </row>
         <row r="71">
@@ -950,10 +972,10 @@
             <v>97000000000070</v>
           </cell>
           <cell r="F71" t="str">
-            <v>Module.Accounting.MasterData.ChartOfAccount.Transaction</v>
+            <v>Module.SupplyChain.Data.PurchaseOrder.Transaction</v>
           </cell>
           <cell r="G71" t="str">
-            <v>Chart of Account</v>
+            <v>Purchase Order</v>
           </cell>
         </row>
         <row r="72">
@@ -961,10 +983,10 @@
             <v>97000000000071</v>
           </cell>
           <cell r="F72" t="str">
-            <v>Module.Accounting.MasterData.DepreciationMethod.Transaction</v>
+            <v>Module.SupplyChain.Data.PurchaseOrder.Report.DataList</v>
           </cell>
           <cell r="G72" t="str">
-            <v>Depreciation Method</v>
+            <v>Report Purchase Order Summary</v>
           </cell>
         </row>
         <row r="73">
@@ -972,10 +994,10 @@
             <v>97000000000072</v>
           </cell>
           <cell r="F73" t="str">
-            <v>Module.Accounting.MasterData.DepreciationRateYears.Transaction</v>
+            <v>Module.SupplyChain.Data.PurchaseOrderToPaymentInstruction.Report.DataList</v>
           </cell>
           <cell r="G73" t="str">
-            <v>Depreciation Rate Years</v>
+            <v>Report Purchase Order to Account Payable Summary</v>
           </cell>
         </row>
         <row r="74">
@@ -983,10 +1005,10 @@
             <v>97000000000073</v>
           </cell>
           <cell r="F74" t="str">
-            <v>Module.Taxation.MasterData.ValueAddedTax.Transaction</v>
+            <v>Module.General.MasterData.Bank.Transaction</v>
           </cell>
           <cell r="G74" t="str">
-            <v>Value Added Tax</v>
+            <v>Bank</v>
           </cell>
         </row>
         <row r="75">
@@ -994,10 +1016,10 @@
             <v>97000000000074</v>
           </cell>
           <cell r="F75" t="str">
-            <v>Module.Accounting.Data.GeneralJournal.Transaction</v>
+            <v>Module.General.MasterData.BankAccount.Transaction</v>
           </cell>
           <cell r="G75" t="str">
-            <v>General Journal</v>
+            <v>Bank Account</v>
           </cell>
         </row>
         <row r="76">
@@ -1005,10 +1027,10 @@
             <v>97000000000075</v>
           </cell>
           <cell r="F76" t="str">
-            <v>Module.Accounting.Data.GeneralJournal.Report.DataList</v>
+            <v>Module.General.MasterData.Currency.Transaction</v>
           </cell>
           <cell r="G76" t="str">
-            <v>General Journal Summary</v>
+            <v>Currency</v>
           </cell>
         </row>
         <row r="77">
@@ -1016,10 +1038,10 @@
             <v>97000000000076</v>
           </cell>
           <cell r="F77" t="str">
-            <v>Module.Finance.Data.Reimbursement.Transaction</v>
+            <v>Module.General.MasterData.CurrencyExchangeRate.Transaction</v>
           </cell>
           <cell r="G77" t="str">
-            <v>Reimbursement</v>
+            <v>Exchange Rate</v>
           </cell>
         </row>
         <row r="78">
@@ -1027,10 +1049,10 @@
             <v>97000000000077</v>
           </cell>
           <cell r="F78" t="str">
-            <v>Module.Finance.Data.Reimbursement.Report.DataList</v>
+            <v>Module.General.MasterData.CurrencyExchangeRate.Report.DataList</v>
           </cell>
           <cell r="G78" t="str">
-            <v>Reimbursement Summary</v>
+            <v>Exchange Rate Summary</v>
           </cell>
         </row>
         <row r="79">
@@ -1038,10 +1060,10 @@
             <v>97000000000078</v>
           </cell>
           <cell r="F79" t="str">
-            <v>Module.Finance.Data.ReimbursementToDebitNote.Report.DataList</v>
+            <v>Module.General.MasterData.PaymentTerm.Transaction</v>
           </cell>
           <cell r="G79" t="str">
-            <v>Reimbursement to Debit Note</v>
+            <v>Payment Term</v>
           </cell>
         </row>
         <row r="80">
@@ -1049,10 +1071,10 @@
             <v>97000000000079</v>
           </cell>
           <cell r="F80" t="str">
-            <v>Module.Finance.Data.DebitNote.Transaction</v>
+            <v>Module.General.MasterData.Period.Transaction</v>
           </cell>
           <cell r="G80" t="str">
-            <v>Debit Note</v>
+            <v>Period</v>
           </cell>
         </row>
         <row r="81">
@@ -1060,10 +1082,10 @@
             <v>97000000000080</v>
           </cell>
           <cell r="F81" t="str">
-            <v>Module.Finance.Data.DebitNote.Report.DataList</v>
+            <v>Module.Accounting.MasterData.AssetCategory.Transaction</v>
           </cell>
           <cell r="G81" t="str">
-            <v>Debit Note Summary</v>
+            <v>Asset Category</v>
           </cell>
         </row>
         <row r="82">
@@ -1071,10 +1093,10 @@
             <v>97000000000081</v>
           </cell>
           <cell r="F82" t="str">
-            <v>Module.Finance.Data.CreditNote.Transaction</v>
+            <v>Module.Accounting.MasterData.ChartOfAccount.Transaction</v>
           </cell>
           <cell r="G82" t="str">
-            <v>Credit Note</v>
+            <v>Chart of Account</v>
           </cell>
         </row>
         <row r="83">
@@ -1082,10 +1104,10 @@
             <v>97000000000082</v>
           </cell>
           <cell r="F83" t="str">
-            <v>Module.Finance.Data.CreditNote.Report.DataList</v>
+            <v>Module.Accounting.MasterData.DepreciationMethod.Transaction</v>
           </cell>
           <cell r="G83" t="str">
-            <v>Credit Note Summary</v>
+            <v>Depreciation Method</v>
           </cell>
         </row>
         <row r="84">
@@ -1093,10 +1115,10 @@
             <v>97000000000083</v>
           </cell>
           <cell r="F84" t="str">
-            <v>Module.Finance.Data.Loan.Transaction</v>
+            <v>Module.Accounting.MasterData.DepreciationRateYears.Transaction</v>
           </cell>
           <cell r="G84" t="str">
-            <v>Loan</v>
+            <v>Depreciation Rate Years</v>
           </cell>
         </row>
         <row r="85">
@@ -1104,10 +1126,10 @@
             <v>97000000000084</v>
           </cell>
           <cell r="F85" t="str">
-            <v>Module.Finance.Data.Loan.Report.DataList</v>
+            <v>Module.Taxation.MasterData.ValueAddedTax.Transaction</v>
           </cell>
           <cell r="G85" t="str">
-            <v>Loan Summary</v>
+            <v>Value Added Tax</v>
           </cell>
         </row>
         <row r="86">
@@ -1115,10 +1137,10 @@
             <v>97000000000085</v>
           </cell>
           <cell r="F86" t="str">
-            <v>Module.Finance.Data.LoanToLoanSettlement.Report.DataList</v>
+            <v>Module.Accounting.Data.BalanceSheet.Report.DataList</v>
           </cell>
           <cell r="G86" t="str">
-            <v>Loan to Loan Settlement</v>
+            <v>Balance Sheet</v>
           </cell>
         </row>
         <row r="87">
@@ -1126,10 +1148,10 @@
             <v>97000000000086</v>
           </cell>
           <cell r="F87" t="str">
-            <v>Module.Finance.Data.LoanSettlement.Transaction</v>
+            <v>Module.Accounting.Data.GeneralJournal.Transaction</v>
           </cell>
           <cell r="G87" t="str">
-            <v>Loan Settlement</v>
+            <v>General Journal</v>
           </cell>
         </row>
         <row r="88">
@@ -1137,10 +1159,10 @@
             <v>97000000000087</v>
           </cell>
           <cell r="F88" t="str">
-            <v>Module.Finance.Data.LoanSettlement.Report.DataList</v>
+            <v>Module.Accounting.Data.GeneralJournal.Report.DataList</v>
           </cell>
           <cell r="G88" t="str">
-            <v>Loan Settlement Summary</v>
+            <v>General Journal Summary</v>
           </cell>
         </row>
         <row r="89">
@@ -1148,10 +1170,10 @@
             <v>97000000000088</v>
           </cell>
           <cell r="F89" t="str">
-            <v>Module.Finance.Data.CashBank.Transaction</v>
+            <v>Module.Accounting.Data.GeneralLedger.Report.DataList</v>
           </cell>
           <cell r="G89" t="str">
-            <v>Cash &amp; Bank</v>
+            <v>General Ledger Summary</v>
           </cell>
         </row>
         <row r="90">
@@ -1159,10 +1181,10 @@
             <v>97000000000089</v>
           </cell>
           <cell r="F90" t="str">
-            <v>Module.Finance.Data.CashBank.Report.DataList</v>
+            <v>Module.Accounting.Data.ProfitLoss.Report.DataList</v>
           </cell>
           <cell r="G90" t="str">
-            <v>Cash &amp; Bank Summary</v>
+            <v>Profit Loss Summary</v>
           </cell>
         </row>
         <row r="91">
@@ -1170,10 +1192,10 @@
             <v>97000000000090</v>
           </cell>
           <cell r="F91" t="str">
-            <v>Module.Finance.Data.PaymentInstruction.Transaction</v>
+            <v>Module.Finance.Data.CashBank.Transaction</v>
           </cell>
           <cell r="G91" t="str">
-            <v>Account Payable</v>
+            <v>Cash &amp; Bank</v>
           </cell>
         </row>
         <row r="92">
@@ -1181,10 +1203,10 @@
             <v>97000000000091</v>
           </cell>
           <cell r="F92" t="str">
-            <v>Module.Finance.Data.PaymentInstruction.Report.DataList</v>
+            <v>Module.Finance.Data.CashBank.Report.DataList</v>
           </cell>
           <cell r="G92" t="str">
-            <v>Account Payable Summary</v>
+            <v>Cash &amp; Bank Summary</v>
           </cell>
         </row>
         <row r="93">
@@ -1192,10 +1214,10 @@
             <v>97000000000092</v>
           </cell>
           <cell r="F93" t="str">
-            <v>Module.Finance.Data.SalesInvoice.Transaction</v>
+            <v>Module.Finance.Data.CreditNote.Transaction</v>
           </cell>
           <cell r="G93" t="str">
-            <v>Sales Invoice</v>
+            <v>Credit Note</v>
           </cell>
         </row>
         <row r="94">
@@ -1203,10 +1225,10 @@
             <v>97000000000093</v>
           </cell>
           <cell r="F94" t="str">
-            <v>Module.Finance.Data.SalesInvoice.Report.DataList</v>
+            <v>Module.Finance.Data.CreditNote.Report.DataList</v>
           </cell>
           <cell r="G94" t="str">
-            <v>Sales Invoice Summary</v>
+            <v>Credit Note Summary</v>
           </cell>
         </row>
         <row r="95">
@@ -1214,10 +1236,10 @@
             <v>97000000000094</v>
           </cell>
           <cell r="F95" t="str">
-            <v>Module.Finance.Data.SalesInvoiceToCreditNote.Report.DataList</v>
+            <v>Module.Finance.Data.DebitNote.Transaction</v>
           </cell>
           <cell r="G95" t="str">
-            <v>Sales Invoice to Credit Note</v>
+            <v>Debit Note</v>
           </cell>
         </row>
         <row r="96">
@@ -1225,10 +1247,10 @@
             <v>97000000000095</v>
           </cell>
           <cell r="F96" t="str">
-            <v>Module.Finance.Data.TaxReconciliation.Transaction</v>
+            <v>Module.Finance.Data.DebitNote.Report.DataList</v>
           </cell>
           <cell r="G96" t="str">
-            <v>Tax Reconciliation</v>
+            <v>Debit Note Summary</v>
           </cell>
         </row>
         <row r="97">
@@ -1236,10 +1258,10 @@
             <v>97000000000096</v>
           </cell>
           <cell r="F97" t="str">
-            <v>Module.Finance.Data.TaxReconciliation.Report.DataList</v>
+            <v>Module.FixedAsset.Data.GoodsIdentity.Transaction</v>
           </cell>
           <cell r="G97" t="str">
-            <v>Tax Reconciliation Summary</v>
+            <v>Fixed Asset</v>
           </cell>
         </row>
         <row r="98">
@@ -1247,13 +1269,212 @@
             <v>97000000000097</v>
           </cell>
           <cell r="F98" t="str">
+            <v>Module.FixedAsset.Data.GoodsIdentity.Report.DataList</v>
+          </cell>
+          <cell r="G98" t="str">
+            <v>Fixed Asset Summary</v>
+          </cell>
+        </row>
+        <row r="99">
+          <cell r="E99">
+            <v>97000000000098</v>
+          </cell>
+          <cell r="F99" t="str">
+            <v>Module.Finance.Data.Loan.Transaction</v>
+          </cell>
+          <cell r="G99" t="str">
+            <v>Loan</v>
+          </cell>
+        </row>
+        <row r="100">
+          <cell r="E100">
+            <v>97000000000099</v>
+          </cell>
+          <cell r="F100" t="str">
+            <v>Module.Finance.Data.Loan.Report.DataList</v>
+          </cell>
+          <cell r="G100" t="str">
+            <v>Loan Summary</v>
+          </cell>
+        </row>
+        <row r="101">
+          <cell r="E101">
+            <v>97000000000100</v>
+          </cell>
+          <cell r="F101" t="str">
+            <v>Module.Finance.Data.LoanToLoanSettlement.Report.DataList</v>
+          </cell>
+          <cell r="G101" t="str">
+            <v>Loan to Loan Settlement Summary</v>
+          </cell>
+        </row>
+        <row r="102">
+          <cell r="E102">
+            <v>97000000000101</v>
+          </cell>
+          <cell r="F102" t="str">
+            <v>Module.Finance.Data.LoanSettlement.Transaction</v>
+          </cell>
+          <cell r="G102" t="str">
+            <v>Loan Settlement</v>
+          </cell>
+        </row>
+        <row r="103">
+          <cell r="E103">
+            <v>97000000000102</v>
+          </cell>
+          <cell r="F103" t="str">
+            <v>Module.Finance.Data.LoanSettlement.Report.DataList</v>
+          </cell>
+          <cell r="G103" t="str">
+            <v>Loan Settlement Summary</v>
+          </cell>
+        </row>
+        <row r="104">
+          <cell r="E104">
+            <v>97000000000103</v>
+          </cell>
+          <cell r="F104" t="str">
+            <v>Module.Finance.Data.PaymentInstruction.Transaction</v>
+          </cell>
+          <cell r="G104" t="str">
+            <v>Account Payable</v>
+          </cell>
+        </row>
+        <row r="105">
+          <cell r="E105">
+            <v>97000000000104</v>
+          </cell>
+          <cell r="F105" t="str">
+            <v>Module.Finance.Data.PaymentInstruction.Report.DataList</v>
+          </cell>
+          <cell r="G105" t="str">
+            <v>Account Payable Summary</v>
+          </cell>
+        </row>
+        <row r="106">
+          <cell r="E106">
+            <v>97000000000105</v>
+          </cell>
+          <cell r="F106" t="str">
+            <v>Module.Finance.Data.Reimbursement.Transaction</v>
+          </cell>
+          <cell r="G106" t="str">
+            <v>Reimbursement</v>
+          </cell>
+        </row>
+        <row r="107">
+          <cell r="E107">
+            <v>97000000000106</v>
+          </cell>
+          <cell r="F107" t="str">
+            <v>Module.Finance.Data.Reimbursement.Report.DataList</v>
+          </cell>
+          <cell r="G107" t="str">
+            <v>Reimbursement Summary</v>
+          </cell>
+        </row>
+        <row r="108">
+          <cell r="E108">
+            <v>97000000000107</v>
+          </cell>
+          <cell r="F108" t="str">
+            <v>Module.Finance.Data.ReimbursementToDebitNote.Report.DataList</v>
+          </cell>
+          <cell r="G108" t="str">
+            <v>Reimbursement to Debit Note Summary</v>
+          </cell>
+        </row>
+        <row r="109">
+          <cell r="E109">
+            <v>97000000000108</v>
+          </cell>
+          <cell r="F109" t="str">
+            <v>Module.Finance.Data.SalesInvoice.Transaction</v>
+          </cell>
+          <cell r="G109" t="str">
+            <v>Sales Invoice</v>
+          </cell>
+        </row>
+        <row r="110">
+          <cell r="E110">
+            <v>97000000000109</v>
+          </cell>
+          <cell r="F110" t="str">
+            <v>Module.Finance.Data.SalesInvoice.Report.DataList</v>
+          </cell>
+          <cell r="G110" t="str">
+            <v>Sales Invoice Summary</v>
+          </cell>
+        </row>
+        <row r="111">
+          <cell r="E111">
+            <v>97000000000110</v>
+          </cell>
+          <cell r="F111" t="str">
+            <v>Module.Finance.Data.SalesInvoiceToCreditNote.Report.DataList</v>
+          </cell>
+          <cell r="G111" t="str">
+            <v>Sales Invoice to Credit Note</v>
+          </cell>
+        </row>
+        <row r="112">
+          <cell r="E112">
+            <v>97000000000111</v>
+          </cell>
+          <cell r="F112" t="str">
+            <v>Module.Finance.Data.TaxReconciliation.Transaction</v>
+          </cell>
+          <cell r="G112" t="str">
+            <v>Tax Reconciliation</v>
+          </cell>
+        </row>
+        <row r="113">
+          <cell r="E113">
+            <v>97000000000112</v>
+          </cell>
+          <cell r="F113" t="str">
+            <v>Module.Finance.Data.TaxReconciliation.Report.DataList</v>
+          </cell>
+          <cell r="G113" t="str">
+            <v>Tax Reconciliation Summary</v>
+          </cell>
+        </row>
+        <row r="114">
+          <cell r="E114">
+            <v>97000000000113</v>
+          </cell>
+          <cell r="F114" t="str">
             <v>Module.CustomerRelation.MasterData.Customer.Transaction</v>
           </cell>
-          <cell r="G98" t="str">
+          <cell r="G114" t="str">
             <v>Customer</v>
+          </cell>
+        </row>
+        <row r="115">
+          <cell r="E115">
+            <v>97000000000114</v>
+          </cell>
+          <cell r="F115" t="str">
+            <v>Module.CustomerRelation.MasterData.CustomerOrder.Transaction</v>
+          </cell>
+          <cell r="G115" t="str">
+            <v>Customer Order</v>
+          </cell>
+        </row>
+        <row r="116">
+          <cell r="E116">
+            <v>97000000000115</v>
+          </cell>
+          <cell r="F116" t="str">
+            <v>Module.CustomerRelation.MasterData.CustomerOrder.Report.DataList</v>
+          </cell>
+          <cell r="G116" t="str">
+            <v>Customer Order Summary</v>
           </cell>
         </row>
       </sheetData>
+      <sheetData sheetId="2"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1670,36 +1891,42 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:K98"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="B1:L116"/>
+  <sheetFormatPr defaultColWidth="10.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.140625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="1.5703125" style="2" customWidth="1"/>
     <col min="2" max="2" width="13.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="72" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="47.42578125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="9.140625" style="2"/>
-    <col min="6" max="6" width="12.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="2"/>
+    <col min="3" max="3" width="39.28515625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="33.28515625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="2.140625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="12.85546875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="19.42578125" style="2" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="10.85546875" style="2" hidden="1" customWidth="1"/>
+    <col min="9" max="10" width="10.7109375" style="2" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="10.7109375" style="11"/>
+    <col min="12" max="16384" width="10.7109375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="1" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B1" s="5" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="5"/>
-    </row>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K1" s="11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B2" s="6">
         <f>[1]Main!$E2</f>
         <v>97000000000001</v>
       </c>
       <c r="C2" s="7" t="str">
-        <f>VLOOKUP($B2, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <f>VLOOKUP($B2, [1]Main!$E$2:$G$374, 2, FALSE)</f>
         <v>System.Login</v>
       </c>
       <c r="D2" s="8" t="str">
-        <f>VLOOKUP($B2, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <f>VLOOKUP($B2, [1]Main!$E$2:$G$374, 3, FALSE)</f>
         <v>Login</v>
       </c>
       <c r="F2" s="10" t="s">
@@ -1716,8 +1943,12 @@
         <f>IF(EXACT(G2, ""), "", CONCATENATE("PERFORM ""SchSysConfig"".""Func_TblAppObject_MenuGroupMember_SET""(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, ", G2, "::bigint, ", B2, "::bigint);"))</f>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000001::bigint, 97000000000001::bigint);</v>
       </c>
-      <c r="K2" s="2" t="str">
-        <f>CONCATENATE(
+      <c r="K2" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L2" s="2" t="str">
+        <f>IF(EXACT(K2, ""), "",
+CONCATENATE(
 "varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT (",
 "'recordID', NULL::bigint,", "'entities', ", "JSON_BUILD_OBJECT (",
 "'sysLoginSession_RefID', varSystemLoginSession::bigint,",
@@ -1730,21 +1961,22 @@
 "'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,",
 "'menuGroup_RefID', ", IF(EXACT($G2, ""), "null", CONCATENATE("'", SUBSTITUTE($G2, "'", "\'"), "'")), "::bigint,",
 "'menu_RefID', ", IF(EXACT($B2, ""), "null", CONCATENATE("'", SUBSTITUTE($B2, "'", "\'"), "'")), "::bigint",
-")))::varchar;")</f>
+")))::varchar;")
+)</f>
         <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000001'::bigint,'menu_RefID', '97000000000001'::bigint)))::varchar;</v>
       </c>
     </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B3" s="6">
         <f>[1]Main!$E3</f>
         <v>97000000000002</v>
       </c>
       <c r="C3" s="7" t="str">
-        <f>VLOOKUP($B3, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <f>VLOOKUP($B3, [1]Main!$E$2:$G$374, 2, FALSE)</f>
         <v>System.Logout</v>
       </c>
       <c r="D3" s="8" t="str">
-        <f>VLOOKUP($B3, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <f>VLOOKUP($B3, [1]Main!$E$2:$G$374, 3, FALSE)</f>
         <v>Logout</v>
       </c>
       <c r="F3" s="10" t="s">
@@ -1758,11 +1990,15 @@
         <v>2</v>
       </c>
       <c r="I3" s="9" t="str">
-        <f t="shared" ref="I3:I66" si="0">IF(EXACT(G3, ""), "", CONCATENATE("PERFORM ""SchSysConfig"".""Func_TblAppObject_MenuGroupMember_SET""(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, ", G3, "::bigint, ", B3, "::bigint);"))</f>
+        <f t="shared" ref="I3:I26" si="0">IF(EXACT(G3, ""), "", CONCATENATE("PERFORM ""SchSysConfig"".""Func_TblAppObject_MenuGroupMember_SET""(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, ", G3, "::bigint, ", B3, "::bigint);"))</f>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000001::bigint, 97000000000002::bigint);</v>
       </c>
-      <c r="K3" s="2" t="str">
-        <f t="shared" ref="K3:K66" si="1">CONCATENATE(
+      <c r="K3" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L3" s="2" t="str">
+        <f t="shared" ref="L3:L66" si="1">IF(EXACT(K3, ""), "",
+CONCATENATE(
 "varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT (",
 "'recordID', NULL::bigint,", "'entities', ", "JSON_BUILD_OBJECT (",
 "'sysLoginSession_RefID', varSystemLoginSession::bigint,",
@@ -1775,21 +2011,22 @@
 "'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,",
 "'menuGroup_RefID', ", IF(EXACT($G3, ""), "null", CONCATENATE("'", SUBSTITUTE($G3, "'", "\'"), "'")), "::bigint,",
 "'menu_RefID', ", IF(EXACT($B3, ""), "null", CONCATENATE("'", SUBSTITUTE($B3, "'", "\'"), "'")), "::bigint",
-")))::varchar;")</f>
+")))::varchar;")
+)</f>
         <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000001'::bigint,'menu_RefID', '97000000000002'::bigint)))::varchar;</v>
       </c>
     </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B4" s="6">
         <f>[1]Main!$E4</f>
         <v>97000000000003</v>
       </c>
       <c r="C4" s="7" t="str">
-        <f>VLOOKUP($B4, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <f>VLOOKUP($B4, [1]Main!$E$2:$G$374, 2, FALSE)</f>
         <v>System.Lock</v>
       </c>
       <c r="D4" s="8" t="str">
-        <f>VLOOKUP($B4, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <f>VLOOKUP($B4, [1]Main!$E$2:$G$374, 3, FALSE)</f>
         <v>Lock</v>
       </c>
       <c r="F4" s="10" t="s">
@@ -1806,22 +2043,22 @@
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000001::bigint, 97000000000003::bigint);</v>
       </c>
-      <c r="K4" s="2" t="str">
+      <c r="L4" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000001'::bigint,'menu_RefID', '97000000000003'::bigint)))::varchar;</v>
-      </c>
-    </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.2">
+        <v/>
+      </c>
+    </row>
+    <row r="5" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B5" s="6">
         <f>[1]Main!$E5</f>
         <v>97000000000004</v>
       </c>
       <c r="C5" s="7" t="str">
-        <f>VLOOKUP($B5, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <f>VLOOKUP($B5, [1]Main!$E$2:$G$374, 2, FALSE)</f>
         <v>Dashboard.Home</v>
       </c>
       <c r="D5" s="8" t="str">
-        <f>VLOOKUP($B5, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <f>VLOOKUP($B5, [1]Main!$E$2:$G$374, 3, FALSE)</f>
         <v>Dashboard</v>
       </c>
       <c r="F5" s="10" t="s">
@@ -1835,25 +2072,28 @@
         <v>4</v>
       </c>
       <c r="I5" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="I5:I68" si="2">IF(EXACT(G5, ""), "", CONCATENATE("PERFORM ""SchSysConfig"".""Func_TblAppObject_MenuGroupMember_SET""(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, ", G5, "::bigint, ", B5, "::bigint);"))</f>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000001::bigint, 97000000000004::bigint);</v>
       </c>
-      <c r="K5" s="2" t="str">
+      <c r="K5" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L5" s="2" t="str">
         <f t="shared" si="1"/>
         <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000001'::bigint,'menu_RefID', '97000000000004'::bigint)))::varchar;</v>
       </c>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B6" s="6">
         <f>[1]Main!$E6</f>
         <v>97000000000005</v>
       </c>
       <c r="C6" s="7" t="str">
-        <f>VLOOKUP($B6, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <f>VLOOKUP($B6, [1]Main!$E$2:$G$374, 2, FALSE)</f>
         <v>Dashboard.DocumentTracking</v>
       </c>
       <c r="D6" s="8" t="str">
-        <f>VLOOKUP($B6, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <f>VLOOKUP($B6, [1]Main!$E$2:$G$374, 3, FALSE)</f>
         <v>Document Tracking</v>
       </c>
       <c r="F6" s="10" t="s">
@@ -1867,25 +2107,28 @@
         <v>5</v>
       </c>
       <c r="I6" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000001::bigint, 97000000000005::bigint);</v>
       </c>
-      <c r="K6" s="2" t="str">
+      <c r="K6" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L6" s="2" t="str">
         <f t="shared" si="1"/>
         <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000001'::bigint,'menu_RefID', '97000000000005'::bigint)))::varchar;</v>
       </c>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B7" s="6">
         <f>[1]Main!$E7</f>
         <v>97000000000006</v>
       </c>
       <c r="C7" s="7" t="str">
-        <f>VLOOKUP($B7, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <f>VLOOKUP($B7, [1]Main!$E$2:$G$374, 2, FALSE)</f>
         <v>Dashboard.MyDocumentTracking</v>
       </c>
       <c r="D7" s="8" t="str">
-        <f>VLOOKUP($B7, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <f>VLOOKUP($B7, [1]Main!$E$2:$G$374, 3, FALSE)</f>
         <v>My Document Tracking</v>
       </c>
       <c r="F7" s="10" t="s">
@@ -1899,25 +2142,28 @@
         <v>6</v>
       </c>
       <c r="I7" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000001::bigint, 97000000000006::bigint);</v>
       </c>
-      <c r="K7" s="2" t="str">
+      <c r="K7" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L7" s="2" t="str">
         <f t="shared" si="1"/>
         <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000001'::bigint,'menu_RefID', '97000000000006'::bigint)))::varchar;</v>
       </c>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B8" s="6">
         <f>[1]Main!$E8</f>
         <v>97000000000007</v>
       </c>
       <c r="C8" s="7" t="str">
-        <f>VLOOKUP($B8, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <f>VLOOKUP($B8, [1]Main!$E$2:$G$374, 2, FALSE)</f>
         <v>Dashboard.MyDocumentDisposition</v>
       </c>
       <c r="D8" s="8" t="str">
-        <f>VLOOKUP($B8, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <f>VLOOKUP($B8, [1]Main!$E$2:$G$374, 3, FALSE)</f>
         <v>My Document Disposition</v>
       </c>
       <c r="F8" s="10" t="s">
@@ -1931,25 +2177,25 @@
         <v>7</v>
       </c>
       <c r="I8" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000001::bigint, 97000000000007::bigint);</v>
       </c>
-      <c r="K8" s="2" t="str">
+      <c r="L8" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000001'::bigint,'menu_RefID', '97000000000007'::bigint)))::varchar;</v>
-      </c>
-    </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.2">
+        <v/>
+      </c>
+    </row>
+    <row r="9" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B9" s="6">
         <f>[1]Main!$E9</f>
         <v>97000000000008</v>
       </c>
       <c r="C9" s="7" t="str">
-        <f>VLOOKUP($B9, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <f>VLOOKUP($B9, [1]Main!$E$2:$G$374, 2, FALSE)</f>
         <v>Module.General.MasterData.Country.Transaction</v>
       </c>
       <c r="D9" s="8" t="str">
-        <f>VLOOKUP($B9, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <f>VLOOKUP($B9, [1]Main!$E$2:$G$374, 3, FALSE)</f>
         <v>Country</v>
       </c>
       <c r="F9" s="10" t="s">
@@ -1963,25 +2209,25 @@
         <v>8</v>
       </c>
       <c r="I9" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000002::bigint, 97000000000008::bigint);</v>
       </c>
-      <c r="K9" s="2" t="str">
+      <c r="L9" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000002'::bigint,'menu_RefID', '97000000000008'::bigint)))::varchar;</v>
-      </c>
-    </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.2">
+        <v/>
+      </c>
+    </row>
+    <row r="10" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B10" s="6">
         <f>[1]Main!$E10</f>
         <v>97000000000009</v>
       </c>
       <c r="C10" s="7" t="str">
-        <f>VLOOKUP($B10, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <f>VLOOKUP($B10, [1]Main!$E$2:$G$374, 2, FALSE)</f>
         <v>Module.General.MasterData.CountryAdministrativeAreaLevel1.Transaction</v>
       </c>
       <c r="D10" s="8" t="str">
-        <f>VLOOKUP($B10, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <f>VLOOKUP($B10, [1]Main!$E$2:$G$374, 3, FALSE)</f>
         <v>Province / State</v>
       </c>
       <c r="F10" s="10" t="s">
@@ -1995,25 +2241,25 @@
         <v>9</v>
       </c>
       <c r="I10" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000002::bigint, 97000000000009::bigint);</v>
       </c>
-      <c r="K10" s="2" t="str">
+      <c r="L10" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000002'::bigint,'menu_RefID', '97000000000009'::bigint)))::varchar;</v>
-      </c>
-    </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.2">
+        <v/>
+      </c>
+    </row>
+    <row r="11" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B11" s="6">
         <f>[1]Main!$E11</f>
         <v>97000000000010</v>
       </c>
       <c r="C11" s="7" t="str">
-        <f>VLOOKUP($B11, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <f>VLOOKUP($B11, [1]Main!$E$2:$G$374, 2, FALSE)</f>
         <v>Module.General.MasterData.CountryAdministrativeAreaLevel2.Transaction</v>
       </c>
       <c r="D11" s="8" t="str">
-        <f>VLOOKUP($B11, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <f>VLOOKUP($B11, [1]Main!$E$2:$G$374, 3, FALSE)</f>
         <v>Municipality / Regency</v>
       </c>
       <c r="F11" s="10" t="s">
@@ -2027,25 +2273,25 @@
         <v>10</v>
       </c>
       <c r="I11" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000002::bigint, 97000000000010::bigint);</v>
       </c>
-      <c r="K11" s="2" t="str">
+      <c r="L11" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000002'::bigint,'menu_RefID', '97000000000010'::bigint)))::varchar;</v>
-      </c>
-    </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.2">
+        <v/>
+      </c>
+    </row>
+    <row r="12" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B12" s="6">
         <f>[1]Main!$E12</f>
         <v>97000000000011</v>
       </c>
       <c r="C12" s="7" t="str">
-        <f>VLOOKUP($B12, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <f>VLOOKUP($B12, [1]Main!$E$2:$G$374, 2, FALSE)</f>
         <v>Module.General.MasterData.CountryAdministrativeAreaLevel3.Transaction</v>
       </c>
       <c r="D12" s="8" t="str">
-        <f>VLOOKUP($B12, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <f>VLOOKUP($B12, [1]Main!$E$2:$G$374, 3, FALSE)</f>
         <v>District</v>
       </c>
       <c r="F12" s="10" t="s">
@@ -2059,25 +2305,25 @@
         <v>11</v>
       </c>
       <c r="I12" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000002::bigint, 97000000000011::bigint);</v>
       </c>
-      <c r="K12" s="2" t="str">
+      <c r="L12" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000002'::bigint,'menu_RefID', '97000000000011'::bigint)))::varchar;</v>
-      </c>
-    </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.2">
+        <v/>
+      </c>
+    </row>
+    <row r="13" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B13" s="6">
         <f>[1]Main!$E13</f>
         <v>97000000000012</v>
       </c>
       <c r="C13" s="7" t="str">
-        <f>VLOOKUP($B13, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <f>VLOOKUP($B13, [1]Main!$E$2:$G$374, 2, FALSE)</f>
         <v>Module.General.MasterData.CountryAdministrativeAreaLevel4.Transaction</v>
       </c>
       <c r="D13" s="8" t="str">
-        <f>VLOOKUP($B13, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <f>VLOOKUP($B13, [1]Main!$E$2:$G$374, 3, FALSE)</f>
         <v>Urban Village / Village</v>
       </c>
       <c r="F13" s="10" t="s">
@@ -2091,25 +2337,25 @@
         <v>12</v>
       </c>
       <c r="I13" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000002::bigint, 97000000000012::bigint);</v>
       </c>
-      <c r="K13" s="2" t="str">
+      <c r="L13" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000002'::bigint,'menu_RefID', '97000000000012'::bigint)))::varchar;</v>
-      </c>
-    </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.2">
+        <v/>
+      </c>
+    </row>
+    <row r="14" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B14" s="6">
         <f>[1]Main!$E14</f>
         <v>97000000000013</v>
       </c>
       <c r="C14" s="7" t="str">
-        <f>VLOOKUP($B14, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <f>VLOOKUP($B14, [1]Main!$E$2:$G$374, 2, FALSE)</f>
         <v>Module.General.MasterData.BusinessDocumentType.Transaction</v>
       </c>
       <c r="D14" s="8" t="str">
-        <f>VLOOKUP($B14, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <f>VLOOKUP($B14, [1]Main!$E$2:$G$374, 3, FALSE)</f>
         <v>Business Document Type</v>
       </c>
       <c r="F14" s="10" t="s">
@@ -2123,25 +2369,25 @@
         <v>13</v>
       </c>
       <c r="I14" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000002::bigint, 97000000000013::bigint);</v>
       </c>
-      <c r="K14" s="2" t="str">
+      <c r="L14" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000002'::bigint,'menu_RefID', '97000000000013'::bigint)))::varchar;</v>
-      </c>
-    </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.2">
+        <v/>
+      </c>
+    </row>
+    <row r="15" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B15" s="6">
         <f>[1]Main!$E15</f>
         <v>97000000000014</v>
       </c>
       <c r="C15" s="7" t="str">
-        <f>VLOOKUP($B15, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <f>VLOOKUP($B15, [1]Main!$E$2:$G$374, 2, FALSE)</f>
         <v>Module.General.MasterData.BusinessDocument.Transaction</v>
       </c>
       <c r="D15" s="8" t="str">
-        <f>VLOOKUP($B15, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <f>VLOOKUP($B15, [1]Main!$E$2:$G$374, 3, FALSE)</f>
         <v>Business Document</v>
       </c>
       <c r="F15" s="10" t="s">
@@ -2155,25 +2401,25 @@
         <v>14</v>
       </c>
       <c r="I15" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000002::bigint, 97000000000014::bigint);</v>
       </c>
-      <c r="K15" s="2" t="str">
+      <c r="L15" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000002'::bigint,'menu_RefID', '97000000000014'::bigint)))::varchar;</v>
-      </c>
-    </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.2">
+        <v/>
+      </c>
+    </row>
+    <row r="16" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B16" s="6">
         <f>[1]Main!$E16</f>
         <v>97000000000015</v>
       </c>
       <c r="C16" s="7" t="str">
-        <f>VLOOKUP($B16, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <f>VLOOKUP($B16, [1]Main!$E$2:$G$374, 2, FALSE)</f>
         <v>Module.General.MasterData.BusinessDocumentVersion.Transaction</v>
       </c>
       <c r="D16" s="8" t="str">
-        <f>VLOOKUP($B16, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <f>VLOOKUP($B16, [1]Main!$E$2:$G$374, 3, FALSE)</f>
         <v>Business Document Version</v>
       </c>
       <c r="F16" s="10" t="s">
@@ -2187,25 +2433,25 @@
         <v>15</v>
       </c>
       <c r="I16" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000002::bigint, 97000000000015::bigint);</v>
       </c>
-      <c r="K16" s="2" t="str">
+      <c r="L16" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000002'::bigint,'menu_RefID', '97000000000015'::bigint)))::varchar;</v>
-      </c>
-    </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.2">
+        <v/>
+      </c>
+    </row>
+    <row r="17" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B17" s="6">
         <f>[1]Main!$E17</f>
         <v>97000000000016</v>
       </c>
       <c r="C17" s="7" t="str">
-        <f>VLOOKUP($B17, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <f>VLOOKUP($B17, [1]Main!$E$2:$G$374, 2, FALSE)</f>
         <v>Module.General.MasterData.MenuManagement.Transaction</v>
       </c>
       <c r="D17" s="8" t="str">
-        <f>VLOOKUP($B17, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <f>VLOOKUP($B17, [1]Main!$E$2:$G$374, 3, FALSE)</f>
         <v>Menu Management</v>
       </c>
       <c r="F17" s="10" t="s">
@@ -2219,89 +2465,98 @@
         <v>16</v>
       </c>
       <c r="I17" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000002::bigint, 97000000000016::bigint);</v>
       </c>
-      <c r="K17" s="2" t="str">
+      <c r="K17" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L17" s="2" t="str">
         <f t="shared" si="1"/>
         <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000002'::bigint,'menu_RefID', '97000000000016'::bigint)))::varchar;</v>
       </c>
     </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B18" s="6">
         <f>[1]Main!$E18</f>
         <v>97000000000017</v>
       </c>
       <c r="C18" s="7" t="str">
-        <f>VLOOKUP($B18, [1]Main!$E$2:$G$358, 2, FALSE)</f>
-        <v>Module.General.MasterData.PrivilegeMenu.Transaction</v>
+        <f>VLOOKUP($B18, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.Budgeting.MasterData.Budget.Transaction</v>
       </c>
       <c r="D18" s="8" t="str">
-        <f>VLOOKUP($B18, [1]Main!$E$2:$G$358, 3, FALSE)</f>
-        <v>Privilege Menu</v>
+        <f>VLOOKUP($B18, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>Budget</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G18" s="6">
         <f>IF(EXACT($F18, ""), "", VLOOKUP($F18, [2]Main!$B$2:$E$30, 4, FALSE))</f>
-        <v>254000000000002</v>
+        <v>254000000000004</v>
       </c>
       <c r="H18" s="2">
         <v>17</v>
       </c>
       <c r="I18" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000002::bigint, 97000000000017::bigint);</v>
-      </c>
-      <c r="K18" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000004::bigint, 97000000000017::bigint);</v>
+      </c>
+      <c r="K18" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L18" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000002'::bigint,'menu_RefID', '97000000000017'::bigint)))::varchar;</v>
-      </c>
-    </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.2">
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000004'::bigint,'menu_RefID', '97000000000017'::bigint)))::varchar;</v>
+      </c>
+    </row>
+    <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="6">
         <f>[1]Main!$E19</f>
         <v>97000000000018</v>
       </c>
       <c r="C19" s="7" t="str">
-        <f>VLOOKUP($B19, [1]Main!$E$2:$G$358, 2, FALSE)</f>
-        <v>Module.General.MasterData.Workflow.Transaction</v>
+        <f>VLOOKUP($B19, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.Budgeting.MasterData.BudgetSection.Transaction</v>
       </c>
       <c r="D19" s="8" t="str">
-        <f>VLOOKUP($B19, [1]Main!$E$2:$G$358, 3, FALSE)</f>
-        <v>Workflow</v>
+        <f>VLOOKUP($B19, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>Sub Budget</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G19" s="6">
         <f>IF(EXACT($F19, ""), "", VLOOKUP($F19, [2]Main!$B$2:$E$30, 4, FALSE))</f>
-        <v>254000000000002</v>
+        <v>254000000000004</v>
       </c>
       <c r="H19" s="2">
         <v>18</v>
       </c>
       <c r="I19" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000002::bigint, 97000000000018::bigint);</v>
-      </c>
-      <c r="K19" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000004::bigint, 97000000000018::bigint);</v>
+      </c>
+      <c r="K19" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L19" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000002'::bigint,'menu_RefID', '97000000000018'::bigint)))::varchar;</v>
-      </c>
-    </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.2">
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000004'::bigint,'menu_RefID', '97000000000018'::bigint)))::varchar;</v>
+      </c>
+    </row>
+    <row r="20" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B20" s="6">
         <f>[1]Main!$E20</f>
         <v>97000000000019</v>
       </c>
       <c r="C20" s="7" t="str">
-        <f>VLOOKUP($B20, [1]Main!$E$2:$G$358, 2, FALSE)</f>
-        <v>Module.Budgeting.MasterData.Budget.Transaction</v>
+        <f>VLOOKUP($B20, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.Budgeting.Data.Budget.Report.Transaction</v>
       </c>
       <c r="D20" s="8" t="str">
-        <f>VLOOKUP($B20, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <f>VLOOKUP($B20, [1]Main!$E$2:$G$374, 3, FALSE)</f>
         <v>Budget</v>
       </c>
       <c r="F20" s="10" t="s">
@@ -2315,26 +2570,29 @@
         <v>19</v>
       </c>
       <c r="I20" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000004::bigint, 97000000000019::bigint);</v>
       </c>
-      <c r="K20" s="2" t="str">
+      <c r="K20" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L20" s="2" t="str">
         <f t="shared" si="1"/>
         <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000004'::bigint,'menu_RefID', '97000000000019'::bigint)))::varchar;</v>
       </c>
     </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B21" s="6">
         <f>[1]Main!$E21</f>
         <v>97000000000020</v>
       </c>
       <c r="C21" s="7" t="str">
-        <f>VLOOKUP($B21, [1]Main!$E$2:$G$358, 2, FALSE)</f>
-        <v>Module.Budgeting.MasterData.BudgetSection.Transaction</v>
+        <f>VLOOKUP($B21, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.Budgeting.Data.Budget.Report.Resume</v>
       </c>
       <c r="D21" s="8" t="str">
-        <f>VLOOKUP($B21, [1]Main!$E$2:$G$358, 3, FALSE)</f>
-        <v>Sub Budget</v>
+        <f>VLOOKUP($B21, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>Report Budget Summary</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>6</v>
@@ -2347,25 +2605,28 @@
         <v>20</v>
       </c>
       <c r="I21" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000004::bigint, 97000000000020::bigint);</v>
       </c>
-      <c r="K21" s="2" t="str">
+      <c r="K21" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L21" s="2" t="str">
         <f t="shared" si="1"/>
         <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000004'::bigint,'menu_RefID', '97000000000020'::bigint)))::varchar;</v>
       </c>
     </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B22" s="6">
         <f>[1]Main!$E22</f>
         <v>97000000000021</v>
       </c>
       <c r="C22" s="7" t="str">
-        <f>VLOOKUP($B22, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <f>VLOOKUP($B22, [1]Main!$E$2:$G$374, 2, FALSE)</f>
         <v>Module.Budgeting.Data.ModifyBudget.Transaction</v>
       </c>
       <c r="D22" s="8" t="str">
-        <f>VLOOKUP($B22, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <f>VLOOKUP($B22, [1]Main!$E$2:$G$374, 3, FALSE)</f>
         <v>Modify Budget</v>
       </c>
       <c r="F22" s="10" t="s">
@@ -2379,25 +2640,28 @@
         <v>21</v>
       </c>
       <c r="I22" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000004::bigint, 97000000000021::bigint);</v>
       </c>
-      <c r="K22" s="2" t="str">
+      <c r="K22" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L22" s="2" t="str">
         <f t="shared" si="1"/>
         <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000004'::bigint,'menu_RefID', '97000000000021'::bigint)))::varchar;</v>
       </c>
     </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B23" s="6">
         <f>[1]Main!$E23</f>
         <v>97000000000022</v>
       </c>
       <c r="C23" s="7" t="str">
-        <f>VLOOKUP($B23, [1]Main!$E$2:$G$358, 2, FALSE)</f>
+        <f>VLOOKUP($B23, [1]Main!$E$2:$G$374, 2, FALSE)</f>
         <v>Module.Budgeting.Data.ModifyBudget.Report.Resume</v>
       </c>
       <c r="D23" s="8" t="str">
-        <f>VLOOKUP($B23, [1]Main!$E$2:$G$358, 3, FALSE)</f>
+        <f>VLOOKUP($B23, [1]Main!$E$2:$G$374, 3, FALSE)</f>
         <v>Report Modify Budget Summary</v>
       </c>
       <c r="F23" s="10" t="s">
@@ -2411,26 +2675,29 @@
         <v>22</v>
       </c>
       <c r="I23" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000004::bigint, 97000000000022::bigint);</v>
       </c>
-      <c r="K23" s="2" t="str">
+      <c r="K23" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L23" s="2" t="str">
         <f t="shared" si="1"/>
         <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000004'::bigint,'menu_RefID', '97000000000022'::bigint)))::varchar;</v>
       </c>
     </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B24" s="6">
         <f>[1]Main!$E24</f>
         <v>97000000000023</v>
       </c>
       <c r="C24" s="7" t="str">
-        <f>VLOOKUP($B24, [1]Main!$E$2:$G$358, 2, FALSE)</f>
-        <v>Module.Budgeting.Data.Work.Transaction</v>
+        <f>VLOOKUP($B24, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.Budgeting.Data.ProgressBudget.Transaction</v>
       </c>
       <c r="D24" s="8" t="str">
-        <f>VLOOKUP($B24, [1]Main!$E$2:$G$358, 3, FALSE)</f>
-        <v>Work</v>
+        <f>VLOOKUP($B24, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>Progress Budget</v>
       </c>
       <c r="F24" s="10" t="s">
         <v>6</v>
@@ -2443,26 +2710,29 @@
         <v>23</v>
       </c>
       <c r="I24" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000004::bigint, 97000000000023::bigint);</v>
       </c>
-      <c r="K24" s="2" t="str">
+      <c r="K24" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L24" s="2" t="str">
         <f t="shared" si="1"/>
         <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000004'::bigint,'menu_RefID', '97000000000023'::bigint)))::varchar;</v>
       </c>
     </row>
-    <row r="25" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B25" s="6">
         <f>[1]Main!$E25</f>
         <v>97000000000024</v>
       </c>
       <c r="C25" s="7" t="str">
-        <f>VLOOKUP($B25, [1]Main!$E$2:$G$358, 2, FALSE)</f>
-        <v>Module.Budgeting.Data.CFS.Report.Resume</v>
+        <f>VLOOKUP($B25, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.Budgeting.Data.ProgressBudget.Report.Resume</v>
       </c>
       <c r="D25" s="8" t="str">
-        <f>VLOOKUP($B25, [1]Main!$E$2:$G$358, 3, FALSE)</f>
-        <v>Report Cost Financial Structure</v>
+        <f>VLOOKUP($B25, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>Report Progress Budget Summary</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>6</v>
@@ -2475,90 +2745,99 @@
         <v>24</v>
       </c>
       <c r="I25" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000004::bigint, 97000000000024::bigint);</v>
       </c>
-      <c r="K25" s="2" t="str">
+      <c r="K25" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L25" s="2" t="str">
         <f t="shared" si="1"/>
         <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000004'::bigint,'menu_RefID', '97000000000024'::bigint)))::varchar;</v>
       </c>
     </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="6">
         <f>[1]Main!$E26</f>
         <v>97000000000025</v>
       </c>
       <c r="C26" s="7" t="str">
-        <f>VLOOKUP($B26, [1]Main!$E$2:$G$358, 2, FALSE)</f>
-        <v>Module.General.MasterData.BloodAglutinogenType.Transaction</v>
+        <f>VLOOKUP($B26, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.Budgeting.Data.SCurve.Report.Resume</v>
       </c>
       <c r="D26" s="8" t="str">
-        <f>VLOOKUP($B26, [1]Main!$E$2:$G$358, 3, FALSE)</f>
-        <v>Blood Aglutinogen Type</v>
+        <f>VLOOKUP($B26, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>S-Curve Summary</v>
       </c>
       <c r="F26" s="10" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G26" s="6">
         <f>IF(EXACT($F26, ""), "", VLOOKUP($F26, [2]Main!$B$2:$E$30, 4, FALSE))</f>
-        <v>254000000000007</v>
+        <v>254000000000004</v>
       </c>
       <c r="H26" s="2">
         <v>25</v>
       </c>
       <c r="I26" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000007::bigint, 97000000000025::bigint);</v>
-      </c>
-      <c r="K26" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000004::bigint, 97000000000025::bigint);</v>
+      </c>
+      <c r="K26" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L26" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000007'::bigint,'menu_RefID', '97000000000025'::bigint)))::varchar;</v>
-      </c>
-    </row>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.2">
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000004'::bigint,'menu_RefID', '97000000000025'::bigint)))::varchar;</v>
+      </c>
+    </row>
+    <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="6">
         <f>[1]Main!$E27</f>
         <v>97000000000026</v>
       </c>
       <c r="C27" s="7" t="str">
-        <f>VLOOKUP($B27, [1]Main!$E$2:$G$358, 2, FALSE)</f>
-        <v>Module.General.MasterData.Person.Transaction</v>
+        <f>VLOOKUP($B27, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.Budgeting.Data.Work.Transaction</v>
       </c>
       <c r="D27" s="8" t="str">
-        <f>VLOOKUP($B27, [1]Main!$E$2:$G$358, 3, FALSE)</f>
-        <v>Person</v>
+        <f>VLOOKUP($B27, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>Work</v>
       </c>
       <c r="F27" s="10" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G27" s="6">
         <f>IF(EXACT($F27, ""), "", VLOOKUP($F27, [2]Main!$B$2:$E$30, 4, FALSE))</f>
-        <v>254000000000007</v>
+        <v>254000000000004</v>
       </c>
       <c r="H27" s="2">
         <v>26</v>
       </c>
       <c r="I27" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000007::bigint, 97000000000026::bigint);</v>
-      </c>
-      <c r="K27" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000004::bigint, 97000000000026::bigint);</v>
+      </c>
+      <c r="K27" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L27" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000007'::bigint,'menu_RefID', '97000000000026'::bigint)))::varchar;</v>
-      </c>
-    </row>
-    <row r="28" spans="2:11" x14ac:dyDescent="0.2">
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000004'::bigint,'menu_RefID', '97000000000026'::bigint)))::varchar;</v>
+      </c>
+    </row>
+    <row r="28" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B28" s="6">
         <f>[1]Main!$E28</f>
         <v>97000000000027</v>
       </c>
       <c r="C28" s="7" t="str">
-        <f>VLOOKUP($B28, [1]Main!$E$2:$G$358, 2, FALSE)</f>
-        <v>Module.General.MasterData.Religion.Transaction</v>
+        <f>VLOOKUP($B28, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.Budgeting.Data.CFS.Report.Resume</v>
       </c>
       <c r="D28" s="8" t="str">
-        <f>VLOOKUP($B28, [1]Main!$E$2:$G$358, 3, FALSE)</f>
-        <v>Religion</v>
+        <f>VLOOKUP($B28, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>Report Cost Financial Structure</v>
       </c>
       <c r="F28" s="10" t="s">
         <v>3</v>
@@ -2571,26 +2850,26 @@
         <v>27</v>
       </c>
       <c r="I28" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000007::bigint, 97000000000027::bigint);</v>
       </c>
-      <c r="K28" s="2" t="str">
+      <c r="L28" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000007'::bigint,'menu_RefID', '97000000000027'::bigint)))::varchar;</v>
-      </c>
-    </row>
-    <row r="29" spans="2:11" x14ac:dyDescent="0.2">
+        <v/>
+      </c>
+    </row>
+    <row r="29" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B29" s="6">
         <f>[1]Main!$E29</f>
         <v>97000000000028</v>
       </c>
       <c r="C29" s="7" t="str">
-        <f>VLOOKUP($B29, [1]Main!$E$2:$G$358, 2, FALSE)</f>
-        <v>Module.General.MasterData.UserRole.Transaction</v>
+        <f>VLOOKUP($B29, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.General.MasterData.BloodAglutinogenType.Transaction</v>
       </c>
       <c r="D29" s="8" t="str">
-        <f>VLOOKUP($B29, [1]Main!$E$2:$G$358, 3, FALSE)</f>
-        <v>Role</v>
+        <f>VLOOKUP($B29, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>Blood Aglutinogen Type</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>3</v>
@@ -2603,26 +2882,26 @@
         <v>28</v>
       </c>
       <c r="I29" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000007::bigint, 97000000000028::bigint);</v>
       </c>
-      <c r="K29" s="2" t="str">
+      <c r="L29" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000007'::bigint,'menu_RefID', '97000000000028'::bigint)))::varchar;</v>
-      </c>
-    </row>
-    <row r="30" spans="2:11" x14ac:dyDescent="0.2">
+        <v/>
+      </c>
+    </row>
+    <row r="30" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B30" s="6">
         <f>[1]Main!$E30</f>
         <v>97000000000029</v>
       </c>
       <c r="C30" s="7" t="str">
-        <f>VLOOKUP($B30, [1]Main!$E$2:$G$358, 2, FALSE)</f>
-        <v>Module.HumanResource.MasterData.OrganizationalDepartment.Transaction</v>
+        <f>VLOOKUP($B30, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.General.MasterData.Person.Transaction</v>
       </c>
       <c r="D30" s="8" t="str">
-        <f>VLOOKUP($B30, [1]Main!$E$2:$G$358, 3, FALSE)</f>
-        <v>Department</v>
+        <f>VLOOKUP($B30, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>Person</v>
       </c>
       <c r="F30" s="10" t="s">
         <v>3</v>
@@ -2635,26 +2914,26 @@
         <v>29</v>
       </c>
       <c r="I30" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000007::bigint, 97000000000029::bigint);</v>
       </c>
-      <c r="K30" s="2" t="str">
+      <c r="L30" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000007'::bigint,'menu_RefID', '97000000000029'::bigint)))::varchar;</v>
-      </c>
-    </row>
-    <row r="31" spans="2:11" x14ac:dyDescent="0.2">
+        <v/>
+      </c>
+    </row>
+    <row r="31" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B31" s="6">
         <f>[1]Main!$E31</f>
         <v>97000000000030</v>
       </c>
       <c r="C31" s="7" t="str">
-        <f>VLOOKUP($B31, [1]Main!$E$2:$G$358, 2, FALSE)</f>
-        <v>Module.HumanResource.Data.PersonWorkTimeSheet.Transaction</v>
+        <f>VLOOKUP($B31, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.General.MasterData.PrivilegeMenu.Transaction</v>
       </c>
       <c r="D31" s="8" t="str">
-        <f>VLOOKUP($B31, [1]Main!$E$2:$G$358, 3, FALSE)</f>
-        <v>Person Work Time Sheet</v>
+        <f>VLOOKUP($B31, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>Privilege Menu</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>3</v>
@@ -2667,26 +2946,29 @@
         <v>30</v>
       </c>
       <c r="I31" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000007::bigint, 97000000000030::bigint);</v>
       </c>
-      <c r="K31" s="2" t="str">
+      <c r="K31" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L31" s="2" t="str">
         <f t="shared" si="1"/>
         <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000007'::bigint,'menu_RefID', '97000000000030'::bigint)))::varchar;</v>
       </c>
     </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B32" s="6">
         <f>[1]Main!$E32</f>
         <v>97000000000031</v>
       </c>
       <c r="C32" s="7" t="str">
-        <f>VLOOKUP($B32, [1]Main!$E$2:$G$358, 2, FALSE)</f>
-        <v>Module.HumanResource.Data.PersonWorkTimeSheet.Report.DataList</v>
+        <f>VLOOKUP($B32, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.General.MasterData.Religion.Transaction</v>
       </c>
       <c r="D32" s="8" t="str">
-        <f>VLOOKUP($B32, [1]Main!$E$2:$G$358, 3, FALSE)</f>
-        <v>Person Work Time Sheet Summary</v>
+        <f>VLOOKUP($B32, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>Religion</v>
       </c>
       <c r="F32" s="10" t="s">
         <v>3</v>
@@ -2699,26 +2981,27 @@
         <v>31</v>
       </c>
       <c r="I32" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000007::bigint, 97000000000031::bigint);</v>
       </c>
-      <c r="K32" s="2" t="str">
+      <c r="K32" s="12"/>
+      <c r="L32" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000007'::bigint,'menu_RefID', '97000000000031'::bigint)))::varchar;</v>
-      </c>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+        <v/>
+      </c>
+    </row>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="6">
         <f>[1]Main!$E33</f>
         <v>97000000000032</v>
       </c>
       <c r="C33" s="7" t="str">
-        <f>VLOOKUP($B33, [1]Main!$E$2:$G$358, 2, FALSE)</f>
-        <v>Module.HumanResource.Data.SallaryAllocation.Transaction</v>
+        <f>VLOOKUP($B33, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.General.MasterData.User.Transaction</v>
       </c>
       <c r="D33" s="8" t="str">
-        <f>VLOOKUP($B33, [1]Main!$E$2:$G$358, 3, FALSE)</f>
-        <v>Sallary Allocation</v>
+        <f>VLOOKUP($B33, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>User</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>3</v>
@@ -2731,26 +3014,29 @@
         <v>32</v>
       </c>
       <c r="I33" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000007::bigint, 97000000000032::bigint);</v>
       </c>
-      <c r="K33" s="2" t="str">
+      <c r="K33" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L33" s="2" t="str">
         <f t="shared" si="1"/>
         <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000007'::bigint,'menu_RefID', '97000000000032'::bigint)))::varchar;</v>
       </c>
     </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="6">
         <f>[1]Main!$E34</f>
         <v>97000000000033</v>
       </c>
       <c r="C34" s="7" t="str">
-        <f>VLOOKUP($B34, [1]Main!$E$2:$G$358, 2, FALSE)</f>
-        <v>Module.HumanResource.Data.SallaryAllocation.Report.DataList</v>
+        <f>VLOOKUP($B34, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.General.MasterData.UserRole.Transaction</v>
       </c>
       <c r="D34" s="8" t="str">
-        <f>VLOOKUP($B34, [1]Main!$E$2:$G$358, 3, FALSE)</f>
-        <v>Sallary Allocation Summary</v>
+        <f>VLOOKUP($B34, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>Role</v>
       </c>
       <c r="F34" s="10" t="s">
         <v>3</v>
@@ -2763,218 +3049,236 @@
         <v>33</v>
       </c>
       <c r="I34" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000007::bigint, 97000000000033::bigint);</v>
       </c>
-      <c r="K34" s="2" t="str">
+      <c r="K34" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L34" s="2" t="str">
         <f t="shared" si="1"/>
         <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000007'::bigint,'menu_RefID', '97000000000033'::bigint)))::varchar;</v>
       </c>
     </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B35" s="6">
         <f>[1]Main!$E35</f>
         <v>97000000000034</v>
       </c>
       <c r="C35" s="7" t="str">
-        <f>VLOOKUP($B35, [1]Main!$E$2:$G$358, 2, FALSE)</f>
-        <v>Module.General.MasterData.Warehouse.Transaction</v>
+        <f>VLOOKUP($B35, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.General.MasterData.Workflow.Transaction</v>
       </c>
       <c r="D35" s="8" t="str">
-        <f>VLOOKUP($B35, [1]Main!$E$2:$G$358, 3, FALSE)</f>
-        <v>Warehouse</v>
+        <f>VLOOKUP($B35, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>Workflow</v>
       </c>
       <c r="F35" s="10" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G35" s="6">
         <f>IF(EXACT($F35, ""), "", VLOOKUP($F35, [2]Main!$B$2:$E$30, 4, FALSE))</f>
-        <v>254000000000009</v>
+        <v>254000000000007</v>
       </c>
       <c r="H35" s="2">
         <v>34</v>
       </c>
       <c r="I35" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000009::bigint, 97000000000034::bigint);</v>
-      </c>
-      <c r="K35" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000007::bigint, 97000000000034::bigint);</v>
+      </c>
+      <c r="K35" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L35" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000009'::bigint,'menu_RefID', '97000000000034'::bigint)))::varchar;</v>
-      </c>
-    </row>
-    <row r="36" spans="2:11" x14ac:dyDescent="0.2">
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000007'::bigint,'menu_RefID', '97000000000034'::bigint)))::varchar;</v>
+      </c>
+    </row>
+    <row r="36" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B36" s="6">
         <f>[1]Main!$E36</f>
         <v>97000000000035</v>
       </c>
       <c r="C36" s="7" t="str">
-        <f>VLOOKUP($B36, [1]Main!$E$2:$G$358, 2, FALSE)</f>
-        <v>Module.General.MasterData.ProductType.Transaction</v>
+        <f>VLOOKUP($B36, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.HumanResource.MasterData.OrganizationalDepartment.Transaction</v>
       </c>
       <c r="D36" s="8" t="str">
-        <f>VLOOKUP($B36, [1]Main!$E$2:$G$358, 3, FALSE)</f>
-        <v>Product Type</v>
+        <f>VLOOKUP($B36, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>Department</v>
       </c>
       <c r="F36" s="10" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G36" s="6">
         <f>IF(EXACT($F36, ""), "", VLOOKUP($F36, [2]Main!$B$2:$E$30, 4, FALSE))</f>
-        <v>254000000000009</v>
+        <v>254000000000007</v>
       </c>
       <c r="H36" s="2">
         <v>35</v>
       </c>
       <c r="I36" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000009::bigint, 97000000000035::bigint);</v>
-      </c>
-      <c r="K36" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000007::bigint, 97000000000035::bigint);</v>
+      </c>
+      <c r="K36" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L36" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000009'::bigint,'menu_RefID', '97000000000035'::bigint)))::varchar;</v>
-      </c>
-    </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000007'::bigint,'menu_RefID', '97000000000035'::bigint)))::varchar;</v>
+      </c>
+    </row>
+    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B37" s="6">
         <f>[1]Main!$E37</f>
         <v>97000000000036</v>
       </c>
       <c r="C37" s="7" t="str">
-        <f>VLOOKUP($B37, [1]Main!$E$2:$G$358, 2, FALSE)</f>
-        <v>Module.General.MasterData.Product.Transaction</v>
+        <f>VLOOKUP($B37, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.HumanResource.Data.PersonWorkTimeSheet.Transaction</v>
       </c>
       <c r="D37" s="8" t="str">
-        <f>VLOOKUP($B37, [1]Main!$E$2:$G$358, 3, FALSE)</f>
-        <v>Product</v>
+        <f>VLOOKUP($B37, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>Person Work Time Sheet</v>
       </c>
       <c r="F37" s="10" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G37" s="6">
         <f>IF(EXACT($F37, ""), "", VLOOKUP($F37, [2]Main!$B$2:$E$30, 4, FALSE))</f>
-        <v>254000000000009</v>
+        <v>254000000000007</v>
       </c>
       <c r="H37" s="2">
         <v>36</v>
       </c>
       <c r="I37" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000009::bigint, 97000000000036::bigint);</v>
-      </c>
-      <c r="K37" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000007::bigint, 97000000000036::bigint);</v>
+      </c>
+      <c r="K37" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L37" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000009'::bigint,'menu_RefID', '97000000000036'::bigint)))::varchar;</v>
-      </c>
-    </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000007'::bigint,'menu_RefID', '97000000000036'::bigint)))::varchar;</v>
+      </c>
+    </row>
+    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B38" s="6">
         <f>[1]Main!$E38</f>
         <v>97000000000037</v>
       </c>
       <c r="C38" s="7" t="str">
-        <f>VLOOKUP($B38, [1]Main!$E$2:$G$358, 2, FALSE)</f>
-        <v>Module.SupplyChain.Data.DeliveryOrder.Transaction</v>
+        <f>VLOOKUP($B38, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.HumanResource.Data.PersonWorkTimeSheet.Report.DataList</v>
       </c>
       <c r="D38" s="8" t="str">
-        <f>VLOOKUP($B38, [1]Main!$E$2:$G$358, 3, FALSE)</f>
-        <v>Delivery Order</v>
+        <f>VLOOKUP($B38, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>Person Work Time Sheet Summary</v>
       </c>
       <c r="F38" s="10" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G38" s="6">
         <f>IF(EXACT($F38, ""), "", VLOOKUP($F38, [2]Main!$B$2:$E$30, 4, FALSE))</f>
-        <v>254000000000009</v>
+        <v>254000000000007</v>
       </c>
       <c r="H38" s="2">
         <v>37</v>
       </c>
       <c r="I38" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000009::bigint, 97000000000037::bigint);</v>
-      </c>
-      <c r="K38" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000007::bigint, 97000000000037::bigint);</v>
+      </c>
+      <c r="K38" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L38" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000009'::bigint,'menu_RefID', '97000000000037'::bigint)))::varchar;</v>
-      </c>
-    </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000007'::bigint,'menu_RefID', '97000000000037'::bigint)))::varchar;</v>
+      </c>
+    </row>
+    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B39" s="6">
         <f>[1]Main!$E39</f>
         <v>97000000000038</v>
       </c>
       <c r="C39" s="7" t="str">
-        <f>VLOOKUP($B39, [1]Main!$E$2:$G$358, 2, FALSE)</f>
-        <v>Module.SupplyChain.Data.DeliveryOrder.Report.DataList</v>
+        <f>VLOOKUP($B39, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.HumanResource.Data.SallaryAllocation.Transaction</v>
       </c>
       <c r="D39" s="8" t="str">
-        <f>VLOOKUP($B39, [1]Main!$E$2:$G$358, 3, FALSE)</f>
-        <v>Report DO Summary</v>
+        <f>VLOOKUP($B39, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>Sallary Allocation</v>
       </c>
       <c r="F39" s="10" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G39" s="6">
         <f>IF(EXACT($F39, ""), "", VLOOKUP($F39, [2]Main!$B$2:$E$30, 4, FALSE))</f>
-        <v>254000000000009</v>
+        <v>254000000000007</v>
       </c>
       <c r="H39" s="2">
         <v>38</v>
       </c>
       <c r="I39" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000009::bigint, 97000000000038::bigint);</v>
-      </c>
-      <c r="K39" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000007::bigint, 97000000000038::bigint);</v>
+      </c>
+      <c r="K39" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L39" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000009'::bigint,'menu_RefID', '97000000000038'::bigint)))::varchar;</v>
-      </c>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000007'::bigint,'menu_RefID', '97000000000038'::bigint)))::varchar;</v>
+      </c>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B40" s="6">
         <f>[1]Main!$E40</f>
         <v>97000000000039</v>
       </c>
       <c r="C40" s="7" t="str">
-        <f>VLOOKUP($B40, [1]Main!$E$2:$G$358, 2, FALSE)</f>
-        <v>Module.SupplyChain.Data.DeliveryOrderToMaterialReceive.Report.DataList</v>
+        <f>VLOOKUP($B40, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.HumanResource.Data.SallaryAllocation.Report.DataList</v>
       </c>
       <c r="D40" s="8" t="str">
-        <f>VLOOKUP($B40, [1]Main!$E$2:$G$358, 3, FALSE)</f>
-        <v>Report DO to Material Receive</v>
+        <f>VLOOKUP($B40, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>Sallary Allocation Summary</v>
       </c>
       <c r="F40" s="10" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G40" s="6">
         <f>IF(EXACT($F40, ""), "", VLOOKUP($F40, [2]Main!$B$2:$E$30, 4, FALSE))</f>
-        <v>254000000000009</v>
+        <v>254000000000007</v>
       </c>
       <c r="H40" s="2">
         <v>39</v>
       </c>
       <c r="I40" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000009::bigint, 97000000000039::bigint);</v>
-      </c>
-      <c r="K40" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000007::bigint, 97000000000039::bigint);</v>
+      </c>
+      <c r="L40" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000009'::bigint,'menu_RefID', '97000000000039'::bigint)))::varchar;</v>
-      </c>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+        <v/>
+      </c>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="6">
         <f>[1]Main!$E41</f>
         <v>97000000000040</v>
       </c>
       <c r="C41" s="7" t="str">
-        <f>VLOOKUP($B41, [1]Main!$E$2:$G$358, 2, FALSE)</f>
-        <v>Module.SupplyChain.Data.MaterialReceive.Transaction</v>
+        <f>VLOOKUP($B41, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.General.MasterData.Product.Transaction</v>
       </c>
       <c r="D41" s="8" t="str">
-        <f>VLOOKUP($B41, [1]Main!$E$2:$G$358, 3, FALSE)</f>
-        <v>Material Receive</v>
+        <f>VLOOKUP($B41, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>Product</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>7</v>
@@ -2987,26 +3291,26 @@
         <v>40</v>
       </c>
       <c r="I41" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000009::bigint, 97000000000040::bigint);</v>
       </c>
-      <c r="K41" s="2" t="str">
+      <c r="L41" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000009'::bigint,'menu_RefID', '97000000000040'::bigint)))::varchar;</v>
-      </c>
-    </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+        <v/>
+      </c>
+    </row>
+    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B42" s="6">
         <f>[1]Main!$E42</f>
         <v>97000000000041</v>
       </c>
       <c r="C42" s="7" t="str">
-        <f>VLOOKUP($B42, [1]Main!$E$2:$G$358, 2, FALSE)</f>
-        <v>Module.SupplyChain.Data.MaterialReceive.Report.DataList</v>
+        <f>VLOOKUP($B42, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.General.MasterData.ProductType.Transaction</v>
       </c>
       <c r="D42" s="8" t="str">
-        <f>VLOOKUP($B42, [1]Main!$E$2:$G$358, 3, FALSE)</f>
-        <v>Report Material Receive Summary</v>
+        <f>VLOOKUP($B42, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>Product Type</v>
       </c>
       <c r="F42" s="10" t="s">
         <v>7</v>
@@ -3019,26 +3323,29 @@
         <v>41</v>
       </c>
       <c r="I42" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000009::bigint, 97000000000041::bigint);</v>
       </c>
-      <c r="K42" s="2" t="str">
+      <c r="K42" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L42" s="2" t="str">
         <f t="shared" si="1"/>
         <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000009'::bigint,'menu_RefID', '97000000000041'::bigint)))::varchar;</v>
       </c>
     </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B43" s="6">
         <f>[1]Main!$E43</f>
         <v>97000000000042</v>
       </c>
       <c r="C43" s="7" t="str">
-        <f>VLOOKUP($B43, [1]Main!$E$2:$G$358, 2, FALSE)</f>
-        <v>Module.SupplyChain.Data.MaterialReceiveToMaterialReturn.Report.DataList</v>
+        <f>VLOOKUP($B43, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.General.MasterData.Warehouse.Transaction</v>
       </c>
       <c r="D43" s="8" t="str">
-        <f>VLOOKUP($B43, [1]Main!$E$2:$G$358, 3, FALSE)</f>
-        <v>Report Material Receive to Material Return</v>
+        <f>VLOOKUP($B43, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>Warehouse</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>7</v>
@@ -3051,26 +3358,26 @@
         <v>42</v>
       </c>
       <c r="I43" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000009::bigint, 97000000000042::bigint);</v>
       </c>
-      <c r="K43" s="2" t="str">
+      <c r="L43" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000009'::bigint,'menu_RefID', '97000000000042'::bigint)))::varchar;</v>
-      </c>
-    </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+        <v/>
+      </c>
+    </row>
+    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B44" s="6">
         <f>[1]Main!$E44</f>
         <v>97000000000043</v>
       </c>
       <c r="C44" s="7" t="str">
-        <f>VLOOKUP($B44, [1]Main!$E$2:$G$358, 2, FALSE)</f>
-        <v>Module.SupplyChain.Data.MaterialReturn.Transaction</v>
+        <f>VLOOKUP($B44, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.General.MasterData.Work.Transaction</v>
       </c>
       <c r="D44" s="8" t="str">
-        <f>VLOOKUP($B44, [1]Main!$E$2:$G$358, 3, FALSE)</f>
-        <v>Material Return</v>
+        <f>VLOOKUP($B44, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>Work</v>
       </c>
       <c r="F44" s="10" t="s">
         <v>7</v>
@@ -3083,26 +3390,29 @@
         <v>43</v>
       </c>
       <c r="I44" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000009::bigint, 97000000000043::bigint);</v>
       </c>
-      <c r="K44" s="2" t="str">
+      <c r="K44" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L44" s="2" t="str">
         <f t="shared" si="1"/>
         <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000009'::bigint,'menu_RefID', '97000000000043'::bigint)))::varchar;</v>
       </c>
     </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B45" s="6">
         <f>[1]Main!$E45</f>
         <v>97000000000044</v>
       </c>
       <c r="C45" s="7" t="str">
-        <f>VLOOKUP($B45, [1]Main!$E$2:$G$358, 2, FALSE)</f>
-        <v>Module.SupplyChain.Data.MaterialReturn.Report.DataList</v>
+        <f>VLOOKUP($B45, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.SupplyChain.Data.DeliveryOrder.Transaction</v>
       </c>
       <c r="D45" s="8" t="str">
-        <f>VLOOKUP($B45, [1]Main!$E$2:$G$358, 3, FALSE)</f>
-        <v>Report Material Return Summary</v>
+        <f>VLOOKUP($B45, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>Delivery Order</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>7</v>
@@ -3115,314 +3425,344 @@
         <v>44</v>
       </c>
       <c r="I45" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000009::bigint, 97000000000044::bigint);</v>
       </c>
-      <c r="K45" s="2" t="str">
+      <c r="K45" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L45" s="2" t="str">
         <f t="shared" si="1"/>
         <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000009'::bigint,'menu_RefID', '97000000000044'::bigint)))::varchar;</v>
       </c>
     </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B46" s="6">
         <f>[1]Main!$E46</f>
         <v>97000000000045</v>
       </c>
       <c r="C46" s="7" t="str">
-        <f>VLOOKUP($B46, [1]Main!$E$2:$G$358, 2, FALSE)</f>
-        <v>Module.Finance.Data.Advance.Transaction</v>
+        <f>VLOOKUP($B46, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.SupplyChain.Data.DeliveryOrder.Report.DataList</v>
       </c>
       <c r="D46" s="8" t="str">
-        <f>VLOOKUP($B46, [1]Main!$E$2:$G$358, 3, FALSE)</f>
-        <v>Advance Request</v>
+        <f>VLOOKUP($B46, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>Report DO Summary</v>
       </c>
       <c r="F46" s="10" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G46" s="6">
         <f>IF(EXACT($F46, ""), "", VLOOKUP($F46, [2]Main!$B$2:$E$30, 4, FALSE))</f>
-        <v>254000000000008</v>
+        <v>254000000000009</v>
       </c>
       <c r="H46" s="2">
         <v>45</v>
       </c>
       <c r="I46" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000008::bigint, 97000000000045::bigint);</v>
-      </c>
-      <c r="K46" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000009::bigint, 97000000000045::bigint);</v>
+      </c>
+      <c r="K46" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L46" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000008'::bigint,'menu_RefID', '97000000000045'::bigint)))::varchar;</v>
-      </c>
-    </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000009'::bigint,'menu_RefID', '97000000000045'::bigint)))::varchar;</v>
+      </c>
+    </row>
+    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B47" s="6">
         <f>[1]Main!$E47</f>
         <v>97000000000046</v>
       </c>
       <c r="C47" s="7" t="str">
-        <f>VLOOKUP($B47, [1]Main!$E$2:$G$358, 2, FALSE)</f>
-        <v>Module.Finance.Data.Advance.Report.DataList</v>
+        <f>VLOOKUP($B47, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.SupplyChain.Data.DeliveryOrderToMaterialReceive.Report.DataList</v>
       </c>
       <c r="D47" s="8" t="str">
-        <f>VLOOKUP($B47, [1]Main!$E$2:$G$358, 3, FALSE)</f>
-        <v>Report Advance Summary</v>
+        <f>VLOOKUP($B47, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>Report DO to Material Receive</v>
       </c>
       <c r="F47" s="10" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G47" s="6">
         <f>IF(EXACT($F47, ""), "", VLOOKUP($F47, [2]Main!$B$2:$E$30, 4, FALSE))</f>
-        <v>254000000000008</v>
+        <v>254000000000009</v>
       </c>
       <c r="H47" s="2">
         <v>46</v>
       </c>
       <c r="I47" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000008::bigint, 97000000000046::bigint);</v>
-      </c>
-      <c r="K47" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000009::bigint, 97000000000046::bigint);</v>
+      </c>
+      <c r="K47" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L47" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000008'::bigint,'menu_RefID', '97000000000046'::bigint)))::varchar;</v>
-      </c>
-    </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000009'::bigint,'menu_RefID', '97000000000046'::bigint)))::varchar;</v>
+      </c>
+    </row>
+    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B48" s="6">
         <f>[1]Main!$E48</f>
         <v>97000000000047</v>
       </c>
       <c r="C48" s="7" t="str">
-        <f>VLOOKUP($B48, [1]Main!$E$2:$G$358, 2, FALSE)</f>
-        <v>Module.Finance.Data.AdvanceToAdvanceSettlement.Report.DataList</v>
+        <f>VLOOKUP($B48, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.SupplyChain.Data.MaterialReceive.Transaction</v>
       </c>
       <c r="D48" s="8" t="str">
-        <f>VLOOKUP($B48, [1]Main!$E$2:$G$358, 3, FALSE)</f>
-        <v>Report Advance to Advance Settlement</v>
+        <f>VLOOKUP($B48, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>Material Receive</v>
       </c>
       <c r="F48" s="10" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G48" s="6">
         <f>IF(EXACT($F48, ""), "", VLOOKUP($F48, [2]Main!$B$2:$E$30, 4, FALSE))</f>
-        <v>254000000000008</v>
+        <v>254000000000009</v>
       </c>
       <c r="H48" s="2">
         <v>47</v>
       </c>
       <c r="I48" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000008::bigint, 97000000000047::bigint);</v>
-      </c>
-      <c r="K48" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000009::bigint, 97000000000047::bigint);</v>
+      </c>
+      <c r="K48" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L48" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000008'::bigint,'menu_RefID', '97000000000047'::bigint)))::varchar;</v>
-      </c>
-    </row>
-    <row r="49" spans="2:11" x14ac:dyDescent="0.2">
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000009'::bigint,'menu_RefID', '97000000000047'::bigint)))::varchar;</v>
+      </c>
+    </row>
+    <row r="49" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B49" s="6">
         <f>[1]Main!$E49</f>
         <v>97000000000048</v>
       </c>
       <c r="C49" s="7" t="str">
-        <f>VLOOKUP($B49, [1]Main!$E$2:$G$358, 2, FALSE)</f>
-        <v>Module.Finance.Data.AdvanceSettlement.Transaction</v>
+        <f>VLOOKUP($B49, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.SupplyChain.Data.MaterialReceive.Report.DataList</v>
       </c>
       <c r="D49" s="8" t="str">
-        <f>VLOOKUP($B49, [1]Main!$E$2:$G$358, 3, FALSE)</f>
-        <v>AdvanceSettlement</v>
+        <f>VLOOKUP($B49, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>Report Material Receive Summary</v>
       </c>
       <c r="F49" s="10" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G49" s="6">
         <f>IF(EXACT($F49, ""), "", VLOOKUP($F49, [2]Main!$B$2:$E$30, 4, FALSE))</f>
-        <v>254000000000008</v>
+        <v>254000000000009</v>
       </c>
       <c r="H49" s="2">
         <v>48</v>
       </c>
       <c r="I49" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000008::bigint, 97000000000048::bigint);</v>
-      </c>
-      <c r="K49" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000009::bigint, 97000000000048::bigint);</v>
+      </c>
+      <c r="K49" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L49" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000008'::bigint,'menu_RefID', '97000000000048'::bigint)))::varchar;</v>
-      </c>
-    </row>
-    <row r="50" spans="2:11" x14ac:dyDescent="0.2">
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000009'::bigint,'menu_RefID', '97000000000048'::bigint)))::varchar;</v>
+      </c>
+    </row>
+    <row r="50" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B50" s="6">
         <f>[1]Main!$E50</f>
         <v>97000000000049</v>
       </c>
       <c r="C50" s="7" t="str">
-        <f>VLOOKUP($B50, [1]Main!$E$2:$G$358, 2, FALSE)</f>
-        <v>Module.Finance.Data.AdvanceSettlement.Report.DataList</v>
+        <f>VLOOKUP($B50, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.SupplyChain.Data.MaterialReceiveToMaterialReturn.Report.DataList</v>
       </c>
       <c r="D50" s="8" t="str">
-        <f>VLOOKUP($B50, [1]Main!$E$2:$G$358, 3, FALSE)</f>
-        <v>Report Advance Settlement Summary</v>
+        <f>VLOOKUP($B50, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>Report Material Receive to Material Return</v>
       </c>
       <c r="F50" s="10" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G50" s="6">
         <f>IF(EXACT($F50, ""), "", VLOOKUP($F50, [2]Main!$B$2:$E$30, 4, FALSE))</f>
-        <v>254000000000008</v>
+        <v>254000000000009</v>
       </c>
       <c r="H50" s="2">
         <v>49</v>
       </c>
       <c r="I50" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000008::bigint, 97000000000049::bigint);</v>
-      </c>
-      <c r="K50" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000009::bigint, 97000000000049::bigint);</v>
+      </c>
+      <c r="K50" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L50" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000008'::bigint,'menu_RefID', '97000000000049'::bigint)))::varchar;</v>
-      </c>
-    </row>
-    <row r="51" spans="2:11" x14ac:dyDescent="0.2">
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000009'::bigint,'menu_RefID', '97000000000049'::bigint)))::varchar;</v>
+      </c>
+    </row>
+    <row r="51" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B51" s="6">
         <f>[1]Main!$E51</f>
         <v>97000000000050</v>
       </c>
       <c r="C51" s="7" t="str">
-        <f>VLOOKUP($B51, [1]Main!$E$2:$G$358, 2, FALSE)</f>
-        <v>Module.Finance.Data.PersonBusinessTrip.Transaction</v>
+        <f>VLOOKUP($B51, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.SupplyChain.Data.MaterialReturn.Transaction</v>
       </c>
       <c r="D51" s="8" t="str">
-        <f>VLOOKUP($B51, [1]Main!$E$2:$G$358, 3, FALSE)</f>
-        <v>BusinessTrip Request</v>
+        <f>VLOOKUP($B51, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>Material Return</v>
       </c>
       <c r="F51" s="10" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G51" s="6">
         <f>IF(EXACT($F51, ""), "", VLOOKUP($F51, [2]Main!$B$2:$E$30, 4, FALSE))</f>
-        <v>254000000000008</v>
+        <v>254000000000009</v>
       </c>
       <c r="H51" s="2">
         <v>50</v>
       </c>
       <c r="I51" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000008::bigint, 97000000000050::bigint);</v>
-      </c>
-      <c r="K51" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000009::bigint, 97000000000050::bigint);</v>
+      </c>
+      <c r="K51" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L51" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000008'::bigint,'menu_RefID', '97000000000050'::bigint)))::varchar;</v>
-      </c>
-    </row>
-    <row r="52" spans="2:11" x14ac:dyDescent="0.2">
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000009'::bigint,'menu_RefID', '97000000000050'::bigint)))::varchar;</v>
+      </c>
+    </row>
+    <row r="52" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B52" s="6">
         <f>[1]Main!$E52</f>
         <v>97000000000051</v>
       </c>
       <c r="C52" s="7" t="str">
-        <f>VLOOKUP($B52, [1]Main!$E$2:$G$358, 2, FALSE)</f>
-        <v>Module.Finance.Data.PersonBusinessTrip.Report.DataList</v>
+        <f>VLOOKUP($B52, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.SupplyChain.Data.MaterialReturn.Report.DataList</v>
       </c>
       <c r="D52" s="8" t="str">
-        <f>VLOOKUP($B52, [1]Main!$E$2:$G$358, 3, FALSE)</f>
-        <v>Report BusinessTrip Request Summary</v>
+        <f>VLOOKUP($B52, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>Report Material Return Summary</v>
       </c>
       <c r="F52" s="10" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G52" s="6">
         <f>IF(EXACT($F52, ""), "", VLOOKUP($F52, [2]Main!$B$2:$E$30, 4, FALSE))</f>
-        <v>254000000000008</v>
+        <v>254000000000009</v>
       </c>
       <c r="H52" s="2">
         <v>51</v>
       </c>
       <c r="I52" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000008::bigint, 97000000000051::bigint);</v>
-      </c>
-      <c r="K52" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000009::bigint, 97000000000051::bigint);</v>
+      </c>
+      <c r="K52" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L52" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000008'::bigint,'menu_RefID', '97000000000051'::bigint)))::varchar;</v>
-      </c>
-    </row>
-    <row r="53" spans="2:11" x14ac:dyDescent="0.2">
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000009'::bigint,'menu_RefID', '97000000000051'::bigint)))::varchar;</v>
+      </c>
+    </row>
+    <row r="53" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B53" s="6">
         <f>[1]Main!$E53</f>
         <v>97000000000052</v>
       </c>
       <c r="C53" s="7" t="str">
-        <f>VLOOKUP($B53, [1]Main!$E$2:$G$358, 2, FALSE)</f>
-        <v>Module.Finance.Data.PersonBusinessTripToPersonBusinessTripSettlement.Report.DataList</v>
+        <f>VLOOKUP($B53, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.SupplyChain.Data.PhysicalInventoryCount.Transaction</v>
       </c>
       <c r="D53" s="8" t="str">
-        <f>VLOOKUP($B53, [1]Main!$E$2:$G$358, 3, FALSE)</f>
-        <v>Report BusinessTrip to BusinessTrip Settlement</v>
+        <f>VLOOKUP($B53, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>Stock Opname</v>
       </c>
       <c r="F53" s="10" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G53" s="6">
         <f>IF(EXACT($F53, ""), "", VLOOKUP($F53, [2]Main!$B$2:$E$30, 4, FALSE))</f>
-        <v>254000000000008</v>
+        <v>254000000000009</v>
       </c>
       <c r="H53" s="2">
         <v>52</v>
       </c>
       <c r="I53" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000008::bigint, 97000000000052::bigint);</v>
-      </c>
-      <c r="K53" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000009::bigint, 97000000000052::bigint);</v>
+      </c>
+      <c r="K53" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L53" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000008'::bigint,'menu_RefID', '97000000000052'::bigint)))::varchar;</v>
-      </c>
-    </row>
-    <row r="54" spans="2:11" x14ac:dyDescent="0.2">
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000009'::bigint,'menu_RefID', '97000000000052'::bigint)))::varchar;</v>
+      </c>
+    </row>
+    <row r="54" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B54" s="6">
         <f>[1]Main!$E54</f>
         <v>97000000000053</v>
       </c>
       <c r="C54" s="7" t="str">
-        <f>VLOOKUP($B54, [1]Main!$E$2:$G$358, 2, FALSE)</f>
-        <v>Module.Finance.Data.PersonBusinessTripSettlement.Transaction</v>
+        <f>VLOOKUP($B54, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.SupplyChain.Data.PhysicalInventoryCount.Report.DataList</v>
       </c>
       <c r="D54" s="8" t="str">
-        <f>VLOOKUP($B54, [1]Main!$E$2:$G$358, 3, FALSE)</f>
-        <v>BusinessTrip Settlement</v>
+        <f>VLOOKUP($B54, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>Report Stock Opname Summary</v>
       </c>
       <c r="F54" s="10" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G54" s="6">
         <f>IF(EXACT($F54, ""), "", VLOOKUP($F54, [2]Main!$B$2:$E$30, 4, FALSE))</f>
-        <v>254000000000008</v>
+        <v>254000000000009</v>
       </c>
       <c r="H54" s="2">
         <v>53</v>
       </c>
       <c r="I54" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000008::bigint, 97000000000053::bigint);</v>
-      </c>
-      <c r="K54" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000009::bigint, 97000000000053::bigint);</v>
+      </c>
+      <c r="K54" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L54" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000008'::bigint,'menu_RefID', '97000000000053'::bigint)))::varchar;</v>
-      </c>
-    </row>
-    <row r="55" spans="2:11" x14ac:dyDescent="0.2">
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000009'::bigint,'menu_RefID', '97000000000053'::bigint)))::varchar;</v>
+      </c>
+    </row>
+    <row r="55" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B55" s="6">
         <f>[1]Main!$E55</f>
         <v>97000000000054</v>
       </c>
       <c r="C55" s="7" t="str">
-        <f>VLOOKUP($B55, [1]Main!$E$2:$G$358, 2, FALSE)</f>
-        <v>Module.Finance.Data.PersonBusinessTripSettlement.Report.DataList</v>
+        <f>VLOOKUP($B55, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.Finance.Data.Advance.Transaction</v>
       </c>
       <c r="D55" s="8" t="str">
-        <f>VLOOKUP($B55, [1]Main!$E$2:$G$358, 3, FALSE)</f>
-        <v>Report BusinessTrip Settlement Summary</v>
+        <f>VLOOKUP($B55, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>Advance Request</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>8</v>
@@ -3435,395 +3775,435 @@
         <v>54</v>
       </c>
       <c r="I55" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000008::bigint, 97000000000054::bigint);</v>
       </c>
-      <c r="K55" s="2" t="str">
+      <c r="K55" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L55" s="2" t="str">
         <f t="shared" si="1"/>
         <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000008'::bigint,'menu_RefID', '97000000000054'::bigint)))::varchar;</v>
       </c>
     </row>
-    <row r="56" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="56" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B56" s="6">
         <f>[1]Main!$E56</f>
         <v>97000000000055</v>
       </c>
       <c r="C56" s="7" t="str">
-        <f>VLOOKUP($B56, [1]Main!$E$2:$G$358, 2, FALSE)</f>
-        <v>Module.SupplyChain.MasterData.Supplier.Transaction</v>
+        <f>VLOOKUP($B56, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.Finance.Data.Advance.Report.DataList</v>
       </c>
       <c r="D56" s="8" t="str">
-        <f>VLOOKUP($B56, [1]Main!$E$2:$G$358, 3, FALSE)</f>
-        <v>Supplier</v>
+        <f>VLOOKUP($B56, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>Report Advance Summary</v>
       </c>
       <c r="F56" s="10" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G56" s="6">
         <f>IF(EXACT($F56, ""), "", VLOOKUP($F56, [2]Main!$B$2:$E$30, 4, FALSE))</f>
-        <v>254000000000010</v>
+        <v>254000000000008</v>
       </c>
       <c r="H56" s="2">
         <v>55</v>
       </c>
       <c r="I56" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000010::bigint, 97000000000055::bigint);</v>
-      </c>
-      <c r="K56" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000008::bigint, 97000000000055::bigint);</v>
+      </c>
+      <c r="K56" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L56" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000010'::bigint,'menu_RefID', '97000000000055'::bigint)))::varchar;</v>
-      </c>
-    </row>
-    <row r="57" spans="2:11" x14ac:dyDescent="0.2">
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000008'::bigint,'menu_RefID', '97000000000055'::bigint)))::varchar;</v>
+      </c>
+    </row>
+    <row r="57" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B57" s="6">
         <f>[1]Main!$E57</f>
         <v>97000000000056</v>
       </c>
       <c r="C57" s="7" t="str">
-        <f>VLOOKUP($B57, [1]Main!$E$2:$G$358, 2, FALSE)</f>
-        <v>Module.SupplyChain.Data.PurchaseRequisition.Transaction</v>
+        <f>VLOOKUP($B57, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.Finance.Data.AdvanceToAdvanceSettlement.Report.DataList</v>
       </c>
       <c r="D57" s="8" t="str">
-        <f>VLOOKUP($B57, [1]Main!$E$2:$G$358, 3, FALSE)</f>
-        <v>Purchase Requisition</v>
+        <f>VLOOKUP($B57, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>Report Advance to Advance Settlement</v>
       </c>
       <c r="F57" s="10" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G57" s="6">
         <f>IF(EXACT($F57, ""), "", VLOOKUP($F57, [2]Main!$B$2:$E$30, 4, FALSE))</f>
-        <v>254000000000010</v>
+        <v>254000000000008</v>
       </c>
       <c r="H57" s="2">
         <v>56</v>
       </c>
       <c r="I57" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000010::bigint, 97000000000056::bigint);</v>
-      </c>
-      <c r="K57" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000008::bigint, 97000000000056::bigint);</v>
+      </c>
+      <c r="K57" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L57" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000010'::bigint,'menu_RefID', '97000000000056'::bigint)))::varchar;</v>
-      </c>
-    </row>
-    <row r="58" spans="2:11" x14ac:dyDescent="0.2">
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000008'::bigint,'menu_RefID', '97000000000056'::bigint)))::varchar;</v>
+      </c>
+    </row>
+    <row r="58" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B58" s="6">
         <f>[1]Main!$E58</f>
         <v>97000000000057</v>
       </c>
       <c r="C58" s="7" t="str">
-        <f>VLOOKUP($B58, [1]Main!$E$2:$G$358, 2, FALSE)</f>
-        <v>Module.SupplyChain.Data.PurchaseRequisition.Report.DataList</v>
+        <f>VLOOKUP($B58, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.Finance.Data.AdvanceSettlement.Transaction</v>
       </c>
       <c r="D58" s="8" t="str">
-        <f>VLOOKUP($B58, [1]Main!$E$2:$G$358, 3, FALSE)</f>
-        <v>Report Purchase Requisition Summary</v>
+        <f>VLOOKUP($B58, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>AdvanceSettlement</v>
       </c>
       <c r="F58" s="10" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G58" s="6">
         <f>IF(EXACT($F58, ""), "", VLOOKUP($F58, [2]Main!$B$2:$E$30, 4, FALSE))</f>
-        <v>254000000000010</v>
+        <v>254000000000008</v>
       </c>
       <c r="H58" s="2">
         <v>57</v>
       </c>
       <c r="I58" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000010::bigint, 97000000000057::bigint);</v>
-      </c>
-      <c r="K58" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000008::bigint, 97000000000057::bigint);</v>
+      </c>
+      <c r="K58" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L58" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000010'::bigint,'menu_RefID', '97000000000057'::bigint)))::varchar;</v>
-      </c>
-    </row>
-    <row r="59" spans="2:11" x14ac:dyDescent="0.2">
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000008'::bigint,'menu_RefID', '97000000000057'::bigint)))::varchar;</v>
+      </c>
+    </row>
+    <row r="59" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B59" s="6">
         <f>[1]Main!$E59</f>
         <v>97000000000058</v>
       </c>
       <c r="C59" s="7" t="str">
-        <f>VLOOKUP($B59, [1]Main!$E$2:$G$358, 2, FALSE)</f>
-        <v>Module.SupplyChain.Data.PurchaseRequisitionToPurchaseOrder.Report.DataList</v>
+        <f>VLOOKUP($B59, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.Finance.Data.AdvanceSettlement.Report.DataList</v>
       </c>
       <c r="D59" s="8" t="str">
-        <f>VLOOKUP($B59, [1]Main!$E$2:$G$358, 3, FALSE)</f>
-        <v>Report Purchase Requisition To Purchase Order</v>
+        <f>VLOOKUP($B59, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>Report Advance Settlement Summary</v>
       </c>
       <c r="F59" s="10" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G59" s="6">
         <f>IF(EXACT($F59, ""), "", VLOOKUP($F59, [2]Main!$B$2:$E$30, 4, FALSE))</f>
-        <v>254000000000010</v>
+        <v>254000000000008</v>
       </c>
       <c r="H59" s="2">
         <v>58</v>
       </c>
       <c r="I59" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000010::bigint, 97000000000058::bigint);</v>
-      </c>
-      <c r="K59" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000008::bigint, 97000000000058::bigint);</v>
+      </c>
+      <c r="K59" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L59" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000010'::bigint,'menu_RefID', '97000000000058'::bigint)))::varchar;</v>
-      </c>
-    </row>
-    <row r="60" spans="2:11" x14ac:dyDescent="0.2">
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000008'::bigint,'menu_RefID', '97000000000058'::bigint)))::varchar;</v>
+      </c>
+    </row>
+    <row r="60" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B60" s="6">
         <f>[1]Main!$E60</f>
         <v>97000000000059</v>
       </c>
       <c r="C60" s="7" t="str">
-        <f>VLOOKUP($B60, [1]Main!$E$2:$G$358, 2, FALSE)</f>
-        <v>Module.SupplyChain.Data.PurchaseOrder.Transaction</v>
+        <f>VLOOKUP($B60, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.Finance.Data.PersonBusinessTrip.Transaction</v>
       </c>
       <c r="D60" s="8" t="str">
-        <f>VLOOKUP($B60, [1]Main!$E$2:$G$358, 3, FALSE)</f>
-        <v>Purchase Order</v>
+        <f>VLOOKUP($B60, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>BusinessTrip Request</v>
       </c>
       <c r="F60" s="10" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G60" s="6">
         <f>IF(EXACT($F60, ""), "", VLOOKUP($F60, [2]Main!$B$2:$E$30, 4, FALSE))</f>
-        <v>254000000000010</v>
+        <v>254000000000008</v>
       </c>
       <c r="H60" s="2">
         <v>59</v>
       </c>
       <c r="I60" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000010::bigint, 97000000000059::bigint);</v>
-      </c>
-      <c r="K60" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000008::bigint, 97000000000059::bigint);</v>
+      </c>
+      <c r="K60" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L60" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000010'::bigint,'menu_RefID', '97000000000059'::bigint)))::varchar;</v>
-      </c>
-    </row>
-    <row r="61" spans="2:11" x14ac:dyDescent="0.2">
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000008'::bigint,'menu_RefID', '97000000000059'::bigint)))::varchar;</v>
+      </c>
+    </row>
+    <row r="61" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B61" s="6">
         <f>[1]Main!$E61</f>
         <v>97000000000060</v>
       </c>
       <c r="C61" s="7" t="str">
-        <f>VLOOKUP($B61, [1]Main!$E$2:$G$358, 2, FALSE)</f>
-        <v>Module.SupplyChain.Data.PurchaseOrder.Report.DataList</v>
+        <f>VLOOKUP($B61, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.Finance.Data.PersonBusinessTrip.Report.DataList</v>
       </c>
       <c r="D61" s="8" t="str">
-        <f>VLOOKUP($B61, [1]Main!$E$2:$G$358, 3, FALSE)</f>
-        <v>Report Purchase Order Summary</v>
+        <f>VLOOKUP($B61, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>Report BusinessTrip Request Summary</v>
       </c>
       <c r="F61" s="10" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G61" s="6">
         <f>IF(EXACT($F61, ""), "", VLOOKUP($F61, [2]Main!$B$2:$E$30, 4, FALSE))</f>
-        <v>254000000000010</v>
+        <v>254000000000008</v>
       </c>
       <c r="H61" s="2">
         <v>60</v>
       </c>
       <c r="I61" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000010::bigint, 97000000000060::bigint);</v>
-      </c>
-      <c r="K61" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000008::bigint, 97000000000060::bigint);</v>
+      </c>
+      <c r="K61" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L61" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000010'::bigint,'menu_RefID', '97000000000060'::bigint)))::varchar;</v>
-      </c>
-    </row>
-    <row r="62" spans="2:11" x14ac:dyDescent="0.2">
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000008'::bigint,'menu_RefID', '97000000000060'::bigint)))::varchar;</v>
+      </c>
+    </row>
+    <row r="62" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B62" s="6">
         <f>[1]Main!$E62</f>
         <v>97000000000061</v>
       </c>
       <c r="C62" s="7" t="str">
-        <f>VLOOKUP($B62, [1]Main!$E$2:$G$358, 2, FALSE)</f>
-        <v>Module.SupplyChain.Data.PurchaseOrderToPaymentInstruction.Report.DataList</v>
+        <f>VLOOKUP($B62, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.Finance.Data.PersonBusinessTripToPersonBusinessTripSettlement.Report.DataList</v>
       </c>
       <c r="D62" s="8" t="str">
-        <f>VLOOKUP($B62, [1]Main!$E$2:$G$358, 3, FALSE)</f>
-        <v>Purchase Order to Account Payable</v>
+        <f>VLOOKUP($B62, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>Report BusinessTrip to BusinessTrip Settlement</v>
       </c>
       <c r="F62" s="10" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G62" s="6">
         <f>IF(EXACT($F62, ""), "", VLOOKUP($F62, [2]Main!$B$2:$E$30, 4, FALSE))</f>
-        <v>254000000000010</v>
+        <v>254000000000008</v>
       </c>
       <c r="H62" s="2">
         <v>61</v>
       </c>
       <c r="I62" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000010::bigint, 97000000000061::bigint);</v>
-      </c>
-      <c r="K62" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000008::bigint, 97000000000061::bigint);</v>
+      </c>
+      <c r="K62" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L62" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000010'::bigint,'menu_RefID', '97000000000061'::bigint)))::varchar;</v>
-      </c>
-    </row>
-    <row r="63" spans="2:11" x14ac:dyDescent="0.2">
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000008'::bigint,'menu_RefID', '97000000000061'::bigint)))::varchar;</v>
+      </c>
+    </row>
+    <row r="63" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B63" s="6">
         <f>[1]Main!$E63</f>
         <v>97000000000062</v>
       </c>
       <c r="C63" s="7" t="str">
-        <f>VLOOKUP($B63, [1]Main!$E$2:$G$358, 2, FALSE)</f>
-        <v>Module.General.MasterData.Bank.Transaction</v>
+        <f>VLOOKUP($B63, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.Finance.Data.PersonBusinessTripSettlement.Transaction</v>
       </c>
       <c r="D63" s="8" t="str">
-        <f>VLOOKUP($B63, [1]Main!$E$2:$G$358, 3, FALSE)</f>
-        <v>Bank</v>
+        <f>VLOOKUP($B63, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>BusinessTrip Settlement</v>
       </c>
       <c r="F63" s="10" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G63" s="6">
         <f>IF(EXACT($F63, ""), "", VLOOKUP($F63, [2]Main!$B$2:$E$30, 4, FALSE))</f>
-        <v>254000000000006</v>
+        <v>254000000000008</v>
       </c>
       <c r="H63" s="2">
         <v>62</v>
       </c>
       <c r="I63" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000062::bigint);</v>
-      </c>
-      <c r="K63" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000008::bigint, 97000000000062::bigint);</v>
+      </c>
+      <c r="K63" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L63" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000006'::bigint,'menu_RefID', '97000000000062'::bigint)))::varchar;</v>
-      </c>
-    </row>
-    <row r="64" spans="2:11" x14ac:dyDescent="0.2">
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000008'::bigint,'menu_RefID', '97000000000062'::bigint)))::varchar;</v>
+      </c>
+    </row>
+    <row r="64" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B64" s="6">
         <f>[1]Main!$E64</f>
         <v>97000000000063</v>
       </c>
       <c r="C64" s="7" t="str">
-        <f>VLOOKUP($B64, [1]Main!$E$2:$G$358, 2, FALSE)</f>
-        <v>Module.General.MasterData.BankAccount.Transaction</v>
+        <f>VLOOKUP($B64, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.Finance.Data.PersonBusinessTripSettlement.Report.DataList</v>
       </c>
       <c r="D64" s="8" t="str">
-        <f>VLOOKUP($B64, [1]Main!$E$2:$G$358, 3, FALSE)</f>
-        <v>Bank Account</v>
+        <f>VLOOKUP($B64, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>Report BusinessTrip Settlement Summary</v>
       </c>
       <c r="F64" s="10" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G64" s="6">
         <f>IF(EXACT($F64, ""), "", VLOOKUP($F64, [2]Main!$B$2:$E$30, 4, FALSE))</f>
-        <v>254000000000006</v>
+        <v>254000000000008</v>
       </c>
       <c r="H64" s="2">
         <v>63</v>
       </c>
       <c r="I64" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000063::bigint);</v>
-      </c>
-      <c r="K64" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000008::bigint, 97000000000063::bigint);</v>
+      </c>
+      <c r="K64" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L64" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000006'::bigint,'menu_RefID', '97000000000063'::bigint)))::varchar;</v>
-      </c>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000008'::bigint,'menu_RefID', '97000000000063'::bigint)))::varchar;</v>
+      </c>
+    </row>
+    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B65" s="6">
         <f>[1]Main!$E65</f>
         <v>97000000000064</v>
       </c>
       <c r="C65" s="7" t="str">
-        <f>VLOOKUP($B65, [1]Main!$E$2:$G$358, 2, FALSE)</f>
-        <v>Module.General.MasterData.Currency.Transaction</v>
+        <f>VLOOKUP($B65, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.SupplyChain.MasterData.Supplier.Transaction</v>
       </c>
       <c r="D65" s="8" t="str">
-        <f>VLOOKUP($B65, [1]Main!$E$2:$G$358, 3, FALSE)</f>
-        <v>Currency</v>
+        <f>VLOOKUP($B65, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>Supplier</v>
       </c>
       <c r="F65" s="10" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G65" s="6">
         <f>IF(EXACT($F65, ""), "", VLOOKUP($F65, [2]Main!$B$2:$E$30, 4, FALSE))</f>
-        <v>254000000000006</v>
+        <v>254000000000010</v>
       </c>
       <c r="H65" s="2">
         <v>64</v>
       </c>
       <c r="I65" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000064::bigint);</v>
-      </c>
-      <c r="K65" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000010::bigint, 97000000000064::bigint);</v>
+      </c>
+      <c r="K65" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L65" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000006'::bigint,'menu_RefID', '97000000000064'::bigint)))::varchar;</v>
-      </c>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000010'::bigint,'menu_RefID', '97000000000064'::bigint)))::varchar;</v>
+      </c>
+    </row>
+    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B66" s="6">
         <f>[1]Main!$E66</f>
         <v>97000000000065</v>
       </c>
       <c r="C66" s="7" t="str">
-        <f>VLOOKUP($B66, [1]Main!$E$2:$G$358, 2, FALSE)</f>
-        <v>Module.General.MasterData.CurrencyExchangeRate.Transaction</v>
+        <f>VLOOKUP($B66, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.SupplyChain.MasterData.SupplierCategory.Transaction</v>
       </c>
       <c r="D66" s="8" t="str">
-        <f>VLOOKUP($B66, [1]Main!$E$2:$G$358, 3, FALSE)</f>
-        <v>Exchange Rate</v>
+        <f>VLOOKUP($B66, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>Supplier Category</v>
       </c>
       <c r="F66" s="10" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G66" s="6">
         <f>IF(EXACT($F66, ""), "", VLOOKUP($F66, [2]Main!$B$2:$E$30, 4, FALSE))</f>
-        <v>254000000000006</v>
+        <v>254000000000010</v>
       </c>
       <c r="H66" s="2">
         <v>65</v>
       </c>
       <c r="I66" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000065::bigint);</v>
-      </c>
-      <c r="K66" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000010::bigint, 97000000000065::bigint);</v>
+      </c>
+      <c r="K66" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L66" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000006'::bigint,'menu_RefID', '97000000000065'::bigint)))::varchar;</v>
-      </c>
-    </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000010'::bigint,'menu_RefID', '97000000000065'::bigint)))::varchar;</v>
+      </c>
+    </row>
+    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B67" s="6">
         <f>[1]Main!$E67</f>
         <v>97000000000066</v>
       </c>
       <c r="C67" s="7" t="str">
-        <f>VLOOKUP($B67, [1]Main!$E$2:$G$358, 2, FALSE)</f>
-        <v>Module.General.MasterData.CurrencyExchangeRate.Report.DataList</v>
+        <f>VLOOKUP($B67, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.SupplyChain.MasterData.SupplierSubCategory.Transaction</v>
       </c>
       <c r="D67" s="8" t="str">
-        <f>VLOOKUP($B67, [1]Main!$E$2:$G$358, 3, FALSE)</f>
-        <v>Exchange Rate Summary</v>
+        <f>VLOOKUP($B67, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>Supplier Sub Category</v>
       </c>
       <c r="F67" s="10" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G67" s="6">
         <f>IF(EXACT($F67, ""), "", VLOOKUP($F67, [2]Main!$B$2:$E$30, 4, FALSE))</f>
-        <v>254000000000006</v>
+        <v>254000000000010</v>
       </c>
       <c r="H67" s="2">
         <v>66</v>
       </c>
       <c r="I67" s="9" t="str">
-        <f t="shared" ref="I67:I98" si="2">IF(EXACT(G67, ""), "", CONCATENATE("PERFORM ""SchSysConfig"".""Func_TblAppObject_MenuGroupMember_SET""(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, ", G67, "::bigint, ", B67, "::bigint);"))</f>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000066::bigint);</v>
-      </c>
-      <c r="K67" s="2" t="str">
-        <f t="shared" ref="K67:K98" si="3">CONCATENATE(
+        <f t="shared" si="2"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000010::bigint, 97000000000066::bigint);</v>
+      </c>
+      <c r="K67" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L67" s="2" t="str">
+        <f t="shared" ref="L67:L116" si="3">IF(EXACT(K67, ""), "",
+CONCATENATE(
 "varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT (",
 "'recordID', NULL::bigint,", "'entities', ", "JSON_BUILD_OBJECT (",
 "'sysLoginSession_RefID', varSystemLoginSession::bigint,",
@@ -3836,214 +4216,233 @@
 "'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,",
 "'menuGroup_RefID', ", IF(EXACT($G67, ""), "null", CONCATENATE("'", SUBSTITUTE($G67, "'", "\'"), "'")), "::bigint,",
 "'menu_RefID', ", IF(EXACT($B67, ""), "null", CONCATENATE("'", SUBSTITUTE($B67, "'", "\'"), "'")), "::bigint",
-")))::varchar;")</f>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000006'::bigint,'menu_RefID', '97000000000066'::bigint)))::varchar;</v>
-      </c>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+")))::varchar;")
+)</f>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000010'::bigint,'menu_RefID', '97000000000066'::bigint)))::varchar;</v>
+      </c>
+    </row>
+    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B68" s="6">
         <f>[1]Main!$E68</f>
         <v>97000000000067</v>
       </c>
       <c r="C68" s="7" t="str">
-        <f>VLOOKUP($B68, [1]Main!$E$2:$G$358, 2, FALSE)</f>
-        <v>Module.General.MasterData.PaymentTerm.Transaction</v>
+        <f>VLOOKUP($B68, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.SupplyChain.Data.PurchaseRequisition.Transaction</v>
       </c>
       <c r="D68" s="8" t="str">
-        <f>VLOOKUP($B68, [1]Main!$E$2:$G$358, 3, FALSE)</f>
-        <v>Payment Term</v>
+        <f>VLOOKUP($B68, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>Purchase Requisition</v>
       </c>
       <c r="F68" s="10" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G68" s="6">
         <f>IF(EXACT($F68, ""), "", VLOOKUP($F68, [2]Main!$B$2:$E$30, 4, FALSE))</f>
-        <v>254000000000006</v>
+        <v>254000000000010</v>
       </c>
       <c r="H68" s="2">
         <v>67</v>
       </c>
       <c r="I68" s="9" t="str">
         <f t="shared" si="2"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000067::bigint);</v>
-      </c>
-      <c r="K68" s="2" t="str">
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000010::bigint, 97000000000067::bigint);</v>
+      </c>
+      <c r="K68" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L68" s="2" t="str">
         <f t="shared" si="3"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000006'::bigint,'menu_RefID', '97000000000067'::bigint)))::varchar;</v>
-      </c>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000010'::bigint,'menu_RefID', '97000000000067'::bigint)))::varchar;</v>
+      </c>
+    </row>
+    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B69" s="6">
         <f>[1]Main!$E69</f>
         <v>97000000000068</v>
       </c>
       <c r="C69" s="7" t="str">
-        <f>VLOOKUP($B69, [1]Main!$E$2:$G$358, 2, FALSE)</f>
-        <v>Module.General.MasterData.Period.Transaction</v>
+        <f>VLOOKUP($B69, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.SupplyChain.Data.PurchaseRequisition.Report.DataList</v>
       </c>
       <c r="D69" s="8" t="str">
-        <f>VLOOKUP($B69, [1]Main!$E$2:$G$358, 3, FALSE)</f>
-        <v>Period</v>
+        <f>VLOOKUP($B69, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>Report Purchase Requisition Summary</v>
       </c>
       <c r="F69" s="10" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G69" s="6">
         <f>IF(EXACT($F69, ""), "", VLOOKUP($F69, [2]Main!$B$2:$E$30, 4, FALSE))</f>
-        <v>254000000000006</v>
+        <v>254000000000010</v>
       </c>
       <c r="H69" s="2">
         <v>68</v>
       </c>
       <c r="I69" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000068::bigint);</v>
-      </c>
-      <c r="K69" s="2" t="str">
+        <f t="shared" ref="I69:I116" si="4">IF(EXACT(G69, ""), "", CONCATENATE("PERFORM ""SchSysConfig"".""Func_TblAppObject_MenuGroupMember_SET""(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, ", G69, "::bigint, ", B69, "::bigint);"))</f>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000010::bigint, 97000000000068::bigint);</v>
+      </c>
+      <c r="K69" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L69" s="2" t="str">
         <f t="shared" si="3"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000006'::bigint,'menu_RefID', '97000000000068'::bigint)))::varchar;</v>
-      </c>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000010'::bigint,'menu_RefID', '97000000000068'::bigint)))::varchar;</v>
+      </c>
+    </row>
+    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B70" s="6">
         <f>[1]Main!$E70</f>
         <v>97000000000069</v>
       </c>
       <c r="C70" s="7" t="str">
-        <f>VLOOKUP($B70, [1]Main!$E$2:$G$358, 2, FALSE)</f>
-        <v>Module.Accounting.MasterData.AssetCategory.Transaction</v>
+        <f>VLOOKUP($B70, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.SupplyChain.Data.PurchaseRequisitionToPurchaseOrder.Report.DataList</v>
       </c>
       <c r="D70" s="8" t="str">
-        <f>VLOOKUP($B70, [1]Main!$E$2:$G$358, 3, FALSE)</f>
-        <v>Asset Category</v>
+        <f>VLOOKUP($B70, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>Report Purchase Requisition To Purchase Order</v>
       </c>
       <c r="F70" s="10" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G70" s="6">
         <f>IF(EXACT($F70, ""), "", VLOOKUP($F70, [2]Main!$B$2:$E$30, 4, FALSE))</f>
-        <v>254000000000006</v>
+        <v>254000000000010</v>
       </c>
       <c r="H70" s="2">
         <v>69</v>
       </c>
       <c r="I70" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000069::bigint);</v>
-      </c>
-      <c r="K70" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000010::bigint, 97000000000069::bigint);</v>
+      </c>
+      <c r="K70" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L70" s="2" t="str">
         <f t="shared" si="3"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000006'::bigint,'menu_RefID', '97000000000069'::bigint)))::varchar;</v>
-      </c>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000010'::bigint,'menu_RefID', '97000000000069'::bigint)))::varchar;</v>
+      </c>
+    </row>
+    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B71" s="6">
         <f>[1]Main!$E71</f>
         <v>97000000000070</v>
       </c>
       <c r="C71" s="7" t="str">
-        <f>VLOOKUP($B71, [1]Main!$E$2:$G$358, 2, FALSE)</f>
-        <v>Module.Accounting.MasterData.ChartOfAccount.Transaction</v>
+        <f>VLOOKUP($B71, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.SupplyChain.Data.PurchaseOrder.Transaction</v>
       </c>
       <c r="D71" s="8" t="str">
-        <f>VLOOKUP($B71, [1]Main!$E$2:$G$358, 3, FALSE)</f>
-        <v>Chart of Account</v>
+        <f>VLOOKUP($B71, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>Purchase Order</v>
       </c>
       <c r="F71" s="10" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G71" s="6">
         <f>IF(EXACT($F71, ""), "", VLOOKUP($F71, [2]Main!$B$2:$E$30, 4, FALSE))</f>
-        <v>254000000000006</v>
+        <v>254000000000010</v>
       </c>
       <c r="H71" s="2">
         <v>70</v>
       </c>
       <c r="I71" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000070::bigint);</v>
-      </c>
-      <c r="K71" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000010::bigint, 97000000000070::bigint);</v>
+      </c>
+      <c r="K71" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L71" s="2" t="str">
         <f t="shared" si="3"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000006'::bigint,'menu_RefID', '97000000000070'::bigint)))::varchar;</v>
-      </c>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000010'::bigint,'menu_RefID', '97000000000070'::bigint)))::varchar;</v>
+      </c>
+    </row>
+    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B72" s="6">
         <f>[1]Main!$E72</f>
         <v>97000000000071</v>
       </c>
       <c r="C72" s="7" t="str">
-        <f>VLOOKUP($B72, [1]Main!$E$2:$G$358, 2, FALSE)</f>
-        <v>Module.Accounting.MasterData.DepreciationMethod.Transaction</v>
+        <f>VLOOKUP($B72, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.SupplyChain.Data.PurchaseOrder.Report.DataList</v>
       </c>
       <c r="D72" s="8" t="str">
-        <f>VLOOKUP($B72, [1]Main!$E$2:$G$358, 3, FALSE)</f>
-        <v>Depreciation Method</v>
+        <f>VLOOKUP($B72, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>Report Purchase Order Summary</v>
       </c>
       <c r="F72" s="10" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G72" s="6">
         <f>IF(EXACT($F72, ""), "", VLOOKUP($F72, [2]Main!$B$2:$E$30, 4, FALSE))</f>
-        <v>254000000000006</v>
+        <v>254000000000010</v>
       </c>
       <c r="H72" s="2">
         <v>71</v>
       </c>
       <c r="I72" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000071::bigint);</v>
-      </c>
-      <c r="K72" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000010::bigint, 97000000000071::bigint);</v>
+      </c>
+      <c r="K72" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L72" s="2" t="str">
         <f t="shared" si="3"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000006'::bigint,'menu_RefID', '97000000000071'::bigint)))::varchar;</v>
-      </c>
-    </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000010'::bigint,'menu_RefID', '97000000000071'::bigint)))::varchar;</v>
+      </c>
+    </row>
+    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B73" s="6">
         <f>[1]Main!$E73</f>
         <v>97000000000072</v>
       </c>
       <c r="C73" s="7" t="str">
-        <f>VLOOKUP($B73, [1]Main!$E$2:$G$358, 2, FALSE)</f>
-        <v>Module.Accounting.MasterData.DepreciationRateYears.Transaction</v>
+        <f>VLOOKUP($B73, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.SupplyChain.Data.PurchaseOrderToPaymentInstruction.Report.DataList</v>
       </c>
       <c r="D73" s="8" t="str">
-        <f>VLOOKUP($B73, [1]Main!$E$2:$G$358, 3, FALSE)</f>
-        <v>Depreciation Rate Years</v>
+        <f>VLOOKUP($B73, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>Report Purchase Order to Account Payable Summary</v>
       </c>
       <c r="F73" s="10" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G73" s="6">
         <f>IF(EXACT($F73, ""), "", VLOOKUP($F73, [2]Main!$B$2:$E$30, 4, FALSE))</f>
-        <v>254000000000006</v>
+        <v>254000000000010</v>
       </c>
       <c r="H73" s="2">
         <v>72</v>
       </c>
       <c r="I73" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000072::bigint);</v>
-      </c>
-      <c r="K73" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000010::bigint, 97000000000072::bigint);</v>
+      </c>
+      <c r="K73" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L73" s="2" t="str">
         <f t="shared" si="3"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000006'::bigint,'menu_RefID', '97000000000072'::bigint)))::varchar;</v>
-      </c>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000010'::bigint,'menu_RefID', '97000000000072'::bigint)))::varchar;</v>
+      </c>
+    </row>
+    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B74" s="6">
         <f>[1]Main!$E74</f>
         <v>97000000000073</v>
       </c>
       <c r="C74" s="7" t="str">
-        <f>VLOOKUP($B74, [1]Main!$E$2:$G$358, 2, FALSE)</f>
-        <v>Module.Taxation.MasterData.ValueAddedTax.Transaction</v>
+        <f>VLOOKUP($B74, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.General.MasterData.Bank.Transaction</v>
       </c>
       <c r="D74" s="8" t="str">
-        <f>VLOOKUP($B74, [1]Main!$E$2:$G$358, 3, FALSE)</f>
-        <v>Value Added Tax</v>
+        <f>VLOOKUP($B74, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>Bank</v>
       </c>
       <c r="F74" s="10" t="s">
         <v>2</v>
@@ -4056,26 +4455,29 @@
         <v>73</v>
       </c>
       <c r="I74" s="9" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000073::bigint);</v>
       </c>
-      <c r="K74" s="2" t="str">
+      <c r="K74" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L74" s="2" t="str">
         <f t="shared" si="3"/>
         <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000006'::bigint,'menu_RefID', '97000000000073'::bigint)))::varchar;</v>
       </c>
     </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B75" s="6">
         <f>[1]Main!$E75</f>
         <v>97000000000074</v>
       </c>
       <c r="C75" s="7" t="str">
-        <f>VLOOKUP($B75, [1]Main!$E$2:$G$358, 2, FALSE)</f>
-        <v>Module.Accounting.Data.GeneralJournal.Transaction</v>
+        <f>VLOOKUP($B75, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.General.MasterData.BankAccount.Transaction</v>
       </c>
       <c r="D75" s="8" t="str">
-        <f>VLOOKUP($B75, [1]Main!$E$2:$G$358, 3, FALSE)</f>
-        <v>General Journal</v>
+        <f>VLOOKUP($B75, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>Bank Account</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>2</v>
@@ -4088,26 +4490,29 @@
         <v>74</v>
       </c>
       <c r="I75" s="9" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000074::bigint);</v>
       </c>
-      <c r="K75" s="2" t="str">
+      <c r="K75" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L75" s="2" t="str">
         <f t="shared" si="3"/>
         <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000006'::bigint,'menu_RefID', '97000000000074'::bigint)))::varchar;</v>
       </c>
     </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B76" s="6">
         <f>[1]Main!$E76</f>
         <v>97000000000075</v>
       </c>
       <c r="C76" s="7" t="str">
-        <f>VLOOKUP($B76, [1]Main!$E$2:$G$358, 2, FALSE)</f>
-        <v>Module.Accounting.Data.GeneralJournal.Report.DataList</v>
+        <f>VLOOKUP($B76, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.General.MasterData.Currency.Transaction</v>
       </c>
       <c r="D76" s="8" t="str">
-        <f>VLOOKUP($B76, [1]Main!$E$2:$G$358, 3, FALSE)</f>
-        <v>General Journal Summary</v>
+        <f>VLOOKUP($B76, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>Currency</v>
       </c>
       <c r="F76" s="10" t="s">
         <v>2</v>
@@ -4120,26 +4525,27 @@
         <v>75</v>
       </c>
       <c r="I76" s="9" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000075::bigint);</v>
       </c>
-      <c r="K76" s="2" t="str">
+      <c r="K76" s="12"/>
+      <c r="L76" s="2" t="str">
         <f t="shared" si="3"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000006'::bigint,'menu_RefID', '97000000000075'::bigint)))::varchar;</v>
-      </c>
-    </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+        <v/>
+      </c>
+    </row>
+    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B77" s="6">
         <f>[1]Main!$E77</f>
         <v>97000000000076</v>
       </c>
       <c r="C77" s="7" t="str">
-        <f>VLOOKUP($B77, [1]Main!$E$2:$G$358, 2, FALSE)</f>
-        <v>Module.Finance.Data.Reimbursement.Transaction</v>
+        <f>VLOOKUP($B77, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.General.MasterData.CurrencyExchangeRate.Transaction</v>
       </c>
       <c r="D77" s="8" t="str">
-        <f>VLOOKUP($B77, [1]Main!$E$2:$G$358, 3, FALSE)</f>
-        <v>Reimbursement</v>
+        <f>VLOOKUP($B77, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>Exchange Rate</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>2</v>
@@ -4152,26 +4558,29 @@
         <v>76</v>
       </c>
       <c r="I77" s="9" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000076::bigint);</v>
       </c>
-      <c r="K77" s="2" t="str">
+      <c r="K77" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L77" s="2" t="str">
         <f t="shared" si="3"/>
         <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000006'::bigint,'menu_RefID', '97000000000076'::bigint)))::varchar;</v>
       </c>
     </row>
-    <row r="78" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="78" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B78" s="6">
         <f>[1]Main!$E78</f>
         <v>97000000000077</v>
       </c>
       <c r="C78" s="7" t="str">
-        <f>VLOOKUP($B78, [1]Main!$E$2:$G$358, 2, FALSE)</f>
-        <v>Module.Finance.Data.Reimbursement.Report.DataList</v>
+        <f>VLOOKUP($B78, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.General.MasterData.CurrencyExchangeRate.Report.DataList</v>
       </c>
       <c r="D78" s="8" t="str">
-        <f>VLOOKUP($B78, [1]Main!$E$2:$G$358, 3, FALSE)</f>
-        <v>Reimbursement Summary</v>
+        <f>VLOOKUP($B78, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>Exchange Rate Summary</v>
       </c>
       <c r="F78" s="10" t="s">
         <v>2</v>
@@ -4184,26 +4593,26 @@
         <v>77</v>
       </c>
       <c r="I78" s="9" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000077::bigint);</v>
       </c>
-      <c r="K78" s="2" t="str">
+      <c r="L78" s="2" t="str">
         <f t="shared" si="3"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000006'::bigint,'menu_RefID', '97000000000077'::bigint)))::varchar;</v>
-      </c>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+        <v/>
+      </c>
+    </row>
+    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B79" s="6">
         <f>[1]Main!$E79</f>
         <v>97000000000078</v>
       </c>
       <c r="C79" s="7" t="str">
-        <f>VLOOKUP($B79, [1]Main!$E$2:$G$358, 2, FALSE)</f>
-        <v>Module.Finance.Data.ReimbursementToDebitNote.Report.DataList</v>
+        <f>VLOOKUP($B79, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.General.MasterData.PaymentTerm.Transaction</v>
       </c>
       <c r="D79" s="8" t="str">
-        <f>VLOOKUP($B79, [1]Main!$E$2:$G$358, 3, FALSE)</f>
-        <v>Reimbursement to Debit Note</v>
+        <f>VLOOKUP($B79, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>Payment Term</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>2</v>
@@ -4216,26 +4625,26 @@
         <v>78</v>
       </c>
       <c r="I79" s="9" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000078::bigint);</v>
       </c>
-      <c r="K79" s="2" t="str">
+      <c r="L79" s="2" t="str">
         <f t="shared" si="3"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000006'::bigint,'menu_RefID', '97000000000078'::bigint)))::varchar;</v>
-      </c>
-    </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+        <v/>
+      </c>
+    </row>
+    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B80" s="6">
         <f>[1]Main!$E80</f>
         <v>97000000000079</v>
       </c>
       <c r="C80" s="7" t="str">
-        <f>VLOOKUP($B80, [1]Main!$E$2:$G$358, 2, FALSE)</f>
-        <v>Module.Finance.Data.DebitNote.Transaction</v>
+        <f>VLOOKUP($B80, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.General.MasterData.Period.Transaction</v>
       </c>
       <c r="D80" s="8" t="str">
-        <f>VLOOKUP($B80, [1]Main!$E$2:$G$358, 3, FALSE)</f>
-        <v>Debit Note</v>
+        <f>VLOOKUP($B80, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>Period</v>
       </c>
       <c r="F80" s="10" t="s">
         <v>2</v>
@@ -4248,26 +4657,29 @@
         <v>79</v>
       </c>
       <c r="I80" s="9" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000079::bigint);</v>
       </c>
-      <c r="K80" s="2" t="str">
+      <c r="K80" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L80" s="2" t="str">
         <f t="shared" si="3"/>
         <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000006'::bigint,'menu_RefID', '97000000000079'::bigint)))::varchar;</v>
       </c>
     </row>
-    <row r="81" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="81" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B81" s="6">
         <f>[1]Main!$E81</f>
         <v>97000000000080</v>
       </c>
       <c r="C81" s="7" t="str">
-        <f>VLOOKUP($B81, [1]Main!$E$2:$G$358, 2, FALSE)</f>
-        <v>Module.Finance.Data.DebitNote.Report.DataList</v>
+        <f>VLOOKUP($B81, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.Accounting.MasterData.AssetCategory.Transaction</v>
       </c>
       <c r="D81" s="8" t="str">
-        <f>VLOOKUP($B81, [1]Main!$E$2:$G$358, 3, FALSE)</f>
-        <v>Debit Note Summary</v>
+        <f>VLOOKUP($B81, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>Asset Category</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>2</v>
@@ -4280,26 +4692,26 @@
         <v>80</v>
       </c>
       <c r="I81" s="9" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000080::bigint);</v>
       </c>
-      <c r="K81" s="2" t="str">
+      <c r="L81" s="2" t="str">
         <f t="shared" si="3"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000006'::bigint,'menu_RefID', '97000000000080'::bigint)))::varchar;</v>
-      </c>
-    </row>
-    <row r="82" spans="2:11" x14ac:dyDescent="0.2">
+        <v/>
+      </c>
+    </row>
+    <row r="82" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B82" s="6">
         <f>[1]Main!$E82</f>
         <v>97000000000081</v>
       </c>
       <c r="C82" s="7" t="str">
-        <f>VLOOKUP($B82, [1]Main!$E$2:$G$358, 2, FALSE)</f>
-        <v>Module.Finance.Data.CreditNote.Transaction</v>
+        <f>VLOOKUP($B82, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.Accounting.MasterData.ChartOfAccount.Transaction</v>
       </c>
       <c r="D82" s="8" t="str">
-        <f>VLOOKUP($B82, [1]Main!$E$2:$G$358, 3, FALSE)</f>
-        <v>Credit Note</v>
+        <f>VLOOKUP($B82, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>Chart of Account</v>
       </c>
       <c r="F82" s="10" t="s">
         <v>2</v>
@@ -4312,26 +4724,29 @@
         <v>81</v>
       </c>
       <c r="I82" s="9" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000081::bigint);</v>
       </c>
-      <c r="K82" s="2" t="str">
+      <c r="K82" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L82" s="2" t="str">
         <f t="shared" si="3"/>
         <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000006'::bigint,'menu_RefID', '97000000000081'::bigint)))::varchar;</v>
       </c>
     </row>
-    <row r="83" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="83" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B83" s="6">
         <f>[1]Main!$E83</f>
         <v>97000000000082</v>
       </c>
       <c r="C83" s="7" t="str">
-        <f>VLOOKUP($B83, [1]Main!$E$2:$G$358, 2, FALSE)</f>
-        <v>Module.Finance.Data.CreditNote.Report.DataList</v>
+        <f>VLOOKUP($B83, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.Accounting.MasterData.DepreciationMethod.Transaction</v>
       </c>
       <c r="D83" s="8" t="str">
-        <f>VLOOKUP($B83, [1]Main!$E$2:$G$358, 3, FALSE)</f>
-        <v>Credit Note Summary</v>
+        <f>VLOOKUP($B83, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>Depreciation Method</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>2</v>
@@ -4344,26 +4759,26 @@
         <v>82</v>
       </c>
       <c r="I83" s="9" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000082::bigint);</v>
       </c>
-      <c r="K83" s="2" t="str">
+      <c r="L83" s="2" t="str">
         <f t="shared" si="3"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000006'::bigint,'menu_RefID', '97000000000082'::bigint)))::varchar;</v>
-      </c>
-    </row>
-    <row r="84" spans="2:11" x14ac:dyDescent="0.2">
+        <v/>
+      </c>
+    </row>
+    <row r="84" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B84" s="6">
         <f>[1]Main!$E84</f>
         <v>97000000000083</v>
       </c>
       <c r="C84" s="7" t="str">
-        <f>VLOOKUP($B84, [1]Main!$E$2:$G$358, 2, FALSE)</f>
-        <v>Module.Finance.Data.Loan.Transaction</v>
+        <f>VLOOKUP($B84, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.Accounting.MasterData.DepreciationRateYears.Transaction</v>
       </c>
       <c r="D84" s="8" t="str">
-        <f>VLOOKUP($B84, [1]Main!$E$2:$G$358, 3, FALSE)</f>
-        <v>Loan</v>
+        <f>VLOOKUP($B84, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>Depreciation Rate Years</v>
       </c>
       <c r="F84" s="10" t="s">
         <v>2</v>
@@ -4376,26 +4791,26 @@
         <v>83</v>
       </c>
       <c r="I84" s="9" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000083::bigint);</v>
       </c>
-      <c r="K84" s="2" t="str">
+      <c r="L84" s="2" t="str">
         <f t="shared" si="3"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000006'::bigint,'menu_RefID', '97000000000083'::bigint)))::varchar;</v>
-      </c>
-    </row>
-    <row r="85" spans="2:11" x14ac:dyDescent="0.2">
+        <v/>
+      </c>
+    </row>
+    <row r="85" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B85" s="6">
         <f>[1]Main!$E85</f>
         <v>97000000000084</v>
       </c>
       <c r="C85" s="7" t="str">
-        <f>VLOOKUP($B85, [1]Main!$E$2:$G$358, 2, FALSE)</f>
-        <v>Module.Finance.Data.Loan.Report.DataList</v>
+        <f>VLOOKUP($B85, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.Taxation.MasterData.ValueAddedTax.Transaction</v>
       </c>
       <c r="D85" s="8" t="str">
-        <f>VLOOKUP($B85, [1]Main!$E$2:$G$358, 3, FALSE)</f>
-        <v>Loan Summary</v>
+        <f>VLOOKUP($B85, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>Value Added Tax</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>2</v>
@@ -4408,26 +4823,26 @@
         <v>84</v>
       </c>
       <c r="I85" s="9" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000084::bigint);</v>
       </c>
-      <c r="K85" s="2" t="str">
+      <c r="L85" s="2" t="str">
         <f t="shared" si="3"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000006'::bigint,'menu_RefID', '97000000000084'::bigint)))::varchar;</v>
-      </c>
-    </row>
-    <row r="86" spans="2:11" x14ac:dyDescent="0.2">
+        <v/>
+      </c>
+    </row>
+    <row r="86" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B86" s="6">
         <f>[1]Main!$E86</f>
         <v>97000000000085</v>
       </c>
       <c r="C86" s="7" t="str">
-        <f>VLOOKUP($B86, [1]Main!$E$2:$G$358, 2, FALSE)</f>
-        <v>Module.Finance.Data.LoanToLoanSettlement.Report.DataList</v>
+        <f>VLOOKUP($B86, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.Accounting.Data.BalanceSheet.Report.DataList</v>
       </c>
       <c r="D86" s="8" t="str">
-        <f>VLOOKUP($B86, [1]Main!$E$2:$G$358, 3, FALSE)</f>
-        <v>Loan to Loan Settlement</v>
+        <f>VLOOKUP($B86, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>Balance Sheet</v>
       </c>
       <c r="F86" s="10" t="s">
         <v>2</v>
@@ -4440,26 +4855,29 @@
         <v>85</v>
       </c>
       <c r="I86" s="9" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000085::bigint);</v>
       </c>
-      <c r="K86" s="2" t="str">
+      <c r="K86" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L86" s="2" t="str">
         <f t="shared" si="3"/>
         <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000006'::bigint,'menu_RefID', '97000000000085'::bigint)))::varchar;</v>
       </c>
     </row>
-    <row r="87" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="87" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B87" s="6">
         <f>[1]Main!$E87</f>
         <v>97000000000086</v>
       </c>
       <c r="C87" s="7" t="str">
-        <f>VLOOKUP($B87, [1]Main!$E$2:$G$358, 2, FALSE)</f>
-        <v>Module.Finance.Data.LoanSettlement.Transaction</v>
+        <f>VLOOKUP($B87, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.Accounting.Data.GeneralJournal.Transaction</v>
       </c>
       <c r="D87" s="8" t="str">
-        <f>VLOOKUP($B87, [1]Main!$E$2:$G$358, 3, FALSE)</f>
-        <v>Loan Settlement</v>
+        <f>VLOOKUP($B87, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>General Journal</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>2</v>
@@ -4472,26 +4890,29 @@
         <v>86</v>
       </c>
       <c r="I87" s="9" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000086::bigint);</v>
       </c>
-      <c r="K87" s="2" t="str">
+      <c r="K87" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L87" s="2" t="str">
         <f t="shared" si="3"/>
         <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000006'::bigint,'menu_RefID', '97000000000086'::bigint)))::varchar;</v>
       </c>
     </row>
-    <row r="88" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="88" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B88" s="6">
         <f>[1]Main!$E88</f>
         <v>97000000000087</v>
       </c>
       <c r="C88" s="7" t="str">
-        <f>VLOOKUP($B88, [1]Main!$E$2:$G$358, 2, FALSE)</f>
-        <v>Module.Finance.Data.LoanSettlement.Report.DataList</v>
+        <f>VLOOKUP($B88, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.Accounting.Data.GeneralJournal.Report.DataList</v>
       </c>
       <c r="D88" s="8" t="str">
-        <f>VLOOKUP($B88, [1]Main!$E$2:$G$358, 3, FALSE)</f>
-        <v>Loan Settlement Summary</v>
+        <f>VLOOKUP($B88, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>General Journal Summary</v>
       </c>
       <c r="F88" s="10" t="s">
         <v>2</v>
@@ -4504,26 +4925,29 @@
         <v>87</v>
       </c>
       <c r="I88" s="9" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000087::bigint);</v>
       </c>
-      <c r="K88" s="2" t="str">
+      <c r="K88" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L88" s="2" t="str">
         <f t="shared" si="3"/>
         <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000006'::bigint,'menu_RefID', '97000000000087'::bigint)))::varchar;</v>
       </c>
     </row>
-    <row r="89" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="89" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B89" s="6">
         <f>[1]Main!$E89</f>
         <v>97000000000088</v>
       </c>
       <c r="C89" s="7" t="str">
-        <f>VLOOKUP($B89, [1]Main!$E$2:$G$358, 2, FALSE)</f>
-        <v>Module.Finance.Data.CashBank.Transaction</v>
+        <f>VLOOKUP($B89, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.Accounting.Data.GeneralLedger.Report.DataList</v>
       </c>
       <c r="D89" s="8" t="str">
-        <f>VLOOKUP($B89, [1]Main!$E$2:$G$358, 3, FALSE)</f>
-        <v>Cash &amp; Bank</v>
+        <f>VLOOKUP($B89, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>General Ledger Summary</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>2</v>
@@ -4536,26 +4960,29 @@
         <v>88</v>
       </c>
       <c r="I89" s="9" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000088::bigint);</v>
       </c>
-      <c r="K89" s="2" t="str">
+      <c r="K89" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L89" s="2" t="str">
         <f t="shared" si="3"/>
         <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000006'::bigint,'menu_RefID', '97000000000088'::bigint)))::varchar;</v>
       </c>
     </row>
-    <row r="90" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="90" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B90" s="6">
         <f>[1]Main!$E90</f>
         <v>97000000000089</v>
       </c>
       <c r="C90" s="7" t="str">
-        <f>VLOOKUP($B90, [1]Main!$E$2:$G$358, 2, FALSE)</f>
-        <v>Module.Finance.Data.CashBank.Report.DataList</v>
+        <f>VLOOKUP($B90, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.Accounting.Data.ProfitLoss.Report.DataList</v>
       </c>
       <c r="D90" s="8" t="str">
-        <f>VLOOKUP($B90, [1]Main!$E$2:$G$358, 3, FALSE)</f>
-        <v>Cash &amp; Bank Summary</v>
+        <f>VLOOKUP($B90, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>Profit Loss Summary</v>
       </c>
       <c r="F90" s="10" t="s">
         <v>2</v>
@@ -4568,26 +4995,29 @@
         <v>89</v>
       </c>
       <c r="I90" s="9" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000089::bigint);</v>
       </c>
-      <c r="K90" s="2" t="str">
+      <c r="K90" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L90" s="2" t="str">
         <f t="shared" si="3"/>
         <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000006'::bigint,'menu_RefID', '97000000000089'::bigint)))::varchar;</v>
       </c>
     </row>
-    <row r="91" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="91" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B91" s="6">
         <f>[1]Main!$E91</f>
         <v>97000000000090</v>
       </c>
       <c r="C91" s="7" t="str">
-        <f>VLOOKUP($B91, [1]Main!$E$2:$G$358, 2, FALSE)</f>
-        <v>Module.Finance.Data.PaymentInstruction.Transaction</v>
+        <f>VLOOKUP($B91, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.Finance.Data.CashBank.Transaction</v>
       </c>
       <c r="D91" s="8" t="str">
-        <f>VLOOKUP($B91, [1]Main!$E$2:$G$358, 3, FALSE)</f>
-        <v>Account Payable</v>
+        <f>VLOOKUP($B91, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>Cash &amp; Bank</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>2</v>
@@ -4600,26 +5030,29 @@
         <v>90</v>
       </c>
       <c r="I91" s="9" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000090::bigint);</v>
       </c>
-      <c r="K91" s="2" t="str">
+      <c r="K91" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L91" s="2" t="str">
         <f t="shared" si="3"/>
         <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000006'::bigint,'menu_RefID', '97000000000090'::bigint)))::varchar;</v>
       </c>
     </row>
-    <row r="92" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="92" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B92" s="6">
         <f>[1]Main!$E92</f>
         <v>97000000000091</v>
       </c>
       <c r="C92" s="7" t="str">
-        <f>VLOOKUP($B92, [1]Main!$E$2:$G$358, 2, FALSE)</f>
-        <v>Module.Finance.Data.PaymentInstruction.Report.DataList</v>
+        <f>VLOOKUP($B92, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.Finance.Data.CashBank.Report.DataList</v>
       </c>
       <c r="D92" s="8" t="str">
-        <f>VLOOKUP($B92, [1]Main!$E$2:$G$358, 3, FALSE)</f>
-        <v>Account Payable Summary</v>
+        <f>VLOOKUP($B92, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>Cash &amp; Bank Summary</v>
       </c>
       <c r="F92" s="10" t="s">
         <v>2</v>
@@ -4632,26 +5065,29 @@
         <v>91</v>
       </c>
       <c r="I92" s="9" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000091::bigint);</v>
       </c>
-      <c r="K92" s="2" t="str">
+      <c r="K92" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L92" s="2" t="str">
         <f t="shared" si="3"/>
         <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000006'::bigint,'menu_RefID', '97000000000091'::bigint)))::varchar;</v>
       </c>
     </row>
-    <row r="93" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="93" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B93" s="6">
         <f>[1]Main!$E93</f>
         <v>97000000000092</v>
       </c>
       <c r="C93" s="7" t="str">
-        <f>VLOOKUP($B93, [1]Main!$E$2:$G$358, 2, FALSE)</f>
-        <v>Module.Finance.Data.SalesInvoice.Transaction</v>
+        <f>VLOOKUP($B93, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.Finance.Data.CreditNote.Transaction</v>
       </c>
       <c r="D93" s="8" t="str">
-        <f>VLOOKUP($B93, [1]Main!$E$2:$G$358, 3, FALSE)</f>
-        <v>Sales Invoice</v>
+        <f>VLOOKUP($B93, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>Credit Note</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>2</v>
@@ -4664,26 +5100,29 @@
         <v>92</v>
       </c>
       <c r="I93" s="9" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000092::bigint);</v>
       </c>
-      <c r="K93" s="2" t="str">
+      <c r="K93" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L93" s="2" t="str">
         <f t="shared" si="3"/>
         <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000006'::bigint,'menu_RefID', '97000000000092'::bigint)))::varchar;</v>
       </c>
     </row>
-    <row r="94" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="94" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B94" s="6">
         <f>[1]Main!$E94</f>
         <v>97000000000093</v>
       </c>
       <c r="C94" s="7" t="str">
-        <f>VLOOKUP($B94, [1]Main!$E$2:$G$358, 2, FALSE)</f>
-        <v>Module.Finance.Data.SalesInvoice.Report.DataList</v>
+        <f>VLOOKUP($B94, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.Finance.Data.CreditNote.Report.DataList</v>
       </c>
       <c r="D94" s="8" t="str">
-        <f>VLOOKUP($B94, [1]Main!$E$2:$G$358, 3, FALSE)</f>
-        <v>Sales Invoice Summary</v>
+        <f>VLOOKUP($B94, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>Credit Note Summary</v>
       </c>
       <c r="F94" s="10" t="s">
         <v>2</v>
@@ -4696,26 +5135,29 @@
         <v>93</v>
       </c>
       <c r="I94" s="9" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000093::bigint);</v>
       </c>
-      <c r="K94" s="2" t="str">
+      <c r="K94" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L94" s="2" t="str">
         <f t="shared" si="3"/>
         <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000006'::bigint,'menu_RefID', '97000000000093'::bigint)))::varchar;</v>
       </c>
     </row>
-    <row r="95" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="95" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B95" s="6">
         <f>[1]Main!$E95</f>
         <v>97000000000094</v>
       </c>
       <c r="C95" s="7" t="str">
-        <f>VLOOKUP($B95, [1]Main!$E$2:$G$358, 2, FALSE)</f>
-        <v>Module.Finance.Data.SalesInvoiceToCreditNote.Report.DataList</v>
+        <f>VLOOKUP($B95, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.Finance.Data.DebitNote.Transaction</v>
       </c>
       <c r="D95" s="8" t="str">
-        <f>VLOOKUP($B95, [1]Main!$E$2:$G$358, 3, FALSE)</f>
-        <v>Sales Invoice to Credit Note</v>
+        <f>VLOOKUP($B95, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>Debit Note</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>2</v>
@@ -4728,26 +5170,29 @@
         <v>94</v>
       </c>
       <c r="I95" s="9" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000094::bigint);</v>
       </c>
-      <c r="K95" s="2" t="str">
+      <c r="K95" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L95" s="2" t="str">
         <f t="shared" si="3"/>
         <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000006'::bigint,'menu_RefID', '97000000000094'::bigint)))::varchar;</v>
       </c>
     </row>
-    <row r="96" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="96" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B96" s="6">
         <f>[1]Main!$E96</f>
         <v>97000000000095</v>
       </c>
       <c r="C96" s="7" t="str">
-        <f>VLOOKUP($B96, [1]Main!$E$2:$G$358, 2, FALSE)</f>
-        <v>Module.Finance.Data.TaxReconciliation.Transaction</v>
+        <f>VLOOKUP($B96, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.Finance.Data.DebitNote.Report.DataList</v>
       </c>
       <c r="D96" s="8" t="str">
-        <f>VLOOKUP($B96, [1]Main!$E$2:$G$358, 3, FALSE)</f>
-        <v>Tax Reconciliation</v>
+        <f>VLOOKUP($B96, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>Debit Note Summary</v>
       </c>
       <c r="F96" s="10" t="s">
         <v>2</v>
@@ -4760,26 +5205,29 @@
         <v>95</v>
       </c>
       <c r="I96" s="9" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000095::bigint);</v>
       </c>
-      <c r="K96" s="2" t="str">
+      <c r="K96" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L96" s="2" t="str">
         <f t="shared" si="3"/>
         <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000006'::bigint,'menu_RefID', '97000000000095'::bigint)))::varchar;</v>
       </c>
     </row>
-    <row r="97" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="97" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B97" s="6">
         <f>[1]Main!$E97</f>
         <v>97000000000096</v>
       </c>
       <c r="C97" s="7" t="str">
-        <f>VLOOKUP($B97, [1]Main!$E$2:$G$358, 2, FALSE)</f>
-        <v>Module.Finance.Data.TaxReconciliation.Report.DataList</v>
+        <f>VLOOKUP($B97, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.FixedAsset.Data.GoodsIdentity.Transaction</v>
       </c>
       <c r="D97" s="8" t="str">
-        <f>VLOOKUP($B97, [1]Main!$E$2:$G$358, 3, FALSE)</f>
-        <v>Tax Reconciliation Summary</v>
+        <f>VLOOKUP($B97, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>Fixed Asset</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>2</v>
@@ -4792,48 +5240,685 @@
         <v>96</v>
       </c>
       <c r="I97" s="9" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000096::bigint);</v>
       </c>
-      <c r="K97" s="2" t="str">
+      <c r="K97" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L97" s="2" t="str">
         <f t="shared" si="3"/>
         <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000006'::bigint,'menu_RefID', '97000000000096'::bigint)))::varchar;</v>
       </c>
     </row>
-    <row r="98" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="98" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B98" s="6">
         <f>[1]Main!$E98</f>
         <v>97000000000097</v>
       </c>
       <c r="C98" s="7" t="str">
-        <f>VLOOKUP($B98, [1]Main!$E$2:$G$358, 2, FALSE)</f>
-        <v>Module.CustomerRelation.MasterData.Customer.Transaction</v>
+        <f>VLOOKUP($B98, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.FixedAsset.Data.GoodsIdentity.Report.DataList</v>
       </c>
       <c r="D98" s="8" t="str">
-        <f>VLOOKUP($B98, [1]Main!$E$2:$G$358, 3, FALSE)</f>
-        <v>Customer</v>
+        <f>VLOOKUP($B98, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>Fixed Asset Summary</v>
       </c>
       <c r="F98" s="10" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G98" s="6">
         <f>IF(EXACT($F98, ""), "", VLOOKUP($F98, [2]Main!$B$2:$E$30, 4, FALSE))</f>
-        <v>254000000000010</v>
+        <v>254000000000006</v>
       </c>
       <c r="H98" s="2">
         <v>97</v>
       </c>
       <c r="I98" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000010::bigint, 97000000000097::bigint);</v>
-      </c>
-      <c r="K98" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000097::bigint);</v>
+      </c>
+      <c r="K98" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L98" s="2" t="str">
         <f t="shared" si="3"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000010'::bigint,'menu_RefID', '97000000000097'::bigint)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000006'::bigint,'menu_RefID', '97000000000097'::bigint)))::varchar;</v>
+      </c>
+    </row>
+    <row r="99" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B99" s="6">
+        <f>[1]Main!$E99</f>
+        <v>97000000000098</v>
+      </c>
+      <c r="C99" s="7" t="str">
+        <f>VLOOKUP($B99, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.Finance.Data.Loan.Transaction</v>
+      </c>
+      <c r="D99" s="8" t="str">
+        <f>VLOOKUP($B99, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>Loan</v>
+      </c>
+      <c r="F99" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="G99" s="6">
+        <f>IF(EXACT($F99, ""), "", VLOOKUP($F99, [2]Main!$B$2:$E$30, 4, FALSE))</f>
+        <v>254000000000006</v>
+      </c>
+      <c r="H99" s="2">
+        <v>98</v>
+      </c>
+      <c r="I99" s="9" t="str">
+        <f t="shared" si="4"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000098::bigint);</v>
+      </c>
+      <c r="K99" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L99" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000006'::bigint,'menu_RefID', '97000000000098'::bigint)))::varchar;</v>
+      </c>
+    </row>
+    <row r="100" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B100" s="6">
+        <f>[1]Main!$E100</f>
+        <v>97000000000099</v>
+      </c>
+      <c r="C100" s="7" t="str">
+        <f>VLOOKUP($B100, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.Finance.Data.Loan.Report.DataList</v>
+      </c>
+      <c r="D100" s="8" t="str">
+        <f>VLOOKUP($B100, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>Loan Summary</v>
+      </c>
+      <c r="F100" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="G100" s="6">
+        <f>IF(EXACT($F100, ""), "", VLOOKUP($F100, [2]Main!$B$2:$E$30, 4, FALSE))</f>
+        <v>254000000000006</v>
+      </c>
+      <c r="H100" s="2">
+        <v>99</v>
+      </c>
+      <c r="I100" s="9" t="str">
+        <f t="shared" si="4"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000099::bigint);</v>
+      </c>
+      <c r="K100" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L100" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000006'::bigint,'menu_RefID', '97000000000099'::bigint)))::varchar;</v>
+      </c>
+    </row>
+    <row r="101" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B101" s="6">
+        <f>[1]Main!$E101</f>
+        <v>97000000000100</v>
+      </c>
+      <c r="C101" s="7" t="str">
+        <f>VLOOKUP($B101, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.Finance.Data.LoanToLoanSettlement.Report.DataList</v>
+      </c>
+      <c r="D101" s="8" t="str">
+        <f>VLOOKUP($B101, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>Loan to Loan Settlement Summary</v>
+      </c>
+      <c r="F101" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="G101" s="6">
+        <f>IF(EXACT($F101, ""), "", VLOOKUP($F101, [2]Main!$B$2:$E$30, 4, FALSE))</f>
+        <v>254000000000006</v>
+      </c>
+      <c r="H101" s="2">
+        <v>100</v>
+      </c>
+      <c r="I101" s="9" t="str">
+        <f t="shared" si="4"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000100::bigint);</v>
+      </c>
+      <c r="K101" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L101" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000006'::bigint,'menu_RefID', '97000000000100'::bigint)))::varchar;</v>
+      </c>
+    </row>
+    <row r="102" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B102" s="6">
+        <f>[1]Main!$E102</f>
+        <v>97000000000101</v>
+      </c>
+      <c r="C102" s="7" t="str">
+        <f>VLOOKUP($B102, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.Finance.Data.LoanSettlement.Transaction</v>
+      </c>
+      <c r="D102" s="8" t="str">
+        <f>VLOOKUP($B102, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>Loan Settlement</v>
+      </c>
+      <c r="F102" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="G102" s="6">
+        <f>IF(EXACT($F102, ""), "", VLOOKUP($F102, [2]Main!$B$2:$E$30, 4, FALSE))</f>
+        <v>254000000000006</v>
+      </c>
+      <c r="H102" s="2">
+        <v>101</v>
+      </c>
+      <c r="I102" s="9" t="str">
+        <f t="shared" si="4"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000101::bigint);</v>
+      </c>
+      <c r="K102" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L102" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000006'::bigint,'menu_RefID', '97000000000101'::bigint)))::varchar;</v>
+      </c>
+    </row>
+    <row r="103" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B103" s="6">
+        <f>[1]Main!$E103</f>
+        <v>97000000000102</v>
+      </c>
+      <c r="C103" s="7" t="str">
+        <f>VLOOKUP($B103, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.Finance.Data.LoanSettlement.Report.DataList</v>
+      </c>
+      <c r="D103" s="8" t="str">
+        <f>VLOOKUP($B103, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>Loan Settlement Summary</v>
+      </c>
+      <c r="F103" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="G103" s="6">
+        <f>IF(EXACT($F103, ""), "", VLOOKUP($F103, [2]Main!$B$2:$E$30, 4, FALSE))</f>
+        <v>254000000000006</v>
+      </c>
+      <c r="H103" s="2">
+        <v>102</v>
+      </c>
+      <c r="I103" s="9" t="str">
+        <f t="shared" si="4"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000102::bigint);</v>
+      </c>
+      <c r="K103" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L103" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000006'::bigint,'menu_RefID', '97000000000102'::bigint)))::varchar;</v>
+      </c>
+    </row>
+    <row r="104" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B104" s="6">
+        <f>[1]Main!$E104</f>
+        <v>97000000000103</v>
+      </c>
+      <c r="C104" s="7" t="str">
+        <f>VLOOKUP($B104, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.Finance.Data.PaymentInstruction.Transaction</v>
+      </c>
+      <c r="D104" s="8" t="str">
+        <f>VLOOKUP($B104, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>Account Payable</v>
+      </c>
+      <c r="F104" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="G104" s="6">
+        <f>IF(EXACT($F104, ""), "", VLOOKUP($F104, [2]Main!$B$2:$E$30, 4, FALSE))</f>
+        <v>254000000000006</v>
+      </c>
+      <c r="H104" s="2">
+        <v>103</v>
+      </c>
+      <c r="I104" s="9" t="str">
+        <f t="shared" si="4"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000103::bigint);</v>
+      </c>
+      <c r="K104" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L104" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000006'::bigint,'menu_RefID', '97000000000103'::bigint)))::varchar;</v>
+      </c>
+    </row>
+    <row r="105" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B105" s="6">
+        <f>[1]Main!$E105</f>
+        <v>97000000000104</v>
+      </c>
+      <c r="C105" s="7" t="str">
+        <f>VLOOKUP($B105, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.Finance.Data.PaymentInstruction.Report.DataList</v>
+      </c>
+      <c r="D105" s="8" t="str">
+        <f>VLOOKUP($B105, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>Account Payable Summary</v>
+      </c>
+      <c r="F105" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="G105" s="6">
+        <f>IF(EXACT($F105, ""), "", VLOOKUP($F105, [2]Main!$B$2:$E$30, 4, FALSE))</f>
+        <v>254000000000006</v>
+      </c>
+      <c r="H105" s="2">
+        <v>104</v>
+      </c>
+      <c r="I105" s="9" t="str">
+        <f t="shared" si="4"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000104::bigint);</v>
+      </c>
+      <c r="K105" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L105" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000006'::bigint,'menu_RefID', '97000000000104'::bigint)))::varchar;</v>
+      </c>
+    </row>
+    <row r="106" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B106" s="6">
+        <f>[1]Main!$E106</f>
+        <v>97000000000105</v>
+      </c>
+      <c r="C106" s="7" t="str">
+        <f>VLOOKUP($B106, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.Finance.Data.Reimbursement.Transaction</v>
+      </c>
+      <c r="D106" s="8" t="str">
+        <f>VLOOKUP($B106, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>Reimbursement</v>
+      </c>
+      <c r="F106" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="G106" s="6">
+        <f>IF(EXACT($F106, ""), "", VLOOKUP($F106, [2]Main!$B$2:$E$30, 4, FALSE))</f>
+        <v>254000000000006</v>
+      </c>
+      <c r="H106" s="2">
+        <v>105</v>
+      </c>
+      <c r="I106" s="9" t="str">
+        <f t="shared" si="4"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000105::bigint);</v>
+      </c>
+      <c r="K106" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L106" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000006'::bigint,'menu_RefID', '97000000000105'::bigint)))::varchar;</v>
+      </c>
+    </row>
+    <row r="107" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B107" s="6">
+        <f>[1]Main!$E107</f>
+        <v>97000000000106</v>
+      </c>
+      <c r="C107" s="7" t="str">
+        <f>VLOOKUP($B107, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.Finance.Data.Reimbursement.Report.DataList</v>
+      </c>
+      <c r="D107" s="8" t="str">
+        <f>VLOOKUP($B107, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>Reimbursement Summary</v>
+      </c>
+      <c r="F107" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="G107" s="6">
+        <f>IF(EXACT($F107, ""), "", VLOOKUP($F107, [2]Main!$B$2:$E$30, 4, FALSE))</f>
+        <v>254000000000006</v>
+      </c>
+      <c r="H107" s="2">
+        <v>106</v>
+      </c>
+      <c r="I107" s="9" t="str">
+        <f t="shared" si="4"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000106::bigint);</v>
+      </c>
+      <c r="K107" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L107" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000006'::bigint,'menu_RefID', '97000000000106'::bigint)))::varchar;</v>
+      </c>
+    </row>
+    <row r="108" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B108" s="6">
+        <f>[1]Main!$E108</f>
+        <v>97000000000107</v>
+      </c>
+      <c r="C108" s="7" t="str">
+        <f>VLOOKUP($B108, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.Finance.Data.ReimbursementToDebitNote.Report.DataList</v>
+      </c>
+      <c r="D108" s="8" t="str">
+        <f>VLOOKUP($B108, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>Reimbursement to Debit Note Summary</v>
+      </c>
+      <c r="F108" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="G108" s="6">
+        <f>IF(EXACT($F108, ""), "", VLOOKUP($F108, [2]Main!$B$2:$E$30, 4, FALSE))</f>
+        <v>254000000000006</v>
+      </c>
+      <c r="H108" s="2">
+        <v>107</v>
+      </c>
+      <c r="I108" s="9" t="str">
+        <f t="shared" si="4"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000107::bigint);</v>
+      </c>
+      <c r="K108" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L108" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000006'::bigint,'menu_RefID', '97000000000107'::bigint)))::varchar;</v>
+      </c>
+    </row>
+    <row r="109" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B109" s="6">
+        <f>[1]Main!$E109</f>
+        <v>97000000000108</v>
+      </c>
+      <c r="C109" s="7" t="str">
+        <f>VLOOKUP($B109, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.Finance.Data.SalesInvoice.Transaction</v>
+      </c>
+      <c r="D109" s="8" t="str">
+        <f>VLOOKUP($B109, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>Sales Invoice</v>
+      </c>
+      <c r="F109" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="G109" s="6">
+        <f>IF(EXACT($F109, ""), "", VLOOKUP($F109, [2]Main!$B$2:$E$30, 4, FALSE))</f>
+        <v>254000000000006</v>
+      </c>
+      <c r="H109" s="2">
+        <v>108</v>
+      </c>
+      <c r="I109" s="9" t="str">
+        <f t="shared" si="4"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000108::bigint);</v>
+      </c>
+      <c r="K109" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L109" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000006'::bigint,'menu_RefID', '97000000000108'::bigint)))::varchar;</v>
+      </c>
+    </row>
+    <row r="110" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B110" s="6">
+        <f>[1]Main!$E110</f>
+        <v>97000000000109</v>
+      </c>
+      <c r="C110" s="7" t="str">
+        <f>VLOOKUP($B110, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.Finance.Data.SalesInvoice.Report.DataList</v>
+      </c>
+      <c r="D110" s="8" t="str">
+        <f>VLOOKUP($B110, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>Sales Invoice Summary</v>
+      </c>
+      <c r="F110" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="G110" s="6">
+        <f>IF(EXACT($F110, ""), "", VLOOKUP($F110, [2]Main!$B$2:$E$30, 4, FALSE))</f>
+        <v>254000000000006</v>
+      </c>
+      <c r="H110" s="2">
+        <v>109</v>
+      </c>
+      <c r="I110" s="9" t="str">
+        <f t="shared" si="4"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000109::bigint);</v>
+      </c>
+      <c r="K110" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L110" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000006'::bigint,'menu_RefID', '97000000000109'::bigint)))::varchar;</v>
+      </c>
+    </row>
+    <row r="111" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B111" s="6">
+        <f>[1]Main!$E111</f>
+        <v>97000000000110</v>
+      </c>
+      <c r="C111" s="7" t="str">
+        <f>VLOOKUP($B111, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.Finance.Data.SalesInvoiceToCreditNote.Report.DataList</v>
+      </c>
+      <c r="D111" s="8" t="str">
+        <f>VLOOKUP($B111, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>Sales Invoice to Credit Note</v>
+      </c>
+      <c r="F111" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="G111" s="6">
+        <f>IF(EXACT($F111, ""), "", VLOOKUP($F111, [2]Main!$B$2:$E$30, 4, FALSE))</f>
+        <v>254000000000006</v>
+      </c>
+      <c r="H111" s="2">
+        <v>110</v>
+      </c>
+      <c r="I111" s="9" t="str">
+        <f t="shared" si="4"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000110::bigint);</v>
+      </c>
+      <c r="K111" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L111" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000006'::bigint,'menu_RefID', '97000000000110'::bigint)))::varchar;</v>
+      </c>
+    </row>
+    <row r="112" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B112" s="6">
+        <f>[1]Main!$E112</f>
+        <v>97000000000111</v>
+      </c>
+      <c r="C112" s="7" t="str">
+        <f>VLOOKUP($B112, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.Finance.Data.TaxReconciliation.Transaction</v>
+      </c>
+      <c r="D112" s="8" t="str">
+        <f>VLOOKUP($B112, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>Tax Reconciliation</v>
+      </c>
+      <c r="F112" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="G112" s="6">
+        <f>IF(EXACT($F112, ""), "", VLOOKUP($F112, [2]Main!$B$2:$E$30, 4, FALSE))</f>
+        <v>254000000000006</v>
+      </c>
+      <c r="H112" s="2">
+        <v>111</v>
+      </c>
+      <c r="I112" s="9" t="str">
+        <f t="shared" si="4"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000111::bigint);</v>
+      </c>
+      <c r="K112" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L112" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000006'::bigint,'menu_RefID', '97000000000111'::bigint)))::varchar;</v>
+      </c>
+    </row>
+    <row r="113" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B113" s="6">
+        <f>[1]Main!$E113</f>
+        <v>97000000000112</v>
+      </c>
+      <c r="C113" s="7" t="str">
+        <f>VLOOKUP($B113, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.Finance.Data.TaxReconciliation.Report.DataList</v>
+      </c>
+      <c r="D113" s="8" t="str">
+        <f>VLOOKUP($B113, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>Tax Reconciliation Summary</v>
+      </c>
+      <c r="F113" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="G113" s="6">
+        <f>IF(EXACT($F113, ""), "", VLOOKUP($F113, [2]Main!$B$2:$E$30, 4, FALSE))</f>
+        <v>254000000000006</v>
+      </c>
+      <c r="H113" s="2">
+        <v>112</v>
+      </c>
+      <c r="I113" s="9" t="str">
+        <f t="shared" si="4"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000006::bigint, 97000000000112::bigint);</v>
+      </c>
+      <c r="K113" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L113" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000006'::bigint,'menu_RefID', '97000000000112'::bigint)))::varchar;</v>
+      </c>
+    </row>
+    <row r="114" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B114" s="6">
+        <f>[1]Main!$E114</f>
+        <v>97000000000113</v>
+      </c>
+      <c r="C114" s="7" t="str">
+        <f>VLOOKUP($B114, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.CustomerRelation.MasterData.Customer.Transaction</v>
+      </c>
+      <c r="D114" s="8" t="str">
+        <f>VLOOKUP($B114, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>Customer</v>
+      </c>
+      <c r="F114" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="G114" s="6">
+        <f>IF(EXACT($F114, ""), "", VLOOKUP($F114, [2]Main!$B$2:$E$30, 4, FALSE))</f>
+        <v>254000000000005</v>
+      </c>
+      <c r="H114" s="2">
+        <v>113</v>
+      </c>
+      <c r="I114" s="9" t="str">
+        <f t="shared" si="4"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000005::bigint, 97000000000113::bigint);</v>
+      </c>
+      <c r="K114" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L114" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000005'::bigint,'menu_RefID', '97000000000113'::bigint)))::varchar;</v>
+      </c>
+    </row>
+    <row r="115" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B115" s="6">
+        <f>[1]Main!$E115</f>
+        <v>97000000000114</v>
+      </c>
+      <c r="C115" s="7" t="str">
+        <f>VLOOKUP($B115, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.CustomerRelation.MasterData.CustomerOrder.Transaction</v>
+      </c>
+      <c r="D115" s="8" t="str">
+        <f>VLOOKUP($B115, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>Customer Order</v>
+      </c>
+      <c r="F115" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="G115" s="6">
+        <f>IF(EXACT($F115, ""), "", VLOOKUP($F115, [2]Main!$B$2:$E$30, 4, FALSE))</f>
+        <v>254000000000005</v>
+      </c>
+      <c r="H115" s="2">
+        <v>114</v>
+      </c>
+      <c r="I115" s="9" t="str">
+        <f t="shared" si="4"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000005::bigint, 97000000000114::bigint);</v>
+      </c>
+      <c r="K115" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L115" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000005'::bigint,'menu_RefID', '97000000000114'::bigint)))::varchar;</v>
+      </c>
+    </row>
+    <row r="116" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B116" s="6">
+        <f>[1]Main!$E116</f>
+        <v>97000000000115</v>
+      </c>
+      <c r="C116" s="7" t="str">
+        <f>VLOOKUP($B116, [1]Main!$E$2:$G$374, 2, FALSE)</f>
+        <v>Module.CustomerRelation.MasterData.CustomerOrder.Report.DataList</v>
+      </c>
+      <c r="D116" s="8" t="str">
+        <f>VLOOKUP($B116, [1]Main!$E$2:$G$374, 3, FALSE)</f>
+        <v>Customer Order Summary</v>
+      </c>
+      <c r="F116" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="G116" s="6">
+        <f>IF(EXACT($F116, ""), "", VLOOKUP($F116, [2]Main!$B$2:$E$30, 4, FALSE))</f>
+        <v>254000000000005</v>
+      </c>
+      <c r="H116" s="2">
+        <v>115</v>
+      </c>
+      <c r="I116" s="9" t="str">
+        <f t="shared" si="4"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000005::bigint, 97000000000115::bigint);</v>
+      </c>
+      <c r="K116" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L116" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000005'::bigint,'menu_RefID', '97000000000115'::bigint)))::varchar;</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -5326,15 +6411,15 @@
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B17" s="1">
-        <f>[1]Main!L19</f>
+        <f>[1]Main!L35</f>
         <v>0</v>
       </c>
       <c r="C17" s="1" t="str">
-        <f>IF(EXACT([1]Main!D19, ""), "", [1]Main!D19)</f>
+        <f>IF(EXACT([1]Main!D35, ""), "", [1]Main!D35)</f>
         <v/>
       </c>
       <c r="D17" s="1">
-        <f>[1]Main!M19</f>
+        <f>[1]Main!M35</f>
         <v>0</v>
       </c>
       <c r="E17" s="1" t="str">
@@ -5357,15 +6442,15 @@
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B18" s="1">
-        <f>[1]Main!L22</f>
+        <f>[1]Main!L20</f>
         <v>0</v>
       </c>
       <c r="C18" s="1" t="str">
-        <f>IF(EXACT([1]Main!D22, ""), "", [1]Main!D22)</f>
+        <f>IF(EXACT([1]Main!D20, ""), "", [1]Main!D20)</f>
         <v/>
       </c>
       <c r="D18" s="1">
-        <f>[1]Main!M22</f>
+        <f>[1]Main!M20</f>
         <v>0</v>
       </c>
       <c r="E18" s="1" t="str">
@@ -5388,15 +6473,15 @@
     </row>
     <row r="19" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B19" s="1">
-        <f>[1]Main!L23</f>
+        <f>[1]Main!L22</f>
         <v>0</v>
       </c>
       <c r="C19" s="1" t="str">
-        <f>IF(EXACT([1]Main!D23, ""), "", [1]Main!D23)</f>
+        <f>IF(EXACT([1]Main!D22, ""), "", [1]Main!D22)</f>
         <v/>
       </c>
       <c r="D19" s="1">
-        <f>[1]Main!M23</f>
+        <f>[1]Main!M22</f>
         <v>0</v>
       </c>
       <c r="E19" s="1" t="str">
@@ -5419,15 +6504,15 @@
     </row>
     <row r="20" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B20" s="1">
-        <f>[1]Main!L25</f>
+        <f>[1]Main!L28</f>
         <v>0</v>
       </c>
       <c r="C20" s="1" t="str">
-        <f>IF(EXACT([1]Main!D25, ""), "", [1]Main!D25)</f>
+        <f>IF(EXACT([1]Main!D28, ""), "", [1]Main!D28)</f>
         <v/>
       </c>
       <c r="D20" s="1">
-        <f>[1]Main!M25</f>
+        <f>[1]Main!M28</f>
         <v>0</v>
       </c>
       <c r="E20" s="1" t="str">
@@ -5450,15 +6535,15 @@
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B21" s="1">
-        <f>[1]Main!L69</f>
+        <f>[1]Main!L80</f>
         <v>0</v>
       </c>
       <c r="C21" s="1" t="str">
-        <f>IF(EXACT([1]Main!D69, ""), "", [1]Main!D69)</f>
+        <f>IF(EXACT([1]Main!D80, ""), "", [1]Main!D80)</f>
         <v/>
       </c>
       <c r="D21" s="1">
-        <f>[1]Main!M69</f>
+        <f>[1]Main!M80</f>
         <v>0</v>
       </c>
       <c r="E21" s="1" t="str">
@@ -5481,15 +6566,15 @@
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B22" s="1">
-        <f>[1]Main!L65</f>
+        <f>[1]Main!L76</f>
         <v>0</v>
       </c>
       <c r="C22" s="1" t="str">
-        <f>IF(EXACT([1]Main!D65, ""), "", [1]Main!D65)</f>
+        <f>IF(EXACT([1]Main!D76, ""), "", [1]Main!D76)</f>
         <v/>
       </c>
       <c r="D22" s="1">
-        <f>[1]Main!M65</f>
+        <f>[1]Main!M76</f>
         <v>0</v>
       </c>
       <c r="E22" s="1" t="str">
@@ -5512,15 +6597,15 @@
     </row>
     <row r="23" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B23" s="1">
-        <f>[1]Main!L27</f>
+        <f>[1]Main!L30</f>
         <v>0</v>
       </c>
       <c r="C23" s="1" t="str">
-        <f>IF(EXACT([1]Main!D27, ""), "", [1]Main!D27)</f>
+        <f>IF(EXACT([1]Main!D30, ""), "", [1]Main!D30)</f>
         <v/>
       </c>
       <c r="D23" s="1">
-        <f>[1]Main!M27</f>
+        <f>[1]Main!M30</f>
         <v>0</v>
       </c>
       <c r="E23" s="1" t="str">
@@ -5543,15 +6628,15 @@
     </row>
     <row r="24" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B24" s="1">
-        <f>[1]Main!L26</f>
+        <f>[1]Main!L29</f>
         <v>0</v>
       </c>
       <c r="C24" s="1" t="str">
-        <f>IF(EXACT([1]Main!D26, ""), "", [1]Main!D26)</f>
+        <f>IF(EXACT([1]Main!D29, ""), "", [1]Main!D29)</f>
         <v/>
       </c>
       <c r="D24" s="1">
-        <f>[1]Main!M26</f>
+        <f>[1]Main!M29</f>
         <v>0</v>
       </c>
       <c r="E24" s="1" t="str">
@@ -5574,15 +6659,15 @@
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B25" s="1">
-        <f>[1]Main!L33</f>
+        <f>[1]Main!L39</f>
         <v>0</v>
       </c>
       <c r="C25" s="1" t="str">
-        <f>IF(EXACT([1]Main!D33, ""), "", [1]Main!D33)</f>
+        <f>IF(EXACT([1]Main!D39, ""), "", [1]Main!D39)</f>
         <v/>
       </c>
       <c r="D25" s="1">
-        <f>[1]Main!M33</f>
+        <f>[1]Main!M39</f>
         <v>0</v>
       </c>
       <c r="E25" s="1" t="str">
@@ -5605,15 +6690,15 @@
     </row>
     <row r="26" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B26" s="1">
-        <f>[1]Main!L35</f>
+        <f>[1]Main!L43</f>
         <v>0</v>
       </c>
       <c r="C26" s="1" t="str">
-        <f>IF(EXACT([1]Main!D35, ""), "", [1]Main!D35)</f>
+        <f>IF(EXACT([1]Main!D43, ""), "", [1]Main!D43)</f>
         <v/>
       </c>
       <c r="D26" s="1">
-        <f>[1]Main!M35</f>
+        <f>[1]Main!M43</f>
         <v>0</v>
       </c>
       <c r="E26" s="1" t="str">
@@ -5636,15 +6721,15 @@
     </row>
     <row r="27" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B27" s="1">
-        <f>[1]Main!L36</f>
+        <f>[1]Main!L41</f>
         <v>0</v>
       </c>
       <c r="C27" s="1" t="str">
-        <f>IF(EXACT([1]Main!D36, ""), "", [1]Main!D36)</f>
+        <f>IF(EXACT([1]Main!D41, ""), "", [1]Main!D41)</f>
         <v/>
       </c>
       <c r="D27" s="1">
-        <f>[1]Main!M36</f>
+        <f>[1]Main!M41</f>
         <v>0</v>
       </c>
       <c r="E27" s="1" t="str">
@@ -5667,15 +6752,15 @@
     </row>
     <row r="28" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B28" s="1">
-        <f>[1]Main!L37</f>
+        <f>[1]Main!L42</f>
         <v>0</v>
       </c>
       <c r="C28" s="1" t="str">
-        <f>IF(EXACT([1]Main!D37, ""), "", [1]Main!D37)</f>
+        <f>IF(EXACT([1]Main!D42, ""), "", [1]Main!D42)</f>
         <v/>
       </c>
       <c r="D28" s="1">
-        <f>[1]Main!M37</f>
+        <f>[1]Main!M42</f>
         <v>0</v>
       </c>
       <c r="E28" s="1" t="str">
@@ -5698,15 +6783,15 @@
     </row>
     <row r="29" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B29" s="1">
-        <f>[1]Main!L39</f>
+        <f>[1]Main!L46</f>
         <v>0</v>
       </c>
       <c r="C29" s="1" t="str">
-        <f>IF(EXACT([1]Main!D39, ""), "", [1]Main!D39)</f>
+        <f>IF(EXACT([1]Main!D46, ""), "", [1]Main!D46)</f>
         <v/>
       </c>
       <c r="D29" s="1">
-        <f>[1]Main!M39</f>
+        <f>[1]Main!M46</f>
         <v>0</v>
       </c>
       <c r="E29" s="1" t="str">
@@ -5729,15 +6814,15 @@
     </row>
     <row r="30" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B30" s="1">
-        <f>[1]Main!L38</f>
+        <f>[1]Main!L45</f>
         <v>0</v>
       </c>
       <c r="C30" s="1" t="str">
-        <f>IF(EXACT([1]Main!D38, ""), "", [1]Main!D38)</f>
+        <f>IF(EXACT([1]Main!D45, ""), "", [1]Main!D45)</f>
         <v/>
       </c>
       <c r="D30" s="1">
-        <f>[1]Main!M38</f>
+        <f>[1]Main!M45</f>
         <v>0</v>
       </c>
       <c r="E30" s="1" t="str">
@@ -5760,15 +6845,15 @@
     </row>
     <row r="31" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B31" s="1">
-        <f>[1]Main!L41</f>
+        <f>[1]Main!L48</f>
         <v>0</v>
       </c>
       <c r="C31" s="1" t="str">
-        <f>IF(EXACT([1]Main!D41, ""), "", [1]Main!D41)</f>
+        <f>IF(EXACT([1]Main!D48, ""), "", [1]Main!D48)</f>
         <v/>
       </c>
       <c r="D31" s="1">
-        <f>[1]Main!M41</f>
+        <f>[1]Main!M48</f>
         <v>0</v>
       </c>
       <c r="E31" s="1" t="str">
@@ -5791,15 +6876,15 @@
     </row>
     <row r="32" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B32" s="1">
-        <f>[1]Main!L42</f>
+        <f>[1]Main!L49</f>
         <v>0</v>
       </c>
       <c r="C32" s="1" t="str">
-        <f>IF(EXACT([1]Main!D42, ""), "", [1]Main!D42)</f>
+        <f>IF(EXACT([1]Main!D49, ""), "", [1]Main!D49)</f>
         <v/>
       </c>
       <c r="D32" s="1">
-        <f>[1]Main!M42</f>
+        <f>[1]Main!M49</f>
         <v>0</v>
       </c>
       <c r="E32" s="1" t="str">
@@ -5821,15 +6906,15 @@
     </row>
     <row r="33" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B33" s="1">
-        <f>[1]Main!L45</f>
+        <f>[1]Main!L52</f>
         <v>0</v>
       </c>
       <c r="C33" s="1" t="str">
-        <f>IF(EXACT([1]Main!D45, ""), "", [1]Main!D45)</f>
+        <f>IF(EXACT([1]Main!D52, ""), "", [1]Main!D52)</f>
         <v/>
       </c>
       <c r="D33" s="1">
-        <f>[1]Main!M45</f>
+        <f>[1]Main!M52</f>
         <v>0</v>
       </c>
       <c r="E33" s="1" t="str">
@@ -5851,15 +6936,15 @@
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B34" s="1">
-        <f>[1]Main!L47</f>
+        <f>[1]Main!L56</f>
         <v>0</v>
       </c>
       <c r="C34" s="1" t="str">
-        <f>IF(EXACT([1]Main!D47, ""), "", [1]Main!D47)</f>
+        <f>IF(EXACT([1]Main!D56, ""), "", [1]Main!D56)</f>
         <v/>
       </c>
       <c r="D34" s="1">
-        <f>[1]Main!M47</f>
+        <f>[1]Main!M56</f>
         <v>0</v>
       </c>
       <c r="E34" s="1" t="str">
@@ -5884,15 +6969,15 @@
     </row>
     <row r="35" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B35" s="1">
-        <f>[1]Main!L46</f>
+        <f>[1]Main!L55</f>
         <v>0</v>
       </c>
       <c r="C35" s="1" t="str">
-        <f>IF(EXACT([1]Main!D46, ""), "", [1]Main!D46)</f>
+        <f>IF(EXACT([1]Main!D55, ""), "", [1]Main!D55)</f>
         <v/>
       </c>
       <c r="D35" s="1">
-        <f>[1]Main!M46</f>
+        <f>[1]Main!M55</f>
         <v>0</v>
       </c>
       <c r="E35" s="1" t="str">
@@ -5917,15 +7002,15 @@
     </row>
     <row r="36" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B36" s="1">
-        <f>[1]Main!L50</f>
+        <f>[1]Main!L59</f>
         <v>0</v>
       </c>
       <c r="C36" s="1" t="str">
-        <f>IF(EXACT([1]Main!D50, ""), "", [1]Main!D50)</f>
+        <f>IF(EXACT([1]Main!D59, ""), "", [1]Main!D59)</f>
         <v/>
       </c>
       <c r="D36" s="1">
-        <f>[1]Main!M50</f>
+        <f>[1]Main!M59</f>
         <v>0</v>
       </c>
       <c r="E36" s="1" t="str">
@@ -5950,15 +7035,15 @@
     </row>
     <row r="37" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B37" s="1">
-        <f>[1]Main!L49</f>
+        <f>[1]Main!L58</f>
         <v>0</v>
       </c>
       <c r="C37" s="1" t="str">
-        <f>IF(EXACT([1]Main!D49, ""), "", [1]Main!D49)</f>
+        <f>IF(EXACT([1]Main!D58, ""), "", [1]Main!D58)</f>
         <v/>
       </c>
       <c r="D37" s="1">
-        <f>[1]Main!M49</f>
+        <f>[1]Main!M58</f>
         <v>0</v>
       </c>
       <c r="E37" s="1" t="str">
@@ -5983,15 +7068,15 @@
     </row>
     <row r="38" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B38" s="1">
-        <f>[1]Main!L55</f>
+        <f>[1]Main!L64</f>
         <v>0</v>
       </c>
       <c r="C38" s="1" t="str">
-        <f>IF(EXACT([1]Main!D55, ""), "", [1]Main!D55)</f>
+        <f>IF(EXACT([1]Main!D64, ""), "", [1]Main!D64)</f>
         <v/>
       </c>
       <c r="D38" s="1">
-        <f>[1]Main!M55</f>
+        <f>[1]Main!M64</f>
         <v>0</v>
       </c>
       <c r="E38" s="1" t="str">
@@ -6016,15 +7101,15 @@
     </row>
     <row r="39" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B39" s="1">
-        <f>[1]Main!L54</f>
+        <f>[1]Main!L63</f>
         <v>0</v>
       </c>
       <c r="C39" s="1" t="str">
-        <f>IF(EXACT([1]Main!D54, ""), "", [1]Main!D54)</f>
+        <f>IF(EXACT([1]Main!D63, ""), "", [1]Main!D63)</f>
         <v/>
       </c>
       <c r="D39" s="1">
-        <f>[1]Main!M54</f>
+        <f>[1]Main!M63</f>
         <v>0</v>
       </c>
       <c r="E39" s="1" t="str">
@@ -6049,15 +7134,15 @@
     </row>
     <row r="40" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B40" s="1">
-        <f>[1]Main!L52</f>
+        <f>[1]Main!L61</f>
         <v>0</v>
       </c>
       <c r="C40" s="1" t="str">
-        <f>IF(EXACT([1]Main!D52, ""), "", [1]Main!D52)</f>
+        <f>IF(EXACT([1]Main!D61, ""), "", [1]Main!D61)</f>
         <v/>
       </c>
       <c r="D40" s="1">
-        <f>[1]Main!M52</f>
+        <f>[1]Main!M61</f>
         <v>0</v>
       </c>
       <c r="E40" s="1" t="str">
@@ -6082,15 +7167,15 @@
     </row>
     <row r="41" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B41" s="1">
-        <f>[1]Main!L51</f>
+        <f>[1]Main!L60</f>
         <v>0</v>
       </c>
       <c r="C41" s="1" t="str">
-        <f>IF(EXACT([1]Main!D51, ""), "", [1]Main!D51)</f>
+        <f>IF(EXACT([1]Main!D60, ""), "", [1]Main!D60)</f>
         <v/>
       </c>
       <c r="D41" s="1">
-        <f>[1]Main!M51</f>
+        <f>[1]Main!M60</f>
         <v>0</v>
       </c>
       <c r="E41" s="1" t="str">
@@ -6115,15 +7200,15 @@
     </row>
     <row r="42" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B42" s="1">
-        <f>[1]Main!L56</f>
+        <f>[1]Main!L65</f>
         <v>0</v>
       </c>
       <c r="C42" s="1" t="str">
-        <f>IF(EXACT([1]Main!D56, ""), "", [1]Main!D56)</f>
+        <f>IF(EXACT([1]Main!D65, ""), "", [1]Main!D65)</f>
         <v/>
       </c>
       <c r="D42" s="1">
-        <f>[1]Main!M56</f>
+        <f>[1]Main!M65</f>
         <v>0</v>
       </c>
       <c r="E42" s="1" t="str">
@@ -6148,15 +7233,15 @@
     </row>
     <row r="43" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B43" s="1">
-        <f>[1]Main!L58</f>
+        <f>[1]Main!L69</f>
         <v>0</v>
       </c>
       <c r="C43" s="1" t="str">
-        <f>IF(EXACT([1]Main!D58, ""), "", [1]Main!D58)</f>
+        <f>IF(EXACT([1]Main!D69, ""), "", [1]Main!D69)</f>
         <v/>
       </c>
       <c r="D43" s="1">
-        <f>[1]Main!M58</f>
+        <f>[1]Main!M69</f>
         <v>0</v>
       </c>
       <c r="E43" s="1" t="str">
@@ -6181,15 +7266,15 @@
     </row>
     <row r="44" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B44" s="1">
-        <f>[1]Main!L59</f>
+        <f>[1]Main!L70</f>
         <v>0</v>
       </c>
       <c r="C44" s="1" t="str">
-        <f>IF(EXACT([1]Main!D59, ""), "", [1]Main!D59)</f>
+        <f>IF(EXACT([1]Main!D70, ""), "", [1]Main!D70)</f>
         <v/>
       </c>
       <c r="D44" s="1">
-        <f>[1]Main!M59</f>
+        <f>[1]Main!M70</f>
         <v>0</v>
       </c>
       <c r="E44" s="1" t="str">
@@ -6214,15 +7299,15 @@
     </row>
     <row r="45" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B45" s="1">
-        <f>[1]Main!L57</f>
+        <f>[1]Main!L68</f>
         <v>0</v>
       </c>
       <c r="C45" s="1" t="str">
-        <f>IF(EXACT([1]Main!D57, ""), "", [1]Main!D57)</f>
+        <f>IF(EXACT([1]Main!D68, ""), "", [1]Main!D68)</f>
         <v/>
       </c>
       <c r="D45" s="1">
-        <f>[1]Main!M57</f>
+        <f>[1]Main!M68</f>
         <v>0</v>
       </c>
       <c r="E45" s="1" t="str">
@@ -6247,15 +7332,15 @@
     </row>
     <row r="46" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B46" s="1">
-        <f>[1]Main!L61</f>
+        <f>[1]Main!L72</f>
         <v>0</v>
       </c>
       <c r="C46" s="1" t="str">
-        <f>IF(EXACT([1]Main!D61, ""), "", [1]Main!D61)</f>
+        <f>IF(EXACT([1]Main!D72, ""), "", [1]Main!D72)</f>
         <v/>
       </c>
       <c r="D46" s="1">
-        <f>[1]Main!M61</f>
+        <f>[1]Main!M72</f>
         <v>0</v>
       </c>
       <c r="E46" s="1" t="str">
@@ -6280,15 +7365,15 @@
     </row>
     <row r="47" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B47" s="1">
-        <f>[1]Main!L60</f>
+        <f>[1]Main!L71</f>
         <v>0</v>
       </c>
       <c r="C47" s="1" t="str">
-        <f>IF(EXACT([1]Main!D60, ""), "", [1]Main!D60)</f>
+        <f>IF(EXACT([1]Main!D71, ""), "", [1]Main!D71)</f>
         <v/>
       </c>
       <c r="D47" s="1">
-        <f>[1]Main!M60</f>
+        <f>[1]Main!M71</f>
         <v>0</v>
       </c>
       <c r="E47" s="1" t="str">
@@ -6313,15 +7398,15 @@
     </row>
     <row r="48" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B48" s="1">
-        <f>[1]Main!L77</f>
+        <f>[1]Main!L91</f>
         <v>0</v>
       </c>
       <c r="C48" s="1" t="str">
-        <f>IF(EXACT([1]Main!D77, ""), "", [1]Main!D77)</f>
+        <f>IF(EXACT([1]Main!D91, ""), "", [1]Main!D91)</f>
         <v/>
       </c>
       <c r="D48" s="1">
-        <f>[1]Main!M77</f>
+        <f>[1]Main!M91</f>
         <v>0</v>
       </c>
       <c r="E48" s="1" t="str">
@@ -6346,15 +7431,15 @@
     </row>
     <row r="49" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B49" s="1">
-        <f>[1]Main!L78</f>
+        <f>[1]Main!L92</f>
         <v>0</v>
       </c>
       <c r="C49" s="1" t="str">
-        <f>IF(EXACT([1]Main!D78, ""), "", [1]Main!D78)</f>
+        <f>IF(EXACT([1]Main!D92, ""), "", [1]Main!D92)</f>
         <v/>
       </c>
       <c r="D49" s="1">
-        <f>[1]Main!M78</f>
+        <f>[1]Main!M92</f>
         <v>0</v>
       </c>
       <c r="E49" s="1" t="str">
@@ -6379,15 +7464,15 @@
     </row>
     <row r="50" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B50" s="1">
-        <f>[1]Main!L80</f>
+        <f>[1]Main!L94</f>
         <v>0</v>
       </c>
       <c r="C50" s="1" t="str">
-        <f>IF(EXACT([1]Main!D80, ""), "", [1]Main!D80)</f>
+        <f>IF(EXACT([1]Main!D94, ""), "", [1]Main!D94)</f>
         <v/>
       </c>
       <c r="D50" s="1">
-        <f>[1]Main!M80</f>
+        <f>[1]Main!M94</f>
         <v>0</v>
       </c>
       <c r="E50" s="1" t="str">
@@ -6412,15 +7497,15 @@
     </row>
     <row r="51" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B51" s="1">
-        <f>[1]Main!L81</f>
+        <f>[1]Main!L95</f>
         <v>0</v>
       </c>
       <c r="C51" s="1" t="str">
-        <f>IF(EXACT([1]Main!D81, ""), "", [1]Main!D81)</f>
+        <f>IF(EXACT([1]Main!D95, ""), "", [1]Main!D95)</f>
         <v/>
       </c>
       <c r="D51" s="1">
-        <f>[1]Main!M81</f>
+        <f>[1]Main!M95</f>
         <v>0</v>
       </c>
       <c r="E51" s="1" t="str">
@@ -6445,15 +7530,15 @@
     </row>
     <row r="52" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B52" s="1">
-        <f>[1]Main!L79</f>
+        <f>[1]Main!L93</f>
         <v>0</v>
       </c>
       <c r="C52" s="1" t="str">
-        <f>IF(EXACT([1]Main!D79, ""), "", [1]Main!D79)</f>
+        <f>IF(EXACT([1]Main!D93, ""), "", [1]Main!D93)</f>
         <v/>
       </c>
       <c r="D52" s="1">
-        <f>[1]Main!M79</f>
+        <f>[1]Main!M93</f>
         <v>0</v>
       </c>
       <c r="E52" s="1" t="str">
@@ -6478,15 +7563,15 @@
     </row>
     <row r="53" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B53" s="1">
-        <f>[1]Main!L82</f>
+        <f>[1]Main!L96</f>
         <v>0</v>
       </c>
       <c r="C53" s="1" t="str">
-        <f>IF(EXACT([1]Main!D82, ""), "", [1]Main!D82)</f>
+        <f>IF(EXACT([1]Main!D96, ""), "", [1]Main!D96)</f>
         <v/>
       </c>
       <c r="D53" s="1">
-        <f>[1]Main!M82</f>
+        <f>[1]Main!M96</f>
         <v>0</v>
       </c>
       <c r="E53" s="1" t="str">
@@ -6511,15 +7596,15 @@
     </row>
     <row r="54" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B54" s="1">
-        <f>[1]Main!L83</f>
+        <f>[1]Main!L97</f>
         <v>0</v>
       </c>
       <c r="C54" s="1" t="str">
-        <f>IF(EXACT([1]Main!D83, ""), "", [1]Main!D83)</f>
+        <f>IF(EXACT([1]Main!D97, ""), "", [1]Main!D97)</f>
         <v/>
       </c>
       <c r="D54" s="1">
-        <f>[1]Main!M83</f>
+        <f>[1]Main!M97</f>
         <v>0</v>
       </c>
       <c r="E54" s="1" t="str">
@@ -6544,15 +7629,15 @@
     </row>
     <row r="55" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B55" s="1">
-        <f>[1]Main!L84</f>
+        <f>[1]Main!L100</f>
         <v>0</v>
       </c>
       <c r="C55" s="1" t="str">
-        <f>IF(EXACT([1]Main!D84, ""), "", [1]Main!D84)</f>
+        <f>IF(EXACT([1]Main!D100, ""), "", [1]Main!D100)</f>
         <v/>
       </c>
       <c r="D55" s="1">
-        <f>[1]Main!M84</f>
+        <f>[1]Main!M100</f>
         <v>0</v>
       </c>
       <c r="E55" s="1" t="str">
@@ -6577,15 +7662,15 @@
     </row>
     <row r="56" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B56" s="1">
-        <f>[1]Main!L85</f>
+        <f>[1]Main!L101</f>
         <v>0</v>
       </c>
       <c r="C56" s="1" t="str">
-        <f>IF(EXACT([1]Main!D85, ""), "", [1]Main!D85)</f>
+        <f>IF(EXACT([1]Main!D101, ""), "", [1]Main!D101)</f>
         <v/>
       </c>
       <c r="D56" s="1">
-        <f>[1]Main!M85</f>
+        <f>[1]Main!M101</f>
         <v>0</v>
       </c>
       <c r="E56" s="1" t="str">
@@ -6610,15 +7695,15 @@
     </row>
     <row r="57" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B57" s="1">
-        <f>[1]Main!L87</f>
+        <f>[1]Main!L103</f>
         <v>0</v>
       </c>
       <c r="C57" s="1" t="str">
-        <f>IF(EXACT([1]Main!D87, ""), "", [1]Main!D87)</f>
+        <f>IF(EXACT([1]Main!D103, ""), "", [1]Main!D103)</f>
         <v/>
       </c>
       <c r="D57" s="1">
-        <f>[1]Main!M87</f>
+        <f>[1]Main!M103</f>
         <v>0</v>
       </c>
       <c r="E57" s="1" t="str">
@@ -6643,15 +7728,15 @@
     </row>
     <row r="58" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B58" s="1">
-        <f>[1]Main!L88</f>
+        <f>[1]Main!L104</f>
         <v>0</v>
       </c>
       <c r="C58" s="1" t="str">
-        <f>IF(EXACT([1]Main!D88, ""), "", [1]Main!D88)</f>
+        <f>IF(EXACT([1]Main!D104, ""), "", [1]Main!D104)</f>
         <v/>
       </c>
       <c r="D58" s="1">
-        <f>[1]Main!M88</f>
+        <f>[1]Main!M104</f>
         <v>0</v>
       </c>
       <c r="E58" s="1" t="str">
@@ -6676,15 +7761,15 @@
     </row>
     <row r="59" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B59" s="1">
-        <f>[1]Main!L86</f>
+        <f>[1]Main!L102</f>
         <v>0</v>
       </c>
       <c r="C59" s="1" t="str">
-        <f>IF(EXACT([1]Main!D86, ""), "", [1]Main!D86)</f>
+        <f>IF(EXACT([1]Main!D102, ""), "", [1]Main!D102)</f>
         <v/>
       </c>
       <c r="D59" s="1">
-        <f>[1]Main!M86</f>
+        <f>[1]Main!M102</f>
         <v>0</v>
       </c>
       <c r="E59" s="1" t="str">
@@ -6709,15 +7794,15 @@
     </row>
     <row r="60" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B60" s="1">
-        <f>[1]Main!L89</f>
+        <f>[1]Main!L105</f>
         <v>0</v>
       </c>
       <c r="C60" s="1" t="str">
-        <f>IF(EXACT([1]Main!D89, ""), "", [1]Main!D89)</f>
+        <f>IF(EXACT([1]Main!D105, ""), "", [1]Main!D105)</f>
         <v/>
       </c>
       <c r="D60" s="1">
-        <f>[1]Main!M89</f>
+        <f>[1]Main!M105</f>
         <v>0</v>
       </c>
       <c r="E60" s="1" t="str">
@@ -6742,15 +7827,15 @@
     </row>
     <row r="61" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B61" s="1">
-        <f>[1]Main!L90</f>
+        <f>[1]Main!L106</f>
         <v>0</v>
       </c>
       <c r="C61" s="1" t="str">
-        <f>IF(EXACT([1]Main!D90, ""), "", [1]Main!D90)</f>
+        <f>IF(EXACT([1]Main!D106, ""), "", [1]Main!D106)</f>
         <v/>
       </c>
       <c r="D61" s="1">
-        <f>[1]Main!M90</f>
+        <f>[1]Main!M106</f>
         <v>0</v>
       </c>
       <c r="E61" s="1" t="str">
@@ -6775,15 +7860,15 @@
     </row>
     <row r="62" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B62" s="1">
-        <f>[1]Main!L91</f>
+        <f>[1]Main!L107</f>
         <v>0</v>
       </c>
       <c r="C62" s="1" t="str">
-        <f>IF(EXACT([1]Main!D91, ""), "", [1]Main!D91)</f>
+        <f>IF(EXACT([1]Main!D107, ""), "", [1]Main!D107)</f>
         <v/>
       </c>
       <c r="D62" s="1">
-        <f>[1]Main!M91</f>
+        <f>[1]Main!M107</f>
         <v>0</v>
       </c>
       <c r="E62" s="1" t="str">

--- a/Documentation/Documents/SQL Generator/Data Initial/SysConfig.TblAppObject_MenuGroupMember.xlsx
+++ b/Documentation/Documents/SQL Generator/Data Initial/SysConfig.TblAppObject_MenuGroupMember.xlsx
@@ -1990,7 +1990,7 @@
         <v>2</v>
       </c>
       <c r="I3" s="9" t="str">
-        <f t="shared" ref="I3:I26" si="0">IF(EXACT(G3, ""), "", CONCATENATE("PERFORM ""SchSysConfig"".""Func_TblAppObject_MenuGroupMember_SET""(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, ", G3, "::bigint, ", B3, "::bigint);"))</f>
+        <f t="shared" ref="I3:I4" si="0">IF(EXACT(G3, ""), "", CONCATENATE("PERFORM ""SchSysConfig"".""Func_TblAppObject_MenuGroupMember_SET""(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, ", G3, "::bigint, ", B3, "::bigint);"))</f>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000001::bigint, 97000000000002::bigint);</v>
       </c>
       <c r="K3" s="12" t="s">
@@ -2818,12 +2818,10 @@
         <f t="shared" si="2"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000004::bigint, 97000000000026::bigint);</v>
       </c>
-      <c r="K27" s="12" t="s">
-        <v>10</v>
-      </c>
+      <c r="K27" s="12"/>
       <c r="L27" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000004'::bigint,'menu_RefID', '97000000000026'::bigint)))::varchar;</v>
+        <v/>
       </c>
     </row>
     <row r="28" spans="2:12" x14ac:dyDescent="0.2">
@@ -3294,9 +3292,12 @@
         <f t="shared" si="2"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000009::bigint, 97000000000040::bigint);</v>
       </c>
+      <c r="K41" s="12" t="s">
+        <v>10</v>
+      </c>
       <c r="L41" s="2" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000009'::bigint,'menu_RefID', '97000000000040'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="42" spans="2:12" x14ac:dyDescent="0.2">
@@ -3326,12 +3327,10 @@
         <f t="shared" si="2"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000009::bigint, 97000000000041::bigint);</v>
       </c>
-      <c r="K42" s="12" t="s">
-        <v>10</v>
-      </c>
+      <c r="K42" s="12"/>
       <c r="L42" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000009'::bigint,'menu_RefID', '97000000000041'::bigint)))::varchar;</v>
+        <v/>
       </c>
     </row>
     <row r="43" spans="2:12" x14ac:dyDescent="0.2">
@@ -3361,9 +3360,12 @@
         <f t="shared" si="2"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_MenuGroupMember_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 254000000000009::bigint, 97000000000042::bigint);</v>
       </c>
+      <c r="K43" s="12" t="s">
+        <v>10</v>
+      </c>
       <c r="L43" s="2" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'menuGroup_RefID', '254000000000009'::bigint,'menu_RefID', '97000000000042'::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="44" spans="2:12" x14ac:dyDescent="0.2">
